--- a/Result/checksun_type/HMI.xlsx
+++ b/Result/checksun_type/HMI.xlsx
@@ -878,42 +878,42 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>-2.0</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>46.0</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>20.05</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>16.0</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>20.45</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-1.63</t>
+          <t>-2.68</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>22.57</t>
+          <t>17.65</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -923,7 +923,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-6.41</t>
+          <t>-8.24</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -988,17 +988,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,72 +1014,72 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>46</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>46.15</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>36.17</t>
+          <t>23.08</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-1.91</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-4.52</t>
+          <t>-3.90</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-2.41</t>
+          <t>-2.98</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-1.36</t>
+          <t>-1.65</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>20.46</t>
+          <t>20.44</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>21.43</t>
+          <t>21.27</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>21.96</t>
+          <t>21.92</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>22.26</t>
+          <t>22.29</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-15.32</t>
+          <t>-16.23</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-0.50</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-106.60</t>
+          <t>-106.88</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1099,41 +1099,41 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>30715.98842257597</t>
+          <t>30673.59971098266</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>326.0</t>
+          <t>922.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>861.4</t>
+          <t>840.4</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>702.8</t>
+          <t>714.3</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>2075.44</t>
+          <t>1889.2</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>158</t>
+          <t>126</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-203.7270186305573</t>
+          <t>-195.1459064225224</t>
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>-176.23</v>
+        <v>-147.95</v>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>-13.53</t>
+          <t>-15.22</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1177,27 +1177,27 @@
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>-13.07532251352476</t>
+          <t>-4.453844239860662</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>9.705882352941176</t>
+          <t>20.1000834028357</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>8.653674911088684</t>
+          <t>10.29997958114718</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
@@ -1207,7 +1207,7 @@
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>72.9</t>
+          <t>86.33</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>597</t>
+          <t>585</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1257,27 +1257,27 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>光電業平上櫃</t>
+          <t>光電業右下上櫃</t>
         </is>
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>20.45</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>20.45</t>
+          <t>20.1</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>20.3</t>
+          <t>19.95</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>20.45</t>
+          <t>20.05</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1309,12 +1309,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-1.19</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1334,17 +1334,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-2.0</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-1.63</t>
+          <t>-2.68</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>22.57</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1354,7 +1354,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -1419,17 +1419,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-1.95</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1445,62 +1445,62 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>46</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>23.08</t>
+          <t>46.15</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>28.41</t>
+          <t>36.17</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-4.33</t>
+          <t>-4.52</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-2.52</t>
+          <t>-2.41</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>-1.36</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>20.53</t>
+          <t>20.46</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>21.46</t>
+          <t>21.43</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>22.01</t>
+          <t>21.96</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>22.23</t>
+          <t>22.26</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-20.19</t>
+          <t>-15.32</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
@@ -1510,7 +1510,7 @@
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-106.34</t>
+          <t>-106.60</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,41 +1530,41 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>30715.98842257597</t>
+          <t>30673.59971098266</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>1362.0</t>
+          <t>326.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>800.4</t>
+          <t>861.4</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>791.6</t>
+          <t>702.8</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>2169.22</t>
+          <t>2075.44</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>158</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-208.7263475380736</t>
+          <t>-203.7270186305573</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>-146.48</v>
+        <v>-176.23</v>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
@@ -1608,27 +1608,27 @@
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>-13.07532251352476</t>
+          <t>-4.453844239860662</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>9.705882352941176</t>
+          <t>20.1000834028357</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>8.653674911088684</t>
+          <t>10.29997958114718</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
@@ -1668,12 +1668,12 @@
       </c>
       <c r="BX3" t="inlineStr">
         <is>
-          <t>72.9</t>
+          <t>86.33</t>
         </is>
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>597</t>
+          <t>585</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1688,17 +1688,17 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>光電業平上櫃</t>
+          <t>光電業右下上櫃</t>
         </is>
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>21.0</t>
+          <t>20.45</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>21.0</t>
+          <t>20.45</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
@@ -1740,12 +1740,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>-1.19</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>36.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>20.7</t>
+          <t>20.45</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1765,17 +1765,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-1.22</t>
+          <t>-2.0</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-1.63</t>
+          <t>-2.68</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-32.18</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1785,7 +1785,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-5.26</t>
+          <t>-6.41</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1850,17 +1850,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>-1.95</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1876,62 +1876,62 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>46</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>39.29</t>
+          <t>23.08</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>20.71</t>
+          <t>28.41</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-4.13</t>
+          <t>-4.33</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-2.66</t>
+          <t>-2.52</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-0.54</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>20.6</t>
+          <t>20.53</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>21.49</t>
+          <t>21.46</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>22.08</t>
+          <t>22.01</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>22.19</t>
+          <t>22.23</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-25.12</t>
+          <t>-20.19</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
@@ -1941,7 +1941,7 @@
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-106.02</t>
+          <t>-106.34</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1961,41 +1961,41 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>30715.98842257597</t>
+          <t>30673.59971098266</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>747.0</t>
+          <t>1362.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>677.8</t>
+          <t>800.4</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>999.4</t>
+          <t>791.6</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>2614.76</t>
+          <t>2169.22</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-321</t>
+          <t>8</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-220.0436966054221</t>
+          <t>-208.7263475380736</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>-209.75</v>
+        <v>-146.48</v>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>-12.47</t>
+          <t>-13.53</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2039,27 +2039,27 @@
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>-13.07532251352476</t>
+          <t>-4.453844239860662</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>9.705882352941176</t>
+          <t>20.1000834028357</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>8.653674911088684</t>
+          <t>10.29997958114718</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
@@ -2069,7 +2069,7 @@
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
@@ -2099,12 +2099,12 @@
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>72.9</t>
+          <t>86.33</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>597</t>
+          <t>585</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2119,27 +2119,27 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>光電業平上櫃</t>
+          <t>光電業右下上櫃</t>
         </is>
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>20.6</t>
+          <t>21.0</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>20.95</t>
+          <t>21.0</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>20.55</t>
+          <t>20.3</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>20.7</t>
+          <t>20.45</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>41.0</t>
+          <t>36.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>20.55</t>
+          <t>20.7</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2196,17 +2196,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-3.24</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-1.63</t>
+          <t>-2.68</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-33.22</t>
+          <t>-32.18</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-5.95</t>
+          <t>-5.26</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2281,17 +2281,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-4.11</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2307,72 +2307,72 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>46</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>22.86</t>
+          <t>39.29</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>19.66</t>
+          <t>20.71</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-4.71</t>
+          <t>-4.13</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-2.98</t>
+          <t>-2.66</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-0.54</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>20.49</t>
+          <t>20.6</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>21.5</t>
+          <t>21.49</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>22.16</t>
+          <t>22.08</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>22.16</t>
+          <t>22.19</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-36.40</t>
+          <t>-25.12</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>-0.50</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-105.65</t>
+          <t>-106.02</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2392,41 +2392,41 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>30715.98842257597</t>
+          <t>30673.59971098266</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>845.0</t>
+          <t>747.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>655.2</t>
+          <t>677.8</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>981.2</t>
+          <t>999.4</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>2840.22</t>
+          <t>2614.76</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-326</t>
+          <t>-321</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-221.9153182728739</t>
+          <t>-220.0436966054221</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>-226.75</v>
+        <v>-209.75</v>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>-13.11</t>
+          <t>-12.47</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2470,27 +2470,27 @@
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>-13.07532251352476</t>
+          <t>-4.453844239860662</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>9.705882352941176</t>
+          <t>20.1000834028357</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>8.653674911088684</t>
+          <t>10.29997958114718</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
@@ -2500,7 +2500,7 @@
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>72.9</t>
+          <t>86.33</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>597</t>
+          <t>585</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2550,27 +2550,27 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>光電業平上櫃</t>
+          <t>光電業右下上櫃</t>
         </is>
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>20.2</t>
+          <t>20.6</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>21.75</t>
+          <t>20.95</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>20.2</t>
+          <t>20.55</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>20.55</t>
+          <t>20.7</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-3.22</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>51.0</t>
+          <t>41.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>20.15</t>
+          <t>20.55</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2627,17 +2627,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>-2.49</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-1.63</t>
+          <t>-2.68</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-37.93</t>
+          <t>-33.22</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2647,7 +2647,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -2702,7 +2702,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-7.78</t>
+          <t>-5.95</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2712,17 +2712,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-0.74</t>
+          <t>-4.11</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2738,72 +2738,72 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>46</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>22.86</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>22.61</t>
+          <t>19.66</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-1.80</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-4.79</t>
+          <t>-4.71</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-2.96</t>
+          <t>-2.98</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>20.52</t>
+          <t>20.49</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>21.55</t>
+          <t>21.5</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>22.21</t>
+          <t>22.16</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>22.13</t>
+          <t>22.16</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-47.43</t>
+          <t>-36.40</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.50</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.37</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2813,7 +2813,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-105.13</t>
+          <t>-105.65</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2823,41 +2823,41 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>30715.98842257597</t>
+          <t>30673.59971098266</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>1027.0</t>
+          <t>845.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>588.2</t>
+          <t>655.2</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>947.7</t>
+          <t>981.2</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>2910.12</t>
+          <t>2840.22</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-359</t>
+          <t>-326</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-221.0362983393635</t>
+          <t>-221.9153182728739</t>
         </is>
       </c>
       <c r="BC6" t="n">
-        <v>-253.44</v>
+        <v>-226.75</v>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>-14.80</t>
+          <t>-13.11</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -2901,22 +2901,22 @@
       </c>
       <c r="BL6" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>-13.07532251352476</t>
+          <t>-4.453844239860662</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
         <is>
-          <t>9.705882352941176</t>
+          <t>20.1000834028357</t>
         </is>
       </c>
       <c r="BO6" t="inlineStr">
         <is>
-          <t>8.653674911088684</t>
+          <t>10.29997958114718</t>
         </is>
       </c>
       <c r="BP6" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BX6" t="inlineStr">
         <is>
-          <t>72.9</t>
+          <t>86.33</t>
         </is>
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>597</t>
+          <t>585</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>光電業平上櫃</t>
+          <t>光電業右下上櫃</t>
         </is>
       </c>
       <c r="CC6" t="inlineStr">
@@ -2991,17 +2991,17 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>20.4</t>
+          <t>21.75</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>20.05</t>
+          <t>20.2</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>20.15</t>
+          <t>20.55</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-3.22</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>51.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>20.8</t>
+          <t>20.15</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-1.71</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-1.63</t>
+          <t>-2.68</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-40.01</t>
+          <t>-37.93</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-4.81</t>
+          <t>-7.78</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.74</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>46</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>36.11</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
@@ -3184,57 +3184,57 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>0.10</t>
+          <t>-1.80</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-4.04</t>
+          <t>-4.79</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-2.72</t>
+          <t>-2.96</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.36</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>20.78</t>
+          <t>20.52</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>21.66</t>
+          <t>21.55</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>22.26</t>
+          <t>22.21</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>22.1</t>
+          <t>22.13</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-47.36</t>
+          <t>-47.43</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>-0.50</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-104.52</t>
+          <t>-105.13</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3254,41 +3254,41 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>30715.98842257597</t>
+          <t>30673.59971098266</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>21.0</t>
+          <t>1027.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>544.2</t>
+          <t>588.2</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>907.2</t>
+          <t>947.7</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>2976.72</t>
+          <t>2910.12</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-363</t>
+          <t>-359</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-215.145144320523</t>
+          <t>-221.0362983393635</t>
         </is>
       </c>
       <c r="BC7" t="n">
-        <v>-302.01</v>
+        <v>-253.44</v>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>-12.05</t>
+          <t>-14.80</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3332,37 +3332,37 @@
       </c>
       <c r="BL7" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>-13.07532251352476</t>
+          <t>-4.453844239860662</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>9.705882352941176</t>
+          <t>20.1000834028357</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr">
         <is>
-          <t>8.653674911088684</t>
+          <t>10.29997958114718</t>
         </is>
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="BX7" t="inlineStr">
         <is>
-          <t>72.9</t>
+          <t>86.33</t>
         </is>
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>597</t>
+          <t>585</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3412,27 +3412,27 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>光電業平上櫃</t>
+          <t>光電業右下上櫃</t>
         </is>
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>20.8</t>
+          <t>20.2</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>20.8</t>
+          <t>20.4</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>20.8</t>
+          <t>20.05</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>20.8</t>
+          <t>20.15</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3464,12 +3464,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>3.17</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>36.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3489,17 +3489,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-1.71</t>
+          <t>-3.74</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-1.63</t>
+          <t>-2.68</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-18.36</t>
+          <t>-40.01</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3509,7 +3509,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -3574,17 +3574,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2.46</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3600,72 +3600,72 @@
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>46</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>31.71</t>
+          <t>36.11</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>10.57</t>
+          <t>22.61</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-0.62</t>
+          <t>0.10</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-3.73</t>
+          <t>-4.04</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-2.59</t>
+          <t>-2.72</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>20.93</t>
+          <t>20.78</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>21.74</t>
+          <t>21.66</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>22.32</t>
+          <t>22.26</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>22.07</t>
+          <t>22.1</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-61.10</t>
+          <t>-47.36</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>-0.44</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-103.99</t>
+          <t>-104.52</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3685,41 +3685,41 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>30715.98842257597</t>
+          <t>30673.59971098266</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>749.0</t>
+          <t>21.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>782.8</t>
+          <t>544.2</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>958.8</t>
+          <t>907.2</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>3076.14</t>
+          <t>2976.72</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-176</t>
+          <t>-363</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-199.3512411554697</t>
+          <t>-215.145144320523</t>
         </is>
       </c>
       <c r="BC8" t="n">
-        <v>-252.83</v>
+        <v>-302.01</v>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
@@ -3763,27 +3763,27 @@
       </c>
       <c r="BL8" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>-13.07532251352476</t>
+          <t>-4.453844239860662</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
         <is>
-          <t>9.705882352941176</t>
+          <t>20.1000834028357</t>
         </is>
       </c>
       <c r="BO8" t="inlineStr">
         <is>
-          <t>8.653674911088684</t>
+          <t>10.29997958114718</t>
         </is>
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
@@ -3823,12 +3823,12 @@
       </c>
       <c r="BX8" t="inlineStr">
         <is>
-          <t>72.9</t>
+          <t>86.33</t>
         </is>
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>597</t>
+          <t>585</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -3843,12 +3843,12 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>光電業平上櫃</t>
+          <t>光電業右下上櫃</t>
         </is>
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>20.5</t>
+          <t>20.8</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
@@ -3858,7 +3858,7 @@
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>20.3</t>
+          <t>20.8</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-2.74</t>
+          <t>3.17</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>31.0</t>
+          <t>36.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>20.15</t>
+          <t>20.8</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3920,17 +3920,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>-3.74</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-1.63</t>
+          <t>-2.68</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>35.06</t>
+          <t>-18.36</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3940,7 +3940,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-7.78</t>
+          <t>-4.81</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>1.10</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-0.74</t>
+          <t>2.46</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4031,72 +4031,72 @@
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>46</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>31.71</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.57</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-4.73</t>
+          <t>-0.62</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-3.16</t>
+          <t>-3.73</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-2.36</t>
+          <t>-2.59</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>21.15</t>
+          <t>20.93</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>21.84</t>
+          <t>21.74</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>22.37</t>
+          <t>22.32</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>22.04</t>
+          <t>22.07</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-78.27</t>
+          <t>-61.10</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-103.38</t>
+          <t>-103.99</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4116,41 +4116,41 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>30715.98842257597</t>
+          <t>30673.59971098266</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>634.0</t>
+          <t>749.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>1321.0</t>
+          <t>782.8</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>978.1</t>
+          <t>958.8</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>3201.08</t>
+          <t>3076.14</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>342</t>
+          <t>-176</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-189.6276215728426</t>
+          <t>-199.3512411554697</t>
         </is>
       </c>
       <c r="BC9" t="n">
-        <v>-251.54</v>
+        <v>-252.83</v>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>-14.80</t>
+          <t>-12.05</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4194,37 +4194,37 @@
       </c>
       <c r="BL9" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>-13.07532251352476</t>
+          <t>-4.453844239860662</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
         <is>
-          <t>9.705882352941176</t>
+          <t>20.1000834028357</t>
         </is>
       </c>
       <c r="BO9" t="inlineStr">
         <is>
-          <t>8.653674911088684</t>
+          <t>10.29997958114718</t>
         </is>
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="BX9" t="inlineStr">
         <is>
-          <t>72.9</t>
+          <t>86.33</t>
         </is>
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>597</t>
+          <t>585</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4274,27 +4274,27 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>光電業平上櫃</t>
+          <t>光電業右下上櫃</t>
         </is>
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>20.05</t>
+          <t>20.5</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>20.45</t>
+          <t>20.8</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>20.3</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>20.15</t>
+          <t>20.8</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4326,12 +4326,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-3.49</t>
+          <t>-2.74</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>24.0</t>
+          <t>31.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4341,7 +4341,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>20.7</t>
+          <t>20.15</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4351,17 +4351,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-1.22</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-1.63</t>
+          <t>-2.68</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>24.06</t>
+          <t>35.06</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -4426,7 +4426,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-5.26</t>
+          <t>-7.78</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4436,17 +4436,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>1.10</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-3.86</t>
+          <t>-0.74</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4462,7 +4462,7 @@
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>46</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
@@ -4477,57 +4477,57 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-3.68</t>
+          <t>-4.73</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-2.20</t>
+          <t>-3.16</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-2.11</t>
+          <t>-2.36</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>21.49</t>
+          <t>21.15</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>21.97</t>
+          <t>21.84</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>22.45</t>
+          <t>22.37</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>22.0</t>
+          <t>22.04</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-62.59</t>
+          <t>-78.27</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4537,7 +4537,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-102.72</t>
+          <t>-103.38</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4547,41 +4547,41 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>30715.98842257597</t>
+          <t>30673.59971098266</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>510.0</t>
+          <t>634.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>1307.2</t>
+          <t>1321.0</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>1053.7</t>
+          <t>978.1</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>4241.22</t>
+          <t>3201.08</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>253</t>
+          <t>342</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-178.3701598816587</t>
+          <t>-189.6276215728426</t>
         </is>
       </c>
       <c r="BC10" t="n">
-        <v>-228.4</v>
+        <v>-251.54</v>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>-12.47</t>
+          <t>-14.80</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -4625,22 +4625,22 @@
       </c>
       <c r="BL10" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>-13.07532251352476</t>
+          <t>-4.453844239860662</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
         <is>
-          <t>9.705882352941176</t>
+          <t>20.1000834028357</t>
         </is>
       </c>
       <c r="BO10" t="inlineStr">
         <is>
-          <t>8.653674911088684</t>
+          <t>10.29997958114718</t>
         </is>
       </c>
       <c r="BP10" t="inlineStr">
@@ -4655,7 +4655,7 @@
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="BX10" t="inlineStr">
         <is>
-          <t>72.9</t>
+          <t>86.33</t>
         </is>
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>597</t>
+          <t>585</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4705,27 +4705,27 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>光電業平上櫃</t>
+          <t>光電業右下上櫃</t>
         </is>
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>21.5</t>
+          <t>20.05</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>21.5</t>
+          <t>20.45</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>20.7</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>20.7</t>
+          <t>20.15</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-0.47</t>
+          <t>-3.49</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>38.0</t>
+          <t>24.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>21.45</t>
+          <t>20.7</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4782,17 +4782,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-4.89</t>
+          <t>-3.24</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-1.63</t>
+          <t>-2.68</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-34.91</t>
+          <t>24.06</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4802,7 +4802,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -4857,7 +4857,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-1.83</t>
+          <t>-5.26</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4867,17 +4867,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2.66</t>
+          <t>-3.86</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4893,7 +4893,7 @@
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>46</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
@@ -4903,62 +4903,62 @@
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-1.33</t>
+          <t>-3.68</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-1.54</t>
+          <t>-2.20</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-1.97</t>
+          <t>-2.11</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>21.74</t>
+          <t>21.49</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>22.08</t>
+          <t>21.97</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>22.52</t>
+          <t>22.45</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>21.96</t>
+          <t>22.0</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-37.68</t>
+          <t>-62.59</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4968,7 +4968,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-102.29</t>
+          <t>-102.72</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4978,12 +4978,12 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>30715.98842257597</t>
+          <t>30673.59971098266</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>807.0</t>
+          <t>510.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
@@ -4993,26 +4993,26 @@
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>2008.4</t>
+          <t>1053.7</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>4309.16</t>
+          <t>4241.22</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-701</t>
+          <t>253</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-169.2739595732266</t>
+          <t>-178.3701598816587</t>
         </is>
       </c>
       <c r="BC11" t="n">
-        <v>-173.89</v>
+        <v>-228.4</v>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
@@ -5031,7 +5031,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>-9.30</t>
+          <t>-12.47</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5056,27 +5056,27 @@
       </c>
       <c r="BL11" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>-13.07532251352476</t>
+          <t>-4.453844239860662</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
         <is>
-          <t>9.705882352941176</t>
+          <t>20.1000834028357</t>
         </is>
       </c>
       <c r="BO11" t="inlineStr">
         <is>
-          <t>8.653674911088684</t>
+          <t>10.29997958114718</t>
         </is>
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5086,7 +5086,7 @@
       </c>
       <c r="BR11" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="BS11" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="BX11" t="inlineStr">
         <is>
-          <t>72.9</t>
+          <t>86.33</t>
         </is>
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>597</t>
+          <t>585</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5136,27 +5136,27 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>光電業平上櫃</t>
+          <t>光電業右下上櫃</t>
         </is>
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>21.1</t>
+          <t>21.5</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>21.55</t>
+          <t>21.5</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>20.8</t>
+          <t>20.7</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>21.45</t>
+          <t>20.7</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-1.61</t>
+          <t>-0.47</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>57.0</t>
+          <t>38.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>21.55</t>
+          <t>21.45</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5213,17 +5213,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-5.38</t>
+          <t>-6.98</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-1.63</t>
+          <t>-2.68</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-50.22</t>
+          <t>-34.91</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5233,7 +5233,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -5288,7 +5288,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-1.37</t>
+          <t>-1.83</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5298,17 +5298,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>2.66</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5324,7 +5324,7 @@
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>46</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -5334,62 +5334,62 @@
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>13.14</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-1.55</t>
+          <t>-1.33</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>-1.54</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-1.98</t>
+          <t>-1.97</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>3.15</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>21.89</t>
+          <t>21.74</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>22.16</t>
+          <t>22.08</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>22.61</t>
+          <t>22.52</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>21.92</t>
+          <t>21.96</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-28.00</t>
+          <t>-37.68</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-102.08</t>
+          <t>-102.29</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5409,41 +5409,41 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>30715.98842257597</t>
+          <t>30673.59971098266</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>1214.0</t>
+          <t>807.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>1270.2</t>
+          <t>1307.2</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>2551.7</t>
+          <t>2008.4</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>4541.96</t>
+          <t>4309.16</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-1281</t>
+          <t>-701</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-168.4341334517733</t>
+          <t>-169.2739595732266</t>
         </is>
       </c>
       <c r="BC12" t="n">
-        <v>-121.64</v>
+        <v>-173.89</v>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>-8.88</t>
+          <t>-9.30</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -5487,22 +5487,22 @@
       </c>
       <c r="BL12" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>-13.07532251352476</t>
+          <t>-4.453844239860662</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
         <is>
-          <t>9.705882352941176</t>
+          <t>20.1000834028357</t>
         </is>
       </c>
       <c r="BO12" t="inlineStr">
         <is>
-          <t>8.653674911088684</t>
+          <t>10.29997958114718</t>
         </is>
       </c>
       <c r="BP12" t="inlineStr">
@@ -5517,7 +5517,7 @@
       </c>
       <c r="BR12" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="BS12" t="inlineStr">
@@ -5547,12 +5547,12 @@
       </c>
       <c r="BX12" t="inlineStr">
         <is>
-          <t>72.9</t>
+          <t>86.33</t>
         </is>
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>597</t>
+          <t>585</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5567,27 +5567,27 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>光電業平上櫃</t>
+          <t>光電業右下上櫃</t>
         </is>
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>21.75</t>
+          <t>21.1</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>21.75</t>
+          <t>21.55</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>21.35</t>
+          <t>20.8</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>21.55</t>
+          <t>21.45</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
@@ -5619,12 +5619,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>167.0</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5634,74 +5634,74 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
+          <t>204.0</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>9.50</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>-50.0</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>2025-11-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>2025-11-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>2025-10-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>2025-11-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
           <t>201.5</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>-2.28</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>21.03</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>2025-11-14</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>-65.0</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>2025-11-14 00:00:00</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>2025-11-16 00:00:00</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>2025-10-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>2025-11-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q13" t="inlineStr">
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
         <is>
           <t>201.5</t>
         </is>
       </c>
-      <c r="R13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>201.5</t>
-        </is>
-      </c>
       <c r="T13" t="inlineStr">
         <is>
           <t>195.5</t>
@@ -5714,7 +5714,7 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
@@ -5729,17 +5729,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>39.29</t>
+          <t>31.53</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5750,12 +5750,12 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>134</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
@@ -5765,195 +5765,195 @@
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>69.23</t>
+          <t>82.05</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>2.87</t>
+          <t>2.96</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>198.8</t>
+          <t>199.5</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>197.15</t>
+          <t>197.7</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>191.65</t>
+          <t>192.01</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>190.08</t>
+          <t>190.29</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>14.82</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
+          <t>2.01</t>
+        </is>
+      </c>
+      <c r="AS13" t="inlineStr">
+        <is>
+          <t>10.01</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr">
+        <is>
+          <t>-79.98</t>
+        </is>
+      </c>
+      <c r="AU13" t="inlineStr">
+        <is>
+          <t>2025/11/14</t>
+        </is>
+      </c>
+      <c r="AV13" t="inlineStr">
+        <is>
+          <t>28263.53540462428</t>
+        </is>
+      </c>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>27388.0</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>15822.8</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>14450.7</t>
+        </is>
+      </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>10277.46</t>
+        </is>
+      </c>
+      <c r="BA13" t="inlineStr">
+        <is>
+          <t>1372</t>
+        </is>
+      </c>
+      <c r="BB13" t="inlineStr">
+        <is>
+          <t>462.1765112122318</t>
+        </is>
+      </c>
+      <c r="BC13" t="n">
+        <v>1986.8</v>
+      </c>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="BE13" t="inlineStr">
+        <is>
+          <t>192.0</t>
+        </is>
+      </c>
+      <c r="BF13" t="inlineStr">
+        <is>
+          <t>2025/10/14</t>
+        </is>
+      </c>
+      <c r="BG13" t="inlineStr">
+        <is>
+          <t>6.25</t>
+        </is>
+      </c>
+      <c r="BH13" t="inlineStr">
+        <is>
+          <t>鼎翰</t>
+        </is>
+      </c>
+      <c r="BI13" t="inlineStr">
+        <is>
+          <t>鼎翰</t>
+        </is>
+      </c>
+      <c r="BJ13" t="inlineStr">
+        <is>
+          <t>電腦及週邊設備業</t>
+        </is>
+      </c>
+      <c r="BK13" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BL13" t="inlineStr">
+        <is>
+          <t>0.56</t>
+        </is>
+      </c>
+      <c r="BM13" t="inlineStr">
+        <is>
+          <t>-11.45161899724185</t>
+        </is>
+      </c>
+      <c r="BN13" t="inlineStr">
+        <is>
+          <t>22.56717409239306</t>
+        </is>
+      </c>
+      <c r="BO13" t="inlineStr">
+        <is>
+          <t>38.82556207928187</t>
+        </is>
+      </c>
+      <c r="BP13" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BQ13" t="inlineStr">
+        <is>
+          <t>價-量增</t>
+        </is>
+      </c>
+      <c r="BR13" t="inlineStr">
+        <is>
           <t>1.93</t>
         </is>
       </c>
-      <c r="AS13" t="inlineStr">
-        <is>
-          <t>10.01</t>
-        </is>
-      </c>
-      <c r="AT13" t="inlineStr">
-        <is>
-          <t>-80.72</t>
-        </is>
-      </c>
-      <c r="AU13" t="inlineStr">
-        <is>
-          <t>2025/11/14</t>
-        </is>
-      </c>
-      <c r="AV13" t="inlineStr">
-        <is>
-          <t>28244.98480463097</t>
-        </is>
-      </c>
-      <c r="AW13" t="inlineStr">
-        <is>
-          <t>33609.0</t>
-        </is>
-      </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>14692.0</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr">
-        <is>
-          <t>12138.8</t>
-        </is>
-      </c>
-      <c r="AZ13" t="inlineStr">
-        <is>
-          <t>9836.78</t>
-        </is>
-      </c>
-      <c r="BA13" t="inlineStr">
-        <is>
-          <t>2553</t>
-        </is>
-      </c>
-      <c r="BB13" t="inlineStr">
-        <is>
-          <t>184.9729413194776</t>
-        </is>
-      </c>
-      <c r="BC13" t="n">
-        <v>1139.99</v>
-      </c>
-      <c r="BD13" t="inlineStr">
-        <is>
-          <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="BE13" t="inlineStr">
-        <is>
-          <t>192.0</t>
-        </is>
-      </c>
-      <c r="BF13" t="inlineStr">
-        <is>
-          <t>2025/10/14</t>
-        </is>
-      </c>
-      <c r="BG13" t="inlineStr">
-        <is>
-          <t>4.95</t>
-        </is>
-      </c>
-      <c r="BH13" t="inlineStr">
-        <is>
-          <t>鼎翰</t>
-        </is>
-      </c>
-      <c r="BI13" t="inlineStr">
-        <is>
-          <t>鼎翰</t>
-        </is>
-      </c>
-      <c r="BJ13" t="inlineStr">
-        <is>
-          <t>電腦及週邊設備業</t>
-        </is>
-      </c>
-      <c r="BK13" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BL13" t="inlineStr">
-        <is>
-          <t>0.56</t>
-        </is>
-      </c>
-      <c r="BM13" t="inlineStr">
-        <is>
-          <t>2.123485354450912</t>
-        </is>
-      </c>
-      <c r="BN13" t="inlineStr">
-        <is>
-          <t>11.6416816819949</t>
-        </is>
-      </c>
-      <c r="BO13" t="inlineStr">
-        <is>
-          <t>39.78581979185335</t>
-        </is>
-      </c>
-      <c r="BP13" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BQ13" t="inlineStr">
-        <is>
-          <t>價漲量增</t>
-        </is>
-      </c>
-      <c r="BR13" t="inlineStr">
-        <is>
-          <t>1.91</t>
-        </is>
-      </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>4.95</t>
+          <t>4.89</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
@@ -5963,7 +5963,7 @@
       </c>
       <c r="BU13" t="inlineStr">
         <is>
-          <t>11.76</t>
+          <t>12.18</t>
         </is>
       </c>
       <c r="BV13" t="inlineStr">
@@ -5978,12 +5978,12 @@
       </c>
       <c r="BX13" t="inlineStr">
         <is>
-          <t>45.88</t>
+          <t>49.69</t>
         </is>
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>9368</t>
+          <t>9701</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
@@ -6003,22 +6003,22 @@
       </c>
       <c r="CC13" t="inlineStr">
         <is>
-          <t>199.0</t>
+          <t>201.5</t>
         </is>
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>202.5</t>
+          <t>206.5</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>198.5</t>
+          <t>201.5</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>201.5</t>
+          <t>204.0</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
@@ -6050,12 +6050,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>19.0</t>
+          <t>167.0</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6065,7 +6065,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>197.0</t>
+          <t>201.5</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6075,27 +6075,27 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
+          <t>1.23</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>21.03</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -6105,7 +6105,7 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>2025-11-16 00:00:00</t>
+          <t>2025-11-18 00:00:00</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -6130,7 +6130,7 @@
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>201.5</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
@@ -6145,7 +6145,7 @@
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
@@ -6160,17 +6160,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>4.47</t>
+          <t>39.29</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>-1.27</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6181,72 +6181,72 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>134</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>46.15</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>51.28</t>
+          <t>69.23</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>2.84</t>
+          <t>2.87</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>197.9</t>
+          <t>198.8</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>196.78</t>
+          <t>197.15</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>191.34</t>
+          <t>191.65</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>190.02</t>
+          <t>190.08</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>-11.24</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
@@ -6261,7 +6261,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-80.75</t>
+          <t>-80.72</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6271,45 +6271,45 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>28244.98480463097</t>
+          <t>28263.53540462428</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>3715.0</t>
+          <t>33609.0</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>9865.0</t>
+          <t>14692.0</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>9864.3</t>
+          <t>12138.8</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>9269.96</t>
+          <t>9836.78</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2553</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>11.33269122891031</t>
+          <t>184.9729413194776</t>
         </is>
       </c>
       <c r="BC14" t="n">
-        <v>-776.97</v>
+        <v>1139.99</v>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
@@ -6324,7 +6324,7 @@
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>2.60</t>
+          <t>4.95</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
@@ -6354,37 +6354,37 @@
       </c>
       <c r="BM14" t="inlineStr">
         <is>
-          <t>2.123485354450912</t>
+          <t>-11.45161899724185</t>
         </is>
       </c>
       <c r="BN14" t="inlineStr">
         <is>
-          <t>11.6416816819949</t>
+          <t>22.56717409239306</t>
         </is>
       </c>
       <c r="BO14" t="inlineStr">
         <is>
-          <t>39.78581979185335</t>
+          <t>38.82556207928187</t>
         </is>
       </c>
       <c r="BP14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>4.95</t>
+          <t>4.89</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
@@ -6394,7 +6394,7 @@
       </c>
       <c r="BU14" t="inlineStr">
         <is>
-          <t>11.76</t>
+          <t>12.18</t>
         </is>
       </c>
       <c r="BV14" t="inlineStr">
@@ -6409,12 +6409,12 @@
       </c>
       <c r="BX14" t="inlineStr">
         <is>
-          <t>45.88</t>
+          <t>49.69</t>
         </is>
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>9368</t>
+          <t>9701</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
@@ -6434,22 +6434,22 @@
       </c>
       <c r="CC14" t="inlineStr">
         <is>
-          <t>199.5</t>
+          <t>199.0</t>
         </is>
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>199.5</t>
+          <t>202.5</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>197.0</t>
+          <t>198.5</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>197.0</t>
+          <t>201.5</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
@@ -6481,12 +6481,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>19.0</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6496,7 +6496,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>198.0</t>
+          <t>197.0</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6506,7 +6506,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>3.43</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -6516,7 +6516,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6526,7 +6526,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -6536,7 +6536,7 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>2025-11-16 00:00:00</t>
+          <t>2025-11-18 00:00:00</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -6591,17 +6591,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>7.06</t>
+          <t>4.47</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>-1.27</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6612,77 +6612,77 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>134</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>61.54</t>
+          <t>46.15</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>69.23</t>
+          <t>51.28</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>0.80</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>2.85</t>
+          <t>2.84</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>0.62</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>198.2</t>
+          <t>197.9</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>196.62</t>
+          <t>196.78</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>191.17</t>
+          <t>191.34</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>189.99</t>
+          <t>190.02</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>-6.74</t>
+          <t>-11.24</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6692,7 +6692,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-80.21</t>
+          <t>-80.75</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6702,41 +6702,41 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>28244.98480463097</t>
+          <t>28263.53540462428</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>5976.0</t>
+          <t>3715.0</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>10613.2</t>
+          <t>9865.0</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>10254.6</t>
+          <t>9864.3</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>9315.64</t>
+          <t>9269.96</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>358</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>154.6608857258293</t>
+          <t>11.33269122891031</t>
         </is>
       </c>
       <c r="BC15" t="n">
-        <v>-284.82</v>
+        <v>-776.97</v>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
@@ -6755,7 +6755,7 @@
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>3.12</t>
+          <t>2.60</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
@@ -6785,37 +6785,37 @@
       </c>
       <c r="BM15" t="inlineStr">
         <is>
-          <t>2.123485354450912</t>
+          <t>-11.45161899724185</t>
         </is>
       </c>
       <c r="BN15" t="inlineStr">
         <is>
-          <t>11.6416816819949</t>
+          <t>22.56717409239306</t>
         </is>
       </c>
       <c r="BO15" t="inlineStr">
         <is>
-          <t>39.78581979185335</t>
+          <t>38.82556207928187</t>
         </is>
       </c>
       <c r="BP15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>4.95</t>
+          <t>4.89</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="BU15" t="inlineStr">
         <is>
-          <t>11.76</t>
+          <t>12.18</t>
         </is>
       </c>
       <c r="BV15" t="inlineStr">
@@ -6840,12 +6840,12 @@
       </c>
       <c r="BX15" t="inlineStr">
         <is>
-          <t>45.88</t>
+          <t>49.69</t>
         </is>
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>9368</t>
+          <t>9701</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
@@ -6865,22 +6865,22 @@
       </c>
       <c r="CC15" t="inlineStr">
         <is>
+          <t>199.5</t>
+        </is>
+      </c>
+      <c r="CD15" t="inlineStr">
+        <is>
+          <t>199.5</t>
+        </is>
+      </c>
+      <c r="CE15" t="inlineStr">
+        <is>
           <t>197.0</t>
         </is>
       </c>
-      <c r="CD15" t="inlineStr">
-        <is>
-          <t>198.5</t>
-        </is>
-      </c>
-      <c r="CE15" t="inlineStr">
+      <c r="CF15" t="inlineStr">
         <is>
           <t>197.0</t>
-        </is>
-      </c>
-      <c r="CF15" t="inlineStr">
-        <is>
-          <t>198.0</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
@@ -6912,12 +6912,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-1.75</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>42.0</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6927,7 +6927,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>197.0</t>
+          <t>198.0</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6937,17 +6937,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
+          <t>2.94</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>16.90</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -6957,7 +6957,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -6967,7 +6967,7 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>2025-11-16 00:00:00</t>
+          <t>2025-11-18 00:00:00</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -7022,17 +7022,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>9.88</t>
+          <t>7.06</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>-1.78</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7043,77 +7043,77 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>134</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>46.15</t>
+          <t>61.54</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>70.94</t>
+          <t>69.23</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>0.60</t>
+          <t>0.80</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>2.8</t>
+          <t>2.85</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>197.5</t>
+          <t>198.2</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>196.32</t>
+          <t>196.62</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>190.97</t>
+          <t>191.17</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>189.94</t>
+          <t>189.99</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>-5.98</t>
+          <t>-6.74</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>1.89</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7123,7 +7123,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-79.87</t>
+          <t>-80.21</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7133,41 +7133,41 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>28244.98480463097</t>
+          <t>28263.53540462428</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>8426.0</t>
+          <t>5976.0</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>12937.0</t>
+          <t>10613.2</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>11067.0</t>
+          <t>10254.6</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>9335.32</t>
+          <t>9315.64</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>1870</t>
+          <t>358</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>234.5662547700167</t>
+          <t>154.6608857258293</t>
         </is>
       </c>
       <c r="BC16" t="n">
-        <v>186.18</v>
+        <v>-284.82</v>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
@@ -7186,7 +7186,7 @@
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>2.60</t>
+          <t>3.12</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
@@ -7216,22 +7216,22 @@
       </c>
       <c r="BM16" t="inlineStr">
         <is>
-          <t>2.123485354450912</t>
+          <t>-11.45161899724185</t>
         </is>
       </c>
       <c r="BN16" t="inlineStr">
         <is>
-          <t>11.6416816819949</t>
+          <t>22.56717409239306</t>
         </is>
       </c>
       <c r="BO16" t="inlineStr">
         <is>
-          <t>39.78581979185335</t>
+          <t>38.82556207928187</t>
         </is>
       </c>
       <c r="BP16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ16" t="inlineStr">
@@ -7241,12 +7241,12 @@
       </c>
       <c r="BR16" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>4.95</t>
+          <t>4.89</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
@@ -7256,7 +7256,7 @@
       </c>
       <c r="BU16" t="inlineStr">
         <is>
-          <t>11.76</t>
+          <t>12.18</t>
         </is>
       </c>
       <c r="BV16" t="inlineStr">
@@ -7271,12 +7271,12 @@
       </c>
       <c r="BX16" t="inlineStr">
         <is>
-          <t>45.88</t>
+          <t>49.69</t>
         </is>
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>9368</t>
+          <t>9701</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
@@ -7296,12 +7296,12 @@
       </c>
       <c r="CC16" t="inlineStr">
         <is>
-          <t>200.5</t>
+          <t>197.0</t>
         </is>
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>200.5</t>
+          <t>198.5</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
@@ -7311,7 +7311,7 @@
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>197.0</t>
+          <t>198.0</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
@@ -7343,12 +7343,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>-1.75</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>108.0</t>
+          <t>42.0</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7358,7 +7358,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>200.5</t>
+          <t>197.0</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7368,102 +7368,102 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
+          <t>3.43</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>16.90</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>-50.0</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>2025-11-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>2025-11-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>2025-10-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>2025-11-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>201.5</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>195.5</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>196.0</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>2.81</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-11-11</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>9.88</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
           <t>-1.78</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>11.96</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>-65.0</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>2025-11-14 00:00:00</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>2025-11-16 00:00:00</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>2025-10-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>2025-11-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q17" t="inlineStr">
-        <is>
-          <t>201.5</t>
-        </is>
-      </c>
-      <c r="R17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>195.5</t>
-        </is>
-      </c>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>196.0</t>
-        </is>
-      </c>
-      <c r="V17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>2.81</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>2025-11-10</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>25.41</t>
-        </is>
-      </c>
-      <c r="AA17" t="inlineStr">
-        <is>
-          <t>-0.74</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7474,77 +7474,77 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>134</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>46.15</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>82.83</t>
+          <t>70.94</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.60</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>2.72</t>
+          <t>2.8</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>196.9</t>
+          <t>197.5</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>196.0</t>
+          <t>196.32</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>190.81</t>
+          <t>190.97</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>189.91</t>
+          <t>189.94</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>-5.98</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>1.89</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7554,7 +7554,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-79.57</t>
+          <t>-79.87</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7564,41 +7564,41 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>28244.98480463097</t>
+          <t>28263.53540462428</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>21734.0</t>
+          <t>8426.0</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>13078.6</t>
+          <t>12937.0</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>11681.7</t>
+          <t>11067.0</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>9341.52</t>
+          <t>9335.32</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>1396</t>
+          <t>1870</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>243.363716734609</t>
+          <t>234.5662547700167</t>
         </is>
       </c>
       <c r="BC17" t="n">
-        <v>589.89</v>
+        <v>186.18</v>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
@@ -7617,7 +7617,7 @@
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>4.43</t>
+          <t>2.60</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
@@ -7647,37 +7647,37 @@
       </c>
       <c r="BM17" t="inlineStr">
         <is>
-          <t>2.123485354450912</t>
+          <t>-11.45161899724185</t>
         </is>
       </c>
       <c r="BN17" t="inlineStr">
         <is>
-          <t>11.6416816819949</t>
+          <t>22.56717409239306</t>
         </is>
       </c>
       <c r="BO17" t="inlineStr">
         <is>
-          <t>39.78581979185335</t>
+          <t>38.82556207928187</t>
         </is>
       </c>
       <c r="BP17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>4.95</t>
+          <t>4.89</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
@@ -7687,7 +7687,7 @@
       </c>
       <c r="BU17" t="inlineStr">
         <is>
-          <t>11.76</t>
+          <t>12.18</t>
         </is>
       </c>
       <c r="BV17" t="inlineStr">
@@ -7702,12 +7702,12 @@
       </c>
       <c r="BX17" t="inlineStr">
         <is>
-          <t>45.88</t>
+          <t>49.69</t>
         </is>
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>9368</t>
+          <t>9701</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
@@ -7727,22 +7727,22 @@
       </c>
       <c r="CC17" t="inlineStr">
         <is>
-          <t>203.5</t>
+          <t>200.5</t>
         </is>
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>203.5</t>
+          <t>200.5</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>199.0</t>
+          <t>197.0</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>200.5</t>
+          <t>197.0</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
@@ -7774,12 +7774,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>48.0</t>
+          <t>108.0</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7789,7 +7789,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>197.0</t>
+          <t>200.5</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7799,17 +7799,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
+          <t>1.72</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-10.99</t>
+          <t>11.96</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7819,7 +7819,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -7829,7 +7829,7 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>2025-11-16 00:00:00</t>
+          <t>2025-11-18 00:00:00</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
@@ -7884,17 +7884,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11.29</t>
+          <t>25.41</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>-0.74</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7905,72 +7905,72 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>134</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>52.27</t>
+          <t>82.83</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>2.72</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
+          <t>196.9</t>
+        </is>
+      </c>
+      <c r="AM18" t="inlineStr">
+        <is>
           <t>196.0</t>
         </is>
       </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>195.48</t>
-        </is>
-      </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>190.59</t>
+          <t>190.81</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>189.82</t>
+          <t>189.91</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>-11.56</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
@@ -7985,7 +7985,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-79.53</t>
+          <t>-79.57</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7995,41 +7995,41 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>28244.98480463097</t>
+          <t>28263.53540462428</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>9474.0</t>
+          <t>21734.0</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>9585.6</t>
+          <t>13078.6</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>10769.2</t>
+          <t>11681.7</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>9013.74</t>
+          <t>9341.52</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>-1183</t>
+          <t>1396</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>180.3595866842333</t>
+          <t>243.363716734609</t>
         </is>
       </c>
       <c r="BC18" t="n">
-        <v>-280.31</v>
+        <v>589.89</v>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
@@ -8048,7 +8048,7 @@
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>2.60</t>
+          <t>4.43</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
@@ -8078,37 +8078,37 @@
       </c>
       <c r="BM18" t="inlineStr">
         <is>
-          <t>2.123485354450912</t>
+          <t>-11.45161899724185</t>
         </is>
       </c>
       <c r="BN18" t="inlineStr">
         <is>
-          <t>11.6416816819949</t>
+          <t>22.56717409239306</t>
         </is>
       </c>
       <c r="BO18" t="inlineStr">
         <is>
-          <t>39.78581979185335</t>
+          <t>38.82556207928187</t>
         </is>
       </c>
       <c r="BP18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>4.95</t>
+          <t>4.89</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
@@ -8118,7 +8118,7 @@
       </c>
       <c r="BU18" t="inlineStr">
         <is>
-          <t>11.76</t>
+          <t>12.18</t>
         </is>
       </c>
       <c r="BV18" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="BX18" t="inlineStr">
         <is>
-          <t>45.88</t>
+          <t>49.69</t>
         </is>
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>9368</t>
+          <t>9701</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
@@ -8158,22 +8158,22 @@
       </c>
       <c r="CC18" t="inlineStr">
         <is>
-          <t>196.0</t>
+          <t>203.5</t>
         </is>
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>197.5</t>
+          <t>203.5</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>195.0</t>
+          <t>199.0</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>197.0</t>
+          <t>200.5</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
@@ -8205,12 +8205,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>-0.77</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>38.0</t>
+          <t>48.0</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8220,7 +8220,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>198.5</t>
+          <t>197.0</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8230,7 +8230,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>3.43</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -8240,7 +8240,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-14.77</t>
+          <t>-10.99</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8250,7 +8250,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -8260,7 +8260,7 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>2025-11-16 00:00:00</t>
+          <t>2025-11-18 00:00:00</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
@@ -8315,17 +8315,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>8.94</t>
+          <t>11.29</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8336,77 +8336,77 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>134</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>81.82</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>30.05</t>
+          <t>52.27</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>2.48</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>195.7</t>
+          <t>196.0</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>195.12</t>
+          <t>195.48</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>190.41</t>
+          <t>190.59</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>189.79</t>
+          <t>189.82</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>-11.44</t>
+          <t>-11.56</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8416,7 +8416,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-78.94</t>
+          <t>-79.53</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8426,41 +8426,41 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>28244.98480463097</t>
+          <t>28263.53540462428</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>7456.0</t>
+          <t>9474.0</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>9863.6</t>
+          <t>9585.6</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>11572.5</t>
+          <t>10769.2</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>9025.16</t>
+          <t>9013.74</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>-1708</t>
+          <t>-1183</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>264.1185869502501</t>
+          <t>180.3595866842333</t>
         </is>
       </c>
       <c r="BC19" t="n">
-        <v>-199.88</v>
+        <v>-280.31</v>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
@@ -8479,7 +8479,7 @@
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>3.39</t>
+          <t>2.60</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">
@@ -8509,37 +8509,37 @@
       </c>
       <c r="BM19" t="inlineStr">
         <is>
-          <t>2.123485354450912</t>
+          <t>-11.45161899724185</t>
         </is>
       </c>
       <c r="BN19" t="inlineStr">
         <is>
-          <t>11.6416816819949</t>
+          <t>22.56717409239306</t>
         </is>
       </c>
       <c r="BO19" t="inlineStr">
         <is>
-          <t>39.78581979185335</t>
+          <t>38.82556207928187</t>
         </is>
       </c>
       <c r="BP19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>4.95</t>
+          <t>4.89</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
@@ -8549,7 +8549,7 @@
       </c>
       <c r="BU19" t="inlineStr">
         <is>
-          <t>11.76</t>
+          <t>12.18</t>
         </is>
       </c>
       <c r="BV19" t="inlineStr">
@@ -8564,12 +8564,12 @@
       </c>
       <c r="BX19" t="inlineStr">
         <is>
-          <t>45.88</t>
+          <t>49.69</t>
         </is>
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>9368</t>
+          <t>9701</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
@@ -8589,22 +8589,22 @@
       </c>
       <c r="CC19" t="inlineStr">
         <is>
+          <t>196.0</t>
+        </is>
+      </c>
+      <c r="CD19" t="inlineStr">
+        <is>
+          <t>197.5</t>
+        </is>
+      </c>
+      <c r="CE19" t="inlineStr">
+        <is>
           <t>195.0</t>
         </is>
       </c>
-      <c r="CD19" t="inlineStr">
-        <is>
-          <t>199.0</t>
-        </is>
-      </c>
-      <c r="CE19" t="inlineStr">
-        <is>
-          <t>195.0</t>
-        </is>
-      </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>198.5</t>
+          <t>197.0</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
@@ -8636,12 +8636,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>38.0</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8651,7 +8651,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>194.5</t>
+          <t>198.5</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8661,7 +8661,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>2.7</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -8671,7 +8671,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>-19.30</t>
+          <t>-14.77</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8681,7 +8681,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -8691,7 +8691,7 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>2025-11-16 00:00:00</t>
+          <t>2025-11-18 00:00:00</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
@@ -8746,17 +8746,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>21.65</t>
+          <t>8.94</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8767,77 +8767,77 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>134</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>8.33</t>
+          <t>81.82</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>6.48</t>
+          <t>30.05</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>2.48</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>195.5</t>
+          <t>195.7</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>194.65</t>
+          <t>195.12</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>190.2</t>
+          <t>190.41</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>189.76</t>
+          <t>189.79</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>-18.96</t>
+          <t>-11.44</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8847,7 +8847,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-78.34</t>
+          <t>-78.94</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8857,41 +8857,41 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>28244.98480463097</t>
+          <t>28263.53540462428</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>17595.0</t>
+          <t>7456.0</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>9896.0</t>
+          <t>9863.6</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>12262.5</t>
+          <t>11572.5</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>9049.34</t>
+          <t>9025.16</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>-2366</t>
+          <t>-1708</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>348.481424646728</t>
+          <t>264.1185869502501</t>
         </is>
       </c>
       <c r="BC20" t="n">
-        <v>138.39</v>
+        <v>-199.88</v>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
@@ -8910,7 +8910,7 @@
       </c>
       <c r="BG20" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>3.39</t>
         </is>
       </c>
       <c r="BH20" t="inlineStr">
@@ -8940,22 +8940,22 @@
       </c>
       <c r="BM20" t="inlineStr">
         <is>
-          <t>2.123485354450912</t>
+          <t>-11.45161899724185</t>
         </is>
       </c>
       <c r="BN20" t="inlineStr">
         <is>
-          <t>11.6416816819949</t>
+          <t>22.56717409239306</t>
         </is>
       </c>
       <c r="BO20" t="inlineStr">
         <is>
-          <t>39.78581979185335</t>
+          <t>38.82556207928187</t>
         </is>
       </c>
       <c r="BP20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ20" t="inlineStr">
@@ -8965,12 +8965,12 @@
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>4.95</t>
+          <t>4.89</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
@@ -8980,7 +8980,7 @@
       </c>
       <c r="BU20" t="inlineStr">
         <is>
-          <t>11.76</t>
+          <t>12.18</t>
         </is>
       </c>
       <c r="BV20" t="inlineStr">
@@ -8995,12 +8995,12 @@
       </c>
       <c r="BX20" t="inlineStr">
         <is>
-          <t>45.88</t>
+          <t>49.69</t>
         </is>
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>9368</t>
+          <t>9701</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
@@ -9020,22 +9020,22 @@
       </c>
       <c r="CC20" t="inlineStr">
         <is>
-          <t>194.0</t>
+          <t>195.0</t>
         </is>
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>194.5</t>
+          <t>199.0</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>190.0</t>
+          <t>195.0</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>194.5</t>
+          <t>198.5</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
@@ -9067,12 +9067,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-1.01</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>47.0</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9082,7 +9082,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>194.0</t>
+          <t>194.5</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9092,7 +9092,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>4.66</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -9102,7 +9102,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>-23.60</t>
+          <t>-19.30</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9112,7 +9112,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -9122,7 +9122,7 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>2025-11-16 00:00:00</t>
+          <t>2025-11-18 00:00:00</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
@@ -9177,17 +9177,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11.06</t>
+          <t>21.65</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>-1.80</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9198,77 +9198,77 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>134</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>8.33</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>12.04</t>
+          <t>6.48</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>-1.17</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>196.3</t>
+          <t>195.5</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>194.38</t>
+          <t>194.65</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>190.1</t>
+          <t>190.2</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>189.75</t>
+          <t>189.76</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>-11.99</t>
+          <t>-18.96</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>2.27</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9278,7 +9278,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-77.31</t>
+          <t>-78.34</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9288,41 +9288,41 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>28244.98480463097</t>
+          <t>28263.53540462428</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>9134.0</t>
+          <t>17595.0</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>9197.0</t>
+          <t>9896.0</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>12037.8</t>
+          <t>12262.5</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>8763.96</t>
+          <t>9049.34</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>-2840</t>
+          <t>-2366</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>386.6804094807498</t>
+          <t>348.481424646728</t>
         </is>
       </c>
       <c r="BC21" t="n">
-        <v>-469.64</v>
+        <v>138.39</v>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
@@ -9341,7 +9341,7 @@
       </c>
       <c r="BG21" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="BH21" t="inlineStr">
@@ -9371,22 +9371,22 @@
       </c>
       <c r="BM21" t="inlineStr">
         <is>
-          <t>2.123485354450912</t>
+          <t>-11.45161899724185</t>
         </is>
       </c>
       <c r="BN21" t="inlineStr">
         <is>
-          <t>11.6416816819949</t>
+          <t>22.56717409239306</t>
         </is>
       </c>
       <c r="BO21" t="inlineStr">
         <is>
-          <t>39.78581979185335</t>
+          <t>38.82556207928187</t>
         </is>
       </c>
       <c r="BP21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ21" t="inlineStr">
@@ -9401,7 +9401,7 @@
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>4.95</t>
+          <t>4.89</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
@@ -9411,7 +9411,7 @@
       </c>
       <c r="BU21" t="inlineStr">
         <is>
-          <t>11.76</t>
+          <t>12.18</t>
         </is>
       </c>
       <c r="BV21" t="inlineStr">
@@ -9426,12 +9426,12 @@
       </c>
       <c r="BX21" t="inlineStr">
         <is>
-          <t>45.88</t>
+          <t>49.69</t>
         </is>
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>9368</t>
+          <t>9701</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
@@ -9451,22 +9451,22 @@
       </c>
       <c r="CC21" t="inlineStr">
         <is>
-          <t>197.5</t>
+          <t>194.0</t>
         </is>
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>197.5</t>
+          <t>194.5</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>194.0</t>
+          <t>190.0</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>194.0</t>
+          <t>194.5</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
@@ -9498,12 +9498,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>-1.01</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>22.0</t>
+          <t>47.0</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9513,87 +9513,87 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
+          <t>194.0</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>4.9</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>-23.60</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>-50.0</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>2025-11-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>2025-11-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>2025-10-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>2025-11-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>201.5</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>195.5</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
           <t>196.0</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>0.51</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>-14.92</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>2025-10-21</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>-65.0</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>2025-11-14 00:00:00</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>2025-11-16 00:00:00</t>
-        </is>
-      </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>2025-10-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>2025-11-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q22" t="inlineStr">
-        <is>
-          <t>201.5</t>
-        </is>
-      </c>
-      <c r="R22" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S22" t="inlineStr">
-        <is>
-          <t>195.5</t>
-        </is>
-      </c>
-      <c r="T22" t="inlineStr">
-        <is>
-          <t>195.5</t>
-        </is>
-      </c>
-      <c r="U22" t="inlineStr">
-        <is>
-          <t>196.0</t>
-        </is>
-      </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W22" t="inlineStr">
@@ -9608,17 +9608,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>5.18</t>
+          <t>11.06</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>-1.80</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9629,77 +9629,77 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>134</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>33.47</t>
+          <t>12.04</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>-1.17</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>2.18</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>197.0</t>
+          <t>196.3</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>194.12</t>
+          <t>194.38</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>189.98</t>
+          <t>190.1</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>189.74</t>
+          <t>189.75</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>-11.99</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>2.33</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>2.27</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9709,7 +9709,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-76.63</t>
+          <t>-77.31</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9719,45 +9719,45 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>28244.98480463097</t>
+          <t>28263.53540462428</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>4269.0</t>
+          <t>9134.0</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>10284.8</t>
+          <t>9197.0</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>12088.4</t>
+          <t>12037.8</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>8808.96</t>
+          <t>8763.96</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>-1803</t>
+          <t>-2840</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>542.3754816252442</t>
+          <t>386.6804094807498</t>
         </is>
       </c>
       <c r="BC22" t="n">
-        <v>-414.95</v>
+        <v>-469.64</v>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BE22" t="inlineStr">
@@ -9772,7 +9772,7 @@
       </c>
       <c r="BG22" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="BH22" t="inlineStr">
@@ -9802,22 +9802,22 @@
       </c>
       <c r="BM22" t="inlineStr">
         <is>
-          <t>2.123485354450912</t>
+          <t>-11.45161899724185</t>
         </is>
       </c>
       <c r="BN22" t="inlineStr">
         <is>
-          <t>11.6416816819949</t>
+          <t>22.56717409239306</t>
         </is>
       </c>
       <c r="BO22" t="inlineStr">
         <is>
-          <t>39.78581979185335</t>
+          <t>38.82556207928187</t>
         </is>
       </c>
       <c r="BP22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ22" t="inlineStr">
@@ -9827,12 +9827,12 @@
       </c>
       <c r="BR22" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>4.95</t>
+          <t>4.89</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
@@ -9842,7 +9842,7 @@
       </c>
       <c r="BU22" t="inlineStr">
         <is>
-          <t>11.76</t>
+          <t>12.18</t>
         </is>
       </c>
       <c r="BV22" t="inlineStr">
@@ -9857,12 +9857,12 @@
       </c>
       <c r="BX22" t="inlineStr">
         <is>
-          <t>45.88</t>
+          <t>49.69</t>
         </is>
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>9368</t>
+          <t>9701</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
@@ -9882,22 +9882,22 @@
       </c>
       <c r="CC22" t="inlineStr">
         <is>
-          <t>195.5</t>
+          <t>197.5</t>
         </is>
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>196.0</t>
+          <t>197.5</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>194.5</t>
+          <t>194.0</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>196.0</t>
+          <t>194.0</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
@@ -9929,12 +9929,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-1.01</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>55.0</t>
+          <t>22.0</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9944,79 +9944,79 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
+          <t>196.0</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>3.92</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>-14.92</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>-50.0</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>2025-11-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>2025-11-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>2025-10-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>2025-11-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>201.5</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
           <t>195.5</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>0.76</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>-3.49</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>2025-10-21</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>-65.0</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>2025-11-14 00:00:00</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>2025-11-16 00:00:00</t>
-        </is>
-      </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>2025-10-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>2025-11-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q23" t="inlineStr">
-        <is>
-          <t>201.5</t>
-        </is>
-      </c>
-      <c r="R23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S23" t="inlineStr">
+      <c r="T23" t="inlineStr">
         <is>
           <t>195.5</t>
         </is>
       </c>
-      <c r="T23" t="inlineStr">
-        <is>
-          <t>195.5</t>
-        </is>
-      </c>
       <c r="U23" t="inlineStr">
         <is>
           <t>196.0</t>
@@ -10024,7 +10024,7 @@
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="W23" t="inlineStr">
@@ -10039,17 +10039,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12.94</t>
+          <t>5.18</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>-1.28</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10060,152 +10060,152 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>134</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>55.95</t>
+          <t>33.47</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>-1.11</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
+          <t>1.48</t>
+        </is>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>2.18</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>0.12</t>
+        </is>
+      </c>
+      <c r="AL23" t="inlineStr">
+        <is>
+          <t>197.0</t>
+        </is>
+      </c>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>194.12</t>
+        </is>
+      </c>
+      <c r="AN23" t="inlineStr">
+        <is>
+          <t>189.98</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>189.74</t>
+        </is>
+      </c>
+      <c r="AP23" t="inlineStr">
+        <is>
+          <t>-0.44</t>
+        </is>
+      </c>
+      <c r="AQ23" t="inlineStr">
+        <is>
+          <t>2.33</t>
+        </is>
+      </c>
+      <c r="AR23" t="inlineStr">
+        <is>
+          <t>2.34</t>
+        </is>
+      </c>
+      <c r="AS23" t="inlineStr">
+        <is>
+          <t>10.01</t>
+        </is>
+      </c>
+      <c r="AT23" t="inlineStr">
+        <is>
+          <t>-76.63</t>
+        </is>
+      </c>
+      <c r="AU23" t="inlineStr">
+        <is>
+          <t>2025/11/14</t>
+        </is>
+      </c>
+      <c r="AV23" t="inlineStr">
+        <is>
+          <t>28263.53540462428</t>
+        </is>
+      </c>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>4269.0</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>10284.8</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>12088.4</t>
+        </is>
+      </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>8808.96</t>
+        </is>
+      </c>
+      <c r="BA23" t="inlineStr">
+        <is>
+          <t>-1803</t>
+        </is>
+      </c>
+      <c r="BB23" t="inlineStr">
+        <is>
+          <t>542.3754816252442</t>
+        </is>
+      </c>
+      <c r="BC23" t="n">
+        <v>-414.95</v>
+      </c>
+      <c r="BD23" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="BE23" t="inlineStr">
+        <is>
+          <t>192.0</t>
+        </is>
+      </c>
+      <c r="BF23" t="inlineStr">
+        <is>
+          <t>2025/10/14</t>
+        </is>
+      </c>
+      <c r="BG23" t="inlineStr">
+        <is>
           <t>2.08</t>
         </is>
       </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>2.03</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>0.06</t>
-        </is>
-      </c>
-      <c r="AL23" t="inlineStr">
-        <is>
-          <t>197.7</t>
-        </is>
-      </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>193.68</t>
-        </is>
-      </c>
-      <c r="AN23" t="inlineStr">
-        <is>
-          <t>189.83</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>189.71</t>
-        </is>
-      </c>
-      <c r="AP23" t="inlineStr">
-        <is>
-          <t>7.31</t>
-        </is>
-      </c>
-      <c r="AQ23" t="inlineStr">
-        <is>
-          <t>2.51</t>
-        </is>
-      </c>
-      <c r="AR23" t="inlineStr">
-        <is>
-          <t>2.34</t>
-        </is>
-      </c>
-      <c r="AS23" t="inlineStr">
-        <is>
-          <t>10.01</t>
-        </is>
-      </c>
-      <c r="AT23" t="inlineStr">
-        <is>
-          <t>-76.60</t>
-        </is>
-      </c>
-      <c r="AU23" t="inlineStr">
-        <is>
-          <t>2025/11/14</t>
-        </is>
-      </c>
-      <c r="AV23" t="inlineStr">
-        <is>
-          <t>28244.98480463097</t>
-        </is>
-      </c>
-      <c r="AW23" t="inlineStr">
-        <is>
-          <t>10864.0</t>
-        </is>
-      </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t>11952.8</t>
-        </is>
-      </c>
-      <c r="AY23" t="inlineStr">
-        <is>
-          <t>12384.7</t>
-        </is>
-      </c>
-      <c r="AZ23" t="inlineStr">
-        <is>
-          <t>8930.12</t>
-        </is>
-      </c>
-      <c r="BA23" t="inlineStr">
-        <is>
-          <t>-431</t>
-        </is>
-      </c>
-      <c r="BB23" t="inlineStr">
-        <is>
-          <t>716.4341858974979</t>
-        </is>
-      </c>
-      <c r="BC23" t="n">
-        <v>199.26</v>
-      </c>
-      <c r="BD23" t="inlineStr">
-        <is>
-          <t>2025-11-03</t>
-        </is>
-      </c>
-      <c r="BE23" t="inlineStr">
-        <is>
-          <t>192.0</t>
-        </is>
-      </c>
-      <c r="BF23" t="inlineStr">
-        <is>
-          <t>2025/10/14</t>
-        </is>
-      </c>
-      <c r="BG23" t="inlineStr">
-        <is>
-          <t>1.82</t>
-        </is>
-      </c>
       <c r="BH23" t="inlineStr">
         <is>
           <t>鼎翰</t>
@@ -10233,22 +10233,22 @@
       </c>
       <c r="BM23" t="inlineStr">
         <is>
-          <t>2.123485354450912</t>
+          <t>-11.45161899724185</t>
         </is>
       </c>
       <c r="BN23" t="inlineStr">
         <is>
-          <t>11.6416816819949</t>
+          <t>22.56717409239306</t>
         </is>
       </c>
       <c r="BO23" t="inlineStr">
         <is>
-          <t>39.78581979185335</t>
+          <t>38.82556207928187</t>
         </is>
       </c>
       <c r="BP23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ23" t="inlineStr">
@@ -10263,7 +10263,7 @@
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>4.95</t>
+          <t>4.89</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
@@ -10273,7 +10273,7 @@
       </c>
       <c r="BU23" t="inlineStr">
         <is>
-          <t>11.76</t>
+          <t>12.18</t>
         </is>
       </c>
       <c r="BV23" t="inlineStr">
@@ -10288,12 +10288,12 @@
       </c>
       <c r="BX23" t="inlineStr">
         <is>
-          <t>45.88</t>
+          <t>49.69</t>
         </is>
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>9368</t>
+          <t>9701</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
@@ -10313,22 +10313,22 @@
       </c>
       <c r="CC23" t="inlineStr">
         <is>
-          <t>197.5</t>
+          <t>195.5</t>
         </is>
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>198.5</t>
+          <t>196.0</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>195.0</t>
+          <t>194.5</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>195.5</t>
+          <t>196.0</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">

--- a/Result/checksun_type/HMI.xlsx
+++ b/Result/checksun_type/HMI.xlsx
@@ -878,12 +878,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-2.0</t>
+          <t>-4.24</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>46.0</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>20.05</t>
+          <t>19.2</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -908,12 +908,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-2.68</t>
+          <t>-4.28</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>17.65</t>
+          <t>21.51</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -923,7 +923,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-8.24</t>
+          <t>-12.13</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -988,17 +988,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>3.15</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>-3.37</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>89</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -1024,62 +1024,62 @@
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>23.08</t>
+          <t>15.38</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-1.91</t>
+          <t>-4.81</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-3.90</t>
+          <t>-4.41</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-2.98</t>
+          <t>-3.49</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-1.65</t>
+          <t>-2.01</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>20.44</t>
+          <t>20.17</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>21.27</t>
+          <t>21.1</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>21.92</t>
+          <t>21.86</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>22.29</t>
+          <t>22.31</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-16.23</t>
+          <t>-25.64</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-106.88</t>
+          <t>-107.35</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1099,41 +1099,41 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>30673.59971098266</t>
+          <t>30633.04978354978</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>922.0</t>
+          <t>1715.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>840.4</t>
+          <t>1014.4</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>714.3</t>
+          <t>834.8</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>1889.2</t>
+          <t>1896.36</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>126</t>
+          <t>179</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-195.1459064225224</t>
+          <t>-175.1202900950192</t>
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>-147.95</v>
+        <v>-64.98</v>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>-15.22</t>
+          <t>-18.82</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1177,7 +1177,7 @@
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="BM2" t="inlineStr">
@@ -1197,7 +1197,7 @@
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
@@ -1207,7 +1207,7 @@
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>86.33</t>
+          <t>84.03</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>585</t>
+          <t>560</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1262,22 +1262,22 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>20.05</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>20.1</t>
+          <t>20.05</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>19.95</t>
+          <t>19.0</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>20.05</t>
+          <t>19.2</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1309,12 +1309,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-2.0</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>16.0</t>
+          <t>46.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>20.45</t>
+          <t>20.05</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1334,17 +1334,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-2.0</t>
+          <t>-4.43</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-2.68</t>
+          <t>-4.28</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>22.57</t>
+          <t>17.65</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1354,7 +1354,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -1409,7 +1409,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-6.41</t>
+          <t>-8.24</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1419,17 +1419,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1440,77 +1440,77 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>89</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>46.15</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>36.17</t>
+          <t>23.08</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-1.91</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-4.52</t>
+          <t>-3.90</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-2.41</t>
+          <t>-2.98</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-1.36</t>
+          <t>-1.65</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>20.46</t>
+          <t>20.44</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>21.43</t>
+          <t>21.27</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>21.96</t>
+          <t>21.92</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>22.26</t>
+          <t>22.29</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-15.32</t>
+          <t>-16.23</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-0.50</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-106.60</t>
+          <t>-106.88</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,41 +1530,41 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>30673.59971098266</t>
+          <t>30633.04978354978</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>326.0</t>
+          <t>922.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>861.4</t>
+          <t>840.4</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>702.8</t>
+          <t>714.3</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>2075.44</t>
+          <t>1889.2</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>158</t>
+          <t>126</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-203.7270186305573</t>
+          <t>-195.1459064225224</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>-176.23</v>
+        <v>-147.95</v>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>-13.53</t>
+          <t>-15.22</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1608,7 +1608,7 @@
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="BM3" t="inlineStr">
@@ -1628,7 +1628,7 @@
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
@@ -1638,7 +1638,7 @@
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
@@ -1668,12 +1668,12 @@
       </c>
       <c r="BX3" t="inlineStr">
         <is>
-          <t>86.33</t>
+          <t>84.03</t>
         </is>
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>585</t>
+          <t>560</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1693,22 +1693,22 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>20.45</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>20.45</t>
+          <t>20.1</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>20.3</t>
+          <t>19.95</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>20.45</t>
+          <t>20.05</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1740,12 +1740,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-1.19</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1765,17 +1765,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-2.0</t>
+          <t>-6.51</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-2.68</t>
+          <t>-4.28</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>22.57</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1785,7 +1785,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -1850,17 +1850,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-1.95</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1871,67 +1871,67 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>89</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>23.08</t>
+          <t>46.15</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>28.41</t>
+          <t>36.17</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-4.33</t>
+          <t>-4.52</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-2.52</t>
+          <t>-2.41</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>-1.36</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>20.53</t>
+          <t>20.46</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>21.46</t>
+          <t>21.43</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>22.01</t>
+          <t>21.96</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>22.23</t>
+          <t>22.26</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-20.19</t>
+          <t>-15.32</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
@@ -1941,7 +1941,7 @@
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-106.34</t>
+          <t>-106.60</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1961,41 +1961,41 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>30673.59971098266</t>
+          <t>30633.04978354978</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>1362.0</t>
+          <t>326.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>800.4</t>
+          <t>861.4</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>791.6</t>
+          <t>702.8</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>2169.22</t>
+          <t>2075.44</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>158</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-208.7263475380736</t>
+          <t>-203.7270186305573</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>-146.48</v>
+        <v>-176.23</v>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
@@ -2039,7 +2039,7 @@
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="BM4" t="inlineStr">
@@ -2059,7 +2059,7 @@
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
@@ -2099,12 +2099,12 @@
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>86.33</t>
+          <t>84.03</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>585</t>
+          <t>560</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>21.0</t>
+          <t>20.45</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>21.0</t>
+          <t>20.45</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>-1.19</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>36.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>20.7</t>
+          <t>20.45</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2196,17 +2196,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-3.24</t>
+          <t>-6.51</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-2.68</t>
+          <t>-4.28</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-32.18</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-5.26</t>
+          <t>-6.41</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2281,17 +2281,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>-1.95</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2302,67 +2302,67 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>89</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>39.29</t>
+          <t>23.08</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>20.71</t>
+          <t>28.41</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-4.13</t>
+          <t>-4.33</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-2.66</t>
+          <t>-2.52</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-0.54</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>20.6</t>
+          <t>20.53</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>21.49</t>
+          <t>21.46</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>22.08</t>
+          <t>22.01</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>22.19</t>
+          <t>22.23</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-25.12</t>
+          <t>-20.19</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
@@ -2372,7 +2372,7 @@
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-106.02</t>
+          <t>-106.34</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2392,41 +2392,41 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>30673.59971098266</t>
+          <t>30633.04978354978</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>747.0</t>
+          <t>1362.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>677.8</t>
+          <t>800.4</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>999.4</t>
+          <t>791.6</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>2614.76</t>
+          <t>2169.22</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-321</t>
+          <t>8</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-220.0436966054221</t>
+          <t>-208.7263475380736</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>-209.75</v>
+        <v>-146.48</v>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>-12.47</t>
+          <t>-13.53</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2470,7 +2470,7 @@
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="BM5" t="inlineStr">
@@ -2490,7 +2490,7 @@
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
@@ -2500,7 +2500,7 @@
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>86.33</t>
+          <t>84.03</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>585</t>
+          <t>560</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2555,22 +2555,22 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>20.6</t>
+          <t>21.0</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>20.95</t>
+          <t>21.0</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>20.55</t>
+          <t>20.3</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>20.7</t>
+          <t>20.45</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>41.0</t>
+          <t>36.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>20.55</t>
+          <t>20.7</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2627,17 +2627,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-2.49</t>
+          <t>-7.81</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-2.68</t>
+          <t>-4.28</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-33.22</t>
+          <t>-32.18</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2647,7 +2647,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -2702,7 +2702,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-5.95</t>
+          <t>-5.26</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2712,17 +2712,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-4.11</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2733,77 +2733,77 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>89</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>22.86</t>
+          <t>39.29</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>19.66</t>
+          <t>20.71</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-4.71</t>
+          <t>-4.13</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-2.98</t>
+          <t>-2.66</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-0.54</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>20.49</t>
+          <t>20.6</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>21.5</t>
+          <t>21.49</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>22.16</t>
+          <t>22.08</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>22.16</t>
+          <t>22.19</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-36.40</t>
+          <t>-25.12</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>-0.50</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2813,7 +2813,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-105.65</t>
+          <t>-106.02</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2823,41 +2823,41 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>30673.59971098266</t>
+          <t>30633.04978354978</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>845.0</t>
+          <t>747.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>655.2</t>
+          <t>677.8</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>981.2</t>
+          <t>999.4</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>2840.22</t>
+          <t>2614.76</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-326</t>
+          <t>-321</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-221.9153182728739</t>
+          <t>-220.0436966054221</t>
         </is>
       </c>
       <c r="BC6" t="n">
-        <v>-226.75</v>
+        <v>-209.75</v>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>-13.11</t>
+          <t>-12.47</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="BL6" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="BM6" t="inlineStr">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BX6" t="inlineStr">
         <is>
-          <t>86.33</t>
+          <t>84.03</t>
         </is>
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>585</t>
+          <t>560</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>20.2</t>
+          <t>20.6</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>21.75</t>
+          <t>20.95</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>20.2</t>
+          <t>20.55</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>20.55</t>
+          <t>20.7</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-3.22</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>51.0</t>
+          <t>41.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>20.15</t>
+          <t>20.55</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>-7.03</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-2.68</t>
+          <t>-4.28</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-37.93</t>
+          <t>-33.22</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-7.78</t>
+          <t>-5.95</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-0.74</t>
+          <t>-4.11</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,77 +3164,77 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>89</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>22.86</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>22.61</t>
+          <t>19.66</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-1.80</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-4.79</t>
+          <t>-4.71</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-2.96</t>
+          <t>-2.98</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>20.52</t>
+          <t>20.49</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>21.55</t>
+          <t>21.5</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>22.21</t>
+          <t>22.16</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>22.13</t>
+          <t>22.16</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-47.43</t>
+          <t>-36.40</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.50</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.37</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-105.13</t>
+          <t>-105.65</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3254,41 +3254,41 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>30673.59971098266</t>
+          <t>30633.04978354978</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>1027.0</t>
+          <t>845.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>588.2</t>
+          <t>655.2</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>947.7</t>
+          <t>981.2</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>2910.12</t>
+          <t>2840.22</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-359</t>
+          <t>-326</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-221.0362983393635</t>
+          <t>-221.9153182728739</t>
         </is>
       </c>
       <c r="BC7" t="n">
-        <v>-253.44</v>
+        <v>-226.75</v>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>-14.80</t>
+          <t>-13.11</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3332,7 +3332,7 @@
       </c>
       <c r="BL7" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="BM7" t="inlineStr">
@@ -3362,7 +3362,7 @@
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="BX7" t="inlineStr">
         <is>
-          <t>86.33</t>
+          <t>84.03</t>
         </is>
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>585</t>
+          <t>560</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3422,17 +3422,17 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>20.4</t>
+          <t>21.75</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>20.05</t>
+          <t>20.2</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>20.15</t>
+          <t>20.55</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3464,12 +3464,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-3.22</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>51.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>20.8</t>
+          <t>20.15</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3489,17 +3489,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-3.74</t>
+          <t>-4.95</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-2.68</t>
+          <t>-4.28</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-40.01</t>
+          <t>-37.93</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3509,7 +3509,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -3564,7 +3564,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-4.81</t>
+          <t>-7.78</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3574,17 +3574,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.74</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3595,17 +3595,17 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>89</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>36.11</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
@@ -3615,57 +3615,57 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>0.10</t>
+          <t>-1.80</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-4.04</t>
+          <t>-4.79</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-2.72</t>
+          <t>-2.96</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.36</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>20.78</t>
+          <t>20.52</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>21.66</t>
+          <t>21.55</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>22.26</t>
+          <t>22.21</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>22.1</t>
+          <t>22.13</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-47.36</t>
+          <t>-47.43</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>-0.50</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-104.52</t>
+          <t>-105.13</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3685,41 +3685,41 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>30673.59971098266</t>
+          <t>30633.04978354978</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>21.0</t>
+          <t>1027.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>544.2</t>
+          <t>588.2</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>907.2</t>
+          <t>947.7</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>2976.72</t>
+          <t>2910.12</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-363</t>
+          <t>-359</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-215.145144320523</t>
+          <t>-221.0362983393635</t>
         </is>
       </c>
       <c r="BC8" t="n">
-        <v>-302.01</v>
+        <v>-253.44</v>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>-12.05</t>
+          <t>-14.80</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -3763,7 +3763,7 @@
       </c>
       <c r="BL8" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="BM8" t="inlineStr">
@@ -3783,17 +3783,17 @@
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
@@ -3823,12 +3823,12 @@
       </c>
       <c r="BX8" t="inlineStr">
         <is>
-          <t>86.33</t>
+          <t>84.03</t>
         </is>
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>585</t>
+          <t>560</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -3848,22 +3848,22 @@
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>20.8</t>
+          <t>20.2</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>20.8</t>
+          <t>20.4</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>20.8</t>
+          <t>20.05</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>20.8</t>
+          <t>20.15</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>3.17</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>36.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3920,17 +3920,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-3.74</t>
+          <t>-8.33</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-2.68</t>
+          <t>-4.28</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-18.36</t>
+          <t>-40.01</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3940,7 +3940,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2.46</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4026,77 +4026,77 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>89</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>31.71</t>
+          <t>36.11</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>10.57</t>
+          <t>22.61</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-0.62</t>
+          <t>0.10</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-3.73</t>
+          <t>-4.04</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-2.59</t>
+          <t>-2.72</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>20.93</t>
+          <t>20.78</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>21.74</t>
+          <t>21.66</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>22.32</t>
+          <t>22.26</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>22.07</t>
+          <t>22.1</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-61.10</t>
+          <t>-47.36</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>-0.44</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-103.99</t>
+          <t>-104.52</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4116,41 +4116,41 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>30673.59971098266</t>
+          <t>30633.04978354978</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>749.0</t>
+          <t>21.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>782.8</t>
+          <t>544.2</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>958.8</t>
+          <t>907.2</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>3076.14</t>
+          <t>2976.72</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-176</t>
+          <t>-363</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-199.3512411554697</t>
+          <t>-215.145144320523</t>
         </is>
       </c>
       <c r="BC9" t="n">
-        <v>-252.83</v>
+        <v>-302.01</v>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
@@ -4194,7 +4194,7 @@
       </c>
       <c r="BL9" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="BM9" t="inlineStr">
@@ -4214,7 +4214,7 @@
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="BX9" t="inlineStr">
         <is>
-          <t>86.33</t>
+          <t>84.03</t>
         </is>
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>585</t>
+          <t>560</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4279,7 +4279,7 @@
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>20.5</t>
+          <t>20.8</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
@@ -4289,7 +4289,7 @@
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>20.3</t>
+          <t>20.8</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
@@ -4326,12 +4326,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-2.74</t>
+          <t>3.17</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>31.0</t>
+          <t>36.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4341,7 +4341,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>20.15</t>
+          <t>20.8</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4351,17 +4351,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>-8.33</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-2.68</t>
+          <t>-4.28</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>35.06</t>
+          <t>-18.36</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -4426,7 +4426,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-7.78</t>
+          <t>-4.81</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4436,17 +4436,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>1.10</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-0.74</t>
+          <t>2.46</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4457,77 +4457,77 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>89</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>31.71</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.57</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-4.73</t>
+          <t>-0.62</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-3.16</t>
+          <t>-3.73</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-2.36</t>
+          <t>-2.59</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>21.15</t>
+          <t>20.93</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>21.84</t>
+          <t>21.74</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>22.37</t>
+          <t>22.32</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>22.04</t>
+          <t>22.07</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-78.27</t>
+          <t>-61.10</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4537,7 +4537,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-103.38</t>
+          <t>-103.99</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4547,41 +4547,41 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>30673.59971098266</t>
+          <t>30633.04978354978</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>634.0</t>
+          <t>749.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>1321.0</t>
+          <t>782.8</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>978.1</t>
+          <t>958.8</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>3201.08</t>
+          <t>3076.14</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>342</t>
+          <t>-176</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-189.6276215728426</t>
+          <t>-199.3512411554697</t>
         </is>
       </c>
       <c r="BC10" t="n">
-        <v>-251.54</v>
+        <v>-252.83</v>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>-14.80</t>
+          <t>-12.05</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -4625,7 +4625,7 @@
       </c>
       <c r="BL10" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="BM10" t="inlineStr">
@@ -4645,17 +4645,17 @@
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="BX10" t="inlineStr">
         <is>
-          <t>86.33</t>
+          <t>84.03</t>
         </is>
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>585</t>
+          <t>560</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4710,22 +4710,22 @@
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>20.05</t>
+          <t>20.5</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>20.45</t>
+          <t>20.8</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>20.3</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>20.15</t>
+          <t>20.8</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-3.49</t>
+          <t>-2.74</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>24.0</t>
+          <t>31.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>20.7</t>
+          <t>20.15</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4782,17 +4782,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-3.24</t>
+          <t>-4.95</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-2.68</t>
+          <t>-4.28</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>24.06</t>
+          <t>35.06</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4802,7 +4802,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -4857,7 +4857,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-5.26</t>
+          <t>-7.78</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4867,17 +4867,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>1.10</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-3.86</t>
+          <t>-0.74</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4888,12 +4888,12 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>89</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
@@ -4908,57 +4908,57 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-3.68</t>
+          <t>-4.73</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-2.20</t>
+          <t>-3.16</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-2.11</t>
+          <t>-2.36</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>21.49</t>
+          <t>21.15</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>21.97</t>
+          <t>21.84</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>22.45</t>
+          <t>22.37</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>22.0</t>
+          <t>22.04</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-62.59</t>
+          <t>-78.27</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4968,7 +4968,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-102.72</t>
+          <t>-103.38</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4978,41 +4978,41 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>30673.59971098266</t>
+          <t>30633.04978354978</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>510.0</t>
+          <t>634.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>1307.2</t>
+          <t>1321.0</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>1053.7</t>
+          <t>978.1</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>4241.22</t>
+          <t>3201.08</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>253</t>
+          <t>342</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-178.3701598816587</t>
+          <t>-189.6276215728426</t>
         </is>
       </c>
       <c r="BC11" t="n">
-        <v>-228.4</v>
+        <v>-251.54</v>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
@@ -5031,7 +5031,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>-12.47</t>
+          <t>-14.80</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5056,7 +5056,7 @@
       </c>
       <c r="BL11" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="BM11" t="inlineStr">
@@ -5086,7 +5086,7 @@
       </c>
       <c r="BR11" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="BS11" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="BX11" t="inlineStr">
         <is>
-          <t>86.33</t>
+          <t>84.03</t>
         </is>
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>585</t>
+          <t>560</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5141,22 +5141,22 @@
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>21.5</t>
+          <t>20.05</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>21.5</t>
+          <t>20.45</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>20.7</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>20.7</t>
+          <t>20.15</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-0.47</t>
+          <t>-3.49</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>38.0</t>
+          <t>24.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>21.45</t>
+          <t>20.7</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5213,17 +5213,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-6.98</t>
+          <t>-7.81</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-2.68</t>
+          <t>-4.28</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-34.91</t>
+          <t>24.06</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5233,7 +5233,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -5288,7 +5288,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-1.83</t>
+          <t>-5.26</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5298,17 +5298,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2.66</t>
+          <t>-3.86</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5319,12 +5319,12 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>89</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -5334,62 +5334,62 @@
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-1.33</t>
+          <t>-3.68</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-1.54</t>
+          <t>-2.20</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-1.97</t>
+          <t>-2.11</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>21.74</t>
+          <t>21.49</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>22.08</t>
+          <t>21.97</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>22.52</t>
+          <t>22.45</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>21.96</t>
+          <t>22.0</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-37.68</t>
+          <t>-62.59</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-102.29</t>
+          <t>-102.72</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5409,12 +5409,12 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>30673.59971098266</t>
+          <t>30633.04978354978</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>807.0</t>
+          <t>510.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
@@ -5424,26 +5424,26 @@
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>2008.4</t>
+          <t>1053.7</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>4309.16</t>
+          <t>4241.22</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-701</t>
+          <t>253</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-169.2739595732266</t>
+          <t>-178.3701598816587</t>
         </is>
       </c>
       <c r="BC12" t="n">
-        <v>-173.89</v>
+        <v>-228.4</v>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>-9.30</t>
+          <t>-12.47</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -5487,7 +5487,7 @@
       </c>
       <c r="BL12" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="BM12" t="inlineStr">
@@ -5507,7 +5507,7 @@
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -5517,7 +5517,7 @@
       </c>
       <c r="BR12" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="BS12" t="inlineStr">
@@ -5547,12 +5547,12 @@
       </c>
       <c r="BX12" t="inlineStr">
         <is>
-          <t>86.33</t>
+          <t>84.03</t>
         </is>
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>585</t>
+          <t>560</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5572,22 +5572,22 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>21.1</t>
+          <t>21.5</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>21.55</t>
+          <t>21.5</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>20.8</t>
+          <t>20.7</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>21.45</t>
+          <t>20.7</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
@@ -5619,12 +5619,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>-2.2</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>107.0</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5634,7 +5634,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>204.0</t>
+          <t>199.5</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5649,12 +5649,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>9.50</t>
+          <t>17.59</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5664,7 +5664,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -5674,7 +5674,7 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>2025-11-18 00:00:00</t>
+          <t>2025-11-19 00:00:00</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -5714,7 +5714,7 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
@@ -5729,17 +5729,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>31.53</t>
+          <t>25.18</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>-2.00</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5750,32 +5750,32 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>134</t>
+          <t>107</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>35.71</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>82.05</t>
+          <t>78.57</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
@@ -5785,240 +5785,240 @@
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
+          <t>200.0</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>197.98</t>
+        </is>
+      </c>
+      <c r="AN13" t="inlineStr">
+        <is>
+          <t>192.28</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>190.44</t>
+        </is>
+      </c>
+      <c r="AP13" t="inlineStr">
+        <is>
+          <t>7.56</t>
+        </is>
+      </c>
+      <c r="AQ13" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="AR13" t="inlineStr">
+        <is>
+          <t>2.04</t>
+        </is>
+      </c>
+      <c r="AS13" t="inlineStr">
+        <is>
+          <t>10.01</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr">
+        <is>
+          <t>-79.59</t>
+        </is>
+      </c>
+      <c r="AU13" t="inlineStr">
+        <is>
+          <t>2025/11/14</t>
+        </is>
+      </c>
+      <c r="AV13" t="inlineStr">
+        <is>
+          <t>28269.50649350649</t>
+        </is>
+      </c>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>21601.0</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>18457.8</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>15697.4</t>
+        </is>
+      </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>10622.98</t>
+        </is>
+      </c>
+      <c r="BA13" t="inlineStr">
+        <is>
+          <t>2760</t>
+        </is>
+      </c>
+      <c r="BB13" t="inlineStr">
+        <is>
+          <t>713.5128205865296</t>
+        </is>
+      </c>
+      <c r="BC13" t="n">
+        <v>2095.86</v>
+      </c>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="BE13" t="inlineStr">
+        <is>
+          <t>192.0</t>
+        </is>
+      </c>
+      <c r="BF13" t="inlineStr">
+        <is>
+          <t>2025/10/14</t>
+        </is>
+      </c>
+      <c r="BG13" t="inlineStr">
+        <is>
+          <t>3.91</t>
+        </is>
+      </c>
+      <c r="BH13" t="inlineStr">
+        <is>
+          <t>鼎翰</t>
+        </is>
+      </c>
+      <c r="BI13" t="inlineStr">
+        <is>
+          <t>鼎翰</t>
+        </is>
+      </c>
+      <c r="BJ13" t="inlineStr">
+        <is>
+          <t>電腦及週邊設備業</t>
+        </is>
+      </c>
+      <c r="BK13" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BL13" t="inlineStr">
+        <is>
+          <t>0.57</t>
+        </is>
+      </c>
+      <c r="BM13" t="inlineStr">
+        <is>
+          <t>-11.45161899724185</t>
+        </is>
+      </c>
+      <c r="BN13" t="inlineStr">
+        <is>
+          <t>22.56717409239306</t>
+        </is>
+      </c>
+      <c r="BO13" t="inlineStr">
+        <is>
+          <t>38.82556207928187</t>
+        </is>
+      </c>
+      <c r="BP13" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BQ13" t="inlineStr">
+        <is>
+          <t>價-量增</t>
+        </is>
+      </c>
+      <c r="BR13" t="inlineStr">
+        <is>
+          <t>1.89</t>
+        </is>
+      </c>
+      <c r="BS13" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="BT13" t="inlineStr">
+        <is>
+          <t>57.78</t>
+        </is>
+      </c>
+      <c r="BU13" t="inlineStr">
+        <is>
+          <t>11.91</t>
+        </is>
+      </c>
+      <c r="BV13" t="inlineStr">
+        <is>
+          <t>33.69%</t>
+        </is>
+      </c>
+      <c r="BW13" t="inlineStr">
+        <is>
+          <t>11.08%</t>
+        </is>
+      </c>
+      <c r="BX13" t="inlineStr">
+        <is>
+          <t>48.7</t>
+        </is>
+      </c>
+      <c r="BY13" t="inlineStr">
+        <is>
+          <t>9487</t>
+        </is>
+      </c>
+      <c r="BZ13" t="inlineStr">
+        <is>
+          <t>條碼印表機及零配件52.71%、印表機各式標籤紙及其耗材41.09%、企業行動電腦6.20% (2024年)</t>
+        </is>
+      </c>
+      <c r="CA13" t="inlineStr">
+        <is>
+          <t>鼎翰-電腦及週邊設備業-上櫃</t>
+        </is>
+      </c>
+      <c r="CB13" t="inlineStr">
+        <is>
+          <t>電腦及週邊設備業右下上櫃</t>
+        </is>
+      </c>
+      <c r="CC13" t="inlineStr">
+        <is>
+          <t>205.0</t>
+        </is>
+      </c>
+      <c r="CD13" t="inlineStr">
+        <is>
+          <t>205.0</t>
+        </is>
+      </c>
+      <c r="CE13" t="inlineStr">
+        <is>
+          <t>198.0</t>
+        </is>
+      </c>
+      <c r="CF13" t="inlineStr">
+        <is>
           <t>199.5</t>
-        </is>
-      </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>197.7</t>
-        </is>
-      </c>
-      <c r="AN13" t="inlineStr">
-        <is>
-          <t>192.01</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>190.29</t>
-        </is>
-      </c>
-      <c r="AP13" t="inlineStr">
-        <is>
-          <t>14.82</t>
-        </is>
-      </c>
-      <c r="AQ13" t="inlineStr">
-        <is>
-          <t>2.30</t>
-        </is>
-      </c>
-      <c r="AR13" t="inlineStr">
-        <is>
-          <t>2.01</t>
-        </is>
-      </c>
-      <c r="AS13" t="inlineStr">
-        <is>
-          <t>10.01</t>
-        </is>
-      </c>
-      <c r="AT13" t="inlineStr">
-        <is>
-          <t>-79.98</t>
-        </is>
-      </c>
-      <c r="AU13" t="inlineStr">
-        <is>
-          <t>2025/11/14</t>
-        </is>
-      </c>
-      <c r="AV13" t="inlineStr">
-        <is>
-          <t>28263.53540462428</t>
-        </is>
-      </c>
-      <c r="AW13" t="inlineStr">
-        <is>
-          <t>27388.0</t>
-        </is>
-      </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>15822.8</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr">
-        <is>
-          <t>14450.7</t>
-        </is>
-      </c>
-      <c r="AZ13" t="inlineStr">
-        <is>
-          <t>10277.46</t>
-        </is>
-      </c>
-      <c r="BA13" t="inlineStr">
-        <is>
-          <t>1372</t>
-        </is>
-      </c>
-      <c r="BB13" t="inlineStr">
-        <is>
-          <t>462.1765112122318</t>
-        </is>
-      </c>
-      <c r="BC13" t="n">
-        <v>1986.8</v>
-      </c>
-      <c r="BD13" t="inlineStr">
-        <is>
-          <t>2025-11-18</t>
-        </is>
-      </c>
-      <c r="BE13" t="inlineStr">
-        <is>
-          <t>192.0</t>
-        </is>
-      </c>
-      <c r="BF13" t="inlineStr">
-        <is>
-          <t>2025/10/14</t>
-        </is>
-      </c>
-      <c r="BG13" t="inlineStr">
-        <is>
-          <t>6.25</t>
-        </is>
-      </c>
-      <c r="BH13" t="inlineStr">
-        <is>
-          <t>鼎翰</t>
-        </is>
-      </c>
-      <c r="BI13" t="inlineStr">
-        <is>
-          <t>鼎翰</t>
-        </is>
-      </c>
-      <c r="BJ13" t="inlineStr">
-        <is>
-          <t>電腦及週邊設備業</t>
-        </is>
-      </c>
-      <c r="BK13" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BL13" t="inlineStr">
-        <is>
-          <t>0.56</t>
-        </is>
-      </c>
-      <c r="BM13" t="inlineStr">
-        <is>
-          <t>-11.45161899724185</t>
-        </is>
-      </c>
-      <c r="BN13" t="inlineStr">
-        <is>
-          <t>22.56717409239306</t>
-        </is>
-      </c>
-      <c r="BO13" t="inlineStr">
-        <is>
-          <t>38.82556207928187</t>
-        </is>
-      </c>
-      <c r="BP13" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BQ13" t="inlineStr">
-        <is>
-          <t>價-量增</t>
-        </is>
-      </c>
-      <c r="BR13" t="inlineStr">
-        <is>
-          <t>1.93</t>
-        </is>
-      </c>
-      <c r="BS13" t="inlineStr">
-        <is>
-          <t>4.89</t>
-        </is>
-      </c>
-      <c r="BT13" t="inlineStr">
-        <is>
-          <t>57.78</t>
-        </is>
-      </c>
-      <c r="BU13" t="inlineStr">
-        <is>
-          <t>12.18</t>
-        </is>
-      </c>
-      <c r="BV13" t="inlineStr">
-        <is>
-          <t>33.69%</t>
-        </is>
-      </c>
-      <c r="BW13" t="inlineStr">
-        <is>
-          <t>11.08%</t>
-        </is>
-      </c>
-      <c r="BX13" t="inlineStr">
-        <is>
-          <t>49.69</t>
-        </is>
-      </c>
-      <c r="BY13" t="inlineStr">
-        <is>
-          <t>9701</t>
-        </is>
-      </c>
-      <c r="BZ13" t="inlineStr">
-        <is>
-          <t>條碼印表機及零配件52.71%、印表機各式標籤紙及其耗材41.09%、企業行動電腦6.20% (2024年)</t>
-        </is>
-      </c>
-      <c r="CA13" t="inlineStr">
-        <is>
-          <t>鼎翰-電腦及週邊設備業-上櫃</t>
-        </is>
-      </c>
-      <c r="CB13" t="inlineStr">
-        <is>
-          <t>電腦及週邊設備業右下上櫃</t>
-        </is>
-      </c>
-      <c r="CC13" t="inlineStr">
-        <is>
-          <t>201.5</t>
-        </is>
-      </c>
-      <c r="CD13" t="inlineStr">
-        <is>
-          <t>206.5</t>
-        </is>
-      </c>
-      <c r="CE13" t="inlineStr">
-        <is>
-          <t>201.5</t>
-        </is>
-      </c>
-      <c r="CF13" t="inlineStr">
-        <is>
-          <t>204.0</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
@@ -6050,12 +6050,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>167.0</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6065,74 +6065,74 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
+          <t>204.0</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>-2.26</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>-1.0</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>9.50</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>-65.0</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>2025-11-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>2025-11-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>2025-10-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>2025-11-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
           <t>201.5</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>1.23</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>21.03</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>2025-11-14</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>-50.0</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>2025-11-14 00:00:00</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>2025-11-18 00:00:00</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>2025-10-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>2025-11-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q14" t="inlineStr">
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
         <is>
           <t>201.5</t>
         </is>
       </c>
-      <c r="R14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>201.5</t>
-        </is>
-      </c>
       <c r="T14" t="inlineStr">
         <is>
           <t>195.5</t>
@@ -6145,7 +6145,7 @@
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
@@ -6160,17 +6160,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>39.29</t>
+          <t>31.53</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6181,12 +6181,12 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>134</t>
+          <t>107</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
@@ -6196,195 +6196,195 @@
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>69.23</t>
+          <t>82.05</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>2.87</t>
+          <t>2.96</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>198.8</t>
+          <t>199.5</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>197.15</t>
+          <t>197.7</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>191.65</t>
+          <t>192.01</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>190.08</t>
+          <t>190.29</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>14.82</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
+          <t>2.01</t>
+        </is>
+      </c>
+      <c r="AS14" t="inlineStr">
+        <is>
+          <t>10.01</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr">
+        <is>
+          <t>-79.98</t>
+        </is>
+      </c>
+      <c r="AU14" t="inlineStr">
+        <is>
+          <t>2025/11/14</t>
+        </is>
+      </c>
+      <c r="AV14" t="inlineStr">
+        <is>
+          <t>28269.50649350649</t>
+        </is>
+      </c>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>27388.0</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>15822.8</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>14450.7</t>
+        </is>
+      </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>10277.46</t>
+        </is>
+      </c>
+      <c r="BA14" t="inlineStr">
+        <is>
+          <t>1372</t>
+        </is>
+      </c>
+      <c r="BB14" t="inlineStr">
+        <is>
+          <t>462.1765112122318</t>
+        </is>
+      </c>
+      <c r="BC14" t="n">
+        <v>1986.8</v>
+      </c>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="BE14" t="inlineStr">
+        <is>
+          <t>192.0</t>
+        </is>
+      </c>
+      <c r="BF14" t="inlineStr">
+        <is>
+          <t>2025/10/14</t>
+        </is>
+      </c>
+      <c r="BG14" t="inlineStr">
+        <is>
+          <t>6.25</t>
+        </is>
+      </c>
+      <c r="BH14" t="inlineStr">
+        <is>
+          <t>鼎翰</t>
+        </is>
+      </c>
+      <c r="BI14" t="inlineStr">
+        <is>
+          <t>鼎翰</t>
+        </is>
+      </c>
+      <c r="BJ14" t="inlineStr">
+        <is>
+          <t>電腦及週邊設備業</t>
+        </is>
+      </c>
+      <c r="BK14" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BL14" t="inlineStr">
+        <is>
+          <t>0.57</t>
+        </is>
+      </c>
+      <c r="BM14" t="inlineStr">
+        <is>
+          <t>-11.45161899724185</t>
+        </is>
+      </c>
+      <c r="BN14" t="inlineStr">
+        <is>
+          <t>22.56717409239306</t>
+        </is>
+      </c>
+      <c r="BO14" t="inlineStr">
+        <is>
+          <t>38.82556207928187</t>
+        </is>
+      </c>
+      <c r="BP14" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BQ14" t="inlineStr">
+        <is>
+          <t>價-量增</t>
+        </is>
+      </c>
+      <c r="BR14" t="inlineStr">
+        <is>
           <t>1.93</t>
         </is>
       </c>
-      <c r="AS14" t="inlineStr">
-        <is>
-          <t>10.01</t>
-        </is>
-      </c>
-      <c r="AT14" t="inlineStr">
-        <is>
-          <t>-80.72</t>
-        </is>
-      </c>
-      <c r="AU14" t="inlineStr">
-        <is>
-          <t>2025/11/14</t>
-        </is>
-      </c>
-      <c r="AV14" t="inlineStr">
-        <is>
-          <t>28263.53540462428</t>
-        </is>
-      </c>
-      <c r="AW14" t="inlineStr">
-        <is>
-          <t>33609.0</t>
-        </is>
-      </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>14692.0</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr">
-        <is>
-          <t>12138.8</t>
-        </is>
-      </c>
-      <c r="AZ14" t="inlineStr">
-        <is>
-          <t>9836.78</t>
-        </is>
-      </c>
-      <c r="BA14" t="inlineStr">
-        <is>
-          <t>2553</t>
-        </is>
-      </c>
-      <c r="BB14" t="inlineStr">
-        <is>
-          <t>184.9729413194776</t>
-        </is>
-      </c>
-      <c r="BC14" t="n">
-        <v>1139.99</v>
-      </c>
-      <c r="BD14" t="inlineStr">
-        <is>
-          <t>2025-11-18</t>
-        </is>
-      </c>
-      <c r="BE14" t="inlineStr">
-        <is>
-          <t>192.0</t>
-        </is>
-      </c>
-      <c r="BF14" t="inlineStr">
-        <is>
-          <t>2025/10/14</t>
-        </is>
-      </c>
-      <c r="BG14" t="inlineStr">
-        <is>
-          <t>4.95</t>
-        </is>
-      </c>
-      <c r="BH14" t="inlineStr">
-        <is>
-          <t>鼎翰</t>
-        </is>
-      </c>
-      <c r="BI14" t="inlineStr">
-        <is>
-          <t>鼎翰</t>
-        </is>
-      </c>
-      <c r="BJ14" t="inlineStr">
-        <is>
-          <t>電腦及週邊設備業</t>
-        </is>
-      </c>
-      <c r="BK14" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BL14" t="inlineStr">
-        <is>
-          <t>0.56</t>
-        </is>
-      </c>
-      <c r="BM14" t="inlineStr">
-        <is>
-          <t>-11.45161899724185</t>
-        </is>
-      </c>
-      <c r="BN14" t="inlineStr">
-        <is>
-          <t>22.56717409239306</t>
-        </is>
-      </c>
-      <c r="BO14" t="inlineStr">
-        <is>
-          <t>38.82556207928187</t>
-        </is>
-      </c>
-      <c r="BP14" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BQ14" t="inlineStr">
-        <is>
-          <t>價漲量增</t>
-        </is>
-      </c>
-      <c r="BR14" t="inlineStr">
-        <is>
-          <t>1.91</t>
-        </is>
-      </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>4.89</t>
+          <t>5</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
@@ -6394,7 +6394,7 @@
       </c>
       <c r="BU14" t="inlineStr">
         <is>
-          <t>12.18</t>
+          <t>11.91</t>
         </is>
       </c>
       <c r="BV14" t="inlineStr">
@@ -6409,12 +6409,12 @@
       </c>
       <c r="BX14" t="inlineStr">
         <is>
-          <t>49.69</t>
+          <t>48.7</t>
         </is>
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>9701</t>
+          <t>9487</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
@@ -6434,22 +6434,22 @@
       </c>
       <c r="CC14" t="inlineStr">
         <is>
-          <t>199.0</t>
+          <t>201.5</t>
         </is>
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>202.5</t>
+          <t>206.5</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>198.5</t>
+          <t>201.5</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>201.5</t>
+          <t>204.0</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
@@ -6481,12 +6481,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>19.0</t>
+          <t>167.0</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6496,7 +6496,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>197.0</t>
+          <t>201.5</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6506,27 +6506,27 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>3.43</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>21.03</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -6536,7 +6536,7 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>2025-11-18 00:00:00</t>
+          <t>2025-11-19 00:00:00</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -6561,7 +6561,7 @@
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>201.5</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
@@ -6576,7 +6576,7 @@
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
@@ -6591,17 +6591,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>4.47</t>
+          <t>39.29</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>-1.27</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6612,177 +6612,177 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>134</t>
+          <t>107</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>46.15</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>51.28</t>
+          <t>69.23</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
+          <t>0.84</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>2.87</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>0.83</t>
+        </is>
+      </c>
+      <c r="AL15" t="inlineStr">
+        <is>
+          <t>198.8</t>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>197.15</t>
+        </is>
+      </c>
+      <c r="AN15" t="inlineStr">
+        <is>
+          <t>191.65</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>190.08</t>
+        </is>
+      </c>
+      <c r="AP15" t="inlineStr">
+        <is>
+          <t>0.64</t>
+        </is>
+      </c>
+      <c r="AQ15" t="inlineStr">
+        <is>
+          <t>1.94</t>
+        </is>
+      </c>
+      <c r="AR15" t="inlineStr">
+        <is>
+          <t>1.93</t>
+        </is>
+      </c>
+      <c r="AS15" t="inlineStr">
+        <is>
+          <t>10.01</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr">
+        <is>
+          <t>-80.72</t>
+        </is>
+      </c>
+      <c r="AU15" t="inlineStr">
+        <is>
+          <t>2025/11/14</t>
+        </is>
+      </c>
+      <c r="AV15" t="inlineStr">
+        <is>
+          <t>28269.50649350649</t>
+        </is>
+      </c>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>33609.0</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>14692.0</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>12138.8</t>
+        </is>
+      </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>9836.78</t>
+        </is>
+      </c>
+      <c r="BA15" t="inlineStr">
+        <is>
+          <t>2553</t>
+        </is>
+      </c>
+      <c r="BB15" t="inlineStr">
+        <is>
+          <t>184.9729413194776</t>
+        </is>
+      </c>
+      <c r="BC15" t="n">
+        <v>1139.99</v>
+      </c>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="BE15" t="inlineStr">
+        <is>
+          <t>192.0</t>
+        </is>
+      </c>
+      <c r="BF15" t="inlineStr">
+        <is>
+          <t>2025/10/14</t>
+        </is>
+      </c>
+      <c r="BG15" t="inlineStr">
+        <is>
+          <t>4.95</t>
+        </is>
+      </c>
+      <c r="BH15" t="inlineStr">
+        <is>
+          <t>鼎翰</t>
+        </is>
+      </c>
+      <c r="BI15" t="inlineStr">
+        <is>
+          <t>鼎翰</t>
+        </is>
+      </c>
+      <c r="BJ15" t="inlineStr">
+        <is>
+          <t>電腦及週邊設備業</t>
+        </is>
+      </c>
+      <c r="BK15" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BL15" t="inlineStr">
+        <is>
           <t>0.57</t>
         </is>
       </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>2.84</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>0.70</t>
-        </is>
-      </c>
-      <c r="AL15" t="inlineStr">
-        <is>
-          <t>197.9</t>
-        </is>
-      </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>196.78</t>
-        </is>
-      </c>
-      <c r="AN15" t="inlineStr">
-        <is>
-          <t>191.34</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>190.02</t>
-        </is>
-      </c>
-      <c r="AP15" t="inlineStr">
-        <is>
-          <t>-11.24</t>
-        </is>
-      </c>
-      <c r="AQ15" t="inlineStr">
-        <is>
-          <t>1.71</t>
-        </is>
-      </c>
-      <c r="AR15" t="inlineStr">
-        <is>
-          <t>1.93</t>
-        </is>
-      </c>
-      <c r="AS15" t="inlineStr">
-        <is>
-          <t>10.01</t>
-        </is>
-      </c>
-      <c r="AT15" t="inlineStr">
-        <is>
-          <t>-80.75</t>
-        </is>
-      </c>
-      <c r="AU15" t="inlineStr">
-        <is>
-          <t>2025/11/14</t>
-        </is>
-      </c>
-      <c r="AV15" t="inlineStr">
-        <is>
-          <t>28263.53540462428</t>
-        </is>
-      </c>
-      <c r="AW15" t="inlineStr">
-        <is>
-          <t>3715.0</t>
-        </is>
-      </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>9865.0</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr">
-        <is>
-          <t>9864.3</t>
-        </is>
-      </c>
-      <c r="AZ15" t="inlineStr">
-        <is>
-          <t>9269.96</t>
-        </is>
-      </c>
-      <c r="BA15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BB15" t="inlineStr">
-        <is>
-          <t>11.33269122891031</t>
-        </is>
-      </c>
-      <c r="BC15" t="n">
-        <v>-776.97</v>
-      </c>
-      <c r="BD15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BE15" t="inlineStr">
-        <is>
-          <t>192.0</t>
-        </is>
-      </c>
-      <c r="BF15" t="inlineStr">
-        <is>
-          <t>2025/10/14</t>
-        </is>
-      </c>
-      <c r="BG15" t="inlineStr">
-        <is>
-          <t>2.60</t>
-        </is>
-      </c>
-      <c r="BH15" t="inlineStr">
-        <is>
-          <t>鼎翰</t>
-        </is>
-      </c>
-      <c r="BI15" t="inlineStr">
-        <is>
-          <t>鼎翰</t>
-        </is>
-      </c>
-      <c r="BJ15" t="inlineStr">
-        <is>
-          <t>電腦及週邊設備業</t>
-        </is>
-      </c>
-      <c r="BK15" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BL15" t="inlineStr">
-        <is>
-          <t>0.56</t>
-        </is>
-      </c>
       <c r="BM15" t="inlineStr">
         <is>
           <t>-11.45161899724185</t>
@@ -6800,22 +6800,22 @@
       </c>
       <c r="BP15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>4.89</t>
+          <t>5</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="BU15" t="inlineStr">
         <is>
-          <t>12.18</t>
+          <t>11.91</t>
         </is>
       </c>
       <c r="BV15" t="inlineStr">
@@ -6840,12 +6840,12 @@
       </c>
       <c r="BX15" t="inlineStr">
         <is>
-          <t>49.69</t>
+          <t>48.7</t>
         </is>
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>9701</t>
+          <t>9487</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
@@ -6865,22 +6865,22 @@
       </c>
       <c r="CC15" t="inlineStr">
         <is>
-          <t>199.5</t>
+          <t>199.0</t>
         </is>
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>199.5</t>
+          <t>202.5</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>197.0</t>
+          <t>198.5</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>197.0</t>
+          <t>201.5</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
@@ -6912,12 +6912,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>19.0</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6927,7 +6927,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>198.0</t>
+          <t>197.0</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6937,17 +6937,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2.94</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -6957,7 +6957,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -6967,7 +6967,7 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>2025-11-18 00:00:00</t>
+          <t>2025-11-19 00:00:00</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -7022,17 +7022,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>7.06</t>
+          <t>4.47</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>-1.27</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7043,77 +7043,77 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>134</t>
+          <t>107</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>61.54</t>
+          <t>46.15</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>69.23</t>
+          <t>51.28</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>0.80</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>2.85</t>
+          <t>2.84</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>0.62</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>198.2</t>
+          <t>197.9</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>196.62</t>
+          <t>196.78</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>191.17</t>
+          <t>191.34</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>189.99</t>
+          <t>190.02</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>-6.74</t>
+          <t>-11.24</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7123,7 +7123,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-80.21</t>
+          <t>-80.75</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7133,41 +7133,41 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>28263.53540462428</t>
+          <t>28269.50649350649</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>5976.0</t>
+          <t>3715.0</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>10613.2</t>
+          <t>9865.0</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>10254.6</t>
+          <t>9864.3</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>9315.64</t>
+          <t>9269.96</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>358</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>154.6608857258293</t>
+          <t>11.33269122891031</t>
         </is>
       </c>
       <c r="BC16" t="n">
-        <v>-284.82</v>
+        <v>-776.97</v>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
@@ -7186,7 +7186,7 @@
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>3.12</t>
+          <t>2.60</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
@@ -7211,7 +7211,7 @@
       </c>
       <c r="BL16" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="BM16" t="inlineStr">
@@ -7231,22 +7231,22 @@
       </c>
       <c r="BP16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>4.89</t>
+          <t>5</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
@@ -7256,7 +7256,7 @@
       </c>
       <c r="BU16" t="inlineStr">
         <is>
-          <t>12.18</t>
+          <t>11.91</t>
         </is>
       </c>
       <c r="BV16" t="inlineStr">
@@ -7271,12 +7271,12 @@
       </c>
       <c r="BX16" t="inlineStr">
         <is>
-          <t>49.69</t>
+          <t>48.7</t>
         </is>
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>9701</t>
+          <t>9487</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
@@ -7296,22 +7296,22 @@
       </c>
       <c r="CC16" t="inlineStr">
         <is>
+          <t>199.5</t>
+        </is>
+      </c>
+      <c r="CD16" t="inlineStr">
+        <is>
+          <t>199.5</t>
+        </is>
+      </c>
+      <c r="CE16" t="inlineStr">
+        <is>
           <t>197.0</t>
         </is>
       </c>
-      <c r="CD16" t="inlineStr">
-        <is>
-          <t>198.5</t>
-        </is>
-      </c>
-      <c r="CE16" t="inlineStr">
+      <c r="CF16" t="inlineStr">
         <is>
           <t>197.0</t>
-        </is>
-      </c>
-      <c r="CF16" t="inlineStr">
-        <is>
-          <t>198.0</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
@@ -7343,12 +7343,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-1.75</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>42.0</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7358,7 +7358,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>197.0</t>
+          <t>198.0</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7368,17 +7368,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>3.43</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>16.90</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7388,7 +7388,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -7398,7 +7398,7 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>2025-11-18 00:00:00</t>
+          <t>2025-11-19 00:00:00</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -7453,17 +7453,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>9.88</t>
+          <t>7.06</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>-1.78</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7474,77 +7474,77 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>134</t>
+          <t>107</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>46.15</t>
+          <t>61.54</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>70.94</t>
+          <t>69.23</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>0.60</t>
+          <t>0.80</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>2.8</t>
+          <t>2.85</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>197.5</t>
+          <t>198.2</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>196.32</t>
+          <t>196.62</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>190.97</t>
+          <t>191.17</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>189.94</t>
+          <t>189.99</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>-5.98</t>
+          <t>-6.74</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>1.89</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7554,7 +7554,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-79.87</t>
+          <t>-80.21</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7564,41 +7564,41 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>28263.53540462428</t>
+          <t>28269.50649350649</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>8426.0</t>
+          <t>5976.0</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>12937.0</t>
+          <t>10613.2</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>11067.0</t>
+          <t>10254.6</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>9335.32</t>
+          <t>9315.64</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>1870</t>
+          <t>358</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>234.5662547700167</t>
+          <t>154.6608857258293</t>
         </is>
       </c>
       <c r="BC17" t="n">
-        <v>186.18</v>
+        <v>-284.82</v>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
@@ -7617,7 +7617,7 @@
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>2.60</t>
+          <t>3.12</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
@@ -7642,7 +7642,7 @@
       </c>
       <c r="BL17" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="BM17" t="inlineStr">
@@ -7662,7 +7662,7 @@
       </c>
       <c r="BP17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ17" t="inlineStr">
@@ -7672,12 +7672,12 @@
       </c>
       <c r="BR17" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>4.89</t>
+          <t>5</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
@@ -7687,7 +7687,7 @@
       </c>
       <c r="BU17" t="inlineStr">
         <is>
-          <t>12.18</t>
+          <t>11.91</t>
         </is>
       </c>
       <c r="BV17" t="inlineStr">
@@ -7702,12 +7702,12 @@
       </c>
       <c r="BX17" t="inlineStr">
         <is>
-          <t>49.69</t>
+          <t>48.7</t>
         </is>
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>9701</t>
+          <t>9487</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
@@ -7727,12 +7727,12 @@
       </c>
       <c r="CC17" t="inlineStr">
         <is>
-          <t>200.5</t>
+          <t>197.0</t>
         </is>
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>200.5</t>
+          <t>198.5</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
@@ -7742,7 +7742,7 @@
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>197.0</t>
+          <t>198.0</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
@@ -7774,12 +7774,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>-1.75</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>108.0</t>
+          <t>42.0</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7789,7 +7789,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>200.5</t>
+          <t>197.0</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7799,17 +7799,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>11.96</t>
+          <t>16.90</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7819,7 +7819,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -7829,7 +7829,7 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>2025-11-18 00:00:00</t>
+          <t>2025-11-19 00:00:00</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
@@ -7884,17 +7884,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>25.41</t>
+          <t>9.88</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>-0.74</t>
+          <t>-1.78</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7905,77 +7905,77 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>134</t>
+          <t>107</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>46.15</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>82.83</t>
+          <t>70.94</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.60</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>2.72</t>
+          <t>2.8</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>196.9</t>
+          <t>197.5</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>196.0</t>
+          <t>196.32</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>190.81</t>
+          <t>190.97</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>189.91</t>
+          <t>189.94</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>-5.98</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>1.89</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -7985,7 +7985,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-79.57</t>
+          <t>-79.87</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7995,41 +7995,41 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>28263.53540462428</t>
+          <t>28269.50649350649</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>21734.0</t>
+          <t>8426.0</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>13078.6</t>
+          <t>12937.0</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>11681.7</t>
+          <t>11067.0</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>9341.52</t>
+          <t>9335.32</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>1396</t>
+          <t>1870</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>243.363716734609</t>
+          <t>234.5662547700167</t>
         </is>
       </c>
       <c r="BC18" t="n">
-        <v>589.89</v>
+        <v>186.18</v>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
@@ -8048,7 +8048,7 @@
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>4.43</t>
+          <t>2.60</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
@@ -8073,7 +8073,7 @@
       </c>
       <c r="BL18" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="BM18" t="inlineStr">
@@ -8093,22 +8093,22 @@
       </c>
       <c r="BP18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>4.89</t>
+          <t>5</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
@@ -8118,7 +8118,7 @@
       </c>
       <c r="BU18" t="inlineStr">
         <is>
-          <t>12.18</t>
+          <t>11.91</t>
         </is>
       </c>
       <c r="BV18" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="BX18" t="inlineStr">
         <is>
-          <t>49.69</t>
+          <t>48.7</t>
         </is>
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>9701</t>
+          <t>9487</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
@@ -8158,22 +8158,22 @@
       </c>
       <c r="CC18" t="inlineStr">
         <is>
-          <t>203.5</t>
+          <t>200.5</t>
         </is>
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>203.5</t>
+          <t>200.5</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>199.0</t>
+          <t>197.0</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>200.5</t>
+          <t>197.0</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
@@ -8205,12 +8205,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>48.0</t>
+          <t>108.0</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8220,7 +8220,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>197.0</t>
+          <t>200.5</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8230,17 +8230,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>3.43</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-10.99</t>
+          <t>11.96</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8250,7 +8250,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -8260,7 +8260,7 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>2025-11-18 00:00:00</t>
+          <t>2025-11-19 00:00:00</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
@@ -8315,17 +8315,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11.29</t>
+          <t>25.41</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>-0.74</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8336,72 +8336,72 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>134</t>
+          <t>107</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>52.27</t>
+          <t>82.83</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>2.72</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
+          <t>196.9</t>
+        </is>
+      </c>
+      <c r="AM19" t="inlineStr">
+        <is>
           <t>196.0</t>
         </is>
       </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>195.48</t>
-        </is>
-      </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>190.59</t>
+          <t>190.81</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>189.82</t>
+          <t>189.91</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>-11.56</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
@@ -8416,7 +8416,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-79.53</t>
+          <t>-79.57</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8426,41 +8426,41 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>28263.53540462428</t>
+          <t>28269.50649350649</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>9474.0</t>
+          <t>21734.0</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>9585.6</t>
+          <t>13078.6</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>10769.2</t>
+          <t>11681.7</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>9013.74</t>
+          <t>9341.52</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>-1183</t>
+          <t>1396</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>180.3595866842333</t>
+          <t>243.363716734609</t>
         </is>
       </c>
       <c r="BC19" t="n">
-        <v>-280.31</v>
+        <v>589.89</v>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
@@ -8479,7 +8479,7 @@
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>2.60</t>
+          <t>4.43</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">
@@ -8504,7 +8504,7 @@
       </c>
       <c r="BL19" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="BM19" t="inlineStr">
@@ -8524,22 +8524,22 @@
       </c>
       <c r="BP19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>4.89</t>
+          <t>5</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
@@ -8549,7 +8549,7 @@
       </c>
       <c r="BU19" t="inlineStr">
         <is>
-          <t>12.18</t>
+          <t>11.91</t>
         </is>
       </c>
       <c r="BV19" t="inlineStr">
@@ -8564,12 +8564,12 @@
       </c>
       <c r="BX19" t="inlineStr">
         <is>
-          <t>49.69</t>
+          <t>48.7</t>
         </is>
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>9701</t>
+          <t>9487</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
@@ -8589,22 +8589,22 @@
       </c>
       <c r="CC19" t="inlineStr">
         <is>
-          <t>196.0</t>
+          <t>203.5</t>
         </is>
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>197.5</t>
+          <t>203.5</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>195.0</t>
+          <t>199.0</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>197.0</t>
+          <t>200.5</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
@@ -8636,12 +8636,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>-0.77</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>38.0</t>
+          <t>48.0</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8651,7 +8651,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>198.5</t>
+          <t>197.0</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8661,17 +8661,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2.7</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>-14.77</t>
+          <t>-10.99</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8681,7 +8681,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -8691,7 +8691,7 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>2025-11-18 00:00:00</t>
+          <t>2025-11-19 00:00:00</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
@@ -8746,17 +8746,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>8.94</t>
+          <t>11.29</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8767,77 +8767,77 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>134</t>
+          <t>107</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>81.82</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>30.05</t>
+          <t>52.27</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>2.48</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>195.7</t>
+          <t>196.0</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>195.12</t>
+          <t>195.48</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>190.41</t>
+          <t>190.59</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>189.79</t>
+          <t>189.82</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>-11.44</t>
+          <t>-11.56</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8847,7 +8847,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-78.94</t>
+          <t>-79.53</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8857,41 +8857,41 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>28263.53540462428</t>
+          <t>28269.50649350649</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>7456.0</t>
+          <t>9474.0</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>9863.6</t>
+          <t>9585.6</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>11572.5</t>
+          <t>10769.2</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>9025.16</t>
+          <t>9013.74</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>-1708</t>
+          <t>-1183</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>264.1185869502501</t>
+          <t>180.3595866842333</t>
         </is>
       </c>
       <c r="BC20" t="n">
-        <v>-199.88</v>
+        <v>-280.31</v>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
@@ -8910,7 +8910,7 @@
       </c>
       <c r="BG20" t="inlineStr">
         <is>
-          <t>3.39</t>
+          <t>2.60</t>
         </is>
       </c>
       <c r="BH20" t="inlineStr">
@@ -8935,7 +8935,7 @@
       </c>
       <c r="BL20" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="BM20" t="inlineStr">
@@ -8955,22 +8955,22 @@
       </c>
       <c r="BP20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>4.89</t>
+          <t>5</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
@@ -8980,7 +8980,7 @@
       </c>
       <c r="BU20" t="inlineStr">
         <is>
-          <t>12.18</t>
+          <t>11.91</t>
         </is>
       </c>
       <c r="BV20" t="inlineStr">
@@ -8995,12 +8995,12 @@
       </c>
       <c r="BX20" t="inlineStr">
         <is>
-          <t>49.69</t>
+          <t>48.7</t>
         </is>
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>9701</t>
+          <t>9487</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
@@ -9020,22 +9020,22 @@
       </c>
       <c r="CC20" t="inlineStr">
         <is>
+          <t>196.0</t>
+        </is>
+      </c>
+      <c r="CD20" t="inlineStr">
+        <is>
+          <t>197.5</t>
+        </is>
+      </c>
+      <c r="CE20" t="inlineStr">
+        <is>
           <t>195.0</t>
         </is>
       </c>
-      <c r="CD20" t="inlineStr">
-        <is>
-          <t>199.0</t>
-        </is>
-      </c>
-      <c r="CE20" t="inlineStr">
-        <is>
-          <t>195.0</t>
-        </is>
-      </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>198.5</t>
+          <t>197.0</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
@@ -9067,12 +9067,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>38.0</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9082,7 +9082,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>194.5</t>
+          <t>198.5</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9092,17 +9092,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>4.66</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>-19.30</t>
+          <t>-14.77</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9112,7 +9112,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -9122,7 +9122,7 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>2025-11-18 00:00:00</t>
+          <t>2025-11-19 00:00:00</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
@@ -9177,17 +9177,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>21.65</t>
+          <t>8.94</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9198,77 +9198,77 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>134</t>
+          <t>107</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>8.33</t>
+          <t>81.82</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>6.48</t>
+          <t>30.05</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>2.48</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>195.5</t>
+          <t>195.7</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>194.65</t>
+          <t>195.12</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>190.2</t>
+          <t>190.41</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>189.76</t>
+          <t>189.79</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>-18.96</t>
+          <t>-11.44</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9278,7 +9278,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-78.34</t>
+          <t>-78.94</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9288,41 +9288,41 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>28263.53540462428</t>
+          <t>28269.50649350649</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>17595.0</t>
+          <t>7456.0</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>9896.0</t>
+          <t>9863.6</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>12262.5</t>
+          <t>11572.5</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>9049.34</t>
+          <t>9025.16</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>-2366</t>
+          <t>-1708</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>348.481424646728</t>
+          <t>264.1185869502501</t>
         </is>
       </c>
       <c r="BC21" t="n">
-        <v>138.39</v>
+        <v>-199.88</v>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
@@ -9341,7 +9341,7 @@
       </c>
       <c r="BG21" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>3.39</t>
         </is>
       </c>
       <c r="BH21" t="inlineStr">
@@ -9366,7 +9366,7 @@
       </c>
       <c r="BL21" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="BM21" t="inlineStr">
@@ -9386,7 +9386,7 @@
       </c>
       <c r="BP21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ21" t="inlineStr">
@@ -9396,12 +9396,12 @@
       </c>
       <c r="BR21" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>4.89</t>
+          <t>5</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
@@ -9411,7 +9411,7 @@
       </c>
       <c r="BU21" t="inlineStr">
         <is>
-          <t>12.18</t>
+          <t>11.91</t>
         </is>
       </c>
       <c r="BV21" t="inlineStr">
@@ -9426,12 +9426,12 @@
       </c>
       <c r="BX21" t="inlineStr">
         <is>
-          <t>49.69</t>
+          <t>48.7</t>
         </is>
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>9701</t>
+          <t>9487</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
@@ -9451,22 +9451,22 @@
       </c>
       <c r="CC21" t="inlineStr">
         <is>
-          <t>194.0</t>
+          <t>195.0</t>
         </is>
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>194.5</t>
+          <t>199.0</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>190.0</t>
+          <t>195.0</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>194.5</t>
+          <t>198.5</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
@@ -9498,12 +9498,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-1.01</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>47.0</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9513,7 +9513,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>194.0</t>
+          <t>194.5</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9523,17 +9523,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>-23.60</t>
+          <t>-19.30</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9543,7 +9543,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -9553,7 +9553,7 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>2025-11-18 00:00:00</t>
+          <t>2025-11-19 00:00:00</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
@@ -9608,17 +9608,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11.06</t>
+          <t>21.65</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>-1.80</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9629,77 +9629,77 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>134</t>
+          <t>107</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>8.33</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>12.04</t>
+          <t>6.48</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>-1.17</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>196.3</t>
+          <t>195.5</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>194.38</t>
+          <t>194.65</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>190.1</t>
+          <t>190.2</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>189.75</t>
+          <t>189.76</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>-11.99</t>
+          <t>-18.96</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>2.27</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9709,7 +9709,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-77.31</t>
+          <t>-78.34</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9719,41 +9719,41 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>28263.53540462428</t>
+          <t>28269.50649350649</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>9134.0</t>
+          <t>17595.0</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>9197.0</t>
+          <t>9896.0</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>12037.8</t>
+          <t>12262.5</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>8763.96</t>
+          <t>9049.34</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>-2840</t>
+          <t>-2366</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>386.6804094807498</t>
+          <t>348.481424646728</t>
         </is>
       </c>
       <c r="BC22" t="n">
-        <v>-469.64</v>
+        <v>138.39</v>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
@@ -9772,7 +9772,7 @@
       </c>
       <c r="BG22" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="BH22" t="inlineStr">
@@ -9797,7 +9797,7 @@
       </c>
       <c r="BL22" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="BM22" t="inlineStr">
@@ -9817,7 +9817,7 @@
       </c>
       <c r="BP22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ22" t="inlineStr">
@@ -9832,7 +9832,7 @@
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>4.89</t>
+          <t>5</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
@@ -9842,7 +9842,7 @@
       </c>
       <c r="BU22" t="inlineStr">
         <is>
-          <t>12.18</t>
+          <t>11.91</t>
         </is>
       </c>
       <c r="BV22" t="inlineStr">
@@ -9857,12 +9857,12 @@
       </c>
       <c r="BX22" t="inlineStr">
         <is>
-          <t>49.69</t>
+          <t>48.7</t>
         </is>
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>9701</t>
+          <t>9487</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
@@ -9882,22 +9882,22 @@
       </c>
       <c r="CC22" t="inlineStr">
         <is>
-          <t>197.5</t>
+          <t>194.0</t>
         </is>
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>197.5</t>
+          <t>194.5</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>194.0</t>
+          <t>190.0</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>194.0</t>
+          <t>194.5</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
@@ -9929,12 +9929,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>-1.01</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>22.0</t>
+          <t>47.0</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9944,87 +9944,87 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
+          <t>194.0</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>2.76</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>-1.0</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>-23.60</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>-65.0</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>2025-11-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>2025-11-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>2025-10-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>2025-11-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>201.5</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>195.5</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
           <t>196.0</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>3.92</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>-14.92</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>2025-10-21</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>-50.0</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>2025-11-14 00:00:00</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>2025-11-18 00:00:00</t>
-        </is>
-      </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>2025-10-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>2025-11-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q23" t="inlineStr">
-        <is>
-          <t>201.5</t>
-        </is>
-      </c>
-      <c r="R23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S23" t="inlineStr">
-        <is>
-          <t>195.5</t>
-        </is>
-      </c>
-      <c r="T23" t="inlineStr">
-        <is>
-          <t>195.5</t>
-        </is>
-      </c>
-      <c r="U23" t="inlineStr">
-        <is>
-          <t>196.0</t>
-        </is>
-      </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W23" t="inlineStr">
@@ -10039,17 +10039,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>5.18</t>
+          <t>11.06</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>-1.80</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10060,77 +10060,77 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>134</t>
+          <t>107</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>33.47</t>
+          <t>12.04</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>-1.17</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>2.18</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>197.0</t>
+          <t>196.3</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>194.12</t>
+          <t>194.38</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>189.98</t>
+          <t>190.1</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>189.74</t>
+          <t>189.75</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>-11.99</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>2.33</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>2.27</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10140,7 +10140,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-76.63</t>
+          <t>-77.31</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10150,45 +10150,45 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>28263.53540462428</t>
+          <t>28269.50649350649</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>4269.0</t>
+          <t>9134.0</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>10284.8</t>
+          <t>9197.0</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>12088.4</t>
+          <t>12037.8</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>8808.96</t>
+          <t>8763.96</t>
         </is>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>-1803</t>
+          <t>-2840</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>542.3754816252442</t>
+          <t>386.6804094807498</t>
         </is>
       </c>
       <c r="BC23" t="n">
-        <v>-414.95</v>
+        <v>-469.64</v>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BE23" t="inlineStr">
@@ -10203,7 +10203,7 @@
       </c>
       <c r="BG23" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="BH23" t="inlineStr">
@@ -10228,7 +10228,7 @@
       </c>
       <c r="BL23" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="BM23" t="inlineStr">
@@ -10248,7 +10248,7 @@
       </c>
       <c r="BP23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ23" t="inlineStr">
@@ -10258,12 +10258,12 @@
       </c>
       <c r="BR23" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>4.89</t>
+          <t>5</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
@@ -10273,7 +10273,7 @@
       </c>
       <c r="BU23" t="inlineStr">
         <is>
-          <t>12.18</t>
+          <t>11.91</t>
         </is>
       </c>
       <c r="BV23" t="inlineStr">
@@ -10288,12 +10288,12 @@
       </c>
       <c r="BX23" t="inlineStr">
         <is>
-          <t>49.69</t>
+          <t>48.7</t>
         </is>
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>9701</t>
+          <t>9487</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
@@ -10313,22 +10313,22 @@
       </c>
       <c r="CC23" t="inlineStr">
         <is>
-          <t>195.5</t>
+          <t>197.5</t>
         </is>
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>196.0</t>
+          <t>197.5</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>194.5</t>
+          <t>194.0</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>196.0</t>
+          <t>194.0</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">

--- a/Result/checksun_type/HMI.xlsx
+++ b/Result/checksun_type/HMI.xlsx
@@ -878,12 +878,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-4.24</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>19.2</t>
+          <t>19.15</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -908,12 +908,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-4.28</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>21.51</t>
+          <t>14.69</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-12.13</t>
+          <t>-12.36</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -988,17 +988,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>3.15</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-3.37</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -1024,62 +1024,62 @@
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>15.38</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-4.81</t>
+          <t>-3.58</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-4.41</t>
+          <t>-5.17</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-3.49</t>
+          <t>-3.97</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-2.01</t>
+          <t>-2.33</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>20.17</t>
+          <t>19.86</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>21.1</t>
+          <t>20.94</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>21.86</t>
+          <t>21.81</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>22.31</t>
+          <t>22.33</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-25.64</t>
+          <t>-28.42</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-107.35</t>
+          <t>-107.91</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1099,41 +1099,41 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>30633.04978354978</t>
+          <t>30589.40922190202</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>1715.0</t>
+          <t>231.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>1014.4</t>
+          <t>911.2</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>834.8</t>
+          <t>794.5</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>1896.36</t>
+          <t>1867.82</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>179</t>
+          <t>116</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-175.1202900950192</t>
+          <t>-166.1134213107396</t>
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>-64.98</v>
+        <v>-116.58</v>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>-18.82</t>
+          <t>-19.03</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1197,7 +1197,7 @@
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
@@ -1207,7 +1207,7 @@
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>84.03</t>
+          <t>84.12</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>560</t>
+          <t>559</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1262,22 +1262,22 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>20.05</t>
+          <t>18.85</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>20.05</t>
+          <t>19.15</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>19.0</t>
+          <t>18.85</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>19.2</t>
+          <t>19.15</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1309,12 +1309,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-2.0</t>
+          <t>-4.24</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>46.0</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>20.05</t>
+          <t>19.2</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1334,17 +1334,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-4.43</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-4.28</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>17.65</t>
+          <t>21.51</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1409,7 +1409,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-8.24</t>
+          <t>-12.13</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1419,17 +1419,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>3.15</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>-3.37</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1440,12 +1440,12 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
@@ -1455,62 +1455,62 @@
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>23.08</t>
+          <t>15.38</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-1.91</t>
+          <t>-4.81</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-3.90</t>
+          <t>-4.41</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-2.98</t>
+          <t>-3.49</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-1.65</t>
+          <t>-2.01</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>20.44</t>
+          <t>20.17</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>21.27</t>
+          <t>21.1</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>21.92</t>
+          <t>21.86</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>22.29</t>
+          <t>22.31</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-16.23</t>
+          <t>-25.64</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-106.88</t>
+          <t>-107.35</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,41 +1530,41 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>30633.04978354978</t>
+          <t>30589.40922190202</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>922.0</t>
+          <t>1715.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>840.4</t>
+          <t>1014.4</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>714.3</t>
+          <t>834.8</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>1889.2</t>
+          <t>1896.36</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>126</t>
+          <t>179</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-195.1459064225224</t>
+          <t>-175.1202900950192</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>-147.95</v>
+        <v>-64.98</v>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>-15.22</t>
+          <t>-18.82</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1628,7 +1628,7 @@
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
@@ -1638,7 +1638,7 @@
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
@@ -1668,12 +1668,12 @@
       </c>
       <c r="BX3" t="inlineStr">
         <is>
-          <t>84.03</t>
+          <t>84.12</t>
         </is>
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>560</t>
+          <t>559</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1693,22 +1693,22 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>20.05</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>20.1</t>
+          <t>20.05</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>19.95</t>
+          <t>19.0</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>20.05</t>
+          <t>19.2</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1740,12 +1740,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-2.0</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>16.0</t>
+          <t>46.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>20.45</t>
+          <t>20.05</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1765,17 +1765,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-6.51</t>
+          <t>-4.7</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-4.28</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>22.57</t>
+          <t>17.65</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-6.41</t>
+          <t>-8.24</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1850,17 +1850,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1871,77 +1871,77 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>46.15</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>36.17</t>
+          <t>23.08</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-1.91</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-4.52</t>
+          <t>-3.90</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-2.41</t>
+          <t>-2.98</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-1.36</t>
+          <t>-1.65</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>20.46</t>
+          <t>20.44</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>21.43</t>
+          <t>21.27</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>21.96</t>
+          <t>21.92</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>22.26</t>
+          <t>22.29</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-15.32</t>
+          <t>-16.23</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-0.50</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-106.60</t>
+          <t>-106.88</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1961,41 +1961,41 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>30633.04978354978</t>
+          <t>30589.40922190202</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>326.0</t>
+          <t>922.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>861.4</t>
+          <t>840.4</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>702.8</t>
+          <t>714.3</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>2075.44</t>
+          <t>1889.2</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>158</t>
+          <t>126</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-203.7270186305573</t>
+          <t>-195.1459064225224</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>-176.23</v>
+        <v>-147.95</v>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>-13.53</t>
+          <t>-15.22</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2059,7 +2059,7 @@
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
@@ -2069,7 +2069,7 @@
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
@@ -2099,12 +2099,12 @@
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>84.03</t>
+          <t>84.12</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>560</t>
+          <t>559</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2124,22 +2124,22 @@
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>20.45</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>20.45</t>
+          <t>20.1</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>20.3</t>
+          <t>19.95</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>20.45</t>
+          <t>20.05</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-1.19</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2196,17 +2196,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-6.51</t>
+          <t>-6.79</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-4.28</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>22.57</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2281,17 +2281,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-1.95</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2302,67 +2302,67 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>23.08</t>
+          <t>46.15</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>28.41</t>
+          <t>36.17</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-4.33</t>
+          <t>-4.52</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-2.52</t>
+          <t>-2.41</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>-1.36</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>20.53</t>
+          <t>20.46</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>21.46</t>
+          <t>21.43</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>22.01</t>
+          <t>21.96</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>22.23</t>
+          <t>22.26</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-20.19</t>
+          <t>-15.32</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
@@ -2372,7 +2372,7 @@
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-106.34</t>
+          <t>-106.60</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2392,41 +2392,41 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>30633.04978354978</t>
+          <t>30589.40922190202</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>1362.0</t>
+          <t>326.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>800.4</t>
+          <t>861.4</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>791.6</t>
+          <t>702.8</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>2169.22</t>
+          <t>2075.44</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>158</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-208.7263475380736</t>
+          <t>-203.7270186305573</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>-146.48</v>
+        <v>-176.23</v>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
@@ -2490,7 +2490,7 @@
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>84.03</t>
+          <t>84.12</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>560</t>
+          <t>559</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2555,12 +2555,12 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>21.0</t>
+          <t>20.45</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>21.0</t>
+          <t>20.45</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>-1.19</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>36.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>20.7</t>
+          <t>20.45</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2627,17 +2627,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-7.81</t>
+          <t>-6.79</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-4.28</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-32.18</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2702,7 +2702,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-5.26</t>
+          <t>-6.41</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2712,17 +2712,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>-1.95</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2733,67 +2733,67 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>39.29</t>
+          <t>23.08</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>20.71</t>
+          <t>28.41</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-4.13</t>
+          <t>-4.33</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-2.66</t>
+          <t>-2.52</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-0.54</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>20.6</t>
+          <t>20.53</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>21.49</t>
+          <t>21.46</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>22.08</t>
+          <t>22.01</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>22.19</t>
+          <t>22.23</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-25.12</t>
+          <t>-20.19</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
@@ -2803,7 +2803,7 @@
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2813,7 +2813,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-106.02</t>
+          <t>-106.34</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2823,41 +2823,41 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>30633.04978354978</t>
+          <t>30589.40922190202</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>747.0</t>
+          <t>1362.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>677.8</t>
+          <t>800.4</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>999.4</t>
+          <t>791.6</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>2614.76</t>
+          <t>2169.22</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-321</t>
+          <t>8</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-220.0436966054221</t>
+          <t>-208.7263475380736</t>
         </is>
       </c>
       <c r="BC6" t="n">
-        <v>-209.75</v>
+        <v>-146.48</v>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>-12.47</t>
+          <t>-13.53</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BX6" t="inlineStr">
         <is>
-          <t>84.03</t>
+          <t>84.12</t>
         </is>
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>560</t>
+          <t>559</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>20.6</t>
+          <t>21.0</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>20.95</t>
+          <t>21.0</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>20.55</t>
+          <t>20.3</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>20.7</t>
+          <t>20.45</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>41.0</t>
+          <t>36.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>20.55</t>
+          <t>20.7</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-7.03</t>
+          <t>-8.09</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-4.28</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-33.22</t>
+          <t>-32.18</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-5.95</t>
+          <t>-5.26</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-4.11</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,77 +3164,77 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>22.86</t>
+          <t>39.29</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>19.66</t>
+          <t>20.71</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-4.71</t>
+          <t>-4.13</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-2.98</t>
+          <t>-2.66</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-0.54</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>20.49</t>
+          <t>20.6</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>21.5</t>
+          <t>21.49</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>22.16</t>
+          <t>22.08</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>22.16</t>
+          <t>22.19</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-36.40</t>
+          <t>-25.12</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>-0.50</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-105.65</t>
+          <t>-106.02</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3254,41 +3254,41 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>30633.04978354978</t>
+          <t>30589.40922190202</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>845.0</t>
+          <t>747.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>655.2</t>
+          <t>677.8</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>981.2</t>
+          <t>999.4</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>2840.22</t>
+          <t>2614.76</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-326</t>
+          <t>-321</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-221.9153182728739</t>
+          <t>-220.0436966054221</t>
         </is>
       </c>
       <c r="BC7" t="n">
-        <v>-226.75</v>
+        <v>-209.75</v>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>-13.11</t>
+          <t>-12.47</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3352,7 +3352,7 @@
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
@@ -3362,7 +3362,7 @@
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="BX7" t="inlineStr">
         <is>
-          <t>84.03</t>
+          <t>84.12</t>
         </is>
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>560</t>
+          <t>559</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3417,22 +3417,22 @@
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>20.2</t>
+          <t>20.6</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>21.75</t>
+          <t>20.95</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>20.2</t>
+          <t>20.55</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>20.55</t>
+          <t>20.7</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3464,12 +3464,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-3.22</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>51.0</t>
+          <t>41.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>20.15</t>
+          <t>20.55</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3489,17 +3489,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-4.95</t>
+          <t>-7.31</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-4.28</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-37.93</t>
+          <t>-33.22</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3564,7 +3564,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-7.78</t>
+          <t>-5.95</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3574,17 +3574,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-0.74</t>
+          <t>-4.11</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3595,77 +3595,77 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>22.86</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>22.61</t>
+          <t>19.66</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-1.80</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-4.79</t>
+          <t>-4.71</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-2.96</t>
+          <t>-2.98</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>20.52</t>
+          <t>20.49</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>21.55</t>
+          <t>21.5</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>22.21</t>
+          <t>22.16</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>22.13</t>
+          <t>22.16</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-47.43</t>
+          <t>-36.40</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.50</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.37</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-105.13</t>
+          <t>-105.65</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3685,41 +3685,41 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>30633.04978354978</t>
+          <t>30589.40922190202</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>1027.0</t>
+          <t>845.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>588.2</t>
+          <t>655.2</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>947.7</t>
+          <t>981.2</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>2910.12</t>
+          <t>2840.22</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-359</t>
+          <t>-326</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-221.0362983393635</t>
+          <t>-221.9153182728739</t>
         </is>
       </c>
       <c r="BC8" t="n">
-        <v>-253.44</v>
+        <v>-226.75</v>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>-14.80</t>
+          <t>-13.11</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -3793,7 +3793,7 @@
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
@@ -3823,12 +3823,12 @@
       </c>
       <c r="BX8" t="inlineStr">
         <is>
-          <t>84.03</t>
+          <t>84.12</t>
         </is>
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>560</t>
+          <t>559</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -3853,17 +3853,17 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>20.4</t>
+          <t>21.75</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>20.05</t>
+          <t>20.2</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>20.15</t>
+          <t>20.55</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-3.22</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>51.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>20.8</t>
+          <t>20.15</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3920,17 +3920,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-8.33</t>
+          <t>-5.22</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-4.28</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-40.01</t>
+          <t>-37.93</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-4.81</t>
+          <t>-7.78</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.74</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4026,17 +4026,17 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>36.11</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
@@ -4046,57 +4046,57 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>0.10</t>
+          <t>-1.80</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-4.04</t>
+          <t>-4.79</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-2.72</t>
+          <t>-2.96</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.36</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>20.78</t>
+          <t>20.52</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>21.66</t>
+          <t>21.55</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>22.26</t>
+          <t>22.21</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>22.1</t>
+          <t>22.13</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-47.36</t>
+          <t>-47.43</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>-0.50</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-104.52</t>
+          <t>-105.13</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4116,41 +4116,41 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>30633.04978354978</t>
+          <t>30589.40922190202</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>21.0</t>
+          <t>1027.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>544.2</t>
+          <t>588.2</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>907.2</t>
+          <t>947.7</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>2976.72</t>
+          <t>2910.12</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-363</t>
+          <t>-359</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-215.145144320523</t>
+          <t>-221.0362983393635</t>
         </is>
       </c>
       <c r="BC9" t="n">
-        <v>-302.01</v>
+        <v>-253.44</v>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>-12.05</t>
+          <t>-14.80</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4214,17 +4214,17 @@
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="BX9" t="inlineStr">
         <is>
-          <t>84.03</t>
+          <t>84.12</t>
         </is>
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>560</t>
+          <t>559</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4279,22 +4279,22 @@
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>20.8</t>
+          <t>20.2</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>20.8</t>
+          <t>20.4</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>20.8</t>
+          <t>20.05</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>20.8</t>
+          <t>20.15</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4326,12 +4326,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>3.17</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>36.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4351,17 +4351,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-8.33</t>
+          <t>-8.62</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-4.28</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-18.36</t>
+          <t>-40.01</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4436,17 +4436,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2.46</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4457,77 +4457,77 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>31.71</t>
+          <t>36.11</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>10.57</t>
+          <t>22.61</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-0.62</t>
+          <t>0.10</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-3.73</t>
+          <t>-4.04</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-2.59</t>
+          <t>-2.72</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>20.93</t>
+          <t>20.78</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>21.74</t>
+          <t>21.66</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>22.32</t>
+          <t>22.26</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>22.07</t>
+          <t>22.1</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-61.10</t>
+          <t>-47.36</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>-0.44</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4537,7 +4537,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-103.99</t>
+          <t>-104.52</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4547,41 +4547,41 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>30633.04978354978</t>
+          <t>30589.40922190202</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>749.0</t>
+          <t>21.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>782.8</t>
+          <t>544.2</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>958.8</t>
+          <t>907.2</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>3076.14</t>
+          <t>2976.72</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-176</t>
+          <t>-363</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-199.3512411554697</t>
+          <t>-215.145144320523</t>
         </is>
       </c>
       <c r="BC10" t="n">
-        <v>-252.83</v>
+        <v>-302.01</v>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
@@ -4645,12 +4645,12 @@
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="BX10" t="inlineStr">
         <is>
-          <t>84.03</t>
+          <t>84.12</t>
         </is>
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>560</t>
+          <t>559</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4710,7 +4710,7 @@
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>20.5</t>
+          <t>20.8</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
@@ -4720,7 +4720,7 @@
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>20.3</t>
+          <t>20.8</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-2.74</t>
+          <t>3.17</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>31.0</t>
+          <t>36.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>20.15</t>
+          <t>20.8</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4782,17 +4782,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-4.95</t>
+          <t>-8.62</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-4.28</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>35.06</t>
+          <t>-18.36</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4857,7 +4857,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-7.78</t>
+          <t>-4.81</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4867,17 +4867,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>1.10</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-0.74</t>
+          <t>2.46</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4888,77 +4888,77 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>31.71</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.57</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-4.73</t>
+          <t>-0.62</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-3.16</t>
+          <t>-3.73</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-2.36</t>
+          <t>-2.59</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>21.15</t>
+          <t>20.93</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>21.84</t>
+          <t>21.74</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>22.37</t>
+          <t>22.32</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>22.04</t>
+          <t>22.07</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-78.27</t>
+          <t>-61.10</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4968,7 +4968,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-103.38</t>
+          <t>-103.99</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4978,41 +4978,41 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>30633.04978354978</t>
+          <t>30589.40922190202</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>634.0</t>
+          <t>749.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>1321.0</t>
+          <t>782.8</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>978.1</t>
+          <t>958.8</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>3201.08</t>
+          <t>3076.14</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>342</t>
+          <t>-176</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-189.6276215728426</t>
+          <t>-199.3512411554697</t>
         </is>
       </c>
       <c r="BC11" t="n">
-        <v>-251.54</v>
+        <v>-252.83</v>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
@@ -5031,7 +5031,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>-14.80</t>
+          <t>-12.05</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5076,7 +5076,7 @@
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5086,7 +5086,7 @@
       </c>
       <c r="BR11" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="BS11" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="BX11" t="inlineStr">
         <is>
-          <t>84.03</t>
+          <t>84.12</t>
         </is>
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>560</t>
+          <t>559</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5141,22 +5141,22 @@
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>20.05</t>
+          <t>20.5</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>20.45</t>
+          <t>20.8</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>20.3</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>20.15</t>
+          <t>20.8</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-3.49</t>
+          <t>-2.74</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>24.0</t>
+          <t>31.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>20.7</t>
+          <t>20.15</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5213,17 +5213,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-7.81</t>
+          <t>-5.22</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-4.28</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>24.06</t>
+          <t>35.06</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5288,7 +5288,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-5.26</t>
+          <t>-7.78</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5298,17 +5298,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>1.10</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-3.86</t>
+          <t>-0.74</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5319,12 +5319,12 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -5339,57 +5339,57 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-3.68</t>
+          <t>-4.73</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-2.20</t>
+          <t>-3.16</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-2.11</t>
+          <t>-2.36</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>21.49</t>
+          <t>21.15</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>21.97</t>
+          <t>21.84</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>22.45</t>
+          <t>22.37</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>22.0</t>
+          <t>22.04</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-62.59</t>
+          <t>-78.27</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-102.72</t>
+          <t>-103.38</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5409,41 +5409,41 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>30633.04978354978</t>
+          <t>30589.40922190202</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>510.0</t>
+          <t>634.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>1307.2</t>
+          <t>1321.0</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>1053.7</t>
+          <t>978.1</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>4241.22</t>
+          <t>3201.08</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>253</t>
+          <t>342</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-178.3701598816587</t>
+          <t>-189.6276215728426</t>
         </is>
       </c>
       <c r="BC12" t="n">
-        <v>-228.4</v>
+        <v>-251.54</v>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>-12.47</t>
+          <t>-14.80</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -5517,7 +5517,7 @@
       </c>
       <c r="BR12" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="BS12" t="inlineStr">
@@ -5547,12 +5547,12 @@
       </c>
       <c r="BX12" t="inlineStr">
         <is>
-          <t>84.03</t>
+          <t>84.12</t>
         </is>
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>560</t>
+          <t>559</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5572,22 +5572,22 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>21.5</t>
+          <t>20.05</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>21.5</t>
+          <t>20.45</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>20.7</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>20.7</t>
+          <t>20.15</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
@@ -5619,12 +5619,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-2.2</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>107.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5634,7 +5634,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>199.5</t>
+          <t>201.0</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5649,12 +5649,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>17.59</t>
+          <t>28.98</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5674,7 +5674,7 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>2025-11-19 00:00:00</t>
+          <t>2025-11-20 00:00:00</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -5714,7 +5714,7 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
@@ -5729,17 +5729,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>25.18</t>
+          <t>11.76</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>-2.00</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5750,77 +5750,77 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>50</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>35.71</t>
+          <t>57.14</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>78.57</t>
+          <t>64.29</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>2.96</t>
+          <t>2.94</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>200.0</t>
+          <t>200.6</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>197.98</t>
+          <t>198.25</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>192.28</t>
+          <t>192.58</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>190.44</t>
+          <t>190.62</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>7.56</t>
+          <t>6.46</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>2.21</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5830,7 +5830,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-79.59</t>
+          <t>-79.25</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5840,45 +5840,45 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>28269.50649350649</t>
+          <t>28250.49639769452</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>21601.0</t>
+          <t>10051.0</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>18457.8</t>
+          <t>19272.8</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>15697.4</t>
+          <t>14943.0</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>10622.98</t>
+          <t>10672.76</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>2760</t>
+          <t>4329</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>713.5128205865296</t>
+          <t>796.5973747512926</t>
         </is>
       </c>
       <c r="BC13" t="n">
-        <v>2095.86</v>
+        <v>1253.56</v>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
@@ -5893,7 +5893,7 @@
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>3.91</t>
+          <t>4.69</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
@@ -5938,22 +5938,22 @@
       </c>
       <c r="BP13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
         <is>
-          <t>1.89</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4.97</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
@@ -5963,7 +5963,7 @@
       </c>
       <c r="BU13" t="inlineStr">
         <is>
-          <t>11.91</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="BV13" t="inlineStr">
@@ -5978,12 +5978,12 @@
       </c>
       <c r="BX13" t="inlineStr">
         <is>
-          <t>48.7</t>
+          <t>48.2</t>
         </is>
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>9487</t>
+          <t>9559</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
@@ -6003,22 +6003,22 @@
       </c>
       <c r="CC13" t="inlineStr">
         <is>
-          <t>205.0</t>
+          <t>199.5</t>
         </is>
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>205.0</t>
+          <t>202.0</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>198.0</t>
+          <t>198.5</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>199.5</t>
+          <t>201.0</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
@@ -6050,12 +6050,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>-2.2</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>107.0</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6065,7 +6065,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>204.0</t>
+          <t>199.5</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6075,17 +6075,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-2.26</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>9.50</t>
+          <t>17.59</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6105,7 +6105,7 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>2025-11-19 00:00:00</t>
+          <t>2025-11-20 00:00:00</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -6145,7 +6145,7 @@
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
@@ -6160,17 +6160,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>31.53</t>
+          <t>25.18</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>-2.00</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6181,32 +6181,32 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>50</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>35.71</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>82.05</t>
+          <t>78.57</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
@@ -6216,240 +6216,240 @@
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
+          <t>200.0</t>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>197.98</t>
+        </is>
+      </c>
+      <c r="AN14" t="inlineStr">
+        <is>
+          <t>192.28</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>190.44</t>
+        </is>
+      </c>
+      <c r="AP14" t="inlineStr">
+        <is>
+          <t>7.56</t>
+        </is>
+      </c>
+      <c r="AQ14" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="AR14" t="inlineStr">
+        <is>
+          <t>2.04</t>
+        </is>
+      </c>
+      <c r="AS14" t="inlineStr">
+        <is>
+          <t>10.01</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr">
+        <is>
+          <t>-79.59</t>
+        </is>
+      </c>
+      <c r="AU14" t="inlineStr">
+        <is>
+          <t>2025/11/14</t>
+        </is>
+      </c>
+      <c r="AV14" t="inlineStr">
+        <is>
+          <t>28250.49639769452</t>
+        </is>
+      </c>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>21601.0</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>18457.8</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>15697.4</t>
+        </is>
+      </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>10622.98</t>
+        </is>
+      </c>
+      <c r="BA14" t="inlineStr">
+        <is>
+          <t>2760</t>
+        </is>
+      </c>
+      <c r="BB14" t="inlineStr">
+        <is>
+          <t>713.5128205865296</t>
+        </is>
+      </c>
+      <c r="BC14" t="n">
+        <v>2095.86</v>
+      </c>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>2025-11-20</t>
+        </is>
+      </c>
+      <c r="BE14" t="inlineStr">
+        <is>
+          <t>192.0</t>
+        </is>
+      </c>
+      <c r="BF14" t="inlineStr">
+        <is>
+          <t>2025/10/14</t>
+        </is>
+      </c>
+      <c r="BG14" t="inlineStr">
+        <is>
+          <t>3.91</t>
+        </is>
+      </c>
+      <c r="BH14" t="inlineStr">
+        <is>
+          <t>鼎翰</t>
+        </is>
+      </c>
+      <c r="BI14" t="inlineStr">
+        <is>
+          <t>鼎翰</t>
+        </is>
+      </c>
+      <c r="BJ14" t="inlineStr">
+        <is>
+          <t>電腦及週邊設備業</t>
+        </is>
+      </c>
+      <c r="BK14" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BL14" t="inlineStr">
+        <is>
+          <t>0.57</t>
+        </is>
+      </c>
+      <c r="BM14" t="inlineStr">
+        <is>
+          <t>-11.45161899724185</t>
+        </is>
+      </c>
+      <c r="BN14" t="inlineStr">
+        <is>
+          <t>22.56717409239306</t>
+        </is>
+      </c>
+      <c r="BO14" t="inlineStr">
+        <is>
+          <t>38.82556207928187</t>
+        </is>
+      </c>
+      <c r="BP14" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BQ14" t="inlineStr">
+        <is>
+          <t>價-量增</t>
+        </is>
+      </c>
+      <c r="BR14" t="inlineStr">
+        <is>
+          <t>1.89</t>
+        </is>
+      </c>
+      <c r="BS14" t="inlineStr">
+        <is>
+          <t>4.97</t>
+        </is>
+      </c>
+      <c r="BT14" t="inlineStr">
+        <is>
+          <t>57.78</t>
+        </is>
+      </c>
+      <c r="BU14" t="inlineStr">
+        <is>
+          <t>12.0</t>
+        </is>
+      </c>
+      <c r="BV14" t="inlineStr">
+        <is>
+          <t>33.69%</t>
+        </is>
+      </c>
+      <c r="BW14" t="inlineStr">
+        <is>
+          <t>11.08%</t>
+        </is>
+      </c>
+      <c r="BX14" t="inlineStr">
+        <is>
+          <t>48.2</t>
+        </is>
+      </c>
+      <c r="BY14" t="inlineStr">
+        <is>
+          <t>9559</t>
+        </is>
+      </c>
+      <c r="BZ14" t="inlineStr">
+        <is>
+          <t>條碼印表機及零配件52.71%、印表機各式標籤紙及其耗材41.09%、企業行動電腦6.20% (2024年)</t>
+        </is>
+      </c>
+      <c r="CA14" t="inlineStr">
+        <is>
+          <t>鼎翰-電腦及週邊設備業-上櫃</t>
+        </is>
+      </c>
+      <c r="CB14" t="inlineStr">
+        <is>
+          <t>電腦及週邊設備業右下上櫃</t>
+        </is>
+      </c>
+      <c r="CC14" t="inlineStr">
+        <is>
+          <t>205.0</t>
+        </is>
+      </c>
+      <c r="CD14" t="inlineStr">
+        <is>
+          <t>205.0</t>
+        </is>
+      </c>
+      <c r="CE14" t="inlineStr">
+        <is>
+          <t>198.0</t>
+        </is>
+      </c>
+      <c r="CF14" t="inlineStr">
+        <is>
           <t>199.5</t>
-        </is>
-      </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>197.7</t>
-        </is>
-      </c>
-      <c r="AN14" t="inlineStr">
-        <is>
-          <t>192.01</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>190.29</t>
-        </is>
-      </c>
-      <c r="AP14" t="inlineStr">
-        <is>
-          <t>14.82</t>
-        </is>
-      </c>
-      <c r="AQ14" t="inlineStr">
-        <is>
-          <t>2.30</t>
-        </is>
-      </c>
-      <c r="AR14" t="inlineStr">
-        <is>
-          <t>2.01</t>
-        </is>
-      </c>
-      <c r="AS14" t="inlineStr">
-        <is>
-          <t>10.01</t>
-        </is>
-      </c>
-      <c r="AT14" t="inlineStr">
-        <is>
-          <t>-79.98</t>
-        </is>
-      </c>
-      <c r="AU14" t="inlineStr">
-        <is>
-          <t>2025/11/14</t>
-        </is>
-      </c>
-      <c r="AV14" t="inlineStr">
-        <is>
-          <t>28269.50649350649</t>
-        </is>
-      </c>
-      <c r="AW14" t="inlineStr">
-        <is>
-          <t>27388.0</t>
-        </is>
-      </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>15822.8</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr">
-        <is>
-          <t>14450.7</t>
-        </is>
-      </c>
-      <c r="AZ14" t="inlineStr">
-        <is>
-          <t>10277.46</t>
-        </is>
-      </c>
-      <c r="BA14" t="inlineStr">
-        <is>
-          <t>1372</t>
-        </is>
-      </c>
-      <c r="BB14" t="inlineStr">
-        <is>
-          <t>462.1765112122318</t>
-        </is>
-      </c>
-      <c r="BC14" t="n">
-        <v>1986.8</v>
-      </c>
-      <c r="BD14" t="inlineStr">
-        <is>
-          <t>2025-11-19</t>
-        </is>
-      </c>
-      <c r="BE14" t="inlineStr">
-        <is>
-          <t>192.0</t>
-        </is>
-      </c>
-      <c r="BF14" t="inlineStr">
-        <is>
-          <t>2025/10/14</t>
-        </is>
-      </c>
-      <c r="BG14" t="inlineStr">
-        <is>
-          <t>6.25</t>
-        </is>
-      </c>
-      <c r="BH14" t="inlineStr">
-        <is>
-          <t>鼎翰</t>
-        </is>
-      </c>
-      <c r="BI14" t="inlineStr">
-        <is>
-          <t>鼎翰</t>
-        </is>
-      </c>
-      <c r="BJ14" t="inlineStr">
-        <is>
-          <t>電腦及週邊設備業</t>
-        </is>
-      </c>
-      <c r="BK14" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BL14" t="inlineStr">
-        <is>
-          <t>0.57</t>
-        </is>
-      </c>
-      <c r="BM14" t="inlineStr">
-        <is>
-          <t>-11.45161899724185</t>
-        </is>
-      </c>
-      <c r="BN14" t="inlineStr">
-        <is>
-          <t>22.56717409239306</t>
-        </is>
-      </c>
-      <c r="BO14" t="inlineStr">
-        <is>
-          <t>38.82556207928187</t>
-        </is>
-      </c>
-      <c r="BP14" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BQ14" t="inlineStr">
-        <is>
-          <t>價-量增</t>
-        </is>
-      </c>
-      <c r="BR14" t="inlineStr">
-        <is>
-          <t>1.93</t>
-        </is>
-      </c>
-      <c r="BS14" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="BT14" t="inlineStr">
-        <is>
-          <t>57.78</t>
-        </is>
-      </c>
-      <c r="BU14" t="inlineStr">
-        <is>
-          <t>11.91</t>
-        </is>
-      </c>
-      <c r="BV14" t="inlineStr">
-        <is>
-          <t>33.69%</t>
-        </is>
-      </c>
-      <c r="BW14" t="inlineStr">
-        <is>
-          <t>11.08%</t>
-        </is>
-      </c>
-      <c r="BX14" t="inlineStr">
-        <is>
-          <t>48.7</t>
-        </is>
-      </c>
-      <c r="BY14" t="inlineStr">
-        <is>
-          <t>9487</t>
-        </is>
-      </c>
-      <c r="BZ14" t="inlineStr">
-        <is>
-          <t>條碼印表機及零配件52.71%、印表機各式標籤紙及其耗材41.09%、企業行動電腦6.20% (2024年)</t>
-        </is>
-      </c>
-      <c r="CA14" t="inlineStr">
-        <is>
-          <t>鼎翰-電腦及週邊設備業-上櫃</t>
-        </is>
-      </c>
-      <c r="CB14" t="inlineStr">
-        <is>
-          <t>電腦及週邊設備業右下上櫃</t>
-        </is>
-      </c>
-      <c r="CC14" t="inlineStr">
-        <is>
-          <t>201.5</t>
-        </is>
-      </c>
-      <c r="CD14" t="inlineStr">
-        <is>
-          <t>206.5</t>
-        </is>
-      </c>
-      <c r="CE14" t="inlineStr">
-        <is>
-          <t>201.5</t>
-        </is>
-      </c>
-      <c r="CF14" t="inlineStr">
-        <is>
-          <t>204.0</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
@@ -6481,12 +6481,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>167.0</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6496,74 +6496,74 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
+          <t>204.0</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>-1.49</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>-0.58</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>9.50</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>-65.0</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>2025-11-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>2025-11-20 00:00:00</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>2025-10-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>2025-11-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
           <t>201.5</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>-1.0</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>-1.0</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>21.03</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>2025-11-14</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>-65.0</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>2025-11-14 00:00:00</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>2025-11-19 00:00:00</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>2025-10-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>2025-11-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q15" t="inlineStr">
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
         <is>
           <t>201.5</t>
         </is>
       </c>
-      <c r="R15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>201.5</t>
-        </is>
-      </c>
       <c r="T15" t="inlineStr">
         <is>
           <t>195.5</t>
@@ -6576,7 +6576,7 @@
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
@@ -6591,17 +6591,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>39.29</t>
+          <t>31.53</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6612,12 +6612,12 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>50</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
@@ -6627,195 +6627,195 @@
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>69.23</t>
+          <t>82.05</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>2.87</t>
+          <t>2.96</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>198.8</t>
+          <t>199.5</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>197.15</t>
+          <t>197.7</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>191.65</t>
+          <t>192.01</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>190.08</t>
+          <t>190.29</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>14.82</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
+          <t>2.01</t>
+        </is>
+      </c>
+      <c r="AS15" t="inlineStr">
+        <is>
+          <t>10.01</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr">
+        <is>
+          <t>-79.98</t>
+        </is>
+      </c>
+      <c r="AU15" t="inlineStr">
+        <is>
+          <t>2025/11/14</t>
+        </is>
+      </c>
+      <c r="AV15" t="inlineStr">
+        <is>
+          <t>28250.49639769452</t>
+        </is>
+      </c>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>27388.0</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>15822.8</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>14450.7</t>
+        </is>
+      </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>10277.46</t>
+        </is>
+      </c>
+      <c r="BA15" t="inlineStr">
+        <is>
+          <t>1372</t>
+        </is>
+      </c>
+      <c r="BB15" t="inlineStr">
+        <is>
+          <t>462.1765112122318</t>
+        </is>
+      </c>
+      <c r="BC15" t="n">
+        <v>1986.8</v>
+      </c>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>2025-11-20</t>
+        </is>
+      </c>
+      <c r="BE15" t="inlineStr">
+        <is>
+          <t>192.0</t>
+        </is>
+      </c>
+      <c r="BF15" t="inlineStr">
+        <is>
+          <t>2025/10/14</t>
+        </is>
+      </c>
+      <c r="BG15" t="inlineStr">
+        <is>
+          <t>6.25</t>
+        </is>
+      </c>
+      <c r="BH15" t="inlineStr">
+        <is>
+          <t>鼎翰</t>
+        </is>
+      </c>
+      <c r="BI15" t="inlineStr">
+        <is>
+          <t>鼎翰</t>
+        </is>
+      </c>
+      <c r="BJ15" t="inlineStr">
+        <is>
+          <t>電腦及週邊設備業</t>
+        </is>
+      </c>
+      <c r="BK15" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BL15" t="inlineStr">
+        <is>
+          <t>0.57</t>
+        </is>
+      </c>
+      <c r="BM15" t="inlineStr">
+        <is>
+          <t>-11.45161899724185</t>
+        </is>
+      </c>
+      <c r="BN15" t="inlineStr">
+        <is>
+          <t>22.56717409239306</t>
+        </is>
+      </c>
+      <c r="BO15" t="inlineStr">
+        <is>
+          <t>38.82556207928187</t>
+        </is>
+      </c>
+      <c r="BP15" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BQ15" t="inlineStr">
+        <is>
+          <t>價-量增</t>
+        </is>
+      </c>
+      <c r="BR15" t="inlineStr">
+        <is>
           <t>1.93</t>
         </is>
       </c>
-      <c r="AS15" t="inlineStr">
-        <is>
-          <t>10.01</t>
-        </is>
-      </c>
-      <c r="AT15" t="inlineStr">
-        <is>
-          <t>-80.72</t>
-        </is>
-      </c>
-      <c r="AU15" t="inlineStr">
-        <is>
-          <t>2025/11/14</t>
-        </is>
-      </c>
-      <c r="AV15" t="inlineStr">
-        <is>
-          <t>28269.50649350649</t>
-        </is>
-      </c>
-      <c r="AW15" t="inlineStr">
-        <is>
-          <t>33609.0</t>
-        </is>
-      </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>14692.0</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr">
-        <is>
-          <t>12138.8</t>
-        </is>
-      </c>
-      <c r="AZ15" t="inlineStr">
-        <is>
-          <t>9836.78</t>
-        </is>
-      </c>
-      <c r="BA15" t="inlineStr">
-        <is>
-          <t>2553</t>
-        </is>
-      </c>
-      <c r="BB15" t="inlineStr">
-        <is>
-          <t>184.9729413194776</t>
-        </is>
-      </c>
-      <c r="BC15" t="n">
-        <v>1139.99</v>
-      </c>
-      <c r="BD15" t="inlineStr">
-        <is>
-          <t>2025-11-19</t>
-        </is>
-      </c>
-      <c r="BE15" t="inlineStr">
-        <is>
-          <t>192.0</t>
-        </is>
-      </c>
-      <c r="BF15" t="inlineStr">
-        <is>
-          <t>2025/10/14</t>
-        </is>
-      </c>
-      <c r="BG15" t="inlineStr">
-        <is>
-          <t>4.95</t>
-        </is>
-      </c>
-      <c r="BH15" t="inlineStr">
-        <is>
-          <t>鼎翰</t>
-        </is>
-      </c>
-      <c r="BI15" t="inlineStr">
-        <is>
-          <t>鼎翰</t>
-        </is>
-      </c>
-      <c r="BJ15" t="inlineStr">
-        <is>
-          <t>電腦及週邊設備業</t>
-        </is>
-      </c>
-      <c r="BK15" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BL15" t="inlineStr">
-        <is>
-          <t>0.57</t>
-        </is>
-      </c>
-      <c r="BM15" t="inlineStr">
-        <is>
-          <t>-11.45161899724185</t>
-        </is>
-      </c>
-      <c r="BN15" t="inlineStr">
-        <is>
-          <t>22.56717409239306</t>
-        </is>
-      </c>
-      <c r="BO15" t="inlineStr">
-        <is>
-          <t>38.82556207928187</t>
-        </is>
-      </c>
-      <c r="BP15" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BQ15" t="inlineStr">
-        <is>
-          <t>價漲量增</t>
-        </is>
-      </c>
-      <c r="BR15" t="inlineStr">
-        <is>
-          <t>1.91</t>
-        </is>
-      </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4.97</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="BU15" t="inlineStr">
         <is>
-          <t>11.91</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="BV15" t="inlineStr">
@@ -6840,12 +6840,12 @@
       </c>
       <c r="BX15" t="inlineStr">
         <is>
-          <t>48.7</t>
+          <t>48.2</t>
         </is>
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>9487</t>
+          <t>9559</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
@@ -6865,22 +6865,22 @@
       </c>
       <c r="CC15" t="inlineStr">
         <is>
-          <t>199.0</t>
+          <t>201.5</t>
         </is>
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>202.5</t>
+          <t>206.5</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>198.5</t>
+          <t>201.5</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>201.5</t>
+          <t>204.0</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
@@ -6912,12 +6912,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>19.0</t>
+          <t>167.0</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6927,7 +6927,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>197.0</t>
+          <t>201.5</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6937,22 +6937,22 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>21.03</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -6967,7 +6967,7 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>2025-11-19 00:00:00</t>
+          <t>2025-11-20 00:00:00</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -6992,7 +6992,7 @@
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>201.5</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
@@ -7007,7 +7007,7 @@
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
@@ -7022,17 +7022,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>4.47</t>
+          <t>39.29</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>-1.27</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7043,177 +7043,177 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>50</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>46.15</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>51.28</t>
+          <t>69.23</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
+          <t>0.84</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>2.87</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>0.83</t>
+        </is>
+      </c>
+      <c r="AL16" t="inlineStr">
+        <is>
+          <t>198.8</t>
+        </is>
+      </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>197.15</t>
+        </is>
+      </c>
+      <c r="AN16" t="inlineStr">
+        <is>
+          <t>191.65</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>190.08</t>
+        </is>
+      </c>
+      <c r="AP16" t="inlineStr">
+        <is>
+          <t>0.64</t>
+        </is>
+      </c>
+      <c r="AQ16" t="inlineStr">
+        <is>
+          <t>1.94</t>
+        </is>
+      </c>
+      <c r="AR16" t="inlineStr">
+        <is>
+          <t>1.93</t>
+        </is>
+      </c>
+      <c r="AS16" t="inlineStr">
+        <is>
+          <t>10.01</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr">
+        <is>
+          <t>-80.72</t>
+        </is>
+      </c>
+      <c r="AU16" t="inlineStr">
+        <is>
+          <t>2025/11/14</t>
+        </is>
+      </c>
+      <c r="AV16" t="inlineStr">
+        <is>
+          <t>28250.49639769452</t>
+        </is>
+      </c>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>33609.0</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>14692.0</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>12138.8</t>
+        </is>
+      </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>9836.78</t>
+        </is>
+      </c>
+      <c r="BA16" t="inlineStr">
+        <is>
+          <t>2553</t>
+        </is>
+      </c>
+      <c r="BB16" t="inlineStr">
+        <is>
+          <t>184.9729413194776</t>
+        </is>
+      </c>
+      <c r="BC16" t="n">
+        <v>1139.99</v>
+      </c>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>2025-11-20</t>
+        </is>
+      </c>
+      <c r="BE16" t="inlineStr">
+        <is>
+          <t>192.0</t>
+        </is>
+      </c>
+      <c r="BF16" t="inlineStr">
+        <is>
+          <t>2025/10/14</t>
+        </is>
+      </c>
+      <c r="BG16" t="inlineStr">
+        <is>
+          <t>4.95</t>
+        </is>
+      </c>
+      <c r="BH16" t="inlineStr">
+        <is>
+          <t>鼎翰</t>
+        </is>
+      </c>
+      <c r="BI16" t="inlineStr">
+        <is>
+          <t>鼎翰</t>
+        </is>
+      </c>
+      <c r="BJ16" t="inlineStr">
+        <is>
+          <t>電腦及週邊設備業</t>
+        </is>
+      </c>
+      <c r="BK16" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BL16" t="inlineStr">
+        <is>
           <t>0.57</t>
         </is>
       </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>2.84</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>0.70</t>
-        </is>
-      </c>
-      <c r="AL16" t="inlineStr">
-        <is>
-          <t>197.9</t>
-        </is>
-      </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>196.78</t>
-        </is>
-      </c>
-      <c r="AN16" t="inlineStr">
-        <is>
-          <t>191.34</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>190.02</t>
-        </is>
-      </c>
-      <c r="AP16" t="inlineStr">
-        <is>
-          <t>-11.24</t>
-        </is>
-      </c>
-      <c r="AQ16" t="inlineStr">
-        <is>
-          <t>1.71</t>
-        </is>
-      </c>
-      <c r="AR16" t="inlineStr">
-        <is>
-          <t>1.93</t>
-        </is>
-      </c>
-      <c r="AS16" t="inlineStr">
-        <is>
-          <t>10.01</t>
-        </is>
-      </c>
-      <c r="AT16" t="inlineStr">
-        <is>
-          <t>-80.75</t>
-        </is>
-      </c>
-      <c r="AU16" t="inlineStr">
-        <is>
-          <t>2025/11/14</t>
-        </is>
-      </c>
-      <c r="AV16" t="inlineStr">
-        <is>
-          <t>28269.50649350649</t>
-        </is>
-      </c>
-      <c r="AW16" t="inlineStr">
-        <is>
-          <t>3715.0</t>
-        </is>
-      </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>9865.0</t>
-        </is>
-      </c>
-      <c r="AY16" t="inlineStr">
-        <is>
-          <t>9864.3</t>
-        </is>
-      </c>
-      <c r="AZ16" t="inlineStr">
-        <is>
-          <t>9269.96</t>
-        </is>
-      </c>
-      <c r="BA16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BB16" t="inlineStr">
-        <is>
-          <t>11.33269122891031</t>
-        </is>
-      </c>
-      <c r="BC16" t="n">
-        <v>-776.97</v>
-      </c>
-      <c r="BD16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BE16" t="inlineStr">
-        <is>
-          <t>192.0</t>
-        </is>
-      </c>
-      <c r="BF16" t="inlineStr">
-        <is>
-          <t>2025/10/14</t>
-        </is>
-      </c>
-      <c r="BG16" t="inlineStr">
-        <is>
-          <t>2.60</t>
-        </is>
-      </c>
-      <c r="BH16" t="inlineStr">
-        <is>
-          <t>鼎翰</t>
-        </is>
-      </c>
-      <c r="BI16" t="inlineStr">
-        <is>
-          <t>鼎翰</t>
-        </is>
-      </c>
-      <c r="BJ16" t="inlineStr">
-        <is>
-          <t>電腦及週邊設備業</t>
-        </is>
-      </c>
-      <c r="BK16" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BL16" t="inlineStr">
-        <is>
-          <t>0.57</t>
-        </is>
-      </c>
       <c r="BM16" t="inlineStr">
         <is>
           <t>-11.45161899724185</t>
@@ -7231,22 +7231,22 @@
       </c>
       <c r="BP16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4.97</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
@@ -7256,7 +7256,7 @@
       </c>
       <c r="BU16" t="inlineStr">
         <is>
-          <t>11.91</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="BV16" t="inlineStr">
@@ -7271,12 +7271,12 @@
       </c>
       <c r="BX16" t="inlineStr">
         <is>
-          <t>48.7</t>
+          <t>48.2</t>
         </is>
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>9487</t>
+          <t>9559</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
@@ -7296,22 +7296,22 @@
       </c>
       <c r="CC16" t="inlineStr">
         <is>
-          <t>199.5</t>
+          <t>199.0</t>
         </is>
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>199.5</t>
+          <t>202.5</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>197.0</t>
+          <t>198.5</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>197.0</t>
+          <t>201.5</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
@@ -7343,12 +7343,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>19.0</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7358,7 +7358,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>198.0</t>
+          <t>197.0</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7368,17 +7368,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7398,7 +7398,7 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>2025-11-19 00:00:00</t>
+          <t>2025-11-20 00:00:00</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -7453,17 +7453,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>7.06</t>
+          <t>4.47</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>-1.27</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7474,77 +7474,77 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>50</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>61.54</t>
+          <t>46.15</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>69.23</t>
+          <t>51.28</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>0.80</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>2.85</t>
+          <t>2.84</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>0.62</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>198.2</t>
+          <t>197.9</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>196.62</t>
+          <t>196.78</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>191.17</t>
+          <t>191.34</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>189.99</t>
+          <t>190.02</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>-6.74</t>
+          <t>-11.24</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7554,7 +7554,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-80.21</t>
+          <t>-80.75</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7564,41 +7564,41 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>28269.50649350649</t>
+          <t>28250.49639769452</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>5976.0</t>
+          <t>3715.0</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>10613.2</t>
+          <t>9865.0</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>10254.6</t>
+          <t>9864.3</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>9315.64</t>
+          <t>9269.96</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>358</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>154.6608857258293</t>
+          <t>11.33269122891031</t>
         </is>
       </c>
       <c r="BC17" t="n">
-        <v>-284.82</v>
+        <v>-776.97</v>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
@@ -7617,7 +7617,7 @@
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>3.12</t>
+          <t>2.60</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
@@ -7662,22 +7662,22 @@
       </c>
       <c r="BP17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4.97</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
@@ -7687,7 +7687,7 @@
       </c>
       <c r="BU17" t="inlineStr">
         <is>
-          <t>11.91</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="BV17" t="inlineStr">
@@ -7702,12 +7702,12 @@
       </c>
       <c r="BX17" t="inlineStr">
         <is>
-          <t>48.7</t>
+          <t>48.2</t>
         </is>
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>9487</t>
+          <t>9559</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
@@ -7727,22 +7727,22 @@
       </c>
       <c r="CC17" t="inlineStr">
         <is>
+          <t>199.5</t>
+        </is>
+      </c>
+      <c r="CD17" t="inlineStr">
+        <is>
+          <t>199.5</t>
+        </is>
+      </c>
+      <c r="CE17" t="inlineStr">
+        <is>
           <t>197.0</t>
         </is>
       </c>
-      <c r="CD17" t="inlineStr">
-        <is>
-          <t>198.5</t>
-        </is>
-      </c>
-      <c r="CE17" t="inlineStr">
+      <c r="CF17" t="inlineStr">
         <is>
           <t>197.0</t>
-        </is>
-      </c>
-      <c r="CF17" t="inlineStr">
-        <is>
-          <t>198.0</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
@@ -7774,12 +7774,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-1.75</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>42.0</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7789,7 +7789,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>197.0</t>
+          <t>198.0</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7799,17 +7799,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>16.90</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7829,7 +7829,7 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>2025-11-19 00:00:00</t>
+          <t>2025-11-20 00:00:00</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
@@ -7884,17 +7884,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>9.88</t>
+          <t>7.06</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>-1.78</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7905,77 +7905,77 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>50</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>46.15</t>
+          <t>61.54</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>70.94</t>
+          <t>69.23</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>0.60</t>
+          <t>0.80</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>2.8</t>
+          <t>2.85</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>197.5</t>
+          <t>198.2</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>196.32</t>
+          <t>196.62</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>190.97</t>
+          <t>191.17</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>189.94</t>
+          <t>189.99</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>-5.98</t>
+          <t>-6.74</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>1.89</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -7985,7 +7985,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-79.87</t>
+          <t>-80.21</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7995,41 +7995,41 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>28269.50649350649</t>
+          <t>28250.49639769452</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>8426.0</t>
+          <t>5976.0</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>12937.0</t>
+          <t>10613.2</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>11067.0</t>
+          <t>10254.6</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>9335.32</t>
+          <t>9315.64</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>1870</t>
+          <t>358</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>234.5662547700167</t>
+          <t>154.6608857258293</t>
         </is>
       </c>
       <c r="BC18" t="n">
-        <v>186.18</v>
+        <v>-284.82</v>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
@@ -8048,7 +8048,7 @@
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>2.60</t>
+          <t>3.12</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
@@ -8093,7 +8093,7 @@
       </c>
       <c r="BP18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ18" t="inlineStr">
@@ -8103,12 +8103,12 @@
       </c>
       <c r="BR18" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4.97</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
@@ -8118,7 +8118,7 @@
       </c>
       <c r="BU18" t="inlineStr">
         <is>
-          <t>11.91</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="BV18" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="BX18" t="inlineStr">
         <is>
-          <t>48.7</t>
+          <t>48.2</t>
         </is>
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>9487</t>
+          <t>9559</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
@@ -8158,12 +8158,12 @@
       </c>
       <c r="CC18" t="inlineStr">
         <is>
-          <t>200.5</t>
+          <t>197.0</t>
         </is>
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>200.5</t>
+          <t>198.5</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
@@ -8173,7 +8173,7 @@
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>197.0</t>
+          <t>198.0</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
@@ -8205,12 +8205,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>-1.75</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>108.0</t>
+          <t>42.0</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8220,7 +8220,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>200.5</t>
+          <t>197.0</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8230,17 +8230,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>11.96</t>
+          <t>16.90</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8260,7 +8260,7 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>2025-11-19 00:00:00</t>
+          <t>2025-11-20 00:00:00</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
@@ -8315,17 +8315,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>25.41</t>
+          <t>9.88</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>-0.74</t>
+          <t>-1.78</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8336,77 +8336,77 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>50</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>46.15</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>82.83</t>
+          <t>70.94</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.60</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>2.72</t>
+          <t>2.8</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>196.9</t>
+          <t>197.5</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>196.0</t>
+          <t>196.32</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>190.81</t>
+          <t>190.97</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>189.91</t>
+          <t>189.94</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>-5.98</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>1.89</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8416,7 +8416,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-79.57</t>
+          <t>-79.87</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8426,41 +8426,41 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>28269.50649350649</t>
+          <t>28250.49639769452</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>21734.0</t>
+          <t>8426.0</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>13078.6</t>
+          <t>12937.0</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>11681.7</t>
+          <t>11067.0</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>9341.52</t>
+          <t>9335.32</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>1396</t>
+          <t>1870</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>243.363716734609</t>
+          <t>234.5662547700167</t>
         </is>
       </c>
       <c r="BC19" t="n">
-        <v>589.89</v>
+        <v>186.18</v>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
@@ -8479,7 +8479,7 @@
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>4.43</t>
+          <t>2.60</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">
@@ -8524,22 +8524,22 @@
       </c>
       <c r="BP19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4.97</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
@@ -8549,7 +8549,7 @@
       </c>
       <c r="BU19" t="inlineStr">
         <is>
-          <t>11.91</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="BV19" t="inlineStr">
@@ -8564,12 +8564,12 @@
       </c>
       <c r="BX19" t="inlineStr">
         <is>
-          <t>48.7</t>
+          <t>48.2</t>
         </is>
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>9487</t>
+          <t>9559</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
@@ -8589,22 +8589,22 @@
       </c>
       <c r="CC19" t="inlineStr">
         <is>
-          <t>203.5</t>
+          <t>200.5</t>
         </is>
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>203.5</t>
+          <t>200.5</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>199.0</t>
+          <t>197.0</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>200.5</t>
+          <t>197.0</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
@@ -8636,12 +8636,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>48.0</t>
+          <t>108.0</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8651,7 +8651,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>197.0</t>
+          <t>200.5</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8661,17 +8661,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>-10.99</t>
+          <t>11.96</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8691,7 +8691,7 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>2025-11-19 00:00:00</t>
+          <t>2025-11-20 00:00:00</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
@@ -8746,17 +8746,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11.29</t>
+          <t>25.41</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>-0.74</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8767,72 +8767,72 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>50</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>52.27</t>
+          <t>82.83</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>2.72</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
+          <t>196.9</t>
+        </is>
+      </c>
+      <c r="AM20" t="inlineStr">
+        <is>
           <t>196.0</t>
         </is>
       </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>195.48</t>
-        </is>
-      </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>190.59</t>
+          <t>190.81</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>189.82</t>
+          <t>189.91</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>-11.56</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
@@ -8847,7 +8847,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-79.53</t>
+          <t>-79.57</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8857,41 +8857,41 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>28269.50649350649</t>
+          <t>28250.49639769452</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>9474.0</t>
+          <t>21734.0</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>9585.6</t>
+          <t>13078.6</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>10769.2</t>
+          <t>11681.7</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>9013.74</t>
+          <t>9341.52</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>-1183</t>
+          <t>1396</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>180.3595866842333</t>
+          <t>243.363716734609</t>
         </is>
       </c>
       <c r="BC20" t="n">
-        <v>-280.31</v>
+        <v>589.89</v>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
@@ -8910,7 +8910,7 @@
       </c>
       <c r="BG20" t="inlineStr">
         <is>
-          <t>2.60</t>
+          <t>4.43</t>
         </is>
       </c>
       <c r="BH20" t="inlineStr">
@@ -8955,22 +8955,22 @@
       </c>
       <c r="BP20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4.97</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
@@ -8980,7 +8980,7 @@
       </c>
       <c r="BU20" t="inlineStr">
         <is>
-          <t>11.91</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="BV20" t="inlineStr">
@@ -8995,12 +8995,12 @@
       </c>
       <c r="BX20" t="inlineStr">
         <is>
-          <t>48.7</t>
+          <t>48.2</t>
         </is>
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>9487</t>
+          <t>9559</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
@@ -9020,22 +9020,22 @@
       </c>
       <c r="CC20" t="inlineStr">
         <is>
-          <t>196.0</t>
+          <t>203.5</t>
         </is>
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>197.5</t>
+          <t>203.5</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>195.0</t>
+          <t>199.0</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>197.0</t>
+          <t>200.5</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
@@ -9067,12 +9067,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>-0.77</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>38.0</t>
+          <t>48.0</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9082,7 +9082,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>198.5</t>
+          <t>197.0</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9092,17 +9092,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>-14.77</t>
+          <t>-10.99</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9122,7 +9122,7 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>2025-11-19 00:00:00</t>
+          <t>2025-11-20 00:00:00</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
@@ -9177,17 +9177,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>8.94</t>
+          <t>11.29</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9198,77 +9198,77 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>50</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>81.82</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>30.05</t>
+          <t>52.27</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>2.48</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>195.7</t>
+          <t>196.0</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>195.12</t>
+          <t>195.48</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>190.41</t>
+          <t>190.59</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>189.79</t>
+          <t>189.82</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>-11.44</t>
+          <t>-11.56</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9278,7 +9278,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-78.94</t>
+          <t>-79.53</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9288,41 +9288,41 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>28269.50649350649</t>
+          <t>28250.49639769452</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>7456.0</t>
+          <t>9474.0</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>9863.6</t>
+          <t>9585.6</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>11572.5</t>
+          <t>10769.2</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>9025.16</t>
+          <t>9013.74</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>-1708</t>
+          <t>-1183</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>264.1185869502501</t>
+          <t>180.3595866842333</t>
         </is>
       </c>
       <c r="BC21" t="n">
-        <v>-199.88</v>
+        <v>-280.31</v>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
@@ -9341,7 +9341,7 @@
       </c>
       <c r="BG21" t="inlineStr">
         <is>
-          <t>3.39</t>
+          <t>2.60</t>
         </is>
       </c>
       <c r="BH21" t="inlineStr">
@@ -9386,7 +9386,7 @@
       </c>
       <c r="BP21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ21" t="inlineStr">
@@ -9396,12 +9396,12 @@
       </c>
       <c r="BR21" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4.97</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
@@ -9411,7 +9411,7 @@
       </c>
       <c r="BU21" t="inlineStr">
         <is>
-          <t>11.91</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="BV21" t="inlineStr">
@@ -9426,12 +9426,12 @@
       </c>
       <c r="BX21" t="inlineStr">
         <is>
-          <t>48.7</t>
+          <t>48.2</t>
         </is>
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>9487</t>
+          <t>9559</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
@@ -9451,22 +9451,22 @@
       </c>
       <c r="CC21" t="inlineStr">
         <is>
+          <t>196.0</t>
+        </is>
+      </c>
+      <c r="CD21" t="inlineStr">
+        <is>
+          <t>197.5</t>
+        </is>
+      </c>
+      <c r="CE21" t="inlineStr">
+        <is>
           <t>195.0</t>
         </is>
       </c>
-      <c r="CD21" t="inlineStr">
-        <is>
-          <t>199.0</t>
-        </is>
-      </c>
-      <c r="CE21" t="inlineStr">
-        <is>
-          <t>195.0</t>
-        </is>
-      </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>198.5</t>
+          <t>197.0</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
@@ -9498,12 +9498,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>38.0</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9513,7 +9513,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>194.5</t>
+          <t>198.5</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9523,17 +9523,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>-19.30</t>
+          <t>-14.77</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9553,7 +9553,7 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>2025-11-19 00:00:00</t>
+          <t>2025-11-20 00:00:00</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
@@ -9608,17 +9608,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>21.65</t>
+          <t>8.94</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9629,77 +9629,77 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>50</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>8.33</t>
+          <t>81.82</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>6.48</t>
+          <t>30.05</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>2.48</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>195.5</t>
+          <t>195.7</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>194.65</t>
+          <t>195.12</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>190.2</t>
+          <t>190.41</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>189.76</t>
+          <t>189.79</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>-18.96</t>
+          <t>-11.44</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9709,7 +9709,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-78.34</t>
+          <t>-78.94</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9719,41 +9719,41 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>28269.50649350649</t>
+          <t>28250.49639769452</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>17595.0</t>
+          <t>7456.0</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>9896.0</t>
+          <t>9863.6</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>12262.5</t>
+          <t>11572.5</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>9049.34</t>
+          <t>9025.16</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>-2366</t>
+          <t>-1708</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>348.481424646728</t>
+          <t>264.1185869502501</t>
         </is>
       </c>
       <c r="BC22" t="n">
-        <v>138.39</v>
+        <v>-199.88</v>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
@@ -9772,7 +9772,7 @@
       </c>
       <c r="BG22" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>3.39</t>
         </is>
       </c>
       <c r="BH22" t="inlineStr">
@@ -9817,7 +9817,7 @@
       </c>
       <c r="BP22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ22" t="inlineStr">
@@ -9827,12 +9827,12 @@
       </c>
       <c r="BR22" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4.97</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
@@ -9842,7 +9842,7 @@
       </c>
       <c r="BU22" t="inlineStr">
         <is>
-          <t>11.91</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="BV22" t="inlineStr">
@@ -9857,12 +9857,12 @@
       </c>
       <c r="BX22" t="inlineStr">
         <is>
-          <t>48.7</t>
+          <t>48.2</t>
         </is>
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>9487</t>
+          <t>9559</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
@@ -9882,22 +9882,22 @@
       </c>
       <c r="CC22" t="inlineStr">
         <is>
-          <t>194.0</t>
+          <t>195.0</t>
         </is>
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>194.5</t>
+          <t>199.0</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>190.0</t>
+          <t>195.0</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>194.5</t>
+          <t>198.5</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
@@ -9929,12 +9929,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-1.01</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>47.0</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9944,7 +9944,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>194.0</t>
+          <t>194.5</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9954,17 +9954,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2.76</t>
+          <t>3.23</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>-23.60</t>
+          <t>-19.30</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -9984,7 +9984,7 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>2025-11-19 00:00:00</t>
+          <t>2025-11-20 00:00:00</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
@@ -10039,17 +10039,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11.06</t>
+          <t>21.65</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>-1.80</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10060,77 +10060,77 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>50</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>8.33</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>12.04</t>
+          <t>6.48</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>-1.17</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>196.3</t>
+          <t>195.5</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>194.38</t>
+          <t>194.65</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>190.1</t>
+          <t>190.2</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>189.75</t>
+          <t>189.76</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>-11.99</t>
+          <t>-18.96</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>2.27</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10140,7 +10140,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-77.31</t>
+          <t>-78.34</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10150,41 +10150,41 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>28269.50649350649</t>
+          <t>28250.49639769452</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>9134.0</t>
+          <t>17595.0</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>9197.0</t>
+          <t>9896.0</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>12037.8</t>
+          <t>12262.5</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>8763.96</t>
+          <t>9049.34</t>
         </is>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>-2840</t>
+          <t>-2366</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>386.6804094807498</t>
+          <t>348.481424646728</t>
         </is>
       </c>
       <c r="BC23" t="n">
-        <v>-469.64</v>
+        <v>138.39</v>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
@@ -10203,7 +10203,7 @@
       </c>
       <c r="BG23" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="BH23" t="inlineStr">
@@ -10248,7 +10248,7 @@
       </c>
       <c r="BP23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ23" t="inlineStr">
@@ -10263,7 +10263,7 @@
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4.97</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
@@ -10273,7 +10273,7 @@
       </c>
       <c r="BU23" t="inlineStr">
         <is>
-          <t>11.91</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="BV23" t="inlineStr">
@@ -10288,12 +10288,12 @@
       </c>
       <c r="BX23" t="inlineStr">
         <is>
-          <t>48.7</t>
+          <t>48.2</t>
         </is>
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>9487</t>
+          <t>9559</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
@@ -10313,22 +10313,22 @@
       </c>
       <c r="CC23" t="inlineStr">
         <is>
-          <t>197.5</t>
+          <t>194.0</t>
         </is>
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>197.5</t>
+          <t>194.5</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>194.0</t>
+          <t>190.0</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>194.0</t>
+          <t>194.5</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">

--- a/Result/checksun_type/HMI.xlsx
+++ b/Result/checksun_type/HMI.xlsx
@@ -878,12 +878,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>26.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>19.15</t>
+          <t>19.5</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -908,12 +908,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>-2.89</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>14.69</t>
+          <t>-4.04</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -923,7 +923,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-12.36</t>
+          <t>-10.76</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -988,17 +988,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>3.17</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,72 +1014,72 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>22.58</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.53</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-3.58</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-5.17</t>
+          <t>-5.39</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-3.97</t>
+          <t>-4.43</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-2.33</t>
+          <t>-2.68</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>19.86</t>
+          <t>19.67</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>20.94</t>
+          <t>20.79</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>21.81</t>
+          <t>21.75</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>22.33</t>
+          <t>22.35</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-28.42</t>
+          <t>-23.19</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-0.68</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-0.55</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-107.91</t>
+          <t>-108.40</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1099,41 +1099,41 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>30589.40922190202</t>
+          <t>30546.46834532374</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>231.0</t>
+          <t>497.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>911.2</t>
+          <t>738.2</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>794.5</t>
+          <t>769.3</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>1867.82</t>
+          <t>1851.22</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>116</t>
+          <t>-31</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-166.1134213107396</t>
+          <t>-160.5311444651931</t>
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>-116.58</v>
+        <v>-129.83</v>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>-19.03</t>
+          <t>-17.55</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1177,7 +1177,7 @@
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="BM2" t="inlineStr">
@@ -1197,17 +1197,17 @@
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>84.12</t>
+          <t>85.54</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>559</t>
+          <t>569</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1262,22 +1262,22 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>18.85</t>
+          <t>19.2</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>19.15</t>
+          <t>19.5</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>18.85</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>19.15</t>
+          <t>19.5</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1309,12 +1309,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-4.24</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>19.2</t>
+          <t>19.15</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1334,17 +1334,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>-2.89</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>21.51</t>
+          <t>14.69</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1354,7 +1354,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -1409,7 +1409,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-12.13</t>
+          <t>-12.36</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1419,17 +1419,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>3.15</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-3.37</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1445,7 +1445,7 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
@@ -1455,62 +1455,62 @@
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>15.38</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-4.81</t>
+          <t>-3.58</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-4.41</t>
+          <t>-5.17</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-3.49</t>
+          <t>-3.97</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-2.01</t>
+          <t>-2.33</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>20.17</t>
+          <t>19.86</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>21.1</t>
+          <t>20.94</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>21.86</t>
+          <t>21.81</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>22.31</t>
+          <t>22.33</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-25.64</t>
+          <t>-28.42</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-107.35</t>
+          <t>-107.91</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,41 +1530,41 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>30589.40922190202</t>
+          <t>30546.46834532374</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>1715.0</t>
+          <t>231.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>1014.4</t>
+          <t>911.2</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>834.8</t>
+          <t>794.5</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>1896.36</t>
+          <t>1867.82</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>179</t>
+          <t>116</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-175.1202900950192</t>
+          <t>-166.1134213107396</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>-64.98</v>
+        <v>-116.58</v>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>-18.82</t>
+          <t>-19.03</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1608,7 +1608,7 @@
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="BM3" t="inlineStr">
@@ -1628,7 +1628,7 @@
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
@@ -1638,7 +1638,7 @@
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
@@ -1668,12 +1668,12 @@
       </c>
       <c r="BX3" t="inlineStr">
         <is>
-          <t>84.12</t>
+          <t>85.54</t>
         </is>
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>559</t>
+          <t>569</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1693,22 +1693,22 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>20.05</t>
+          <t>18.85</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>20.05</t>
+          <t>19.15</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>19.0</t>
+          <t>18.85</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>19.2</t>
+          <t>19.15</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1740,12 +1740,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-2.0</t>
+          <t>-4.24</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>46.0</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>20.05</t>
+          <t>19.2</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1765,17 +1765,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-4.7</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>-2.89</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>17.65</t>
+          <t>21.51</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1785,7 +1785,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-8.24</t>
+          <t>-12.13</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1850,17 +1850,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>3.15</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>-3.37</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1876,7 +1876,7 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
@@ -1886,62 +1886,62 @@
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>23.08</t>
+          <t>15.38</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-1.91</t>
+          <t>-4.81</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-3.90</t>
+          <t>-4.41</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-2.98</t>
+          <t>-3.49</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-1.65</t>
+          <t>-2.01</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>20.44</t>
+          <t>20.17</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>21.27</t>
+          <t>21.1</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>21.92</t>
+          <t>21.86</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>22.29</t>
+          <t>22.31</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-16.23</t>
+          <t>-25.64</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-106.88</t>
+          <t>-107.35</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1961,41 +1961,41 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>30589.40922190202</t>
+          <t>30546.46834532374</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>922.0</t>
+          <t>1715.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>840.4</t>
+          <t>1014.4</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>714.3</t>
+          <t>834.8</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>1889.2</t>
+          <t>1896.36</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>126</t>
+          <t>179</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-195.1459064225224</t>
+          <t>-175.1202900950192</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>-147.95</v>
+        <v>-64.98</v>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>-15.22</t>
+          <t>-18.82</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="BM4" t="inlineStr">
@@ -2059,7 +2059,7 @@
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
@@ -2069,7 +2069,7 @@
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
@@ -2099,12 +2099,12 @@
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>84.12</t>
+          <t>85.54</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>559</t>
+          <t>569</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2124,22 +2124,22 @@
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>20.05</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>20.1</t>
+          <t>20.05</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>19.95</t>
+          <t>19.0</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>20.05</t>
+          <t>19.2</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-2.0</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>16.0</t>
+          <t>46.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>20.45</t>
+          <t>20.05</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2196,17 +2196,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-6.79</t>
+          <t>-2.82</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>-2.89</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>22.57</t>
+          <t>17.65</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-6.41</t>
+          <t>-8.24</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2281,17 +2281,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2307,72 +2307,72 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>46.15</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>36.17</t>
+          <t>23.08</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-1.91</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-4.52</t>
+          <t>-3.90</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-2.41</t>
+          <t>-2.98</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-1.36</t>
+          <t>-1.65</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>20.46</t>
+          <t>20.44</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>21.43</t>
+          <t>21.27</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>21.96</t>
+          <t>21.92</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>22.26</t>
+          <t>22.29</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-15.32</t>
+          <t>-16.23</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-0.50</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-106.60</t>
+          <t>-106.88</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2392,41 +2392,41 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>30589.40922190202</t>
+          <t>30546.46834532374</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>326.0</t>
+          <t>922.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>861.4</t>
+          <t>840.4</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>702.8</t>
+          <t>714.3</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>2075.44</t>
+          <t>1889.2</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>158</t>
+          <t>126</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-203.7270186305573</t>
+          <t>-195.1459064225224</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>-176.23</v>
+        <v>-147.95</v>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>-13.53</t>
+          <t>-15.22</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2470,7 +2470,7 @@
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="BM5" t="inlineStr">
@@ -2490,7 +2490,7 @@
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
@@ -2500,7 +2500,7 @@
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>84.12</t>
+          <t>85.54</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>559</t>
+          <t>569</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2555,22 +2555,22 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>20.45</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>20.45</t>
+          <t>20.1</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>20.3</t>
+          <t>19.95</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>20.45</t>
+          <t>20.05</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-1.19</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2627,17 +2627,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-6.79</t>
+          <t>-4.87</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>-2.89</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>22.57</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2647,7 +2647,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -2712,17 +2712,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-1.95</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2738,62 +2738,62 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>23.08</t>
+          <t>46.15</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>28.41</t>
+          <t>36.17</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-4.33</t>
+          <t>-4.52</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-2.52</t>
+          <t>-2.41</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>-1.36</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>20.53</t>
+          <t>20.46</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>21.46</t>
+          <t>21.43</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>22.01</t>
+          <t>21.96</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>22.23</t>
+          <t>22.26</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-20.19</t>
+          <t>-15.32</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
@@ -2803,7 +2803,7 @@
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2813,7 +2813,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-106.34</t>
+          <t>-106.60</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2823,41 +2823,41 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>30589.40922190202</t>
+          <t>30546.46834532374</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>1362.0</t>
+          <t>326.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>800.4</t>
+          <t>861.4</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>791.6</t>
+          <t>702.8</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>2169.22</t>
+          <t>2075.44</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>158</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-208.7263475380736</t>
+          <t>-203.7270186305573</t>
         </is>
       </c>
       <c r="BC6" t="n">
-        <v>-146.48</v>
+        <v>-176.23</v>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
@@ -2901,7 +2901,7 @@
       </c>
       <c r="BL6" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="BM6" t="inlineStr">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BX6" t="inlineStr">
         <is>
-          <t>84.12</t>
+          <t>85.54</t>
         </is>
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>559</t>
+          <t>569</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>21.0</t>
+          <t>20.45</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>21.0</t>
+          <t>20.45</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>-1.19</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>36.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>20.7</t>
+          <t>20.45</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-8.09</t>
+          <t>-4.87</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>-2.89</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-32.18</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-5.26</t>
+          <t>-6.41</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>-1.95</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3169,62 +3169,62 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>39.29</t>
+          <t>23.08</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>20.71</t>
+          <t>28.41</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-4.13</t>
+          <t>-4.33</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-2.66</t>
+          <t>-2.52</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-0.54</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>20.6</t>
+          <t>20.53</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>21.49</t>
+          <t>21.46</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>22.08</t>
+          <t>22.01</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>22.19</t>
+          <t>22.23</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-25.12</t>
+          <t>-20.19</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
@@ -3234,7 +3234,7 @@
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-106.02</t>
+          <t>-106.34</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3254,41 +3254,41 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>30589.40922190202</t>
+          <t>30546.46834532374</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>747.0</t>
+          <t>1362.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>677.8</t>
+          <t>800.4</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>999.4</t>
+          <t>791.6</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>2614.76</t>
+          <t>2169.22</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-321</t>
+          <t>8</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-220.0436966054221</t>
+          <t>-208.7263475380736</t>
         </is>
       </c>
       <c r="BC7" t="n">
-        <v>-209.75</v>
+        <v>-146.48</v>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>-12.47</t>
+          <t>-13.53</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3332,7 +3332,7 @@
       </c>
       <c r="BL7" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="BM7" t="inlineStr">
@@ -3352,7 +3352,7 @@
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
@@ -3362,7 +3362,7 @@
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="BX7" t="inlineStr">
         <is>
-          <t>84.12</t>
+          <t>85.54</t>
         </is>
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>559</t>
+          <t>569</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3417,22 +3417,22 @@
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>20.6</t>
+          <t>21.0</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>20.95</t>
+          <t>21.0</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>20.55</t>
+          <t>20.3</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>20.7</t>
+          <t>20.45</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3464,12 +3464,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>41.0</t>
+          <t>36.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>20.55</t>
+          <t>20.7</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3489,17 +3489,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-7.31</t>
+          <t>-6.15</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>-2.89</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-33.22</t>
+          <t>-32.18</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3509,7 +3509,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -3564,7 +3564,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-5.95</t>
+          <t>-5.26</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3574,17 +3574,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-4.11</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3600,72 +3600,72 @@
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>22.86</t>
+          <t>39.29</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>19.66</t>
+          <t>20.71</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-4.71</t>
+          <t>-4.13</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-2.98</t>
+          <t>-2.66</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-0.54</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>20.49</t>
+          <t>20.6</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>21.5</t>
+          <t>21.49</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>22.16</t>
+          <t>22.08</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>22.16</t>
+          <t>22.19</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-36.40</t>
+          <t>-25.12</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>-0.50</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-105.65</t>
+          <t>-106.02</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3685,41 +3685,41 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>30589.40922190202</t>
+          <t>30546.46834532374</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>845.0</t>
+          <t>747.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>655.2</t>
+          <t>677.8</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>981.2</t>
+          <t>999.4</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>2840.22</t>
+          <t>2614.76</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-326</t>
+          <t>-321</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-221.9153182728739</t>
+          <t>-220.0436966054221</t>
         </is>
       </c>
       <c r="BC8" t="n">
-        <v>-226.75</v>
+        <v>-209.75</v>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>-13.11</t>
+          <t>-12.47</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -3763,7 +3763,7 @@
       </c>
       <c r="BL8" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="BM8" t="inlineStr">
@@ -3783,7 +3783,7 @@
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
@@ -3793,7 +3793,7 @@
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
@@ -3823,12 +3823,12 @@
       </c>
       <c r="BX8" t="inlineStr">
         <is>
-          <t>84.12</t>
+          <t>85.54</t>
         </is>
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>559</t>
+          <t>569</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -3848,22 +3848,22 @@
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>20.2</t>
+          <t>20.6</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>21.75</t>
+          <t>20.95</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>20.2</t>
+          <t>20.55</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>20.55</t>
+          <t>20.7</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-3.22</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>51.0</t>
+          <t>41.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>20.15</t>
+          <t>20.55</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3920,17 +3920,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-5.22</t>
+          <t>-5.38</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>-2.89</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-37.93</t>
+          <t>-33.22</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3940,7 +3940,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-7.78</t>
+          <t>-5.95</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-0.74</t>
+          <t>-4.11</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4031,72 +4031,72 @@
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>22.86</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>22.61</t>
+          <t>19.66</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-1.80</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-4.79</t>
+          <t>-4.71</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-2.96</t>
+          <t>-2.98</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>20.52</t>
+          <t>20.49</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>21.55</t>
+          <t>21.5</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>22.21</t>
+          <t>22.16</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>22.13</t>
+          <t>22.16</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-47.43</t>
+          <t>-36.40</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.50</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.37</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-105.13</t>
+          <t>-105.65</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4116,41 +4116,41 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>30589.40922190202</t>
+          <t>30546.46834532374</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>1027.0</t>
+          <t>845.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>588.2</t>
+          <t>655.2</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>947.7</t>
+          <t>981.2</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>2910.12</t>
+          <t>2840.22</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-359</t>
+          <t>-326</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-221.0362983393635</t>
+          <t>-221.9153182728739</t>
         </is>
       </c>
       <c r="BC9" t="n">
-        <v>-253.44</v>
+        <v>-226.75</v>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>-14.80</t>
+          <t>-13.11</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4194,7 +4194,7 @@
       </c>
       <c r="BL9" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="BM9" t="inlineStr">
@@ -4224,7 +4224,7 @@
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="BX9" t="inlineStr">
         <is>
-          <t>84.12</t>
+          <t>85.54</t>
         </is>
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>559</t>
+          <t>569</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4284,17 +4284,17 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>20.4</t>
+          <t>21.75</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>20.05</t>
+          <t>20.2</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>20.15</t>
+          <t>20.55</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4326,12 +4326,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-3.22</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>51.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4341,7 +4341,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>20.8</t>
+          <t>20.15</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4351,17 +4351,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-8.62</t>
+          <t>-3.33</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>-2.89</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-40.01</t>
+          <t>-37.93</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -4426,7 +4426,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-4.81</t>
+          <t>-7.78</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4436,17 +4436,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.74</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4462,12 +4462,12 @@
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>36.11</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
@@ -4477,57 +4477,57 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>0.10</t>
+          <t>-1.80</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-4.04</t>
+          <t>-4.79</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-2.72</t>
+          <t>-2.96</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.36</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>20.78</t>
+          <t>20.52</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>21.66</t>
+          <t>21.55</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>22.26</t>
+          <t>22.21</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>22.1</t>
+          <t>22.13</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-47.36</t>
+          <t>-47.43</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>-0.50</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4537,7 +4537,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-104.52</t>
+          <t>-105.13</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4547,41 +4547,41 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>30589.40922190202</t>
+          <t>30546.46834532374</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>21.0</t>
+          <t>1027.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>544.2</t>
+          <t>588.2</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>907.2</t>
+          <t>947.7</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>2976.72</t>
+          <t>2910.12</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-363</t>
+          <t>-359</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-215.145144320523</t>
+          <t>-221.0362983393635</t>
         </is>
       </c>
       <c r="BC10" t="n">
-        <v>-302.01</v>
+        <v>-253.44</v>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>-12.05</t>
+          <t>-14.80</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -4625,7 +4625,7 @@
       </c>
       <c r="BL10" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="BM10" t="inlineStr">
@@ -4645,17 +4645,17 @@
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="BX10" t="inlineStr">
         <is>
-          <t>84.12</t>
+          <t>85.54</t>
         </is>
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>559</t>
+          <t>569</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4710,22 +4710,22 @@
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>20.8</t>
+          <t>20.2</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>20.8</t>
+          <t>20.4</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>20.8</t>
+          <t>20.05</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>20.8</t>
+          <t>20.15</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>3.17</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>36.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4782,17 +4782,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-8.62</t>
+          <t>-6.67</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>-2.89</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-18.36</t>
+          <t>-40.01</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4802,7 +4802,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -4867,17 +4867,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2.46</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4893,72 +4893,72 @@
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>31.71</t>
+          <t>36.11</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>10.57</t>
+          <t>22.61</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-0.62</t>
+          <t>0.10</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-3.73</t>
+          <t>-4.04</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-2.59</t>
+          <t>-2.72</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>20.93</t>
+          <t>20.78</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>21.74</t>
+          <t>21.66</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>22.32</t>
+          <t>22.26</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>22.07</t>
+          <t>22.1</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-61.10</t>
+          <t>-47.36</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>-0.44</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4968,7 +4968,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-103.99</t>
+          <t>-104.52</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4978,41 +4978,41 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>30589.40922190202</t>
+          <t>30546.46834532374</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>749.0</t>
+          <t>21.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>782.8</t>
+          <t>544.2</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>958.8</t>
+          <t>907.2</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>3076.14</t>
+          <t>2976.72</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-176</t>
+          <t>-363</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-199.3512411554697</t>
+          <t>-215.145144320523</t>
         </is>
       </c>
       <c r="BC11" t="n">
-        <v>-252.83</v>
+        <v>-302.01</v>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
@@ -5056,7 +5056,7 @@
       </c>
       <c r="BL11" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="BM11" t="inlineStr">
@@ -5076,7 +5076,7 @@
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="BX11" t="inlineStr">
         <is>
-          <t>84.12</t>
+          <t>85.54</t>
         </is>
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>559</t>
+          <t>569</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5141,7 +5141,7 @@
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>20.5</t>
+          <t>20.8</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
@@ -5151,7 +5151,7 @@
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>20.3</t>
+          <t>20.8</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-2.74</t>
+          <t>3.17</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>31.0</t>
+          <t>36.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>20.15</t>
+          <t>20.8</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5213,17 +5213,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-5.22</t>
+          <t>-6.67</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>-2.89</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>35.06</t>
+          <t>-18.36</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5233,7 +5233,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -5288,7 +5288,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-7.78</t>
+          <t>-4.81</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5298,17 +5298,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>1.10</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-0.74</t>
+          <t>2.46</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5324,72 +5324,72 @@
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>31.71</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.57</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-4.73</t>
+          <t>-0.62</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-3.16</t>
+          <t>-3.73</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-2.36</t>
+          <t>-2.59</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>21.15</t>
+          <t>20.93</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>21.84</t>
+          <t>21.74</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>22.37</t>
+          <t>22.32</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>22.04</t>
+          <t>22.07</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-78.27</t>
+          <t>-61.10</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-103.38</t>
+          <t>-103.99</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5409,41 +5409,41 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>30589.40922190202</t>
+          <t>30546.46834532374</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>634.0</t>
+          <t>749.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>1321.0</t>
+          <t>782.8</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>978.1</t>
+          <t>958.8</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>3201.08</t>
+          <t>3076.14</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>342</t>
+          <t>-176</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-189.6276215728426</t>
+          <t>-199.3512411554697</t>
         </is>
       </c>
       <c r="BC12" t="n">
-        <v>-251.54</v>
+        <v>-252.83</v>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>-14.80</t>
+          <t>-12.05</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -5487,7 +5487,7 @@
       </c>
       <c r="BL12" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="BM12" t="inlineStr">
@@ -5507,7 +5507,7 @@
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -5517,7 +5517,7 @@
       </c>
       <c r="BR12" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="BS12" t="inlineStr">
@@ -5547,12 +5547,12 @@
       </c>
       <c r="BX12" t="inlineStr">
         <is>
-          <t>84.12</t>
+          <t>85.54</t>
         </is>
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>559</t>
+          <t>569</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5572,22 +5572,22 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>20.05</t>
+          <t>20.5</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>20.45</t>
+          <t>20.8</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>20.3</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>20.15</t>
+          <t>20.8</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
@@ -5619,12 +5619,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>112.0</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5634,7 +5634,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>201.0</t>
+          <t>204.5</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5649,12 +5649,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-1.67</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>28.98</t>
+          <t>40.09</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5664,7 +5664,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -5674,7 +5674,7 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>2025-11-20 00:00:00</t>
+          <t>2025-11-21 00:00:00</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -5714,7 +5714,7 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
@@ -5729,17 +5729,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11.76</t>
+          <t>26.35</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5750,17 +5750,17 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>112</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>57.14</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
@@ -5770,57 +5770,57 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>2.94</t>
+          <t>2.93</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>200.6</t>
+          <t>202.1</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>198.25</t>
+          <t>198.58</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>192.58</t>
+          <t>192.93</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>190.62</t>
+          <t>190.87</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>6.46</t>
+          <t>14.78</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>2.21</t>
+          <t>2.48</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>2.16</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5830,7 +5830,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-79.25</t>
+          <t>-78.46</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5840,45 +5840,45 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>28250.49639769452</t>
+          <t>28258.84748201439</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>10051.0</t>
+          <t>22703.0</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>19272.8</t>
+          <t>23070.4</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>14943.0</t>
+          <t>16467.7</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>10672.76</t>
+          <t>11056.48</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>4329</t>
+          <t>6602</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>796.5973747512926</t>
+          <t>917.3536697818137</t>
         </is>
       </c>
       <c r="BC13" t="n">
-        <v>1253.56</v>
+        <v>1581.51</v>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
@@ -5893,7 +5893,7 @@
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>4.69</t>
+          <t>6.51</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
@@ -5938,22 +5938,22 @@
       </c>
       <c r="BP13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>4.97</t>
+          <t>4.88</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
@@ -5963,7 +5963,7 @@
       </c>
       <c r="BU13" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>12.21</t>
         </is>
       </c>
       <c r="BV13" t="inlineStr">
@@ -5978,12 +5978,12 @@
       </c>
       <c r="BX13" t="inlineStr">
         <is>
-          <t>48.2</t>
+          <t>48.69</t>
         </is>
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>9559</t>
+          <t>9725</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
@@ -6003,22 +6003,22 @@
       </c>
       <c r="CC13" t="inlineStr">
         <is>
-          <t>199.5</t>
+          <t>202.0</t>
         </is>
       </c>
       <c r="CD13" t="inlineStr">
         <is>
+          <t>205.0</t>
+        </is>
+      </c>
+      <c r="CE13" t="inlineStr">
+        <is>
           <t>202.0</t>
         </is>
       </c>
-      <c r="CE13" t="inlineStr">
-        <is>
-          <t>198.5</t>
-        </is>
-      </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>201.0</t>
+          <t>204.5</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
@@ -6050,12 +6050,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-2.2</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>107.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6065,7 +6065,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>199.5</t>
+          <t>201.0</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6075,17 +6075,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-1.67</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>17.59</t>
+          <t>28.98</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6095,7 +6095,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -6105,7 +6105,7 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>2025-11-20 00:00:00</t>
+          <t>2025-11-21 00:00:00</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -6145,7 +6145,7 @@
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
@@ -6160,17 +6160,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>25.18</t>
+          <t>11.76</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>-2.00</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6181,77 +6181,77 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>112</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>35.71</t>
+          <t>57.14</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>78.57</t>
+          <t>64.29</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>2.96</t>
+          <t>2.94</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>200.0</t>
+          <t>200.6</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>197.98</t>
+          <t>198.25</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>192.28</t>
+          <t>192.58</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>190.44</t>
+          <t>190.62</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>7.56</t>
+          <t>6.46</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>2.21</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6261,7 +6261,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-79.59</t>
+          <t>-79.25</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6271,45 +6271,45 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>28250.49639769452</t>
+          <t>28258.84748201439</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>21601.0</t>
+          <t>10051.0</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>18457.8</t>
+          <t>19272.8</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>15697.4</t>
+          <t>14943.0</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>10622.98</t>
+          <t>10672.76</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>2760</t>
+          <t>4329</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>713.5128205865296</t>
+          <t>796.5973747512926</t>
         </is>
       </c>
       <c r="BC14" t="n">
-        <v>2095.86</v>
+        <v>1253.56</v>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
@@ -6324,7 +6324,7 @@
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>3.91</t>
+          <t>4.69</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
@@ -6369,22 +6369,22 @@
       </c>
       <c r="BP14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
         <is>
-          <t>1.89</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>4.97</t>
+          <t>4.88</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
@@ -6394,7 +6394,7 @@
       </c>
       <c r="BU14" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>12.21</t>
         </is>
       </c>
       <c r="BV14" t="inlineStr">
@@ -6409,12 +6409,12 @@
       </c>
       <c r="BX14" t="inlineStr">
         <is>
-          <t>48.2</t>
+          <t>48.69</t>
         </is>
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>9559</t>
+          <t>9725</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
@@ -6434,22 +6434,22 @@
       </c>
       <c r="CC14" t="inlineStr">
         <is>
-          <t>205.0</t>
+          <t>199.5</t>
         </is>
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>205.0</t>
+          <t>202.0</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>198.0</t>
+          <t>198.5</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>199.5</t>
+          <t>201.0</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
@@ -6481,12 +6481,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>-2.2</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>107.0</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6496,7 +6496,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>204.0</t>
+          <t>199.5</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6506,17 +6506,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-1.49</t>
+          <t>2.44</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-1.67</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>9.50</t>
+          <t>17.59</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6526,7 +6526,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -6536,7 +6536,7 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>2025-11-20 00:00:00</t>
+          <t>2025-11-21 00:00:00</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -6576,7 +6576,7 @@
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
@@ -6591,17 +6591,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>31.53</t>
+          <t>25.18</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>-2.00</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6612,32 +6612,32 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>112</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>35.71</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>82.05</t>
+          <t>78.57</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
@@ -6647,240 +6647,240 @@
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
+          <t>200.0</t>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>197.98</t>
+        </is>
+      </c>
+      <c r="AN15" t="inlineStr">
+        <is>
+          <t>192.28</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>190.44</t>
+        </is>
+      </c>
+      <c r="AP15" t="inlineStr">
+        <is>
+          <t>7.56</t>
+        </is>
+      </c>
+      <c r="AQ15" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="AR15" t="inlineStr">
+        <is>
+          <t>2.04</t>
+        </is>
+      </c>
+      <c r="AS15" t="inlineStr">
+        <is>
+          <t>10.01</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr">
+        <is>
+          <t>-79.59</t>
+        </is>
+      </c>
+      <c r="AU15" t="inlineStr">
+        <is>
+          <t>2025/11/14</t>
+        </is>
+      </c>
+      <c r="AV15" t="inlineStr">
+        <is>
+          <t>28258.84748201439</t>
+        </is>
+      </c>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>21601.0</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>18457.8</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>15697.4</t>
+        </is>
+      </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>10622.98</t>
+        </is>
+      </c>
+      <c r="BA15" t="inlineStr">
+        <is>
+          <t>2760</t>
+        </is>
+      </c>
+      <c r="BB15" t="inlineStr">
+        <is>
+          <t>713.5128205865296</t>
+        </is>
+      </c>
+      <c r="BC15" t="n">
+        <v>2095.86</v>
+      </c>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>2025-11-21</t>
+        </is>
+      </c>
+      <c r="BE15" t="inlineStr">
+        <is>
+          <t>192.0</t>
+        </is>
+      </c>
+      <c r="BF15" t="inlineStr">
+        <is>
+          <t>2025/10/14</t>
+        </is>
+      </c>
+      <c r="BG15" t="inlineStr">
+        <is>
+          <t>3.91</t>
+        </is>
+      </c>
+      <c r="BH15" t="inlineStr">
+        <is>
+          <t>鼎翰</t>
+        </is>
+      </c>
+      <c r="BI15" t="inlineStr">
+        <is>
+          <t>鼎翰</t>
+        </is>
+      </c>
+      <c r="BJ15" t="inlineStr">
+        <is>
+          <t>電腦及週邊設備業</t>
+        </is>
+      </c>
+      <c r="BK15" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BL15" t="inlineStr">
+        <is>
+          <t>0.57</t>
+        </is>
+      </c>
+      <c r="BM15" t="inlineStr">
+        <is>
+          <t>-11.45161899724185</t>
+        </is>
+      </c>
+      <c r="BN15" t="inlineStr">
+        <is>
+          <t>22.56717409239306</t>
+        </is>
+      </c>
+      <c r="BO15" t="inlineStr">
+        <is>
+          <t>38.82556207928187</t>
+        </is>
+      </c>
+      <c r="BP15" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BQ15" t="inlineStr">
+        <is>
+          <t>價-量增</t>
+        </is>
+      </c>
+      <c r="BR15" t="inlineStr">
+        <is>
+          <t>1.89</t>
+        </is>
+      </c>
+      <c r="BS15" t="inlineStr">
+        <is>
+          <t>4.88</t>
+        </is>
+      </c>
+      <c r="BT15" t="inlineStr">
+        <is>
+          <t>57.78</t>
+        </is>
+      </c>
+      <c r="BU15" t="inlineStr">
+        <is>
+          <t>12.21</t>
+        </is>
+      </c>
+      <c r="BV15" t="inlineStr">
+        <is>
+          <t>33.69%</t>
+        </is>
+      </c>
+      <c r="BW15" t="inlineStr">
+        <is>
+          <t>11.08%</t>
+        </is>
+      </c>
+      <c r="BX15" t="inlineStr">
+        <is>
+          <t>48.69</t>
+        </is>
+      </c>
+      <c r="BY15" t="inlineStr">
+        <is>
+          <t>9725</t>
+        </is>
+      </c>
+      <c r="BZ15" t="inlineStr">
+        <is>
+          <t>條碼印表機及零配件52.71%、印表機各式標籤紙及其耗材41.09%、企業行動電腦6.20% (2024年)</t>
+        </is>
+      </c>
+      <c r="CA15" t="inlineStr">
+        <is>
+          <t>鼎翰-電腦及週邊設備業-上櫃</t>
+        </is>
+      </c>
+      <c r="CB15" t="inlineStr">
+        <is>
+          <t>電腦及週邊設備業右下上櫃</t>
+        </is>
+      </c>
+      <c r="CC15" t="inlineStr">
+        <is>
+          <t>205.0</t>
+        </is>
+      </c>
+      <c r="CD15" t="inlineStr">
+        <is>
+          <t>205.0</t>
+        </is>
+      </c>
+      <c r="CE15" t="inlineStr">
+        <is>
+          <t>198.0</t>
+        </is>
+      </c>
+      <c r="CF15" t="inlineStr">
+        <is>
           <t>199.5</t>
-        </is>
-      </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>197.7</t>
-        </is>
-      </c>
-      <c r="AN15" t="inlineStr">
-        <is>
-          <t>192.01</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>190.29</t>
-        </is>
-      </c>
-      <c r="AP15" t="inlineStr">
-        <is>
-          <t>14.82</t>
-        </is>
-      </c>
-      <c r="AQ15" t="inlineStr">
-        <is>
-          <t>2.30</t>
-        </is>
-      </c>
-      <c r="AR15" t="inlineStr">
-        <is>
-          <t>2.01</t>
-        </is>
-      </c>
-      <c r="AS15" t="inlineStr">
-        <is>
-          <t>10.01</t>
-        </is>
-      </c>
-      <c r="AT15" t="inlineStr">
-        <is>
-          <t>-79.98</t>
-        </is>
-      </c>
-      <c r="AU15" t="inlineStr">
-        <is>
-          <t>2025/11/14</t>
-        </is>
-      </c>
-      <c r="AV15" t="inlineStr">
-        <is>
-          <t>28250.49639769452</t>
-        </is>
-      </c>
-      <c r="AW15" t="inlineStr">
-        <is>
-          <t>27388.0</t>
-        </is>
-      </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>15822.8</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr">
-        <is>
-          <t>14450.7</t>
-        </is>
-      </c>
-      <c r="AZ15" t="inlineStr">
-        <is>
-          <t>10277.46</t>
-        </is>
-      </c>
-      <c r="BA15" t="inlineStr">
-        <is>
-          <t>1372</t>
-        </is>
-      </c>
-      <c r="BB15" t="inlineStr">
-        <is>
-          <t>462.1765112122318</t>
-        </is>
-      </c>
-      <c r="BC15" t="n">
-        <v>1986.8</v>
-      </c>
-      <c r="BD15" t="inlineStr">
-        <is>
-          <t>2025-11-20</t>
-        </is>
-      </c>
-      <c r="BE15" t="inlineStr">
-        <is>
-          <t>192.0</t>
-        </is>
-      </c>
-      <c r="BF15" t="inlineStr">
-        <is>
-          <t>2025/10/14</t>
-        </is>
-      </c>
-      <c r="BG15" t="inlineStr">
-        <is>
-          <t>6.25</t>
-        </is>
-      </c>
-      <c r="BH15" t="inlineStr">
-        <is>
-          <t>鼎翰</t>
-        </is>
-      </c>
-      <c r="BI15" t="inlineStr">
-        <is>
-          <t>鼎翰</t>
-        </is>
-      </c>
-      <c r="BJ15" t="inlineStr">
-        <is>
-          <t>電腦及週邊設備業</t>
-        </is>
-      </c>
-      <c r="BK15" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BL15" t="inlineStr">
-        <is>
-          <t>0.57</t>
-        </is>
-      </c>
-      <c r="BM15" t="inlineStr">
-        <is>
-          <t>-11.45161899724185</t>
-        </is>
-      </c>
-      <c r="BN15" t="inlineStr">
-        <is>
-          <t>22.56717409239306</t>
-        </is>
-      </c>
-      <c r="BO15" t="inlineStr">
-        <is>
-          <t>38.82556207928187</t>
-        </is>
-      </c>
-      <c r="BP15" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BQ15" t="inlineStr">
-        <is>
-          <t>價-量增</t>
-        </is>
-      </c>
-      <c r="BR15" t="inlineStr">
-        <is>
-          <t>1.93</t>
-        </is>
-      </c>
-      <c r="BS15" t="inlineStr">
-        <is>
-          <t>4.97</t>
-        </is>
-      </c>
-      <c r="BT15" t="inlineStr">
-        <is>
-          <t>57.78</t>
-        </is>
-      </c>
-      <c r="BU15" t="inlineStr">
-        <is>
-          <t>12.0</t>
-        </is>
-      </c>
-      <c r="BV15" t="inlineStr">
-        <is>
-          <t>33.69%</t>
-        </is>
-      </c>
-      <c r="BW15" t="inlineStr">
-        <is>
-          <t>11.08%</t>
-        </is>
-      </c>
-      <c r="BX15" t="inlineStr">
-        <is>
-          <t>48.2</t>
-        </is>
-      </c>
-      <c r="BY15" t="inlineStr">
-        <is>
-          <t>9559</t>
-        </is>
-      </c>
-      <c r="BZ15" t="inlineStr">
-        <is>
-          <t>條碼印表機及零配件52.71%、印表機各式標籤紙及其耗材41.09%、企業行動電腦6.20% (2024年)</t>
-        </is>
-      </c>
-      <c r="CA15" t="inlineStr">
-        <is>
-          <t>鼎翰-電腦及週邊設備業-上櫃</t>
-        </is>
-      </c>
-      <c r="CB15" t="inlineStr">
-        <is>
-          <t>電腦及週邊設備業右下上櫃</t>
-        </is>
-      </c>
-      <c r="CC15" t="inlineStr">
-        <is>
-          <t>201.5</t>
-        </is>
-      </c>
-      <c r="CD15" t="inlineStr">
-        <is>
-          <t>206.5</t>
-        </is>
-      </c>
-      <c r="CE15" t="inlineStr">
-        <is>
-          <t>201.5</t>
-        </is>
-      </c>
-      <c r="CF15" t="inlineStr">
-        <is>
-          <t>204.0</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
@@ -6912,12 +6912,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>167.0</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6927,74 +6927,74 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
+          <t>204.0</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>0.24</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>-1.67</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>9.50</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>-50.0</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>2025-11-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>2025-11-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>2025-10-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>2025-11-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
           <t>201.5</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>-0.25</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>-0.58</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>21.03</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>2025-11-14</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>-65.0</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>2025-11-14 00:00:00</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>2025-11-20 00:00:00</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>2025-10-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>2025-11-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q16" t="inlineStr">
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
         <is>
           <t>201.5</t>
         </is>
       </c>
-      <c r="R16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>201.5</t>
-        </is>
-      </c>
       <c r="T16" t="inlineStr">
         <is>
           <t>195.5</t>
@@ -7007,7 +7007,7 @@
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
@@ -7022,17 +7022,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>39.29</t>
+          <t>31.53</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7043,12 +7043,12 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>112</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
@@ -7058,195 +7058,195 @@
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>69.23</t>
+          <t>82.05</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>2.87</t>
+          <t>2.96</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>198.8</t>
+          <t>199.5</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>197.15</t>
+          <t>197.7</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>191.65</t>
+          <t>192.01</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>190.08</t>
+          <t>190.29</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>14.82</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
+          <t>2.01</t>
+        </is>
+      </c>
+      <c r="AS16" t="inlineStr">
+        <is>
+          <t>10.01</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr">
+        <is>
+          <t>-79.98</t>
+        </is>
+      </c>
+      <c r="AU16" t="inlineStr">
+        <is>
+          <t>2025/11/14</t>
+        </is>
+      </c>
+      <c r="AV16" t="inlineStr">
+        <is>
+          <t>28258.84748201439</t>
+        </is>
+      </c>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>27388.0</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>15822.8</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>14450.7</t>
+        </is>
+      </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>10277.46</t>
+        </is>
+      </c>
+      <c r="BA16" t="inlineStr">
+        <is>
+          <t>1372</t>
+        </is>
+      </c>
+      <c r="BB16" t="inlineStr">
+        <is>
+          <t>462.1765112122318</t>
+        </is>
+      </c>
+      <c r="BC16" t="n">
+        <v>1986.8</v>
+      </c>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>2025-11-21</t>
+        </is>
+      </c>
+      <c r="BE16" t="inlineStr">
+        <is>
+          <t>192.0</t>
+        </is>
+      </c>
+      <c r="BF16" t="inlineStr">
+        <is>
+          <t>2025/10/14</t>
+        </is>
+      </c>
+      <c r="BG16" t="inlineStr">
+        <is>
+          <t>6.25</t>
+        </is>
+      </c>
+      <c r="BH16" t="inlineStr">
+        <is>
+          <t>鼎翰</t>
+        </is>
+      </c>
+      <c r="BI16" t="inlineStr">
+        <is>
+          <t>鼎翰</t>
+        </is>
+      </c>
+      <c r="BJ16" t="inlineStr">
+        <is>
+          <t>電腦及週邊設備業</t>
+        </is>
+      </c>
+      <c r="BK16" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BL16" t="inlineStr">
+        <is>
+          <t>0.57</t>
+        </is>
+      </c>
+      <c r="BM16" t="inlineStr">
+        <is>
+          <t>-11.45161899724185</t>
+        </is>
+      </c>
+      <c r="BN16" t="inlineStr">
+        <is>
+          <t>22.56717409239306</t>
+        </is>
+      </c>
+      <c r="BO16" t="inlineStr">
+        <is>
+          <t>38.82556207928187</t>
+        </is>
+      </c>
+      <c r="BP16" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BQ16" t="inlineStr">
+        <is>
+          <t>價-量增</t>
+        </is>
+      </c>
+      <c r="BR16" t="inlineStr">
+        <is>
           <t>1.93</t>
         </is>
       </c>
-      <c r="AS16" t="inlineStr">
-        <is>
-          <t>10.01</t>
-        </is>
-      </c>
-      <c r="AT16" t="inlineStr">
-        <is>
-          <t>-80.72</t>
-        </is>
-      </c>
-      <c r="AU16" t="inlineStr">
-        <is>
-          <t>2025/11/14</t>
-        </is>
-      </c>
-      <c r="AV16" t="inlineStr">
-        <is>
-          <t>28250.49639769452</t>
-        </is>
-      </c>
-      <c r="AW16" t="inlineStr">
-        <is>
-          <t>33609.0</t>
-        </is>
-      </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>14692.0</t>
-        </is>
-      </c>
-      <c r="AY16" t="inlineStr">
-        <is>
-          <t>12138.8</t>
-        </is>
-      </c>
-      <c r="AZ16" t="inlineStr">
-        <is>
-          <t>9836.78</t>
-        </is>
-      </c>
-      <c r="BA16" t="inlineStr">
-        <is>
-          <t>2553</t>
-        </is>
-      </c>
-      <c r="BB16" t="inlineStr">
-        <is>
-          <t>184.9729413194776</t>
-        </is>
-      </c>
-      <c r="BC16" t="n">
-        <v>1139.99</v>
-      </c>
-      <c r="BD16" t="inlineStr">
-        <is>
-          <t>2025-11-20</t>
-        </is>
-      </c>
-      <c r="BE16" t="inlineStr">
-        <is>
-          <t>192.0</t>
-        </is>
-      </c>
-      <c r="BF16" t="inlineStr">
-        <is>
-          <t>2025/10/14</t>
-        </is>
-      </c>
-      <c r="BG16" t="inlineStr">
-        <is>
-          <t>4.95</t>
-        </is>
-      </c>
-      <c r="BH16" t="inlineStr">
-        <is>
-          <t>鼎翰</t>
-        </is>
-      </c>
-      <c r="BI16" t="inlineStr">
-        <is>
-          <t>鼎翰</t>
-        </is>
-      </c>
-      <c r="BJ16" t="inlineStr">
-        <is>
-          <t>電腦及週邊設備業</t>
-        </is>
-      </c>
-      <c r="BK16" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BL16" t="inlineStr">
-        <is>
-          <t>0.57</t>
-        </is>
-      </c>
-      <c r="BM16" t="inlineStr">
-        <is>
-          <t>-11.45161899724185</t>
-        </is>
-      </c>
-      <c r="BN16" t="inlineStr">
-        <is>
-          <t>22.56717409239306</t>
-        </is>
-      </c>
-      <c r="BO16" t="inlineStr">
-        <is>
-          <t>38.82556207928187</t>
-        </is>
-      </c>
-      <c r="BP16" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BQ16" t="inlineStr">
-        <is>
-          <t>價漲量增</t>
-        </is>
-      </c>
-      <c r="BR16" t="inlineStr">
-        <is>
-          <t>1.91</t>
-        </is>
-      </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>4.97</t>
+          <t>4.88</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
@@ -7256,7 +7256,7 @@
       </c>
       <c r="BU16" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>12.21</t>
         </is>
       </c>
       <c r="BV16" t="inlineStr">
@@ -7271,12 +7271,12 @@
       </c>
       <c r="BX16" t="inlineStr">
         <is>
-          <t>48.2</t>
+          <t>48.69</t>
         </is>
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>9559</t>
+          <t>9725</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
@@ -7296,22 +7296,22 @@
       </c>
       <c r="CC16" t="inlineStr">
         <is>
-          <t>199.0</t>
+          <t>201.5</t>
         </is>
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>202.5</t>
+          <t>206.5</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>198.5</t>
+          <t>201.5</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>201.5</t>
+          <t>204.0</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
@@ -7343,12 +7343,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>19.0</t>
+          <t>167.0</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7358,7 +7358,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>197.0</t>
+          <t>201.5</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7368,27 +7368,27 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-1.67</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>21.03</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -7398,7 +7398,7 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>2025-11-20 00:00:00</t>
+          <t>2025-11-21 00:00:00</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -7423,7 +7423,7 @@
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>201.5</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
@@ -7438,7 +7438,7 @@
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
@@ -7453,17 +7453,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>4.47</t>
+          <t>39.29</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>-1.27</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7474,177 +7474,177 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>112</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>46.15</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>51.28</t>
+          <t>69.23</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
+          <t>0.84</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>2.87</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>0.83</t>
+        </is>
+      </c>
+      <c r="AL17" t="inlineStr">
+        <is>
+          <t>198.8</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>197.15</t>
+        </is>
+      </c>
+      <c r="AN17" t="inlineStr">
+        <is>
+          <t>191.65</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>190.08</t>
+        </is>
+      </c>
+      <c r="AP17" t="inlineStr">
+        <is>
+          <t>0.64</t>
+        </is>
+      </c>
+      <c r="AQ17" t="inlineStr">
+        <is>
+          <t>1.94</t>
+        </is>
+      </c>
+      <c r="AR17" t="inlineStr">
+        <is>
+          <t>1.93</t>
+        </is>
+      </c>
+      <c r="AS17" t="inlineStr">
+        <is>
+          <t>10.01</t>
+        </is>
+      </c>
+      <c r="AT17" t="inlineStr">
+        <is>
+          <t>-80.72</t>
+        </is>
+      </c>
+      <c r="AU17" t="inlineStr">
+        <is>
+          <t>2025/11/14</t>
+        </is>
+      </c>
+      <c r="AV17" t="inlineStr">
+        <is>
+          <t>28258.84748201439</t>
+        </is>
+      </c>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>33609.0</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>14692.0</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>12138.8</t>
+        </is>
+      </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>9836.78</t>
+        </is>
+      </c>
+      <c r="BA17" t="inlineStr">
+        <is>
+          <t>2553</t>
+        </is>
+      </c>
+      <c r="BB17" t="inlineStr">
+        <is>
+          <t>184.9729413194776</t>
+        </is>
+      </c>
+      <c r="BC17" t="n">
+        <v>1139.99</v>
+      </c>
+      <c r="BD17" t="inlineStr">
+        <is>
+          <t>2025-11-21</t>
+        </is>
+      </c>
+      <c r="BE17" t="inlineStr">
+        <is>
+          <t>192.0</t>
+        </is>
+      </c>
+      <c r="BF17" t="inlineStr">
+        <is>
+          <t>2025/10/14</t>
+        </is>
+      </c>
+      <c r="BG17" t="inlineStr">
+        <is>
+          <t>4.95</t>
+        </is>
+      </c>
+      <c r="BH17" t="inlineStr">
+        <is>
+          <t>鼎翰</t>
+        </is>
+      </c>
+      <c r="BI17" t="inlineStr">
+        <is>
+          <t>鼎翰</t>
+        </is>
+      </c>
+      <c r="BJ17" t="inlineStr">
+        <is>
+          <t>電腦及週邊設備業</t>
+        </is>
+      </c>
+      <c r="BK17" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BL17" t="inlineStr">
+        <is>
           <t>0.57</t>
         </is>
       </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>2.84</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>0.70</t>
-        </is>
-      </c>
-      <c r="AL17" t="inlineStr">
-        <is>
-          <t>197.9</t>
-        </is>
-      </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>196.78</t>
-        </is>
-      </c>
-      <c r="AN17" t="inlineStr">
-        <is>
-          <t>191.34</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>190.02</t>
-        </is>
-      </c>
-      <c r="AP17" t="inlineStr">
-        <is>
-          <t>-11.24</t>
-        </is>
-      </c>
-      <c r="AQ17" t="inlineStr">
-        <is>
-          <t>1.71</t>
-        </is>
-      </c>
-      <c r="AR17" t="inlineStr">
-        <is>
-          <t>1.93</t>
-        </is>
-      </c>
-      <c r="AS17" t="inlineStr">
-        <is>
-          <t>10.01</t>
-        </is>
-      </c>
-      <c r="AT17" t="inlineStr">
-        <is>
-          <t>-80.75</t>
-        </is>
-      </c>
-      <c r="AU17" t="inlineStr">
-        <is>
-          <t>2025/11/14</t>
-        </is>
-      </c>
-      <c r="AV17" t="inlineStr">
-        <is>
-          <t>28250.49639769452</t>
-        </is>
-      </c>
-      <c r="AW17" t="inlineStr">
-        <is>
-          <t>3715.0</t>
-        </is>
-      </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>9865.0</t>
-        </is>
-      </c>
-      <c r="AY17" t="inlineStr">
-        <is>
-          <t>9864.3</t>
-        </is>
-      </c>
-      <c r="AZ17" t="inlineStr">
-        <is>
-          <t>9269.96</t>
-        </is>
-      </c>
-      <c r="BA17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BB17" t="inlineStr">
-        <is>
-          <t>11.33269122891031</t>
-        </is>
-      </c>
-      <c r="BC17" t="n">
-        <v>-776.97</v>
-      </c>
-      <c r="BD17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BE17" t="inlineStr">
-        <is>
-          <t>192.0</t>
-        </is>
-      </c>
-      <c r="BF17" t="inlineStr">
-        <is>
-          <t>2025/10/14</t>
-        </is>
-      </c>
-      <c r="BG17" t="inlineStr">
-        <is>
-          <t>2.60</t>
-        </is>
-      </c>
-      <c r="BH17" t="inlineStr">
-        <is>
-          <t>鼎翰</t>
-        </is>
-      </c>
-      <c r="BI17" t="inlineStr">
-        <is>
-          <t>鼎翰</t>
-        </is>
-      </c>
-      <c r="BJ17" t="inlineStr">
-        <is>
-          <t>電腦及週邊設備業</t>
-        </is>
-      </c>
-      <c r="BK17" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BL17" t="inlineStr">
-        <is>
-          <t>0.57</t>
-        </is>
-      </c>
       <c r="BM17" t="inlineStr">
         <is>
           <t>-11.45161899724185</t>
@@ -7662,22 +7662,22 @@
       </c>
       <c r="BP17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>4.97</t>
+          <t>4.88</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
@@ -7687,7 +7687,7 @@
       </c>
       <c r="BU17" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>12.21</t>
         </is>
       </c>
       <c r="BV17" t="inlineStr">
@@ -7702,12 +7702,12 @@
       </c>
       <c r="BX17" t="inlineStr">
         <is>
-          <t>48.2</t>
+          <t>48.69</t>
         </is>
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>9559</t>
+          <t>9725</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
@@ -7727,22 +7727,22 @@
       </c>
       <c r="CC17" t="inlineStr">
         <is>
-          <t>199.5</t>
+          <t>199.0</t>
         </is>
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>199.5</t>
+          <t>202.5</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>197.0</t>
+          <t>198.5</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>197.0</t>
+          <t>201.5</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
@@ -7774,12 +7774,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>19.0</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7789,7 +7789,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>198.0</t>
+          <t>197.0</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7799,17 +7799,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>3.67</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-1.67</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7819,7 +7819,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -7829,7 +7829,7 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>2025-11-20 00:00:00</t>
+          <t>2025-11-21 00:00:00</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
@@ -7884,17 +7884,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>7.06</t>
+          <t>4.47</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>-1.27</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7905,77 +7905,77 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>112</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>61.54</t>
+          <t>46.15</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>69.23</t>
+          <t>51.28</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>0.80</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>2.85</t>
+          <t>2.84</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>0.62</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>198.2</t>
+          <t>197.9</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>196.62</t>
+          <t>196.78</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>191.17</t>
+          <t>191.34</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>189.99</t>
+          <t>190.02</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>-6.74</t>
+          <t>-11.24</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -7985,7 +7985,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-80.21</t>
+          <t>-80.75</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7995,41 +7995,41 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>28250.49639769452</t>
+          <t>28258.84748201439</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>5976.0</t>
+          <t>3715.0</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>10613.2</t>
+          <t>9865.0</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>10254.6</t>
+          <t>9864.3</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>9315.64</t>
+          <t>9269.96</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>358</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>154.6608857258293</t>
+          <t>11.33269122891031</t>
         </is>
       </c>
       <c r="BC18" t="n">
-        <v>-284.82</v>
+        <v>-776.97</v>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
@@ -8048,7 +8048,7 @@
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>3.12</t>
+          <t>2.60</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
@@ -8093,22 +8093,22 @@
       </c>
       <c r="BP18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>4.97</t>
+          <t>4.88</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
@@ -8118,7 +8118,7 @@
       </c>
       <c r="BU18" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>12.21</t>
         </is>
       </c>
       <c r="BV18" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="BX18" t="inlineStr">
         <is>
-          <t>48.2</t>
+          <t>48.69</t>
         </is>
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>9559</t>
+          <t>9725</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
@@ -8158,22 +8158,22 @@
       </c>
       <c r="CC18" t="inlineStr">
         <is>
+          <t>199.5</t>
+        </is>
+      </c>
+      <c r="CD18" t="inlineStr">
+        <is>
+          <t>199.5</t>
+        </is>
+      </c>
+      <c r="CE18" t="inlineStr">
+        <is>
           <t>197.0</t>
         </is>
       </c>
-      <c r="CD18" t="inlineStr">
-        <is>
-          <t>198.5</t>
-        </is>
-      </c>
-      <c r="CE18" t="inlineStr">
+      <c r="CF18" t="inlineStr">
         <is>
           <t>197.0</t>
-        </is>
-      </c>
-      <c r="CF18" t="inlineStr">
-        <is>
-          <t>198.0</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
@@ -8205,12 +8205,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-1.75</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>42.0</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8220,7 +8220,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>197.0</t>
+          <t>198.0</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8230,17 +8230,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>3.18</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-1.67</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>16.90</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8250,7 +8250,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -8260,7 +8260,7 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>2025-11-20 00:00:00</t>
+          <t>2025-11-21 00:00:00</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
@@ -8315,17 +8315,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>9.88</t>
+          <t>7.06</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>-1.78</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8336,77 +8336,77 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>112</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>46.15</t>
+          <t>61.54</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>70.94</t>
+          <t>69.23</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>0.60</t>
+          <t>0.80</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>2.8</t>
+          <t>2.85</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>197.5</t>
+          <t>198.2</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>196.32</t>
+          <t>196.62</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>190.97</t>
+          <t>191.17</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>189.94</t>
+          <t>189.99</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>-5.98</t>
+          <t>-6.74</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>1.89</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8416,7 +8416,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-79.87</t>
+          <t>-80.21</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8426,41 +8426,41 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>28250.49639769452</t>
+          <t>28258.84748201439</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>8426.0</t>
+          <t>5976.0</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>12937.0</t>
+          <t>10613.2</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>11067.0</t>
+          <t>10254.6</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>9335.32</t>
+          <t>9315.64</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>1870</t>
+          <t>358</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>234.5662547700167</t>
+          <t>154.6608857258293</t>
         </is>
       </c>
       <c r="BC19" t="n">
-        <v>186.18</v>
+        <v>-284.82</v>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
@@ -8479,7 +8479,7 @@
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>2.60</t>
+          <t>3.12</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">
@@ -8524,7 +8524,7 @@
       </c>
       <c r="BP19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ19" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="BR19" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>4.97</t>
+          <t>4.88</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
@@ -8549,7 +8549,7 @@
       </c>
       <c r="BU19" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>12.21</t>
         </is>
       </c>
       <c r="BV19" t="inlineStr">
@@ -8564,12 +8564,12 @@
       </c>
       <c r="BX19" t="inlineStr">
         <is>
-          <t>48.2</t>
+          <t>48.69</t>
         </is>
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>9559</t>
+          <t>9725</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
@@ -8589,12 +8589,12 @@
       </c>
       <c r="CC19" t="inlineStr">
         <is>
-          <t>200.5</t>
+          <t>197.0</t>
         </is>
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>200.5</t>
+          <t>198.5</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
@@ -8604,7 +8604,7 @@
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>197.0</t>
+          <t>198.0</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
@@ -8636,12 +8636,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>-1.75</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>108.0</t>
+          <t>42.0</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8651,7 +8651,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>200.5</t>
+          <t>197.0</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8661,17 +8661,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>3.67</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-1.67</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>11.96</t>
+          <t>16.90</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8681,7 +8681,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -8691,7 +8691,7 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>2025-11-20 00:00:00</t>
+          <t>2025-11-21 00:00:00</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
@@ -8746,17 +8746,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>25.41</t>
+          <t>9.88</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>-0.74</t>
+          <t>-1.78</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8767,77 +8767,77 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>112</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>46.15</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>82.83</t>
+          <t>70.94</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.60</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>2.72</t>
+          <t>2.8</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>196.9</t>
+          <t>197.5</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>196.0</t>
+          <t>196.32</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>190.81</t>
+          <t>190.97</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>189.91</t>
+          <t>189.94</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>-5.98</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>1.89</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8847,7 +8847,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-79.57</t>
+          <t>-79.87</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8857,41 +8857,41 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>28250.49639769452</t>
+          <t>28258.84748201439</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>21734.0</t>
+          <t>8426.0</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>13078.6</t>
+          <t>12937.0</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>11681.7</t>
+          <t>11067.0</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>9341.52</t>
+          <t>9335.32</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>1396</t>
+          <t>1870</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>243.363716734609</t>
+          <t>234.5662547700167</t>
         </is>
       </c>
       <c r="BC20" t="n">
-        <v>589.89</v>
+        <v>186.18</v>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
@@ -8910,7 +8910,7 @@
       </c>
       <c r="BG20" t="inlineStr">
         <is>
-          <t>4.43</t>
+          <t>2.60</t>
         </is>
       </c>
       <c r="BH20" t="inlineStr">
@@ -8955,22 +8955,22 @@
       </c>
       <c r="BP20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>4.97</t>
+          <t>4.88</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
@@ -8980,7 +8980,7 @@
       </c>
       <c r="BU20" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>12.21</t>
         </is>
       </c>
       <c r="BV20" t="inlineStr">
@@ -8995,12 +8995,12 @@
       </c>
       <c r="BX20" t="inlineStr">
         <is>
-          <t>48.2</t>
+          <t>48.69</t>
         </is>
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>9559</t>
+          <t>9725</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
@@ -9020,22 +9020,22 @@
       </c>
       <c r="CC20" t="inlineStr">
         <is>
-          <t>203.5</t>
+          <t>200.5</t>
         </is>
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>203.5</t>
+          <t>200.5</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>199.0</t>
+          <t>197.0</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>200.5</t>
+          <t>197.0</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
@@ -9067,12 +9067,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>48.0</t>
+          <t>108.0</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9082,7 +9082,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>197.0</t>
+          <t>200.5</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9092,17 +9092,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-1.67</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>-10.99</t>
+          <t>11.96</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9112,7 +9112,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -9122,7 +9122,7 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>2025-11-20 00:00:00</t>
+          <t>2025-11-21 00:00:00</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
@@ -9177,17 +9177,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11.29</t>
+          <t>25.41</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>-0.74</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9198,72 +9198,72 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>112</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>52.27</t>
+          <t>82.83</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>2.72</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
+          <t>196.9</t>
+        </is>
+      </c>
+      <c r="AM21" t="inlineStr">
+        <is>
           <t>196.0</t>
         </is>
       </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>195.48</t>
-        </is>
-      </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>190.59</t>
+          <t>190.81</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>189.82</t>
+          <t>189.91</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>-11.56</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
@@ -9278,7 +9278,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-79.53</t>
+          <t>-79.57</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9288,41 +9288,41 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>28250.49639769452</t>
+          <t>28258.84748201439</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>9474.0</t>
+          <t>21734.0</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>9585.6</t>
+          <t>13078.6</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>10769.2</t>
+          <t>11681.7</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>9013.74</t>
+          <t>9341.52</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>-1183</t>
+          <t>1396</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>180.3595866842333</t>
+          <t>243.363716734609</t>
         </is>
       </c>
       <c r="BC21" t="n">
-        <v>-280.31</v>
+        <v>589.89</v>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
@@ -9341,7 +9341,7 @@
       </c>
       <c r="BG21" t="inlineStr">
         <is>
-          <t>2.60</t>
+          <t>4.43</t>
         </is>
       </c>
       <c r="BH21" t="inlineStr">
@@ -9386,22 +9386,22 @@
       </c>
       <c r="BP21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>4.97</t>
+          <t>4.88</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
@@ -9411,7 +9411,7 @@
       </c>
       <c r="BU21" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>12.21</t>
         </is>
       </c>
       <c r="BV21" t="inlineStr">
@@ -9426,12 +9426,12 @@
       </c>
       <c r="BX21" t="inlineStr">
         <is>
-          <t>48.2</t>
+          <t>48.69</t>
         </is>
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>9559</t>
+          <t>9725</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
@@ -9451,22 +9451,22 @@
       </c>
       <c r="CC21" t="inlineStr">
         <is>
-          <t>196.0</t>
+          <t>203.5</t>
         </is>
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>197.5</t>
+          <t>203.5</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>195.0</t>
+          <t>199.0</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>197.0</t>
+          <t>200.5</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
@@ -9498,12 +9498,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>-0.77</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>38.0</t>
+          <t>48.0</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9513,7 +9513,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>198.5</t>
+          <t>197.0</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9523,17 +9523,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>3.67</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-1.67</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>-14.77</t>
+          <t>-10.99</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9543,7 +9543,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -9553,7 +9553,7 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>2025-11-20 00:00:00</t>
+          <t>2025-11-21 00:00:00</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
@@ -9608,17 +9608,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>8.94</t>
+          <t>11.29</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9629,77 +9629,77 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>112</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>81.82</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>30.05</t>
+          <t>52.27</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>2.48</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>195.7</t>
+          <t>196.0</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>195.12</t>
+          <t>195.48</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>190.41</t>
+          <t>190.59</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>189.79</t>
+          <t>189.82</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>-11.44</t>
+          <t>-11.56</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9709,7 +9709,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-78.94</t>
+          <t>-79.53</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9719,41 +9719,41 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>28250.49639769452</t>
+          <t>28258.84748201439</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>7456.0</t>
+          <t>9474.0</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>9863.6</t>
+          <t>9585.6</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>11572.5</t>
+          <t>10769.2</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>9025.16</t>
+          <t>9013.74</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>-1708</t>
+          <t>-1183</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>264.1185869502501</t>
+          <t>180.3595866842333</t>
         </is>
       </c>
       <c r="BC22" t="n">
-        <v>-199.88</v>
+        <v>-280.31</v>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
@@ -9772,7 +9772,7 @@
       </c>
       <c r="BG22" t="inlineStr">
         <is>
-          <t>3.39</t>
+          <t>2.60</t>
         </is>
       </c>
       <c r="BH22" t="inlineStr">
@@ -9817,7 +9817,7 @@
       </c>
       <c r="BP22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ22" t="inlineStr">
@@ -9827,12 +9827,12 @@
       </c>
       <c r="BR22" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>4.97</t>
+          <t>4.88</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
@@ -9842,7 +9842,7 @@
       </c>
       <c r="BU22" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>12.21</t>
         </is>
       </c>
       <c r="BV22" t="inlineStr">
@@ -9857,12 +9857,12 @@
       </c>
       <c r="BX22" t="inlineStr">
         <is>
-          <t>48.2</t>
+          <t>48.69</t>
         </is>
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>9559</t>
+          <t>9725</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
@@ -9882,22 +9882,22 @@
       </c>
       <c r="CC22" t="inlineStr">
         <is>
+          <t>196.0</t>
+        </is>
+      </c>
+      <c r="CD22" t="inlineStr">
+        <is>
+          <t>197.5</t>
+        </is>
+      </c>
+      <c r="CE22" t="inlineStr">
+        <is>
           <t>195.0</t>
         </is>
       </c>
-      <c r="CD22" t="inlineStr">
-        <is>
-          <t>199.0</t>
-        </is>
-      </c>
-      <c r="CE22" t="inlineStr">
-        <is>
-          <t>195.0</t>
-        </is>
-      </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>198.5</t>
+          <t>197.0</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
@@ -9929,12 +9929,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>38.0</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9944,7 +9944,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>194.5</t>
+          <t>198.5</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9954,17 +9954,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>3.23</t>
+          <t>2.93</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-1.67</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>-19.30</t>
+          <t>-14.77</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -9974,7 +9974,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -9984,7 +9984,7 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>2025-11-20 00:00:00</t>
+          <t>2025-11-21 00:00:00</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
@@ -10039,17 +10039,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>21.65</t>
+          <t>8.94</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10060,77 +10060,77 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>112</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>8.33</t>
+          <t>81.82</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>6.48</t>
+          <t>30.05</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>2.48</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>195.5</t>
+          <t>195.7</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>194.65</t>
+          <t>195.12</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>190.2</t>
+          <t>190.41</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>189.76</t>
+          <t>189.79</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>-18.96</t>
+          <t>-11.44</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10140,7 +10140,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-78.34</t>
+          <t>-78.94</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10150,41 +10150,41 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>28250.49639769452</t>
+          <t>28258.84748201439</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>17595.0</t>
+          <t>7456.0</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>9896.0</t>
+          <t>9863.6</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>12262.5</t>
+          <t>11572.5</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>9049.34</t>
+          <t>9025.16</t>
         </is>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>-2366</t>
+          <t>-1708</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>348.481424646728</t>
+          <t>264.1185869502501</t>
         </is>
       </c>
       <c r="BC23" t="n">
-        <v>138.39</v>
+        <v>-199.88</v>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
@@ -10203,7 +10203,7 @@
       </c>
       <c r="BG23" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>3.39</t>
         </is>
       </c>
       <c r="BH23" t="inlineStr">
@@ -10248,7 +10248,7 @@
       </c>
       <c r="BP23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ23" t="inlineStr">
@@ -10258,12 +10258,12 @@
       </c>
       <c r="BR23" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>4.97</t>
+          <t>4.88</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
@@ -10273,7 +10273,7 @@
       </c>
       <c r="BU23" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>12.21</t>
         </is>
       </c>
       <c r="BV23" t="inlineStr">
@@ -10288,12 +10288,12 @@
       </c>
       <c r="BX23" t="inlineStr">
         <is>
-          <t>48.2</t>
+          <t>48.69</t>
         </is>
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>9559</t>
+          <t>9725</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
@@ -10313,22 +10313,22 @@
       </c>
       <c r="CC23" t="inlineStr">
         <is>
-          <t>194.0</t>
+          <t>195.0</t>
         </is>
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>194.5</t>
+          <t>199.0</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>190.0</t>
+          <t>195.0</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>194.5</t>
+          <t>198.5</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">

--- a/Result/checksun_type/HMI.xlsx
+++ b/Result/checksun_type/HMI.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-1.53</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-1.46</t>
+          <t>-0.83</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>3.85</t>
+          <t>-2.21</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,12 +1014,12 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -1029,62 +1029,62 @@
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>9.68</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-1.13</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-5.90</t>
+          <t>-6.04</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-4.83</t>
+          <t>-5.2</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-3.05</t>
+          <t>-3.45</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>19.42</t>
+          <t>19.25</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>20.64</t>
+          <t>20.49</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>21.68</t>
+          <t>21.61</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>22.37</t>
+          <t>22.38</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-21.10</t>
+          <t>-17.72</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-108.86</t>
+          <t>-109.27</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1104,46 +1104,46 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>30505.35344827586</t>
+          <t>30462.21090387375</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>1287.0</t>
+          <t>290.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>930.4</t>
+          <t>804.0</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>895.9</t>
+          <t>822.2</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>1833.62</t>
+          <t>1439.06</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>-18</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-147.6201978461726</t>
+          <t>-142.1735059305047</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-76.60999144155971</t>
+          <t>-112.2167003943315</t>
         </is>
       </c>
       <c r="BD2" t="n">
-        <v>1287</v>
+        <v>290</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1187,7 +1187,7 @@
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
@@ -1207,7 +1207,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>83.58</t>
+          <t>84.96</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1272,17 +1272,17 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>19.55</t>
+          <t>19.2</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>19.65</t>
+          <t>19.3</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>18.85</t>
+          <t>19.2</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1319,12 +1319,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>-1.53</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>26.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>19.5</t>
+          <t>19.2</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1344,17 +1344,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-1.56</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-1.46</t>
+          <t>-0.83</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-4.04</t>
+          <t>3.85</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-10.76</t>
+          <t>-12.13</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1429,17 +1429,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>3.17</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1450,77 +1450,77 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>22.58</t>
+          <t>3.23</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>7.53</t>
+          <t>8.6</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>-1.13</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-5.39</t>
+          <t>-5.90</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-4.43</t>
+          <t>-4.83</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-2.68</t>
+          <t>-3.05</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>19.67</t>
+          <t>19.42</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>20.79</t>
+          <t>20.64</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>21.75</t>
+          <t>21.68</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>22.35</t>
+          <t>22.37</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-23.19</t>
+          <t>-21.10</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-0.68</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-108.40</t>
+          <t>-108.86</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1540,46 +1540,46 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>30505.35344827586</t>
+          <t>30462.21090387375</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>497.0</t>
+          <t>1287.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>738.2</t>
+          <t>930.4</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>769.3</t>
+          <t>895.9</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>1851.22</t>
+          <t>1833.62</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-31</t>
+          <t>34</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-160.5311444651931</t>
+          <t>-147.6201978461726</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-129.8286218146873</t>
+          <t>-76.60999144155971</t>
         </is>
       </c>
       <c r="BD3" t="n">
-        <v>497</v>
+        <v>1287</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-17.55</t>
+          <t>-18.82</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1623,7 +1623,7 @@
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
@@ -1648,12 +1648,12 @@
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1683,7 +1683,7 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>83.58</t>
+          <t>84.96</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1708,22 +1708,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
+          <t>19.55</t>
+        </is>
+      </c>
+      <c r="CE3" t="inlineStr">
+        <is>
+          <t>19.65</t>
+        </is>
+      </c>
+      <c r="CF3" t="inlineStr">
+        <is>
+          <t>18.85</t>
+        </is>
+      </c>
+      <c r="CG3" t="inlineStr">
+        <is>
           <t>19.2</t>
-        </is>
-      </c>
-      <c r="CE3" t="inlineStr">
-        <is>
-          <t>19.5</t>
-        </is>
-      </c>
-      <c r="CF3" t="inlineStr">
-        <is>
-          <t>18.9</t>
-        </is>
-      </c>
-      <c r="CG3" t="inlineStr">
-        <is>
-          <t>19.5</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1755,12 +1755,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>26.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>19.15</t>
+          <t>19.5</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1780,17 +1780,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>-1.56</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-1.46</t>
+          <t>-0.83</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>14.69</t>
+          <t>-4.04</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-12.36</t>
+          <t>-10.76</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1865,17 +1865,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>3.17</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1886,77 +1886,77 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>22.58</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.53</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-3.58</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-5.17</t>
+          <t>-5.39</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-3.97</t>
+          <t>-4.43</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-2.33</t>
+          <t>-2.68</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>19.86</t>
+          <t>19.67</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>20.94</t>
+          <t>20.79</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>21.81</t>
+          <t>21.75</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>22.33</t>
+          <t>22.35</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-28.42</t>
+          <t>-23.19</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-0.68</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-0.55</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-107.91</t>
+          <t>-108.40</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1976,46 +1976,46 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>30505.35344827586</t>
+          <t>30462.21090387375</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>231.0</t>
+          <t>497.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>911.2</t>
+          <t>738.2</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>794.5</t>
+          <t>769.3</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>1867.82</t>
+          <t>1851.22</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>116</t>
+          <t>-31</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-166.1134213107396</t>
+          <t>-160.5311444651931</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-116.5756429972018</t>
+          <t>-129.8286218146873</t>
         </is>
       </c>
       <c r="BD4" t="n">
-        <v>231</v>
+        <v>497</v>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2034,7 +2034,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-19.03</t>
+          <t>-17.55</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2059,7 +2059,7 @@
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
@@ -2079,17 +2079,17 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2119,7 +2119,7 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>83.58</t>
+          <t>84.96</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2144,22 +2144,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>18.85</t>
+          <t>19.2</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>19.15</t>
+          <t>19.5</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>18.85</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>19.15</t>
+          <t>19.5</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-4.24</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2206,7 +2206,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>19.2</t>
+          <t>19.15</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2216,17 +2216,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-1.46</t>
+          <t>-0.83</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>21.51</t>
+          <t>14.69</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2291,7 +2291,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-12.13</t>
+          <t>-12.36</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2301,17 +2301,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>3.15</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-3.37</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2322,12 +2322,12 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -2337,62 +2337,62 @@
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>15.38</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-4.81</t>
+          <t>-3.58</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-4.41</t>
+          <t>-5.17</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-3.49</t>
+          <t>-3.97</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-2.01</t>
+          <t>-2.33</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>20.17</t>
+          <t>19.86</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>21.1</t>
+          <t>20.94</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>21.86</t>
+          <t>21.81</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>22.31</t>
+          <t>22.33</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-25.64</t>
+          <t>-28.42</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2402,7 +2402,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-107.35</t>
+          <t>-107.91</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2412,46 +2412,46 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>30505.35344827586</t>
+          <t>30462.21090387375</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>1715.0</t>
+          <t>231.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>1014.4</t>
+          <t>911.2</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>834.8</t>
+          <t>794.5</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>1896.36</t>
+          <t>1867.82</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>179</t>
+          <t>116</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-175.1202900950192</t>
+          <t>-166.1134213107396</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-64.97940029375127</t>
+          <t>-116.5756429972018</t>
         </is>
       </c>
       <c r="BD5" t="n">
-        <v>1715</v>
+        <v>231</v>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-18.82</t>
+          <t>-19.03</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2495,7 +2495,7 @@
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2525,7 +2525,7 @@
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2555,7 +2555,7 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>83.58</t>
+          <t>84.96</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2580,22 +2580,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>20.05</t>
+          <t>18.85</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>20.05</t>
+          <t>19.15</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>19.0</t>
+          <t>18.85</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>19.2</t>
+          <t>19.15</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-2.0</t>
+          <t>-4.24</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>46.0</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2642,7 +2642,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>20.05</t>
+          <t>19.2</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2652,17 +2652,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-4.43</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-1.46</t>
+          <t>-0.83</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>17.65</t>
+          <t>21.51</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2727,7 +2727,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-8.24</t>
+          <t>-12.13</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2737,17 +2737,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>3.15</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>-3.37</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2758,12 +2758,12 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -2773,62 +2773,62 @@
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>23.08</t>
+          <t>15.38</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-1.91</t>
+          <t>-4.81</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-3.90</t>
+          <t>-4.41</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-2.98</t>
+          <t>-3.49</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-1.65</t>
+          <t>-2.01</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>20.44</t>
+          <t>20.17</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>21.27</t>
+          <t>21.1</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>21.92</t>
+          <t>21.86</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>22.29</t>
+          <t>22.31</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-16.23</t>
+          <t>-25.64</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2838,7 +2838,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-106.88</t>
+          <t>-107.35</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2848,46 +2848,46 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>30505.35344827586</t>
+          <t>30462.21090387375</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>922.0</t>
+          <t>1715.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>840.4</t>
+          <t>1014.4</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>714.3</t>
+          <t>834.8</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>1889.2</t>
+          <t>1896.36</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>126</t>
+          <t>179</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-195.1459064225224</t>
+          <t>-175.1202900950192</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-147.9497892783307</t>
+          <t>-64.97940029375127</t>
         </is>
       </c>
       <c r="BD6" t="n">
-        <v>922</v>
+        <v>1715</v>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-15.22</t>
+          <t>-18.82</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
@@ -2951,7 +2951,7 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -2961,7 +2961,7 @@
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2991,7 +2991,7 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>83.58</t>
+          <t>84.96</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -3016,22 +3016,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>20.05</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>20.1</t>
+          <t>20.05</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>19.95</t>
+          <t>19.0</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>20.05</t>
+          <t>19.2</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-2.0</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>16.0</t>
+          <t>46.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>20.45</t>
+          <t>20.05</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3088,17 +3088,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-6.51</t>
+          <t>-4.43</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-1.46</t>
+          <t>-0.83</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>22.57</t>
+          <t>17.65</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3163,7 +3163,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-6.41</t>
+          <t>-8.24</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3173,17 +3173,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3194,77 +3194,77 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>46.15</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>36.17</t>
+          <t>23.08</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-1.91</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-4.52</t>
+          <t>-3.90</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-2.41</t>
+          <t>-2.98</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-1.36</t>
+          <t>-1.65</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>20.46</t>
+          <t>20.44</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>21.43</t>
+          <t>21.27</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>21.96</t>
+          <t>21.92</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>22.26</t>
+          <t>22.29</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-15.32</t>
+          <t>-16.23</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.50</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3274,7 +3274,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-106.60</t>
+          <t>-106.88</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3284,46 +3284,46 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>30505.35344827586</t>
+          <t>30462.21090387375</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>326.0</t>
+          <t>922.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>861.4</t>
+          <t>840.4</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>702.8</t>
+          <t>714.3</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>2075.44</t>
+          <t>1889.2</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>158</t>
+          <t>126</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-203.7270186305573</t>
+          <t>-195.1459064225224</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-176.2307096392179</t>
+          <t>-147.9497892783307</t>
         </is>
       </c>
       <c r="BD7" t="n">
-        <v>326</v>
+        <v>922</v>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-13.53</t>
+          <t>-15.22</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3367,7 +3367,7 @@
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
@@ -3387,7 +3387,7 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3397,7 +3397,7 @@
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3427,7 +3427,7 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>83.58</t>
+          <t>84.96</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3452,22 +3452,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>20.45</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>20.45</t>
+          <t>20.1</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>20.3</t>
+          <t>19.95</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>20.45</t>
+          <t>20.05</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3499,12 +3499,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-1.19</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-1.46</t>
+          <t>-0.83</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>22.57</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3609,17 +3609,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-1.95</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3630,67 +3630,67 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>23.08</t>
+          <t>46.15</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>28.41</t>
+          <t>36.17</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-4.33</t>
+          <t>-4.52</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-2.52</t>
+          <t>-2.41</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>-1.36</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>20.53</t>
+          <t>20.46</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>21.46</t>
+          <t>21.43</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>22.01</t>
+          <t>21.96</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>22.23</t>
+          <t>22.26</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-20.19</t>
+          <t>-15.32</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
@@ -3700,7 +3700,7 @@
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-106.34</t>
+          <t>-106.60</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3720,46 +3720,46 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>30505.35344827586</t>
+          <t>30462.21090387375</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>1362.0</t>
+          <t>326.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>800.4</t>
+          <t>861.4</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>791.6</t>
+          <t>702.8</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>2169.22</t>
+          <t>2075.44</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>158</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-208.7263475380736</t>
+          <t>-203.7270186305573</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-146.4809276676563</t>
+          <t>-176.2307096392179</t>
         </is>
       </c>
       <c r="BD8" t="n">
-        <v>1362</v>
+        <v>326</v>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
@@ -3823,7 +3823,7 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -3863,7 +3863,7 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>83.58</t>
+          <t>84.96</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -3888,12 +3888,12 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>21.0</t>
+          <t>20.45</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>21.0</t>
+          <t>20.45</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
@@ -3935,12 +3935,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>-1.19</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>36.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3950,7 +3950,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>20.7</t>
+          <t>20.45</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3960,17 +3960,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-7.81</t>
+          <t>-6.51</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-1.46</t>
+          <t>-0.83</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-32.18</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4035,7 +4035,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-5.26</t>
+          <t>-6.41</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4045,17 +4045,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>-1.95</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4066,67 +4066,67 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>39.29</t>
+          <t>23.08</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>20.71</t>
+          <t>28.41</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-4.13</t>
+          <t>-4.33</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-2.66</t>
+          <t>-2.52</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-0.54</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>20.6</t>
+          <t>20.53</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>21.49</t>
+          <t>21.46</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>22.08</t>
+          <t>22.01</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>22.19</t>
+          <t>22.23</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-25.12</t>
+          <t>-20.19</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-106.02</t>
+          <t>-106.34</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4156,46 +4156,46 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>30505.35344827586</t>
+          <t>30462.21090387375</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>747.0</t>
+          <t>1362.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>677.8</t>
+          <t>800.4</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>999.4</t>
+          <t>791.6</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>2614.76</t>
+          <t>2169.22</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-321</t>
+          <t>8</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-220.0436966054221</t>
+          <t>-208.7263475380736</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-209.7497774344375</t>
+          <t>-146.4809276676563</t>
         </is>
       </c>
       <c r="BD9" t="n">
-        <v>747</v>
+        <v>1362</v>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4214,7 +4214,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-12.47</t>
+          <t>-13.53</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
@@ -4259,7 +4259,7 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4269,7 +4269,7 @@
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4299,7 +4299,7 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>83.58</t>
+          <t>84.96</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4324,22 +4324,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>20.6</t>
+          <t>21.0</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>20.95</t>
+          <t>21.0</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>20.55</t>
+          <t>20.3</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>20.7</t>
+          <t>20.45</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4371,12 +4371,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>41.0</t>
+          <t>36.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4386,7 +4386,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>20.55</t>
+          <t>20.7</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4396,17 +4396,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-7.03</t>
+          <t>-7.81</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-1.46</t>
+          <t>-0.83</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-33.22</t>
+          <t>-32.18</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4471,7 +4471,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-5.95</t>
+          <t>-5.26</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4481,17 +4481,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-4.11</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4502,77 +4502,77 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>22.86</t>
+          <t>39.29</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>19.66</t>
+          <t>20.71</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-4.71</t>
+          <t>-4.13</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-2.98</t>
+          <t>-2.66</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-0.54</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>20.49</t>
+          <t>20.6</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>21.5</t>
+          <t>21.49</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>22.16</t>
+          <t>22.08</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>22.16</t>
+          <t>22.19</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-36.40</t>
+          <t>-25.12</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>-0.50</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4582,7 +4582,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-105.65</t>
+          <t>-106.02</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4592,46 +4592,46 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>30505.35344827586</t>
+          <t>30462.21090387375</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>845.0</t>
+          <t>747.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>655.2</t>
+          <t>677.8</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>981.2</t>
+          <t>999.4</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>2840.22</t>
+          <t>2614.76</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-326</t>
+          <t>-321</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-221.9153182728739</t>
+          <t>-220.0436966054221</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-226.749927907181</t>
+          <t>-209.7497774344375</t>
         </is>
       </c>
       <c r="BD10" t="n">
-        <v>845</v>
+        <v>747</v>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-13.11</t>
+          <t>-12.47</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4675,7 +4675,7 @@
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
@@ -4695,7 +4695,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4705,7 +4705,7 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4735,7 +4735,7 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>83.58</t>
+          <t>84.96</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4760,22 +4760,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>20.2</t>
+          <t>20.6</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>21.75</t>
+          <t>20.95</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>20.2</t>
+          <t>20.55</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>20.55</t>
+          <t>20.7</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4807,12 +4807,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-3.22</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>51.0</t>
+          <t>41.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4822,7 +4822,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>20.15</t>
+          <t>20.55</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4832,17 +4832,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-4.95</t>
+          <t>-7.03</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-1.46</t>
+          <t>-0.83</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-37.93</t>
+          <t>-33.22</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-7.78</t>
+          <t>-5.95</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4917,17 +4917,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-0.74</t>
+          <t>-4.11</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4938,77 +4938,77 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>22.86</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>22.61</t>
+          <t>19.66</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-1.80</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-4.79</t>
+          <t>-4.71</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-2.96</t>
+          <t>-2.98</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>20.52</t>
+          <t>20.49</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>21.55</t>
+          <t>21.5</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>22.21</t>
+          <t>22.16</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>22.13</t>
+          <t>22.16</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-47.43</t>
+          <t>-36.40</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.50</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.37</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -5018,7 +5018,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-105.13</t>
+          <t>-105.65</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -5028,46 +5028,46 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>30505.35344827586</t>
+          <t>30462.21090387375</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>1027.0</t>
+          <t>845.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>588.2</t>
+          <t>655.2</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>947.7</t>
+          <t>981.2</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>2910.12</t>
+          <t>2840.22</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-359</t>
+          <t>-326</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-221.0362983393635</t>
+          <t>-221.9153182728739</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-253.4376454429865</t>
+          <t>-226.749927907181</t>
         </is>
       </c>
       <c r="BD11" t="n">
-        <v>1027</v>
+        <v>845</v>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5086,7 +5086,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-14.80</t>
+          <t>-13.11</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5111,7 +5111,7 @@
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
@@ -5141,7 +5141,7 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5171,7 +5171,7 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>83.58</t>
+          <t>84.96</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5201,17 +5201,17 @@
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>20.4</t>
+          <t>21.75</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>20.05</t>
+          <t>20.2</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>20.15</t>
+          <t>20.55</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5243,12 +5243,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-3.22</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>51.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5258,7 +5258,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>20.8</t>
+          <t>20.15</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5268,17 +5268,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-8.33</t>
+          <t>-4.95</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-1.46</t>
+          <t>-0.83</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-40.01</t>
+          <t>-37.93</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5343,7 +5343,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-4.81</t>
+          <t>-7.78</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5353,17 +5353,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.74</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5374,17 +5374,17 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>36.11</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
@@ -5394,57 +5394,57 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>0.10</t>
+          <t>-1.80</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-4.04</t>
+          <t>-4.79</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-2.72</t>
+          <t>-2.96</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.36</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>20.78</t>
+          <t>20.52</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>21.66</t>
+          <t>21.55</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>22.26</t>
+          <t>22.21</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>22.1</t>
+          <t>22.13</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-47.36</t>
+          <t>-47.43</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>-0.50</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5454,7 +5454,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-104.52</t>
+          <t>-105.13</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5464,46 +5464,46 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>30505.35344827586</t>
+          <t>30462.21090387375</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>21.0</t>
+          <t>1027.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>544.2</t>
+          <t>588.2</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>907.2</t>
+          <t>947.7</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>2976.72</t>
+          <t>2910.12</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-363</t>
+          <t>-359</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-215.145144320523</t>
+          <t>-221.0362983393635</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-302.0116117283162</t>
+          <t>-253.4376454429865</t>
         </is>
       </c>
       <c r="BD12" t="n">
-        <v>21</v>
+        <v>1027</v>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5522,7 +5522,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-12.05</t>
+          <t>-14.80</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5547,7 +5547,7 @@
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
@@ -5567,7 +5567,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5577,7 +5577,7 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5607,7 +5607,7 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>83.58</t>
+          <t>84.96</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5632,22 +5632,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>20.8</t>
+          <t>20.2</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>20.8</t>
+          <t>20.4</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>20.8</t>
+          <t>20.05</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>20.8</t>
+          <t>20.15</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5679,12 +5679,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>105.0</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5694,7 +5694,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>207.0</t>
+          <t>210.5</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5709,12 +5709,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>-2.32</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>19.04</t>
+          <t>13.00</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5734,7 +5734,7 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>2025-11-22 00:00:00</t>
+          <t>2025-11-25 00:00:00</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -5774,7 +5774,7 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>2.73</t>
+          <t>4.47</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
@@ -5789,17 +5789,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>30.12</t>
+          <t>24.71</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5815,7 +5815,7 @@
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>105</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
@@ -5825,62 +5825,62 @@
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>85.71</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>2.93</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>2.52</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>2.89</t>
+          <t>2.93</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>203.2</t>
+          <t>204.5</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>198.92</t>
+          <t>199.48</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>193.33</t>
+          <t>193.8</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>191.14</t>
+          <t>191.47</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>24.29</t>
+          <t>34.99</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>2.85</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>2.52</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5890,7 +5890,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-77.07</t>
+          <t>-74.87</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5900,50 +5900,50 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>28274.88146551724</t>
+          <t>28281.92324246772</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>26279.0</t>
+          <t>22122.0</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>21604.4</t>
+          <t>20551.2</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>18148.2</t>
+          <t>18187.0</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>11512.0</t>
+          <t>11819.44</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>3456</t>
+          <t>2364</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>1090.028654275838</t>
+          <t>1229.675320671625</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>2039.741068992971</t>
+          <t>1997.731985848452</t>
         </is>
       </c>
       <c r="BD13" t="n">
-        <v>26279</v>
+        <v>22122</v>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
-          <t>2025-11-22</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="BF13" t="inlineStr">
@@ -5958,7 +5958,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>7.81</t>
+          <t>9.64</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -6008,17 +6008,17 @@
       </c>
       <c r="BR13" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
         <is>
-          <t>4.82</t>
+          <t>4.74</t>
         </is>
       </c>
       <c r="BU13" t="inlineStr">
@@ -6028,7 +6028,7 @@
       </c>
       <c r="BV13" t="inlineStr">
         <is>
-          <t>12.36</t>
+          <t>12.57</t>
         </is>
       </c>
       <c r="BW13" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>47.09</t>
+          <t>47.65</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>9844</t>
+          <t>10010</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -6068,22 +6068,22 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>203.5</t>
+          <t>208.5</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
+          <t>211.0</t>
+        </is>
+      </c>
+      <c r="CF13" t="inlineStr">
+        <is>
           <t>208.0</t>
         </is>
       </c>
-      <c r="CF13" t="inlineStr">
-        <is>
-          <t>202.0</t>
-        </is>
-      </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>207.0</t>
+          <t>210.5</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6115,12 +6115,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>112.0</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6130,7 +6130,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>204.5</t>
+          <t>207.0</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6140,17 +6140,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>-2.32</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>40.09</t>
+          <t>19.04</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6170,7 +6170,7 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>2025-11-22 00:00:00</t>
+          <t>2025-11-25 00:00:00</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -6210,7 +6210,7 @@
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>2.73</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
@@ -6225,17 +6225,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>26.35</t>
+          <t>30.12</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6251,7 +6251,7 @@
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>105</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
@@ -6261,62 +6261,62 @@
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>64.29</t>
+          <t>85.71</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>2.93</t>
+          <t>2.89</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>202.1</t>
+          <t>203.2</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>198.58</t>
+          <t>198.92</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>192.93</t>
+          <t>193.33</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>190.87</t>
+          <t>191.14</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>14.78</t>
+          <t>24.29</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>2.48</t>
+          <t>2.85</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6326,7 +6326,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-78.46</t>
+          <t>-77.07</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6336,50 +6336,50 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>28274.88146551724</t>
+          <t>28281.92324246772</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>22703.0</t>
+          <t>26279.0</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>23070.4</t>
+          <t>21604.4</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>16467.7</t>
+          <t>18148.2</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>11056.48</t>
+          <t>11512.0</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>6602</t>
+          <t>3456</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>917.3536697818137</t>
+          <t>1090.028654275838</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>1581.513292449679</t>
+          <t>2039.741068992971</t>
         </is>
       </c>
       <c r="BD14" t="n">
-        <v>22703</v>
+        <v>26279</v>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
-          <t>2025-11-22</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="BF14" t="inlineStr">
@@ -6394,7 +6394,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>6.51</t>
+          <t>7.81</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -6439,22 +6439,22 @@
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
         <is>
-          <t>4.82</t>
+          <t>4.74</t>
         </is>
       </c>
       <c r="BU14" t="inlineStr">
@@ -6464,7 +6464,7 @@
       </c>
       <c r="BV14" t="inlineStr">
         <is>
-          <t>12.36</t>
+          <t>12.57</t>
         </is>
       </c>
       <c r="BW14" t="inlineStr">
@@ -6479,12 +6479,12 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>47.09</t>
+          <t>47.65</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>9844</t>
+          <t>10010</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -6504,22 +6504,22 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
+          <t>203.5</t>
+        </is>
+      </c>
+      <c r="CE14" t="inlineStr">
+        <is>
+          <t>208.0</t>
+        </is>
+      </c>
+      <c r="CF14" t="inlineStr">
+        <is>
           <t>202.0</t>
         </is>
       </c>
-      <c r="CE14" t="inlineStr">
-        <is>
-          <t>205.0</t>
-        </is>
-      </c>
-      <c r="CF14" t="inlineStr">
-        <is>
-          <t>202.0</t>
-        </is>
-      </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>204.5</t>
+          <t>207.0</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -6551,12 +6551,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>112.0</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6566,7 +6566,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>201.0</t>
+          <t>204.5</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6576,17 +6576,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2.9</t>
+          <t>2.85</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>-2.32</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>28.98</t>
+          <t>40.09</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6606,7 +6606,7 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>2025-11-22 00:00:00</t>
+          <t>2025-11-25 00:00:00</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -6646,7 +6646,7 @@
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
@@ -6661,17 +6661,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11.76</t>
+          <t>26.35</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6687,12 +6687,12 @@
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>105</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>57.14</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
@@ -6702,57 +6702,57 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>2.94</t>
+          <t>2.93</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>200.6</t>
+          <t>202.1</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>198.25</t>
+          <t>198.58</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>192.58</t>
+          <t>192.93</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>190.62</t>
+          <t>190.87</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>6.46</t>
+          <t>14.78</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>2.21</t>
+          <t>2.48</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>2.16</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6762,7 +6762,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-79.25</t>
+          <t>-78.46</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6772,50 +6772,50 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>28274.88146551724</t>
+          <t>28281.92324246772</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>10051.0</t>
+          <t>22703.0</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>19272.8</t>
+          <t>23070.4</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>14943.0</t>
+          <t>16467.7</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>10672.76</t>
+          <t>11056.48</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>4329</t>
+          <t>6602</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>796.5973747512926</t>
+          <t>917.3536697818137</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>1253.562422657489</t>
+          <t>1581.513292449679</t>
         </is>
       </c>
       <c r="BD15" t="n">
-        <v>10051</v>
+        <v>22703</v>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
-          <t>2025-11-22</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="BF15" t="inlineStr">
@@ -6830,7 +6830,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>4.69</t>
+          <t>6.51</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -6875,22 +6875,22 @@
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
         <is>
-          <t>4.82</t>
+          <t>4.74</t>
         </is>
       </c>
       <c r="BU15" t="inlineStr">
@@ -6900,7 +6900,7 @@
       </c>
       <c r="BV15" t="inlineStr">
         <is>
-          <t>12.36</t>
+          <t>12.57</t>
         </is>
       </c>
       <c r="BW15" t="inlineStr">
@@ -6915,12 +6915,12 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>47.09</t>
+          <t>47.65</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>9844</t>
+          <t>10010</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -6940,22 +6940,22 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>199.5</t>
+          <t>202.0</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
+          <t>205.0</t>
+        </is>
+      </c>
+      <c r="CF15" t="inlineStr">
+        <is>
           <t>202.0</t>
         </is>
       </c>
-      <c r="CF15" t="inlineStr">
-        <is>
-          <t>198.5</t>
-        </is>
-      </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>201.0</t>
+          <t>204.5</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-2.2</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>107.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -7002,7 +7002,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>199.5</t>
+          <t>201.0</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -7012,17 +7012,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>3.62</t>
+          <t>4.51</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>-2.32</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>17.59</t>
+          <t>28.98</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7042,7 +7042,7 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>2025-11-22 00:00:00</t>
+          <t>2025-11-25 00:00:00</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -7082,7 +7082,7 @@
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
@@ -7097,17 +7097,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>25.18</t>
+          <t>11.76</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>-2.00</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7123,72 +7123,72 @@
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>105</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>35.71</t>
+          <t>57.14</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>78.57</t>
+          <t>64.29</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>2.96</t>
+          <t>2.94</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>200.0</t>
+          <t>200.6</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>197.98</t>
+          <t>198.25</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>192.28</t>
+          <t>192.58</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>190.44</t>
+          <t>190.62</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>7.56</t>
+          <t>6.46</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>2.21</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7198,7 +7198,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-79.59</t>
+          <t>-79.25</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7208,50 +7208,50 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>28274.88146551724</t>
+          <t>28281.92324246772</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>21601.0</t>
+          <t>10051.0</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>18457.8</t>
+          <t>19272.8</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>15697.4</t>
+          <t>14943.0</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>10622.98</t>
+          <t>10672.76</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>2760</t>
+          <t>4329</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>713.5128205865296</t>
+          <t>796.5973747512926</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>2095.862522145168</t>
+          <t>1253.562422657489</t>
         </is>
       </c>
       <c r="BD16" t="n">
-        <v>21601</v>
+        <v>10051</v>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
-          <t>2025-11-22</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="BF16" t="inlineStr">
@@ -7266,7 +7266,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>3.91</t>
+          <t>4.69</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -7311,22 +7311,22 @@
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>1.89</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
         <is>
-          <t>4.82</t>
+          <t>4.74</t>
         </is>
       </c>
       <c r="BU16" t="inlineStr">
@@ -7336,7 +7336,7 @@
       </c>
       <c r="BV16" t="inlineStr">
         <is>
-          <t>12.36</t>
+          <t>12.57</t>
         </is>
       </c>
       <c r="BW16" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>47.09</t>
+          <t>47.65</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>9844</t>
+          <t>10010</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -7376,22 +7376,22 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>205.0</t>
+          <t>199.5</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>205.0</t>
+          <t>202.0</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>198.0</t>
+          <t>198.5</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>199.5</t>
+          <t>201.0</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>-2.2</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>107.0</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7438,7 +7438,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>204.0</t>
+          <t>199.5</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7448,17 +7448,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>5.23</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>-2.32</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>9.50</t>
+          <t>17.59</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7478,7 +7478,7 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>2025-11-22 00:00:00</t>
+          <t>2025-11-25 00:00:00</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -7518,7 +7518,7 @@
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
@@ -7533,17 +7533,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>31.53</t>
+          <t>25.18</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>-2.00</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7559,27 +7559,27 @@
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>105</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>35.71</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>82.05</t>
+          <t>78.57</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
@@ -7589,245 +7589,245 @@
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
+          <t>200.0</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>197.98</t>
+        </is>
+      </c>
+      <c r="AN17" t="inlineStr">
+        <is>
+          <t>192.28</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>190.44</t>
+        </is>
+      </c>
+      <c r="AP17" t="inlineStr">
+        <is>
+          <t>7.56</t>
+        </is>
+      </c>
+      <c r="AQ17" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="AR17" t="inlineStr">
+        <is>
+          <t>2.04</t>
+        </is>
+      </c>
+      <c r="AS17" t="inlineStr">
+        <is>
+          <t>10.01</t>
+        </is>
+      </c>
+      <c r="AT17" t="inlineStr">
+        <is>
+          <t>-79.59</t>
+        </is>
+      </c>
+      <c r="AU17" t="inlineStr">
+        <is>
+          <t>2025/11/14</t>
+        </is>
+      </c>
+      <c r="AV17" t="inlineStr">
+        <is>
+          <t>28281.92324246772</t>
+        </is>
+      </c>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>21601.0</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>18457.8</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>15697.4</t>
+        </is>
+      </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>10622.98</t>
+        </is>
+      </c>
+      <c r="BA17" t="inlineStr">
+        <is>
+          <t>2760</t>
+        </is>
+      </c>
+      <c r="BB17" t="inlineStr">
+        <is>
+          <t>713.5128205865296</t>
+        </is>
+      </c>
+      <c r="BC17" t="inlineStr">
+        <is>
+          <t>2095.862522145168</t>
+        </is>
+      </c>
+      <c r="BD17" t="n">
+        <v>21601</v>
+      </c>
+      <c r="BE17" t="inlineStr">
+        <is>
+          <t>2025-11-25</t>
+        </is>
+      </c>
+      <c r="BF17" t="inlineStr">
+        <is>
+          <t>192.0</t>
+        </is>
+      </c>
+      <c r="BG17" t="inlineStr">
+        <is>
+          <t>2025/10/14</t>
+        </is>
+      </c>
+      <c r="BH17" t="inlineStr">
+        <is>
+          <t>3.91</t>
+        </is>
+      </c>
+      <c r="BI17" t="inlineStr">
+        <is>
+          <t>鼎翰</t>
+        </is>
+      </c>
+      <c r="BJ17" t="inlineStr">
+        <is>
+          <t>鼎翰</t>
+        </is>
+      </c>
+      <c r="BK17" t="inlineStr">
+        <is>
+          <t>電腦及週邊設備業</t>
+        </is>
+      </c>
+      <c r="BL17" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BM17" t="inlineStr">
+        <is>
+          <t>0.56</t>
+        </is>
+      </c>
+      <c r="BN17" t="inlineStr">
+        <is>
+          <t>-11.45161899724185</t>
+        </is>
+      </c>
+      <c r="BO17" t="inlineStr">
+        <is>
+          <t>22.56717409239306</t>
+        </is>
+      </c>
+      <c r="BP17" t="inlineStr">
+        <is>
+          <t>38.82556207928187</t>
+        </is>
+      </c>
+      <c r="BQ17" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR17" t="inlineStr">
+        <is>
+          <t>價-量增</t>
+        </is>
+      </c>
+      <c r="BS17" t="inlineStr">
+        <is>
+          <t>1.89</t>
+        </is>
+      </c>
+      <c r="BT17" t="inlineStr">
+        <is>
+          <t>4.74</t>
+        </is>
+      </c>
+      <c r="BU17" t="inlineStr">
+        <is>
+          <t>57.78</t>
+        </is>
+      </c>
+      <c r="BV17" t="inlineStr">
+        <is>
+          <t>12.57</t>
+        </is>
+      </c>
+      <c r="BW17" t="inlineStr">
+        <is>
+          <t>33.69%</t>
+        </is>
+      </c>
+      <c r="BX17" t="inlineStr">
+        <is>
+          <t>11.08%</t>
+        </is>
+      </c>
+      <c r="BY17" t="inlineStr">
+        <is>
+          <t>47.65</t>
+        </is>
+      </c>
+      <c r="BZ17" t="inlineStr">
+        <is>
+          <t>10010</t>
+        </is>
+      </c>
+      <c r="CA17" t="inlineStr">
+        <is>
+          <t>條碼印表機及零配件52.71%、印表機各式標籤紙及其耗材41.09%、企業行動電腦6.20% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB17" t="inlineStr">
+        <is>
+          <t>鼎翰-電腦及週邊設備業-上櫃</t>
+        </is>
+      </c>
+      <c r="CC17" t="inlineStr">
+        <is>
+          <t>電腦及週邊設備業平上櫃</t>
+        </is>
+      </c>
+      <c r="CD17" t="inlineStr">
+        <is>
+          <t>205.0</t>
+        </is>
+      </c>
+      <c r="CE17" t="inlineStr">
+        <is>
+          <t>205.0</t>
+        </is>
+      </c>
+      <c r="CF17" t="inlineStr">
+        <is>
+          <t>198.0</t>
+        </is>
+      </c>
+      <c r="CG17" t="inlineStr">
+        <is>
           <t>199.5</t>
-        </is>
-      </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>197.7</t>
-        </is>
-      </c>
-      <c r="AN17" t="inlineStr">
-        <is>
-          <t>192.01</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>190.29</t>
-        </is>
-      </c>
-      <c r="AP17" t="inlineStr">
-        <is>
-          <t>14.82</t>
-        </is>
-      </c>
-      <c r="AQ17" t="inlineStr">
-        <is>
-          <t>2.30</t>
-        </is>
-      </c>
-      <c r="AR17" t="inlineStr">
-        <is>
-          <t>2.01</t>
-        </is>
-      </c>
-      <c r="AS17" t="inlineStr">
-        <is>
-          <t>10.01</t>
-        </is>
-      </c>
-      <c r="AT17" t="inlineStr">
-        <is>
-          <t>-79.98</t>
-        </is>
-      </c>
-      <c r="AU17" t="inlineStr">
-        <is>
-          <t>2025/11/14</t>
-        </is>
-      </c>
-      <c r="AV17" t="inlineStr">
-        <is>
-          <t>28274.88146551724</t>
-        </is>
-      </c>
-      <c r="AW17" t="inlineStr">
-        <is>
-          <t>27388.0</t>
-        </is>
-      </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>15822.8</t>
-        </is>
-      </c>
-      <c r="AY17" t="inlineStr">
-        <is>
-          <t>14450.7</t>
-        </is>
-      </c>
-      <c r="AZ17" t="inlineStr">
-        <is>
-          <t>10277.46</t>
-        </is>
-      </c>
-      <c r="BA17" t="inlineStr">
-        <is>
-          <t>1372</t>
-        </is>
-      </c>
-      <c r="BB17" t="inlineStr">
-        <is>
-          <t>462.1765112122318</t>
-        </is>
-      </c>
-      <c r="BC17" t="inlineStr">
-        <is>
-          <t>1986.79614562238</t>
-        </is>
-      </c>
-      <c r="BD17" t="n">
-        <v>27388</v>
-      </c>
-      <c r="BE17" t="inlineStr">
-        <is>
-          <t>2025-11-22</t>
-        </is>
-      </c>
-      <c r="BF17" t="inlineStr">
-        <is>
-          <t>192.0</t>
-        </is>
-      </c>
-      <c r="BG17" t="inlineStr">
-        <is>
-          <t>2025/10/14</t>
-        </is>
-      </c>
-      <c r="BH17" t="inlineStr">
-        <is>
-          <t>6.25</t>
-        </is>
-      </c>
-      <c r="BI17" t="inlineStr">
-        <is>
-          <t>鼎翰</t>
-        </is>
-      </c>
-      <c r="BJ17" t="inlineStr">
-        <is>
-          <t>鼎翰</t>
-        </is>
-      </c>
-      <c r="BK17" t="inlineStr">
-        <is>
-          <t>電腦及週邊設備業</t>
-        </is>
-      </c>
-      <c r="BL17" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BM17" t="inlineStr">
-        <is>
-          <t>0.56</t>
-        </is>
-      </c>
-      <c r="BN17" t="inlineStr">
-        <is>
-          <t>-11.45161899724185</t>
-        </is>
-      </c>
-      <c r="BO17" t="inlineStr">
-        <is>
-          <t>22.56717409239306</t>
-        </is>
-      </c>
-      <c r="BP17" t="inlineStr">
-        <is>
-          <t>38.82556207928187</t>
-        </is>
-      </c>
-      <c r="BQ17" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR17" t="inlineStr">
-        <is>
-          <t>價-量增</t>
-        </is>
-      </c>
-      <c r="BS17" t="inlineStr">
-        <is>
-          <t>1.93</t>
-        </is>
-      </c>
-      <c r="BT17" t="inlineStr">
-        <is>
-          <t>4.82</t>
-        </is>
-      </c>
-      <c r="BU17" t="inlineStr">
-        <is>
-          <t>57.78</t>
-        </is>
-      </c>
-      <c r="BV17" t="inlineStr">
-        <is>
-          <t>12.36</t>
-        </is>
-      </c>
-      <c r="BW17" t="inlineStr">
-        <is>
-          <t>33.69%</t>
-        </is>
-      </c>
-      <c r="BX17" t="inlineStr">
-        <is>
-          <t>11.08%</t>
-        </is>
-      </c>
-      <c r="BY17" t="inlineStr">
-        <is>
-          <t>47.09</t>
-        </is>
-      </c>
-      <c r="BZ17" t="inlineStr">
-        <is>
-          <t>9844</t>
-        </is>
-      </c>
-      <c r="CA17" t="inlineStr">
-        <is>
-          <t>條碼印表機及零配件52.71%、印表機各式標籤紙及其耗材41.09%、企業行動電腦6.20% (2024年)</t>
-        </is>
-      </c>
-      <c r="CB17" t="inlineStr">
-        <is>
-          <t>鼎翰-電腦及週邊設備業-上櫃</t>
-        </is>
-      </c>
-      <c r="CC17" t="inlineStr">
-        <is>
-          <t>電腦及週邊設備業平上櫃</t>
-        </is>
-      </c>
-      <c r="CD17" t="inlineStr">
-        <is>
-          <t>201.5</t>
-        </is>
-      </c>
-      <c r="CE17" t="inlineStr">
-        <is>
-          <t>206.5</t>
-        </is>
-      </c>
-      <c r="CF17" t="inlineStr">
-        <is>
-          <t>201.5</t>
-        </is>
-      </c>
-      <c r="CG17" t="inlineStr">
-        <is>
-          <t>204.0</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7859,12 +7859,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>167.0</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7874,74 +7874,74 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
+          <t>204.0</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>3.09</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>-2.32</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>9.50</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>2025-11-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>2025-11-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>2025-10-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>2025-11-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
           <t>201.5</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>2.66</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>-0.5</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>21.03</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>2025-11-14</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>2025-11-14 00:00:00</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>2025-11-22 00:00:00</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>2025-10-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>2025-11-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q18" t="inlineStr">
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
         <is>
           <t>201.5</t>
         </is>
       </c>
-      <c r="R18" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>201.5</t>
-        </is>
-      </c>
       <c r="T18" t="inlineStr">
         <is>
           <t>195.5</t>
@@ -7954,7 +7954,7 @@
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="W18" t="inlineStr">
@@ -7969,17 +7969,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>39.29</t>
+          <t>31.53</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7995,7 +7995,7 @@
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>105</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
@@ -8005,200 +8005,200 @@
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>69.23</t>
+          <t>82.05</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>2.87</t>
+          <t>2.96</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>198.8</t>
+          <t>199.5</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>197.15</t>
+          <t>197.7</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>191.65</t>
+          <t>192.01</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>190.08</t>
+          <t>190.29</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>14.82</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
+          <t>2.01</t>
+        </is>
+      </c>
+      <c r="AS18" t="inlineStr">
+        <is>
+          <t>10.01</t>
+        </is>
+      </c>
+      <c r="AT18" t="inlineStr">
+        <is>
+          <t>-79.98</t>
+        </is>
+      </c>
+      <c r="AU18" t="inlineStr">
+        <is>
+          <t>2025/11/14</t>
+        </is>
+      </c>
+      <c r="AV18" t="inlineStr">
+        <is>
+          <t>28281.92324246772</t>
+        </is>
+      </c>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>27388.0</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>15822.8</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>14450.7</t>
+        </is>
+      </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>10277.46</t>
+        </is>
+      </c>
+      <c r="BA18" t="inlineStr">
+        <is>
+          <t>1372</t>
+        </is>
+      </c>
+      <c r="BB18" t="inlineStr">
+        <is>
+          <t>462.1765112122318</t>
+        </is>
+      </c>
+      <c r="BC18" t="inlineStr">
+        <is>
+          <t>1986.79614562238</t>
+        </is>
+      </c>
+      <c r="BD18" t="n">
+        <v>27388</v>
+      </c>
+      <c r="BE18" t="inlineStr">
+        <is>
+          <t>2025-11-25</t>
+        </is>
+      </c>
+      <c r="BF18" t="inlineStr">
+        <is>
+          <t>192.0</t>
+        </is>
+      </c>
+      <c r="BG18" t="inlineStr">
+        <is>
+          <t>2025/10/14</t>
+        </is>
+      </c>
+      <c r="BH18" t="inlineStr">
+        <is>
+          <t>6.25</t>
+        </is>
+      </c>
+      <c r="BI18" t="inlineStr">
+        <is>
+          <t>鼎翰</t>
+        </is>
+      </c>
+      <c r="BJ18" t="inlineStr">
+        <is>
+          <t>鼎翰</t>
+        </is>
+      </c>
+      <c r="BK18" t="inlineStr">
+        <is>
+          <t>電腦及週邊設備業</t>
+        </is>
+      </c>
+      <c r="BL18" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BM18" t="inlineStr">
+        <is>
+          <t>0.56</t>
+        </is>
+      </c>
+      <c r="BN18" t="inlineStr">
+        <is>
+          <t>-11.45161899724185</t>
+        </is>
+      </c>
+      <c r="BO18" t="inlineStr">
+        <is>
+          <t>22.56717409239306</t>
+        </is>
+      </c>
+      <c r="BP18" t="inlineStr">
+        <is>
+          <t>38.82556207928187</t>
+        </is>
+      </c>
+      <c r="BQ18" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR18" t="inlineStr">
+        <is>
+          <t>價-量增</t>
+        </is>
+      </c>
+      <c r="BS18" t="inlineStr">
+        <is>
           <t>1.93</t>
         </is>
       </c>
-      <c r="AS18" t="inlineStr">
-        <is>
-          <t>10.01</t>
-        </is>
-      </c>
-      <c r="AT18" t="inlineStr">
-        <is>
-          <t>-80.72</t>
-        </is>
-      </c>
-      <c r="AU18" t="inlineStr">
-        <is>
-          <t>2025/11/14</t>
-        </is>
-      </c>
-      <c r="AV18" t="inlineStr">
-        <is>
-          <t>28274.88146551724</t>
-        </is>
-      </c>
-      <c r="AW18" t="inlineStr">
-        <is>
-          <t>33609.0</t>
-        </is>
-      </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>14692.0</t>
-        </is>
-      </c>
-      <c r="AY18" t="inlineStr">
-        <is>
-          <t>12138.8</t>
-        </is>
-      </c>
-      <c r="AZ18" t="inlineStr">
-        <is>
-          <t>9836.78</t>
-        </is>
-      </c>
-      <c r="BA18" t="inlineStr">
-        <is>
-          <t>2553</t>
-        </is>
-      </c>
-      <c r="BB18" t="inlineStr">
-        <is>
-          <t>184.9729413194776</t>
-        </is>
-      </c>
-      <c r="BC18" t="inlineStr">
-        <is>
-          <t>1139.994316817598</t>
-        </is>
-      </c>
-      <c r="BD18" t="n">
-        <v>33609</v>
-      </c>
-      <c r="BE18" t="inlineStr">
-        <is>
-          <t>2025-11-22</t>
-        </is>
-      </c>
-      <c r="BF18" t="inlineStr">
-        <is>
-          <t>192.0</t>
-        </is>
-      </c>
-      <c r="BG18" t="inlineStr">
-        <is>
-          <t>2025/10/14</t>
-        </is>
-      </c>
-      <c r="BH18" t="inlineStr">
-        <is>
-          <t>4.95</t>
-        </is>
-      </c>
-      <c r="BI18" t="inlineStr">
-        <is>
-          <t>鼎翰</t>
-        </is>
-      </c>
-      <c r="BJ18" t="inlineStr">
-        <is>
-          <t>鼎翰</t>
-        </is>
-      </c>
-      <c r="BK18" t="inlineStr">
-        <is>
-          <t>電腦及週邊設備業</t>
-        </is>
-      </c>
-      <c r="BL18" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BM18" t="inlineStr">
-        <is>
-          <t>0.56</t>
-        </is>
-      </c>
-      <c r="BN18" t="inlineStr">
-        <is>
-          <t>-11.45161899724185</t>
-        </is>
-      </c>
-      <c r="BO18" t="inlineStr">
-        <is>
-          <t>22.56717409239306</t>
-        </is>
-      </c>
-      <c r="BP18" t="inlineStr">
-        <is>
-          <t>38.82556207928187</t>
-        </is>
-      </c>
-      <c r="BQ18" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR18" t="inlineStr">
-        <is>
-          <t>價漲量增</t>
-        </is>
-      </c>
-      <c r="BS18" t="inlineStr">
-        <is>
-          <t>1.91</t>
-        </is>
-      </c>
       <c r="BT18" t="inlineStr">
         <is>
-          <t>4.82</t>
+          <t>4.74</t>
         </is>
       </c>
       <c r="BU18" t="inlineStr">
@@ -8208,7 +8208,7 @@
       </c>
       <c r="BV18" t="inlineStr">
         <is>
-          <t>12.36</t>
+          <t>12.57</t>
         </is>
       </c>
       <c r="BW18" t="inlineStr">
@@ -8223,12 +8223,12 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>47.09</t>
+          <t>47.65</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>9844</t>
+          <t>10010</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -8248,22 +8248,22 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>199.0</t>
+          <t>201.5</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>202.5</t>
+          <t>206.5</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>198.5</t>
+          <t>201.5</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>201.5</t>
+          <t>204.0</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -8295,12 +8295,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>19.0</t>
+          <t>167.0</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8310,7 +8310,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>197.0</t>
+          <t>201.5</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8320,22 +8320,22 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>4.83</t>
+          <t>4.28</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>-2.32</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>21.03</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -8350,7 +8350,7 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>2025-11-22 00:00:00</t>
+          <t>2025-11-25 00:00:00</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
@@ -8375,7 +8375,7 @@
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>201.5</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
@@ -8390,7 +8390,7 @@
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">
@@ -8405,17 +8405,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>4.47</t>
+          <t>39.29</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>-1.27</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8431,67 +8431,67 @@
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>105</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>46.15</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>51.28</t>
+          <t>69.23</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>2.84</t>
+          <t>2.87</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>197.9</t>
+          <t>198.8</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>196.78</t>
+          <t>197.15</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>191.34</t>
+          <t>191.65</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>190.02</t>
+          <t>190.08</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>-11.24</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
@@ -8506,7 +8506,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-80.75</t>
+          <t>-80.72</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8516,50 +8516,50 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>28274.88146551724</t>
+          <t>28281.92324246772</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>3715.0</t>
+          <t>33609.0</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>9865.0</t>
+          <t>14692.0</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>9864.3</t>
+          <t>12138.8</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>9269.96</t>
+          <t>9836.78</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2553</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>11.33269122891031</t>
+          <t>184.9729413194776</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>-776.9723785041442</t>
+          <t>1139.994316817598</t>
         </is>
       </c>
       <c r="BD19" t="n">
-        <v>3715</v>
+        <v>33609</v>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="BF19" t="inlineStr">
@@ -8574,7 +8574,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2.60</t>
+          <t>4.95</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -8619,22 +8619,22 @@
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
         <is>
-          <t>4.82</t>
+          <t>4.74</t>
         </is>
       </c>
       <c r="BU19" t="inlineStr">
@@ -8644,7 +8644,7 @@
       </c>
       <c r="BV19" t="inlineStr">
         <is>
-          <t>12.36</t>
+          <t>12.57</t>
         </is>
       </c>
       <c r="BW19" t="inlineStr">
@@ -8659,12 +8659,12 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>47.09</t>
+          <t>47.65</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>9844</t>
+          <t>10010</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -8684,22 +8684,22 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>199.5</t>
+          <t>199.0</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>199.5</t>
+          <t>202.5</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>197.0</t>
+          <t>198.5</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>197.0</t>
+          <t>201.5</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8731,12 +8731,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>19.0</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8746,7 +8746,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>198.0</t>
+          <t>197.0</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8756,17 +8756,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>4.35</t>
+          <t>6.41</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>-2.32</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8786,7 +8786,7 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>2025-11-22 00:00:00</t>
+          <t>2025-11-25 00:00:00</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
@@ -8841,17 +8841,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>7.06</t>
+          <t>4.47</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>-1.27</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8867,72 +8867,72 @@
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>105</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>61.54</t>
+          <t>46.15</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>69.23</t>
+          <t>51.28</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>0.80</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>2.85</t>
+          <t>2.84</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>0.62</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>198.2</t>
+          <t>197.9</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>196.62</t>
+          <t>196.78</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>191.17</t>
+          <t>191.34</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>189.99</t>
+          <t>190.02</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>-6.74</t>
+          <t>-11.24</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8942,7 +8942,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-80.21</t>
+          <t>-80.75</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8952,46 +8952,46 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>28274.88146551724</t>
+          <t>28281.92324246772</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>5976.0</t>
+          <t>3715.0</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>10613.2</t>
+          <t>9865.0</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>10254.6</t>
+          <t>9864.3</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>9315.64</t>
+          <t>9269.96</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>358</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>154.6608857258293</t>
+          <t>11.33269122891031</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>-284.8186440172012</t>
+          <t>-776.9723785041442</t>
         </is>
       </c>
       <c r="BD20" t="n">
-        <v>5976</v>
+        <v>3715</v>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
@@ -9010,7 +9010,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>3.12</t>
+          <t>2.60</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -9055,22 +9055,22 @@
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
         <is>
-          <t>4.82</t>
+          <t>4.74</t>
         </is>
       </c>
       <c r="BU20" t="inlineStr">
@@ -9080,7 +9080,7 @@
       </c>
       <c r="BV20" t="inlineStr">
         <is>
-          <t>12.36</t>
+          <t>12.57</t>
         </is>
       </c>
       <c r="BW20" t="inlineStr">
@@ -9095,12 +9095,12 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>47.09</t>
+          <t>47.65</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>9844</t>
+          <t>10010</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
@@ -9120,22 +9120,22 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
+          <t>199.5</t>
+        </is>
+      </c>
+      <c r="CE20" t="inlineStr">
+        <is>
+          <t>199.5</t>
+        </is>
+      </c>
+      <c r="CF20" t="inlineStr">
+        <is>
           <t>197.0</t>
         </is>
       </c>
-      <c r="CE20" t="inlineStr">
-        <is>
-          <t>198.5</t>
-        </is>
-      </c>
-      <c r="CF20" t="inlineStr">
+      <c r="CG20" t="inlineStr">
         <is>
           <t>197.0</t>
-        </is>
-      </c>
-      <c r="CG20" t="inlineStr">
-        <is>
-          <t>198.0</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -9167,12 +9167,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-1.75</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>42.0</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9182,7 +9182,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>197.0</t>
+          <t>198.0</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9192,17 +9192,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>4.83</t>
+          <t>5.94</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>-2.32</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>16.90</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9222,7 +9222,7 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>2025-11-22 00:00:00</t>
+          <t>2025-11-25 00:00:00</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
@@ -9277,17 +9277,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>9.88</t>
+          <t>7.06</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>-1.78</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9303,72 +9303,72 @@
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>105</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>46.15</t>
+          <t>61.54</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>70.94</t>
+          <t>69.23</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>0.60</t>
+          <t>0.80</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>2.8</t>
+          <t>2.85</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>197.5</t>
+          <t>198.2</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>196.32</t>
+          <t>196.62</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>190.97</t>
+          <t>191.17</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>189.94</t>
+          <t>189.99</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>-5.98</t>
+          <t>-6.74</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>1.89</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9378,7 +9378,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-79.87</t>
+          <t>-80.21</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9388,46 +9388,46 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>28274.88146551724</t>
+          <t>28281.92324246772</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>8426.0</t>
+          <t>5976.0</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>12937.0</t>
+          <t>10613.2</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>11067.0</t>
+          <t>10254.6</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>9335.32</t>
+          <t>9315.64</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>1870</t>
+          <t>358</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>234.5662547700167</t>
+          <t>154.6608857258293</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>186.1802139647589</t>
+          <t>-284.8186440172012</t>
         </is>
       </c>
       <c r="BD21" t="n">
-        <v>8426</v>
+        <v>5976</v>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
@@ -9446,7 +9446,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2.60</t>
+          <t>3.12</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
@@ -9491,7 +9491,7 @@
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
@@ -9501,12 +9501,12 @@
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
         <is>
-          <t>4.82</t>
+          <t>4.74</t>
         </is>
       </c>
       <c r="BU21" t="inlineStr">
@@ -9516,7 +9516,7 @@
       </c>
       <c r="BV21" t="inlineStr">
         <is>
-          <t>12.36</t>
+          <t>12.57</t>
         </is>
       </c>
       <c r="BW21" t="inlineStr">
@@ -9531,12 +9531,12 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>47.09</t>
+          <t>47.65</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>9844</t>
+          <t>10010</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
@@ -9556,12 +9556,12 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>200.5</t>
+          <t>197.0</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>200.5</t>
+          <t>198.5</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
@@ -9571,7 +9571,7 @@
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>197.0</t>
+          <t>198.0</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -9603,12 +9603,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>-1.75</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>108.0</t>
+          <t>42.0</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9618,7 +9618,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>200.5</t>
+          <t>197.0</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9628,17 +9628,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>3.14</t>
+          <t>6.41</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>-2.32</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>11.96</t>
+          <t>16.90</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9658,7 +9658,7 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>2025-11-22 00:00:00</t>
+          <t>2025-11-25 00:00:00</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
@@ -9713,17 +9713,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>25.41</t>
+          <t>9.88</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>-0.74</t>
+          <t>-1.78</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9739,72 +9739,72 @@
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>105</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>46.15</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>82.83</t>
+          <t>70.94</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.60</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>2.72</t>
+          <t>2.8</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>196.9</t>
+          <t>197.5</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>196.0</t>
+          <t>196.32</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>190.81</t>
+          <t>190.97</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>189.91</t>
+          <t>189.94</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>-5.98</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>1.89</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9814,7 +9814,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-79.57</t>
+          <t>-79.87</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9824,46 +9824,46 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>28274.88146551724</t>
+          <t>28281.92324246772</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>21734.0</t>
+          <t>8426.0</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>13078.6</t>
+          <t>12937.0</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>11681.7</t>
+          <t>11067.0</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>9341.52</t>
+          <t>9335.32</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>1396</t>
+          <t>1870</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>243.363716734609</t>
+          <t>234.5662547700167</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>589.8864320116754</t>
+          <t>186.1802139647589</t>
         </is>
       </c>
       <c r="BD22" t="n">
-        <v>21734</v>
+        <v>8426</v>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
@@ -9882,7 +9882,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>4.43</t>
+          <t>2.60</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
@@ -9927,7 +9927,7 @@
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -9937,12 +9937,12 @@
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
         <is>
-          <t>4.82</t>
+          <t>4.74</t>
         </is>
       </c>
       <c r="BU22" t="inlineStr">
@@ -9952,7 +9952,7 @@
       </c>
       <c r="BV22" t="inlineStr">
         <is>
-          <t>12.36</t>
+          <t>12.57</t>
         </is>
       </c>
       <c r="BW22" t="inlineStr">
@@ -9967,12 +9967,12 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>47.09</t>
+          <t>47.65</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>9844</t>
+          <t>10010</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
@@ -9992,22 +9992,22 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>203.5</t>
+          <t>200.5</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>203.5</t>
+          <t>200.5</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>199.0</t>
+          <t>197.0</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>200.5</t>
+          <t>197.0</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -10039,12 +10039,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>48.0</t>
+          <t>108.0</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -10054,7 +10054,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>197.0</t>
+          <t>200.5</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -10064,17 +10064,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>4.83</t>
+          <t>4.75</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>-2.32</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>-10.99</t>
+          <t>11.96</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10094,7 +10094,7 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>2025-11-22 00:00:00</t>
+          <t>2025-11-25 00:00:00</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
@@ -10149,17 +10149,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11.29</t>
+          <t>25.41</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>-0.74</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10175,67 +10175,67 @@
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>105</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>52.27</t>
+          <t>82.83</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>2.72</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
+          <t>196.9</t>
+        </is>
+      </c>
+      <c r="AM23" t="inlineStr">
+        <is>
           <t>196.0</t>
         </is>
       </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>195.48</t>
-        </is>
-      </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>190.59</t>
+          <t>190.81</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>189.82</t>
+          <t>189.91</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>-11.56</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
@@ -10250,7 +10250,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-79.53</t>
+          <t>-79.57</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10260,46 +10260,46 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>28274.88146551724</t>
+          <t>28281.92324246772</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>9474.0</t>
+          <t>21734.0</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>9585.6</t>
+          <t>13078.6</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>10769.2</t>
+          <t>11681.7</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>9013.74</t>
+          <t>9341.52</t>
         </is>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>-1183</t>
+          <t>1396</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>180.3595866842333</t>
+          <t>243.363716734609</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>-280.314914778859</t>
+          <t>589.8864320116754</t>
         </is>
       </c>
       <c r="BD23" t="n">
-        <v>9474</v>
+        <v>21734</v>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
@@ -10318,7 +10318,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2.60</t>
+          <t>4.43</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
@@ -10363,7 +10363,7 @@
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -10373,12 +10373,12 @@
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
         <is>
-          <t>4.82</t>
+          <t>4.74</t>
         </is>
       </c>
       <c r="BU23" t="inlineStr">
@@ -10388,7 +10388,7 @@
       </c>
       <c r="BV23" t="inlineStr">
         <is>
-          <t>12.36</t>
+          <t>12.57</t>
         </is>
       </c>
       <c r="BW23" t="inlineStr">
@@ -10403,12 +10403,12 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>47.09</t>
+          <t>47.65</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>9844</t>
+          <t>10010</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
@@ -10428,22 +10428,22 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>196.0</t>
+          <t>203.5</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>197.5</t>
+          <t>203.5</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>195.0</t>
+          <t>199.0</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>197.0</t>
+          <t>200.5</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">

--- a/Result/checksun_type/HMI.xlsx
+++ b/Result/checksun_type/HMI.xlsx
@@ -883,42 +883,42 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>9.0</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>19.5</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>15.0</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>19.2</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-0.83</t>
+          <t>-1.77</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-2.21</t>
+          <t>-34.48</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-12.13</t>
+          <t>-10.76</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1019,52 +1019,52 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>3.23</t>
+          <t>26.92</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>9.68</t>
+          <t>11.12</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-6.04</t>
+          <t>-5.18</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-5.2</t>
+          <t>-5.44</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-3.45</t>
+          <t>-3.78</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>19.25</t>
+          <t>19.31</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>20.49</t>
+          <t>20.36</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>21.61</t>
+          <t>21.54</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
@@ -1074,17 +1074,17 @@
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-17.72</t>
+          <t>-10.91</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>-0.70</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-0.63</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-109.27</t>
+          <t>-109.53</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1104,46 +1104,46 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>30462.21090387375</t>
+          <t>30418.92550143267</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>290.0</t>
+          <t>166.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>804.0</t>
+          <t>494.2</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>822.2</t>
+          <t>754.3</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>1439.06</t>
+          <t>1394.4</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-18</t>
+          <t>-260</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-142.1735059305047</t>
+          <t>-142.3985018106445</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-112.2167003943315</t>
+          <t>-143.6359791514134</t>
         </is>
       </c>
       <c r="BD2" t="n">
-        <v>290</v>
+        <v>166</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-18.82</t>
+          <t>-17.55</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1207,7 +1207,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1217,7 +1217,7 @@
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
@@ -1247,12 +1247,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>84.96</t>
+          <t>86.4</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>560</t>
+          <t>569</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1272,22 +1272,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>19.2</t>
+          <t>19.3</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
+          <t>19.5</t>
+        </is>
+      </c>
+      <c r="CF2" t="inlineStr">
+        <is>
           <t>19.3</t>
         </is>
       </c>
-      <c r="CF2" t="inlineStr">
-        <is>
-          <t>19.2</t>
-        </is>
-      </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>19.2</t>
+          <t>19.5</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1319,12 +1319,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-1.53</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1344,17 +1344,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-0.83</t>
+          <t>-1.77</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>3.85</t>
+          <t>-2.21</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -1429,17 +1429,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1455,7 +1455,7 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
@@ -1465,62 +1465,62 @@
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>9.68</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-1.13</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-5.90</t>
+          <t>-6.04</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-4.83</t>
+          <t>-5.2</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-3.05</t>
+          <t>-3.45</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>19.42</t>
+          <t>19.25</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>20.64</t>
+          <t>20.49</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>21.68</t>
+          <t>21.61</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>22.37</t>
+          <t>22.38</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-21.10</t>
+          <t>-17.72</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-108.86</t>
+          <t>-109.27</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1540,46 +1540,46 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>30462.21090387375</t>
+          <t>30418.92550143267</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>1287.0</t>
+          <t>290.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>930.4</t>
+          <t>804.0</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>895.9</t>
+          <t>822.2</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>1833.62</t>
+          <t>1439.06</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>-18</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-147.6201978461726</t>
+          <t>-142.1735059305047</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-76.60999144155971</t>
+          <t>-112.2167003943315</t>
         </is>
       </c>
       <c r="BD3" t="n">
-        <v>1287</v>
+        <v>290</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1643,7 +1643,7 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1683,12 +1683,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>84.96</t>
+          <t>86.4</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>560</t>
+          <t>569</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1708,17 +1708,17 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>19.55</t>
+          <t>19.2</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>19.65</t>
+          <t>19.3</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>18.85</t>
+          <t>19.2</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1755,12 +1755,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>-1.53</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>26.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>19.5</t>
+          <t>19.2</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1780,17 +1780,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-1.56</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-0.83</t>
+          <t>-1.77</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-4.04</t>
+          <t>3.85</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1800,7 +1800,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-10.76</t>
+          <t>-12.13</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1865,17 +1865,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>3.17</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1891,72 +1891,72 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>22.58</t>
+          <t>3.23</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>7.53</t>
+          <t>8.6</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>-1.13</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-5.39</t>
+          <t>-5.90</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-4.43</t>
+          <t>-4.83</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-2.68</t>
+          <t>-3.05</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>19.67</t>
+          <t>19.42</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>20.79</t>
+          <t>20.64</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>21.75</t>
+          <t>21.68</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>22.35</t>
+          <t>22.37</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-23.19</t>
+          <t>-21.10</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-0.68</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-108.40</t>
+          <t>-108.86</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1976,46 +1976,46 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>30462.21090387375</t>
+          <t>30418.92550143267</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>497.0</t>
+          <t>1287.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>738.2</t>
+          <t>930.4</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>769.3</t>
+          <t>895.9</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>1851.22</t>
+          <t>1833.62</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-31</t>
+          <t>34</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-160.5311444651931</t>
+          <t>-147.6201978461726</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-129.8286218146873</t>
+          <t>-76.60999144155971</t>
         </is>
       </c>
       <c r="BD4" t="n">
-        <v>497</v>
+        <v>1287</v>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2034,7 +2034,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-17.55</t>
+          <t>-18.82</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2084,12 +2084,12 @@
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>84.96</t>
+          <t>86.4</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>560</t>
+          <t>569</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2144,22 +2144,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
+          <t>19.55</t>
+        </is>
+      </c>
+      <c r="CE4" t="inlineStr">
+        <is>
+          <t>19.65</t>
+        </is>
+      </c>
+      <c r="CF4" t="inlineStr">
+        <is>
+          <t>18.85</t>
+        </is>
+      </c>
+      <c r="CG4" t="inlineStr">
+        <is>
           <t>19.2</t>
-        </is>
-      </c>
-      <c r="CE4" t="inlineStr">
-        <is>
-          <t>19.5</t>
-        </is>
-      </c>
-      <c r="CF4" t="inlineStr">
-        <is>
-          <t>18.9</t>
-        </is>
-      </c>
-      <c r="CG4" t="inlineStr">
-        <is>
-          <t>19.5</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>26.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2206,7 +2206,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>19.15</t>
+          <t>19.5</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2216,17 +2216,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-0.83</t>
+          <t>-1.77</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>14.69</t>
+          <t>-4.04</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -2291,7 +2291,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-12.36</t>
+          <t>-10.76</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2301,17 +2301,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>3.17</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2327,72 +2327,72 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>22.58</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.53</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-3.58</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-5.17</t>
+          <t>-5.39</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-3.97</t>
+          <t>-4.43</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-2.33</t>
+          <t>-2.68</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>19.86</t>
+          <t>19.67</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>20.94</t>
+          <t>20.79</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>21.81</t>
+          <t>21.75</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>22.33</t>
+          <t>22.35</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-28.42</t>
+          <t>-23.19</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-0.68</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-0.55</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2402,7 +2402,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-107.91</t>
+          <t>-108.40</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2412,46 +2412,46 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>30462.21090387375</t>
+          <t>30418.92550143267</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>231.0</t>
+          <t>497.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>911.2</t>
+          <t>738.2</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>794.5</t>
+          <t>769.3</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>1867.82</t>
+          <t>1851.22</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>116</t>
+          <t>-31</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-166.1134213107396</t>
+          <t>-160.5311444651931</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-116.5756429972018</t>
+          <t>-129.8286218146873</t>
         </is>
       </c>
       <c r="BD5" t="n">
-        <v>231</v>
+        <v>497</v>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-19.03</t>
+          <t>-17.55</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2515,17 +2515,17 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2555,12 +2555,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>84.96</t>
+          <t>86.4</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>560</t>
+          <t>569</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2580,22 +2580,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>18.85</t>
+          <t>19.2</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>19.15</t>
+          <t>19.5</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>18.85</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>19.15</t>
+          <t>19.5</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-4.24</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2642,7 +2642,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>19.2</t>
+          <t>19.15</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2652,17 +2652,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-0.83</t>
+          <t>-1.77</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>21.51</t>
+          <t>14.69</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2672,7 +2672,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -2727,7 +2727,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-12.13</t>
+          <t>-12.36</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2737,17 +2737,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>3.15</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-3.37</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2763,7 +2763,7 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -2773,62 +2773,62 @@
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>15.38</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-4.81</t>
+          <t>-3.58</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-4.41</t>
+          <t>-5.17</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-3.49</t>
+          <t>-3.97</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-2.01</t>
+          <t>-2.33</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>20.17</t>
+          <t>19.86</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>21.1</t>
+          <t>20.94</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>21.86</t>
+          <t>21.81</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>22.31</t>
+          <t>22.33</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-25.64</t>
+          <t>-28.42</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2838,7 +2838,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-107.35</t>
+          <t>-107.91</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2848,46 +2848,46 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>30462.21090387375</t>
+          <t>30418.92550143267</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>1715.0</t>
+          <t>231.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>1014.4</t>
+          <t>911.2</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>834.8</t>
+          <t>794.5</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>1896.36</t>
+          <t>1867.82</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>179</t>
+          <t>116</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-175.1202900950192</t>
+          <t>-166.1134213107396</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-64.97940029375127</t>
+          <t>-116.5756429972018</t>
         </is>
       </c>
       <c r="BD6" t="n">
-        <v>1715</v>
+        <v>231</v>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-18.82</t>
+          <t>-19.03</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2951,7 +2951,7 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -2961,7 +2961,7 @@
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2991,12 +2991,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>84.96</t>
+          <t>86.4</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>560</t>
+          <t>569</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -3016,22 +3016,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>20.05</t>
+          <t>18.85</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>20.05</t>
+          <t>19.15</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>19.0</t>
+          <t>18.85</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>19.2</t>
+          <t>19.15</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-2.0</t>
+          <t>-4.24</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>46.0</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>20.05</t>
+          <t>19.2</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3088,17 +3088,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-4.43</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-0.83</t>
+          <t>-1.77</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>17.65</t>
+          <t>21.51</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3108,7 +3108,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -3163,7 +3163,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-8.24</t>
+          <t>-12.13</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3173,17 +3173,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>3.15</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>-3.37</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3199,7 +3199,7 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -3209,62 +3209,62 @@
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>23.08</t>
+          <t>15.38</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-1.91</t>
+          <t>-4.81</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-3.90</t>
+          <t>-4.41</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-2.98</t>
+          <t>-3.49</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-1.65</t>
+          <t>-2.01</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>20.44</t>
+          <t>20.17</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>21.27</t>
+          <t>21.1</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>21.92</t>
+          <t>21.86</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>22.29</t>
+          <t>22.31</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-16.23</t>
+          <t>-25.64</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3274,7 +3274,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-106.88</t>
+          <t>-107.35</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3284,46 +3284,46 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>30462.21090387375</t>
+          <t>30418.92550143267</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>922.0</t>
+          <t>1715.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>840.4</t>
+          <t>1014.4</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>714.3</t>
+          <t>834.8</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>1889.2</t>
+          <t>1896.36</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>126</t>
+          <t>179</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-195.1459064225224</t>
+          <t>-175.1202900950192</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-147.9497892783307</t>
+          <t>-64.97940029375127</t>
         </is>
       </c>
       <c r="BD7" t="n">
-        <v>922</v>
+        <v>1715</v>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-15.22</t>
+          <t>-18.82</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3387,7 +3387,7 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3397,7 +3397,7 @@
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>84.96</t>
+          <t>86.4</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>560</t>
+          <t>569</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3452,22 +3452,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>20.05</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>20.1</t>
+          <t>20.05</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>19.95</t>
+          <t>19.0</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>20.05</t>
+          <t>19.2</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3499,12 +3499,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-2.0</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>16.0</t>
+          <t>46.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>20.45</t>
+          <t>20.05</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3524,17 +3524,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-6.51</t>
+          <t>-2.82</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-0.83</t>
+          <t>-1.77</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>22.57</t>
+          <t>17.65</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3544,7 +3544,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-6.41</t>
+          <t>-8.24</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3609,17 +3609,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3635,72 +3635,72 @@
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>46.15</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>36.17</t>
+          <t>23.08</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-1.91</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-4.52</t>
+          <t>-3.90</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-2.41</t>
+          <t>-2.98</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-1.36</t>
+          <t>-1.65</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>20.46</t>
+          <t>20.44</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>21.43</t>
+          <t>21.27</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>21.96</t>
+          <t>21.92</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>22.26</t>
+          <t>22.29</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-15.32</t>
+          <t>-16.23</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.50</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-106.60</t>
+          <t>-106.88</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3720,46 +3720,46 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>30462.21090387375</t>
+          <t>30418.92550143267</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>326.0</t>
+          <t>922.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>861.4</t>
+          <t>840.4</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>702.8</t>
+          <t>714.3</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>2075.44</t>
+          <t>1889.2</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>158</t>
+          <t>126</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-203.7270186305573</t>
+          <t>-195.1459064225224</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-176.2307096392179</t>
+          <t>-147.9497892783307</t>
         </is>
       </c>
       <c r="BD8" t="n">
-        <v>326</v>
+        <v>922</v>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3778,7 +3778,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-13.53</t>
+          <t>-15.22</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3823,7 +3823,7 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -3833,7 +3833,7 @@
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>84.96</t>
+          <t>86.4</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>560</t>
+          <t>569</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3888,22 +3888,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>20.45</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>20.45</t>
+          <t>20.1</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>20.3</t>
+          <t>19.95</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>20.45</t>
+          <t>20.05</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3935,12 +3935,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-1.19</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3960,17 +3960,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-6.51</t>
+          <t>-4.87</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-0.83</t>
+          <t>-1.77</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>22.57</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3980,7 +3980,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -4045,17 +4045,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-1.95</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4071,62 +4071,62 @@
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>23.08</t>
+          <t>46.15</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>28.41</t>
+          <t>36.17</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-4.33</t>
+          <t>-4.52</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-2.52</t>
+          <t>-2.41</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>-1.36</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>20.53</t>
+          <t>20.46</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>21.46</t>
+          <t>21.43</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>22.01</t>
+          <t>21.96</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>22.23</t>
+          <t>22.26</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-20.19</t>
+          <t>-15.32</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-106.34</t>
+          <t>-106.60</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4156,46 +4156,46 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>30462.21090387375</t>
+          <t>30418.92550143267</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>1362.0</t>
+          <t>326.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>800.4</t>
+          <t>861.4</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>791.6</t>
+          <t>702.8</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>2169.22</t>
+          <t>2075.44</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>158</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-208.7263475380736</t>
+          <t>-203.7270186305573</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-146.4809276676563</t>
+          <t>-176.2307096392179</t>
         </is>
       </c>
       <c r="BD9" t="n">
-        <v>1362</v>
+        <v>326</v>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4259,7 +4259,7 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4299,12 +4299,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>84.96</t>
+          <t>86.4</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>560</t>
+          <t>569</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4324,12 +4324,12 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>21.0</t>
+          <t>20.45</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>21.0</t>
+          <t>20.45</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
@@ -4371,12 +4371,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>-1.19</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>36.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4386,7 +4386,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>20.7</t>
+          <t>20.45</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4396,17 +4396,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-7.81</t>
+          <t>-4.87</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-0.83</t>
+          <t>-1.77</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-32.18</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -4471,7 +4471,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-5.26</t>
+          <t>-6.41</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4481,17 +4481,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>-1.95</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4507,62 +4507,62 @@
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>39.29</t>
+          <t>23.08</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>20.71</t>
+          <t>28.41</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-4.13</t>
+          <t>-4.33</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-2.66</t>
+          <t>-2.52</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-0.54</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>20.6</t>
+          <t>20.53</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>21.49</t>
+          <t>21.46</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>22.08</t>
+          <t>22.01</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>22.19</t>
+          <t>22.23</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-25.12</t>
+          <t>-20.19</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
@@ -4572,7 +4572,7 @@
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4582,7 +4582,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-106.02</t>
+          <t>-106.34</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4592,46 +4592,46 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>30462.21090387375</t>
+          <t>30418.92550143267</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>747.0</t>
+          <t>1362.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>677.8</t>
+          <t>800.4</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>999.4</t>
+          <t>791.6</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>2614.76</t>
+          <t>2169.22</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-321</t>
+          <t>8</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-220.0436966054221</t>
+          <t>-208.7263475380736</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-209.7497774344375</t>
+          <t>-146.4809276676563</t>
         </is>
       </c>
       <c r="BD10" t="n">
-        <v>747</v>
+        <v>1362</v>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-12.47</t>
+          <t>-13.53</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4695,7 +4695,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4705,7 +4705,7 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4735,12 +4735,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>84.96</t>
+          <t>86.4</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>560</t>
+          <t>569</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4760,22 +4760,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>20.6</t>
+          <t>21.0</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>20.95</t>
+          <t>21.0</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>20.55</t>
+          <t>20.3</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>20.7</t>
+          <t>20.45</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4807,12 +4807,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>41.0</t>
+          <t>36.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4822,7 +4822,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>20.55</t>
+          <t>20.7</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4832,17 +4832,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-7.03</t>
+          <t>-6.15</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-0.83</t>
+          <t>-1.77</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-33.22</t>
+          <t>-32.18</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4852,7 +4852,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-5.95</t>
+          <t>-5.26</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4917,17 +4917,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-4.11</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4943,72 +4943,72 @@
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>22.86</t>
+          <t>39.29</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>19.66</t>
+          <t>20.71</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-4.71</t>
+          <t>-4.13</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-2.98</t>
+          <t>-2.66</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-0.54</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>20.49</t>
+          <t>20.6</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>21.5</t>
+          <t>21.49</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>22.16</t>
+          <t>22.08</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>22.16</t>
+          <t>22.19</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-36.40</t>
+          <t>-25.12</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>-0.50</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -5018,7 +5018,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-105.65</t>
+          <t>-106.02</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -5028,46 +5028,46 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>30462.21090387375</t>
+          <t>30418.92550143267</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>845.0</t>
+          <t>747.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>655.2</t>
+          <t>677.8</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>981.2</t>
+          <t>999.4</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>2840.22</t>
+          <t>2614.76</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-326</t>
+          <t>-321</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-221.9153182728739</t>
+          <t>-220.0436966054221</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-226.749927907181</t>
+          <t>-209.7497774344375</t>
         </is>
       </c>
       <c r="BD11" t="n">
-        <v>845</v>
+        <v>747</v>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5086,7 +5086,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-13.11</t>
+          <t>-12.47</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5131,7 +5131,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5141,7 +5141,7 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5171,12 +5171,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>84.96</t>
+          <t>86.4</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>560</t>
+          <t>569</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5196,22 +5196,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>20.2</t>
+          <t>20.6</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>21.75</t>
+          <t>20.95</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>20.2</t>
+          <t>20.55</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>20.55</t>
+          <t>20.7</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5243,12 +5243,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-3.22</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>51.0</t>
+          <t>41.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5258,7 +5258,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>20.15</t>
+          <t>20.55</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5268,17 +5268,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-4.95</t>
+          <t>-5.38</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-0.83</t>
+          <t>-1.77</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-37.93</t>
+          <t>-33.22</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5288,7 +5288,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -5343,7 +5343,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-7.78</t>
+          <t>-5.95</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5353,17 +5353,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-0.74</t>
+          <t>-4.11</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5379,72 +5379,72 @@
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>22.86</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>22.61</t>
+          <t>19.66</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-1.80</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-4.79</t>
+          <t>-4.71</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-2.96</t>
+          <t>-2.98</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>20.52</t>
+          <t>20.49</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>21.55</t>
+          <t>21.5</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>22.21</t>
+          <t>22.16</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>22.13</t>
+          <t>22.16</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-47.43</t>
+          <t>-36.40</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.50</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.37</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5454,7 +5454,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-105.13</t>
+          <t>-105.65</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5464,46 +5464,46 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>30462.21090387375</t>
+          <t>30418.92550143267</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>1027.0</t>
+          <t>845.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>588.2</t>
+          <t>655.2</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>947.7</t>
+          <t>981.2</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>2910.12</t>
+          <t>2840.22</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-359</t>
+          <t>-326</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-221.0362983393635</t>
+          <t>-221.9153182728739</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-253.4376454429865</t>
+          <t>-226.749927907181</t>
         </is>
       </c>
       <c r="BD12" t="n">
-        <v>1027</v>
+        <v>845</v>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5522,7 +5522,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-14.80</t>
+          <t>-13.11</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5577,7 +5577,7 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5607,12 +5607,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>84.96</t>
+          <t>86.4</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>560</t>
+          <t>569</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5637,17 +5637,17 @@
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>20.4</t>
+          <t>21.75</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>20.05</t>
+          <t>20.2</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>20.15</t>
+          <t>20.55</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5679,12 +5679,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>105.0</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5694,7 +5694,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>210.5</t>
+          <t>214.0</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5709,12 +5709,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-2.32</t>
+          <t>-0.79</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>13.00</t>
+          <t>7.97</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5734,7 +5734,7 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>2025-11-25 00:00:00</t>
+          <t>2025-11-26 00:00:00</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -5774,7 +5774,7 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>4.47</t>
+          <t>6.20</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
@@ -5789,17 +5789,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>24.71</t>
+          <t>30.12</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5815,7 +5815,7 @@
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>128</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
@@ -5830,57 +5830,57 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>2.93</t>
+          <t>3.18</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>2.52</t>
+          <t>3.54</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>2.93</t>
+          <t>3.07</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>204.5</t>
+          <t>207.4</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>199.48</t>
+          <t>200.3</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>193.8</t>
+          <t>194.34</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>191.47</t>
+          <t>191.84</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>34.99</t>
+          <t>43.78</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>4.06</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>2.52</t>
+          <t>2.83</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5890,7 +5890,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-74.87</t>
+          <t>-71.78</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5900,50 +5900,50 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>28281.92324246772</t>
+          <t>28299.69197707737</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>22122.0</t>
+          <t>27123.0</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>20551.2</t>
+          <t>21655.6</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>18187.0</t>
+          <t>20056.7</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>11819.44</t>
+          <t>12284.3</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>2364</t>
+          <t>1598</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>1229.675320671625</t>
+          <t>1393.334091030001</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>1997.731985848452</t>
+          <t>2293.457328001074</t>
         </is>
       </c>
       <c r="BD13" t="n">
-        <v>22122</v>
+        <v>27123</v>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="BF13" t="inlineStr">
@@ -5958,7 +5958,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>9.64</t>
+          <t>11.46</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -6003,7 +6003,7 @@
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
         <is>
-          <t>4.74</t>
+          <t>4.66</t>
         </is>
       </c>
       <c r="BU13" t="inlineStr">
@@ -6028,7 +6028,7 @@
       </c>
       <c r="BV13" t="inlineStr">
         <is>
-          <t>12.57</t>
+          <t>12.78</t>
         </is>
       </c>
       <c r="BW13" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>47.65</t>
+          <t>48.44</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>10010</t>
+          <t>10177</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -6068,22 +6068,22 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>208.5</t>
+          <t>211.0</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>211.0</t>
+          <t>214.0</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>208.0</t>
+          <t>210.5</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>210.5</t>
+          <t>214.0</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6115,12 +6115,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>105.0</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6130,7 +6130,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>207.0</t>
+          <t>210.5</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6140,17 +6140,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-2.32</t>
+          <t>-0.79</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>19.04</t>
+          <t>13.00</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6170,7 +6170,7 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>2025-11-25 00:00:00</t>
+          <t>2025-11-26 00:00:00</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -6210,7 +6210,7 @@
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>2.73</t>
+          <t>4.47</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
@@ -6225,17 +6225,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>30.12</t>
+          <t>24.71</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6251,7 +6251,7 @@
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>128</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
@@ -6261,62 +6261,62 @@
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>85.71</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>2.93</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>2.52</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>2.89</t>
+          <t>2.93</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>203.2</t>
+          <t>204.5</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>198.92</t>
+          <t>199.48</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>193.33</t>
+          <t>193.8</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>191.14</t>
+          <t>191.47</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>24.29</t>
+          <t>34.99</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>2.85</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>2.52</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6326,7 +6326,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-77.07</t>
+          <t>-74.87</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6336,50 +6336,50 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>28281.92324246772</t>
+          <t>28299.69197707737</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>26279.0</t>
+          <t>22122.0</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>21604.4</t>
+          <t>20551.2</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>18148.2</t>
+          <t>18187.0</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>11512.0</t>
+          <t>11819.44</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>3456</t>
+          <t>2364</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>1090.028654275838</t>
+          <t>1229.675320671625</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>2039.741068992971</t>
+          <t>1997.731985848452</t>
         </is>
       </c>
       <c r="BD14" t="n">
-        <v>26279</v>
+        <v>22122</v>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="BF14" t="inlineStr">
@@ -6394,7 +6394,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>7.81</t>
+          <t>9.64</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -6444,17 +6444,17 @@
       </c>
       <c r="BR14" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
         <is>
-          <t>4.74</t>
+          <t>4.66</t>
         </is>
       </c>
       <c r="BU14" t="inlineStr">
@@ -6464,7 +6464,7 @@
       </c>
       <c r="BV14" t="inlineStr">
         <is>
-          <t>12.57</t>
+          <t>12.78</t>
         </is>
       </c>
       <c r="BW14" t="inlineStr">
@@ -6479,12 +6479,12 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>47.65</t>
+          <t>48.44</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>10010</t>
+          <t>10177</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -6504,22 +6504,22 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>203.5</t>
+          <t>208.5</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
+          <t>211.0</t>
+        </is>
+      </c>
+      <c r="CF14" t="inlineStr">
+        <is>
           <t>208.0</t>
         </is>
       </c>
-      <c r="CF14" t="inlineStr">
-        <is>
-          <t>202.0</t>
-        </is>
-      </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>207.0</t>
+          <t>210.5</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -6551,12 +6551,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>112.0</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6566,7 +6566,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>204.5</t>
+          <t>207.0</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6576,17 +6576,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2.85</t>
+          <t>3.27</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-2.32</t>
+          <t>-0.79</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>40.09</t>
+          <t>19.04</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6606,7 +6606,7 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>2025-11-25 00:00:00</t>
+          <t>2025-11-26 00:00:00</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -6646,7 +6646,7 @@
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>2.73</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
@@ -6661,17 +6661,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>26.35</t>
+          <t>30.12</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6687,7 +6687,7 @@
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>128</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
@@ -6697,62 +6697,62 @@
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>64.29</t>
+          <t>85.71</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>2.93</t>
+          <t>2.89</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>202.1</t>
+          <t>203.2</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>198.58</t>
+          <t>198.92</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>192.93</t>
+          <t>193.33</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>190.87</t>
+          <t>191.14</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>14.78</t>
+          <t>24.29</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>2.48</t>
+          <t>2.85</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6762,7 +6762,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-78.46</t>
+          <t>-77.07</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6772,50 +6772,50 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>28281.92324246772</t>
+          <t>28299.69197707737</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>22703.0</t>
+          <t>26279.0</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>23070.4</t>
+          <t>21604.4</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>16467.7</t>
+          <t>18148.2</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>11056.48</t>
+          <t>11512.0</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>6602</t>
+          <t>3456</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>917.3536697818137</t>
+          <t>1090.028654275838</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>1581.513292449679</t>
+          <t>2039.741068992971</t>
         </is>
       </c>
       <c r="BD15" t="n">
-        <v>22703</v>
+        <v>26279</v>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="BF15" t="inlineStr">
@@ -6830,7 +6830,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>6.51</t>
+          <t>7.81</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -6875,22 +6875,22 @@
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
         <is>
-          <t>4.74</t>
+          <t>4.66</t>
         </is>
       </c>
       <c r="BU15" t="inlineStr">
@@ -6900,7 +6900,7 @@
       </c>
       <c r="BV15" t="inlineStr">
         <is>
-          <t>12.57</t>
+          <t>12.78</t>
         </is>
       </c>
       <c r="BW15" t="inlineStr">
@@ -6915,12 +6915,12 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>47.65</t>
+          <t>48.44</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>10010</t>
+          <t>10177</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -6940,22 +6940,22 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
+          <t>203.5</t>
+        </is>
+      </c>
+      <c r="CE15" t="inlineStr">
+        <is>
+          <t>208.0</t>
+        </is>
+      </c>
+      <c r="CF15" t="inlineStr">
+        <is>
           <t>202.0</t>
         </is>
       </c>
-      <c r="CE15" t="inlineStr">
-        <is>
-          <t>205.0</t>
-        </is>
-      </c>
-      <c r="CF15" t="inlineStr">
-        <is>
-          <t>202.0</t>
-        </is>
-      </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>204.5</t>
+          <t>207.0</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>112.0</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -7002,7 +7002,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>201.0</t>
+          <t>204.5</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -7012,17 +7012,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>4.51</t>
+          <t>4.44</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-2.32</t>
+          <t>-0.79</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>28.98</t>
+          <t>40.09</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7042,7 +7042,7 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>2025-11-25 00:00:00</t>
+          <t>2025-11-26 00:00:00</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -7082,7 +7082,7 @@
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
@@ -7097,17 +7097,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11.76</t>
+          <t>26.35</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7123,12 +7123,12 @@
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>128</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>57.14</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
@@ -7138,57 +7138,57 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>2.94</t>
+          <t>2.93</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>200.6</t>
+          <t>202.1</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>198.25</t>
+          <t>198.58</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>192.58</t>
+          <t>192.93</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>190.62</t>
+          <t>190.87</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>6.46</t>
+          <t>14.78</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>2.21</t>
+          <t>2.48</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>2.16</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7198,7 +7198,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-79.25</t>
+          <t>-78.46</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7208,50 +7208,50 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>28281.92324246772</t>
+          <t>28299.69197707737</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>10051.0</t>
+          <t>22703.0</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>19272.8</t>
+          <t>23070.4</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>14943.0</t>
+          <t>16467.7</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>10672.76</t>
+          <t>11056.48</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>4329</t>
+          <t>6602</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>796.5973747512926</t>
+          <t>917.3536697818137</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>1253.562422657489</t>
+          <t>1581.513292449679</t>
         </is>
       </c>
       <c r="BD16" t="n">
-        <v>10051</v>
+        <v>22703</v>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="BF16" t="inlineStr">
@@ -7266,7 +7266,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>4.69</t>
+          <t>6.51</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -7311,22 +7311,22 @@
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
         <is>
-          <t>4.74</t>
+          <t>4.66</t>
         </is>
       </c>
       <c r="BU16" t="inlineStr">
@@ -7336,7 +7336,7 @@
       </c>
       <c r="BV16" t="inlineStr">
         <is>
-          <t>12.57</t>
+          <t>12.78</t>
         </is>
       </c>
       <c r="BW16" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>47.65</t>
+          <t>48.44</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>10010</t>
+          <t>10177</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -7376,22 +7376,22 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>199.5</t>
+          <t>202.0</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
+          <t>205.0</t>
+        </is>
+      </c>
+      <c r="CF16" t="inlineStr">
+        <is>
           <t>202.0</t>
         </is>
       </c>
-      <c r="CF16" t="inlineStr">
-        <is>
-          <t>198.5</t>
-        </is>
-      </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>201.0</t>
+          <t>204.5</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-2.2</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>107.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7438,7 +7438,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>199.5</t>
+          <t>201.0</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7448,17 +7448,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>5.23</t>
+          <t>6.07</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-2.32</t>
+          <t>-0.79</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>17.59</t>
+          <t>28.98</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7478,7 +7478,7 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>2025-11-25 00:00:00</t>
+          <t>2025-11-26 00:00:00</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -7518,7 +7518,7 @@
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
@@ -7533,17 +7533,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>25.18</t>
+          <t>11.76</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>-2.00</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7559,72 +7559,72 @@
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>128</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>35.71</t>
+          <t>57.14</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>78.57</t>
+          <t>64.29</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>2.96</t>
+          <t>2.94</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>200.0</t>
+          <t>200.6</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>197.98</t>
+          <t>198.25</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>192.28</t>
+          <t>192.58</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>190.44</t>
+          <t>190.62</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>7.56</t>
+          <t>6.46</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>2.21</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7634,7 +7634,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-79.59</t>
+          <t>-79.25</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7644,50 +7644,50 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>28281.92324246772</t>
+          <t>28299.69197707737</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>21601.0</t>
+          <t>10051.0</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>18457.8</t>
+          <t>19272.8</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>15697.4</t>
+          <t>14943.0</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>10622.98</t>
+          <t>10672.76</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>2760</t>
+          <t>4329</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>713.5128205865296</t>
+          <t>796.5973747512926</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>2095.862522145168</t>
+          <t>1253.562422657489</t>
         </is>
       </c>
       <c r="BD17" t="n">
-        <v>21601</v>
+        <v>10051</v>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="BF17" t="inlineStr">
@@ -7702,7 +7702,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>3.91</t>
+          <t>4.69</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -7747,22 +7747,22 @@
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>1.89</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
         <is>
-          <t>4.74</t>
+          <t>4.66</t>
         </is>
       </c>
       <c r="BU17" t="inlineStr">
@@ -7772,7 +7772,7 @@
       </c>
       <c r="BV17" t="inlineStr">
         <is>
-          <t>12.57</t>
+          <t>12.78</t>
         </is>
       </c>
       <c r="BW17" t="inlineStr">
@@ -7787,12 +7787,12 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>47.65</t>
+          <t>48.44</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>10010</t>
+          <t>10177</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -7812,22 +7812,22 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>205.0</t>
+          <t>199.5</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>205.0</t>
+          <t>202.0</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>198.0</t>
+          <t>198.5</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>199.5</t>
+          <t>201.0</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7859,12 +7859,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>-2.2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>107.0</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7874,7 +7874,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>204.0</t>
+          <t>199.5</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7884,17 +7884,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>3.09</t>
+          <t>6.78</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-2.32</t>
+          <t>-0.79</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>9.50</t>
+          <t>17.59</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7914,7 +7914,7 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>2025-11-25 00:00:00</t>
+          <t>2025-11-26 00:00:00</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
@@ -7954,7 +7954,7 @@
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="W18" t="inlineStr">
@@ -7969,17 +7969,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>31.53</t>
+          <t>25.18</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>-2.00</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7995,27 +7995,27 @@
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>128</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>35.71</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>82.05</t>
+          <t>78.57</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
@@ -8025,245 +8025,245 @@
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
+          <t>200.0</t>
+        </is>
+      </c>
+      <c r="AM18" t="inlineStr">
+        <is>
+          <t>197.98</t>
+        </is>
+      </c>
+      <c r="AN18" t="inlineStr">
+        <is>
+          <t>192.28</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>190.44</t>
+        </is>
+      </c>
+      <c r="AP18" t="inlineStr">
+        <is>
+          <t>7.56</t>
+        </is>
+      </c>
+      <c r="AQ18" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="AR18" t="inlineStr">
+        <is>
+          <t>2.04</t>
+        </is>
+      </c>
+      <c r="AS18" t="inlineStr">
+        <is>
+          <t>10.01</t>
+        </is>
+      </c>
+      <c r="AT18" t="inlineStr">
+        <is>
+          <t>-79.59</t>
+        </is>
+      </c>
+      <c r="AU18" t="inlineStr">
+        <is>
+          <t>2025/11/14</t>
+        </is>
+      </c>
+      <c r="AV18" t="inlineStr">
+        <is>
+          <t>28299.69197707737</t>
+        </is>
+      </c>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>21601.0</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>18457.8</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>15697.4</t>
+        </is>
+      </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>10622.98</t>
+        </is>
+      </c>
+      <c r="BA18" t="inlineStr">
+        <is>
+          <t>2760</t>
+        </is>
+      </c>
+      <c r="BB18" t="inlineStr">
+        <is>
+          <t>713.5128205865296</t>
+        </is>
+      </c>
+      <c r="BC18" t="inlineStr">
+        <is>
+          <t>2095.862522145168</t>
+        </is>
+      </c>
+      <c r="BD18" t="n">
+        <v>21601</v>
+      </c>
+      <c r="BE18" t="inlineStr">
+        <is>
+          <t>2025-11-26</t>
+        </is>
+      </c>
+      <c r="BF18" t="inlineStr">
+        <is>
+          <t>192.0</t>
+        </is>
+      </c>
+      <c r="BG18" t="inlineStr">
+        <is>
+          <t>2025/10/14</t>
+        </is>
+      </c>
+      <c r="BH18" t="inlineStr">
+        <is>
+          <t>3.91</t>
+        </is>
+      </c>
+      <c r="BI18" t="inlineStr">
+        <is>
+          <t>鼎翰</t>
+        </is>
+      </c>
+      <c r="BJ18" t="inlineStr">
+        <is>
+          <t>鼎翰</t>
+        </is>
+      </c>
+      <c r="BK18" t="inlineStr">
+        <is>
+          <t>電腦及週邊設備業</t>
+        </is>
+      </c>
+      <c r="BL18" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BM18" t="inlineStr">
+        <is>
+          <t>0.56</t>
+        </is>
+      </c>
+      <c r="BN18" t="inlineStr">
+        <is>
+          <t>-11.45161899724185</t>
+        </is>
+      </c>
+      <c r="BO18" t="inlineStr">
+        <is>
+          <t>22.56717409239306</t>
+        </is>
+      </c>
+      <c r="BP18" t="inlineStr">
+        <is>
+          <t>38.82556207928187</t>
+        </is>
+      </c>
+      <c r="BQ18" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR18" t="inlineStr">
+        <is>
+          <t>價-量增</t>
+        </is>
+      </c>
+      <c r="BS18" t="inlineStr">
+        <is>
+          <t>1.89</t>
+        </is>
+      </c>
+      <c r="BT18" t="inlineStr">
+        <is>
+          <t>4.66</t>
+        </is>
+      </c>
+      <c r="BU18" t="inlineStr">
+        <is>
+          <t>57.78</t>
+        </is>
+      </c>
+      <c r="BV18" t="inlineStr">
+        <is>
+          <t>12.78</t>
+        </is>
+      </c>
+      <c r="BW18" t="inlineStr">
+        <is>
+          <t>33.69%</t>
+        </is>
+      </c>
+      <c r="BX18" t="inlineStr">
+        <is>
+          <t>11.08%</t>
+        </is>
+      </c>
+      <c r="BY18" t="inlineStr">
+        <is>
+          <t>48.44</t>
+        </is>
+      </c>
+      <c r="BZ18" t="inlineStr">
+        <is>
+          <t>10177</t>
+        </is>
+      </c>
+      <c r="CA18" t="inlineStr">
+        <is>
+          <t>條碼印表機及零配件52.71%、印表機各式標籤紙及其耗材41.09%、企業行動電腦6.20% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB18" t="inlineStr">
+        <is>
+          <t>鼎翰-電腦及週邊設備業-上櫃</t>
+        </is>
+      </c>
+      <c r="CC18" t="inlineStr">
+        <is>
+          <t>電腦及週邊設備業平上櫃</t>
+        </is>
+      </c>
+      <c r="CD18" t="inlineStr">
+        <is>
+          <t>205.0</t>
+        </is>
+      </c>
+      <c r="CE18" t="inlineStr">
+        <is>
+          <t>205.0</t>
+        </is>
+      </c>
+      <c r="CF18" t="inlineStr">
+        <is>
+          <t>198.0</t>
+        </is>
+      </c>
+      <c r="CG18" t="inlineStr">
+        <is>
           <t>199.5</t>
-        </is>
-      </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>197.7</t>
-        </is>
-      </c>
-      <c r="AN18" t="inlineStr">
-        <is>
-          <t>192.01</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>190.29</t>
-        </is>
-      </c>
-      <c r="AP18" t="inlineStr">
-        <is>
-          <t>14.82</t>
-        </is>
-      </c>
-      <c r="AQ18" t="inlineStr">
-        <is>
-          <t>2.30</t>
-        </is>
-      </c>
-      <c r="AR18" t="inlineStr">
-        <is>
-          <t>2.01</t>
-        </is>
-      </c>
-      <c r="AS18" t="inlineStr">
-        <is>
-          <t>10.01</t>
-        </is>
-      </c>
-      <c r="AT18" t="inlineStr">
-        <is>
-          <t>-79.98</t>
-        </is>
-      </c>
-      <c r="AU18" t="inlineStr">
-        <is>
-          <t>2025/11/14</t>
-        </is>
-      </c>
-      <c r="AV18" t="inlineStr">
-        <is>
-          <t>28281.92324246772</t>
-        </is>
-      </c>
-      <c r="AW18" t="inlineStr">
-        <is>
-          <t>27388.0</t>
-        </is>
-      </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>15822.8</t>
-        </is>
-      </c>
-      <c r="AY18" t="inlineStr">
-        <is>
-          <t>14450.7</t>
-        </is>
-      </c>
-      <c r="AZ18" t="inlineStr">
-        <is>
-          <t>10277.46</t>
-        </is>
-      </c>
-      <c r="BA18" t="inlineStr">
-        <is>
-          <t>1372</t>
-        </is>
-      </c>
-      <c r="BB18" t="inlineStr">
-        <is>
-          <t>462.1765112122318</t>
-        </is>
-      </c>
-      <c r="BC18" t="inlineStr">
-        <is>
-          <t>1986.79614562238</t>
-        </is>
-      </c>
-      <c r="BD18" t="n">
-        <v>27388</v>
-      </c>
-      <c r="BE18" t="inlineStr">
-        <is>
-          <t>2025-11-25</t>
-        </is>
-      </c>
-      <c r="BF18" t="inlineStr">
-        <is>
-          <t>192.0</t>
-        </is>
-      </c>
-      <c r="BG18" t="inlineStr">
-        <is>
-          <t>2025/10/14</t>
-        </is>
-      </c>
-      <c r="BH18" t="inlineStr">
-        <is>
-          <t>6.25</t>
-        </is>
-      </c>
-      <c r="BI18" t="inlineStr">
-        <is>
-          <t>鼎翰</t>
-        </is>
-      </c>
-      <c r="BJ18" t="inlineStr">
-        <is>
-          <t>鼎翰</t>
-        </is>
-      </c>
-      <c r="BK18" t="inlineStr">
-        <is>
-          <t>電腦及週邊設備業</t>
-        </is>
-      </c>
-      <c r="BL18" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BM18" t="inlineStr">
-        <is>
-          <t>0.56</t>
-        </is>
-      </c>
-      <c r="BN18" t="inlineStr">
-        <is>
-          <t>-11.45161899724185</t>
-        </is>
-      </c>
-      <c r="BO18" t="inlineStr">
-        <is>
-          <t>22.56717409239306</t>
-        </is>
-      </c>
-      <c r="BP18" t="inlineStr">
-        <is>
-          <t>38.82556207928187</t>
-        </is>
-      </c>
-      <c r="BQ18" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR18" t="inlineStr">
-        <is>
-          <t>價-量增</t>
-        </is>
-      </c>
-      <c r="BS18" t="inlineStr">
-        <is>
-          <t>1.93</t>
-        </is>
-      </c>
-      <c r="BT18" t="inlineStr">
-        <is>
-          <t>4.74</t>
-        </is>
-      </c>
-      <c r="BU18" t="inlineStr">
-        <is>
-          <t>57.78</t>
-        </is>
-      </c>
-      <c r="BV18" t="inlineStr">
-        <is>
-          <t>12.57</t>
-        </is>
-      </c>
-      <c r="BW18" t="inlineStr">
-        <is>
-          <t>33.69%</t>
-        </is>
-      </c>
-      <c r="BX18" t="inlineStr">
-        <is>
-          <t>11.08%</t>
-        </is>
-      </c>
-      <c r="BY18" t="inlineStr">
-        <is>
-          <t>47.65</t>
-        </is>
-      </c>
-      <c r="BZ18" t="inlineStr">
-        <is>
-          <t>10010</t>
-        </is>
-      </c>
-      <c r="CA18" t="inlineStr">
-        <is>
-          <t>條碼印表機及零配件52.71%、印表機各式標籤紙及其耗材41.09%、企業行動電腦6.20% (2024年)</t>
-        </is>
-      </c>
-      <c r="CB18" t="inlineStr">
-        <is>
-          <t>鼎翰-電腦及週邊設備業-上櫃</t>
-        </is>
-      </c>
-      <c r="CC18" t="inlineStr">
-        <is>
-          <t>電腦及週邊設備業平上櫃</t>
-        </is>
-      </c>
-      <c r="CD18" t="inlineStr">
-        <is>
-          <t>201.5</t>
-        </is>
-      </c>
-      <c r="CE18" t="inlineStr">
-        <is>
-          <t>206.5</t>
-        </is>
-      </c>
-      <c r="CF18" t="inlineStr">
-        <is>
-          <t>201.5</t>
-        </is>
-      </c>
-      <c r="CG18" t="inlineStr">
-        <is>
-          <t>204.0</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -8295,12 +8295,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>167.0</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8310,74 +8310,74 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
+          <t>204.0</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>4.67</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>-0.79</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>9.50</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>2025-11-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>2025-11-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>2025-10-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>2025-11-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
           <t>201.5</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>4.28</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>-2.32</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>21.03</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>2025-11-14</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>2025-11-14 00:00:00</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>2025-11-25 00:00:00</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>2025-10-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>2025-11-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q19" t="inlineStr">
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
         <is>
           <t>201.5</t>
         </is>
       </c>
-      <c r="R19" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>201.5</t>
-        </is>
-      </c>
       <c r="T19" t="inlineStr">
         <is>
           <t>195.5</t>
@@ -8390,7 +8390,7 @@
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">
@@ -8405,17 +8405,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>39.29</t>
+          <t>31.53</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8431,7 +8431,7 @@
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>128</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
@@ -8441,200 +8441,200 @@
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>69.23</t>
+          <t>82.05</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>2.87</t>
+          <t>2.96</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>198.8</t>
+          <t>199.5</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>197.15</t>
+          <t>197.7</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>191.65</t>
+          <t>192.01</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>190.08</t>
+          <t>190.29</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>14.82</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
+          <t>2.01</t>
+        </is>
+      </c>
+      <c r="AS19" t="inlineStr">
+        <is>
+          <t>10.01</t>
+        </is>
+      </c>
+      <c r="AT19" t="inlineStr">
+        <is>
+          <t>-79.98</t>
+        </is>
+      </c>
+      <c r="AU19" t="inlineStr">
+        <is>
+          <t>2025/11/14</t>
+        </is>
+      </c>
+      <c r="AV19" t="inlineStr">
+        <is>
+          <t>28299.69197707737</t>
+        </is>
+      </c>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>27388.0</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>15822.8</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>14450.7</t>
+        </is>
+      </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>10277.46</t>
+        </is>
+      </c>
+      <c r="BA19" t="inlineStr">
+        <is>
+          <t>1372</t>
+        </is>
+      </c>
+      <c r="BB19" t="inlineStr">
+        <is>
+          <t>462.1765112122318</t>
+        </is>
+      </c>
+      <c r="BC19" t="inlineStr">
+        <is>
+          <t>1986.79614562238</t>
+        </is>
+      </c>
+      <c r="BD19" t="n">
+        <v>27388</v>
+      </c>
+      <c r="BE19" t="inlineStr">
+        <is>
+          <t>2025-11-26</t>
+        </is>
+      </c>
+      <c r="BF19" t="inlineStr">
+        <is>
+          <t>192.0</t>
+        </is>
+      </c>
+      <c r="BG19" t="inlineStr">
+        <is>
+          <t>2025/10/14</t>
+        </is>
+      </c>
+      <c r="BH19" t="inlineStr">
+        <is>
+          <t>6.25</t>
+        </is>
+      </c>
+      <c r="BI19" t="inlineStr">
+        <is>
+          <t>鼎翰</t>
+        </is>
+      </c>
+      <c r="BJ19" t="inlineStr">
+        <is>
+          <t>鼎翰</t>
+        </is>
+      </c>
+      <c r="BK19" t="inlineStr">
+        <is>
+          <t>電腦及週邊設備業</t>
+        </is>
+      </c>
+      <c r="BL19" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BM19" t="inlineStr">
+        <is>
+          <t>0.56</t>
+        </is>
+      </c>
+      <c r="BN19" t="inlineStr">
+        <is>
+          <t>-11.45161899724185</t>
+        </is>
+      </c>
+      <c r="BO19" t="inlineStr">
+        <is>
+          <t>22.56717409239306</t>
+        </is>
+      </c>
+      <c r="BP19" t="inlineStr">
+        <is>
+          <t>38.82556207928187</t>
+        </is>
+      </c>
+      <c r="BQ19" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR19" t="inlineStr">
+        <is>
+          <t>價-量增</t>
+        </is>
+      </c>
+      <c r="BS19" t="inlineStr">
+        <is>
           <t>1.93</t>
         </is>
       </c>
-      <c r="AS19" t="inlineStr">
-        <is>
-          <t>10.01</t>
-        </is>
-      </c>
-      <c r="AT19" t="inlineStr">
-        <is>
-          <t>-80.72</t>
-        </is>
-      </c>
-      <c r="AU19" t="inlineStr">
-        <is>
-          <t>2025/11/14</t>
-        </is>
-      </c>
-      <c r="AV19" t="inlineStr">
-        <is>
-          <t>28281.92324246772</t>
-        </is>
-      </c>
-      <c r="AW19" t="inlineStr">
-        <is>
-          <t>33609.0</t>
-        </is>
-      </c>
-      <c r="AX19" t="inlineStr">
-        <is>
-          <t>14692.0</t>
-        </is>
-      </c>
-      <c r="AY19" t="inlineStr">
-        <is>
-          <t>12138.8</t>
-        </is>
-      </c>
-      <c r="AZ19" t="inlineStr">
-        <is>
-          <t>9836.78</t>
-        </is>
-      </c>
-      <c r="BA19" t="inlineStr">
-        <is>
-          <t>2553</t>
-        </is>
-      </c>
-      <c r="BB19" t="inlineStr">
-        <is>
-          <t>184.9729413194776</t>
-        </is>
-      </c>
-      <c r="BC19" t="inlineStr">
-        <is>
-          <t>1139.994316817598</t>
-        </is>
-      </c>
-      <c r="BD19" t="n">
-        <v>33609</v>
-      </c>
-      <c r="BE19" t="inlineStr">
-        <is>
-          <t>2025-11-25</t>
-        </is>
-      </c>
-      <c r="BF19" t="inlineStr">
-        <is>
-          <t>192.0</t>
-        </is>
-      </c>
-      <c r="BG19" t="inlineStr">
-        <is>
-          <t>2025/10/14</t>
-        </is>
-      </c>
-      <c r="BH19" t="inlineStr">
-        <is>
-          <t>4.95</t>
-        </is>
-      </c>
-      <c r="BI19" t="inlineStr">
-        <is>
-          <t>鼎翰</t>
-        </is>
-      </c>
-      <c r="BJ19" t="inlineStr">
-        <is>
-          <t>鼎翰</t>
-        </is>
-      </c>
-      <c r="BK19" t="inlineStr">
-        <is>
-          <t>電腦及週邊設備業</t>
-        </is>
-      </c>
-      <c r="BL19" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BM19" t="inlineStr">
-        <is>
-          <t>0.56</t>
-        </is>
-      </c>
-      <c r="BN19" t="inlineStr">
-        <is>
-          <t>-11.45161899724185</t>
-        </is>
-      </c>
-      <c r="BO19" t="inlineStr">
-        <is>
-          <t>22.56717409239306</t>
-        </is>
-      </c>
-      <c r="BP19" t="inlineStr">
-        <is>
-          <t>38.82556207928187</t>
-        </is>
-      </c>
-      <c r="BQ19" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR19" t="inlineStr">
-        <is>
-          <t>價漲量增</t>
-        </is>
-      </c>
-      <c r="BS19" t="inlineStr">
-        <is>
-          <t>1.91</t>
-        </is>
-      </c>
       <c r="BT19" t="inlineStr">
         <is>
-          <t>4.74</t>
+          <t>4.66</t>
         </is>
       </c>
       <c r="BU19" t="inlineStr">
@@ -8644,7 +8644,7 @@
       </c>
       <c r="BV19" t="inlineStr">
         <is>
-          <t>12.57</t>
+          <t>12.78</t>
         </is>
       </c>
       <c r="BW19" t="inlineStr">
@@ -8659,12 +8659,12 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>47.65</t>
+          <t>48.44</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>10010</t>
+          <t>10177</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -8684,22 +8684,22 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>199.0</t>
+          <t>201.5</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>202.5</t>
+          <t>206.5</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>198.5</t>
+          <t>201.5</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>201.5</t>
+          <t>204.0</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8731,12 +8731,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>19.0</t>
+          <t>167.0</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8746,7 +8746,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>197.0</t>
+          <t>201.5</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8756,22 +8756,22 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>6.41</t>
+          <t>5.84</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-2.32</t>
+          <t>-0.79</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>21.03</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -8786,7 +8786,7 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>2025-11-25 00:00:00</t>
+          <t>2025-11-26 00:00:00</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
@@ -8811,7 +8811,7 @@
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>201.5</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
@@ -8826,7 +8826,7 @@
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
@@ -8841,17 +8841,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>4.47</t>
+          <t>39.29</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>-1.27</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8867,67 +8867,67 @@
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>128</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>46.15</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>51.28</t>
+          <t>69.23</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>2.84</t>
+          <t>2.87</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>197.9</t>
+          <t>198.8</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>196.78</t>
+          <t>197.15</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>191.34</t>
+          <t>191.65</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>190.02</t>
+          <t>190.08</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>-11.24</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
@@ -8942,7 +8942,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-80.75</t>
+          <t>-80.72</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8952,50 +8952,50 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>28281.92324246772</t>
+          <t>28299.69197707737</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>3715.0</t>
+          <t>33609.0</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>9865.0</t>
+          <t>14692.0</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>9864.3</t>
+          <t>12138.8</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>9269.96</t>
+          <t>9836.78</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2553</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>11.33269122891031</t>
+          <t>184.9729413194776</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>-776.9723785041442</t>
+          <t>1139.994316817598</t>
         </is>
       </c>
       <c r="BD20" t="n">
-        <v>3715</v>
+        <v>33609</v>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="BF20" t="inlineStr">
@@ -9010,7 +9010,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2.60</t>
+          <t>4.95</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -9055,22 +9055,22 @@
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
         <is>
-          <t>4.74</t>
+          <t>4.66</t>
         </is>
       </c>
       <c r="BU20" t="inlineStr">
@@ -9080,7 +9080,7 @@
       </c>
       <c r="BV20" t="inlineStr">
         <is>
-          <t>12.57</t>
+          <t>12.78</t>
         </is>
       </c>
       <c r="BW20" t="inlineStr">
@@ -9095,12 +9095,12 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>47.65</t>
+          <t>48.44</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>10010</t>
+          <t>10177</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
@@ -9120,22 +9120,22 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>199.5</t>
+          <t>199.0</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>199.5</t>
+          <t>202.5</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>197.0</t>
+          <t>198.5</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>197.0</t>
+          <t>201.5</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -9167,12 +9167,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>19.0</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9182,7 +9182,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>198.0</t>
+          <t>197.0</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9192,17 +9192,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>5.94</t>
+          <t>7.94</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-2.32</t>
+          <t>-0.79</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9222,7 +9222,7 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>2025-11-25 00:00:00</t>
+          <t>2025-11-26 00:00:00</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
@@ -9277,17 +9277,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>7.06</t>
+          <t>4.47</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>-1.27</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9303,72 +9303,72 @@
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>128</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>61.54</t>
+          <t>46.15</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>69.23</t>
+          <t>51.28</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>0.80</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>2.85</t>
+          <t>2.84</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>0.62</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>198.2</t>
+          <t>197.9</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>196.62</t>
+          <t>196.78</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>191.17</t>
+          <t>191.34</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>189.99</t>
+          <t>190.02</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>-6.74</t>
+          <t>-11.24</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9378,7 +9378,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-80.21</t>
+          <t>-80.75</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9388,46 +9388,46 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>28281.92324246772</t>
+          <t>28299.69197707737</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>5976.0</t>
+          <t>3715.0</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>10613.2</t>
+          <t>9865.0</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>10254.6</t>
+          <t>9864.3</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>9315.64</t>
+          <t>9269.96</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>358</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>154.6608857258293</t>
+          <t>11.33269122891031</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>-284.8186440172012</t>
+          <t>-776.9723785041442</t>
         </is>
       </c>
       <c r="BD21" t="n">
-        <v>5976</v>
+        <v>3715</v>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
@@ -9446,7 +9446,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>3.12</t>
+          <t>2.60</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
@@ -9491,7 +9491,7 @@
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
@@ -9501,12 +9501,12 @@
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
         <is>
-          <t>4.74</t>
+          <t>4.66</t>
         </is>
       </c>
       <c r="BU21" t="inlineStr">
@@ -9516,7 +9516,7 @@
       </c>
       <c r="BV21" t="inlineStr">
         <is>
-          <t>12.57</t>
+          <t>12.78</t>
         </is>
       </c>
       <c r="BW21" t="inlineStr">
@@ -9531,12 +9531,12 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>47.65</t>
+          <t>48.44</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>10010</t>
+          <t>10177</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
@@ -9556,22 +9556,22 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
+          <t>199.5</t>
+        </is>
+      </c>
+      <c r="CE21" t="inlineStr">
+        <is>
+          <t>199.5</t>
+        </is>
+      </c>
+      <c r="CF21" t="inlineStr">
+        <is>
           <t>197.0</t>
         </is>
       </c>
-      <c r="CE21" t="inlineStr">
-        <is>
-          <t>198.5</t>
-        </is>
-      </c>
-      <c r="CF21" t="inlineStr">
+      <c r="CG21" t="inlineStr">
         <is>
           <t>197.0</t>
-        </is>
-      </c>
-      <c r="CG21" t="inlineStr">
-        <is>
-          <t>198.0</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -9603,12 +9603,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-1.75</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>42.0</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9618,7 +9618,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>197.0</t>
+          <t>198.0</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9628,17 +9628,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>6.41</t>
+          <t>7.48</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-2.32</t>
+          <t>-0.79</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>16.90</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9658,7 +9658,7 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>2025-11-25 00:00:00</t>
+          <t>2025-11-26 00:00:00</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
@@ -9713,17 +9713,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>9.88</t>
+          <t>7.06</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>-1.78</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9739,72 +9739,72 @@
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>128</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>46.15</t>
+          <t>61.54</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>70.94</t>
+          <t>69.23</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>0.60</t>
+          <t>0.80</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>2.8</t>
+          <t>2.85</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>197.5</t>
+          <t>198.2</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>196.32</t>
+          <t>196.62</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>190.97</t>
+          <t>191.17</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>189.94</t>
+          <t>189.99</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>-5.98</t>
+          <t>-6.74</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>1.89</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9814,7 +9814,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-79.87</t>
+          <t>-80.21</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9824,46 +9824,46 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>28281.92324246772</t>
+          <t>28299.69197707737</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>8426.0</t>
+          <t>5976.0</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>12937.0</t>
+          <t>10613.2</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>11067.0</t>
+          <t>10254.6</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>9335.32</t>
+          <t>9315.64</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>1870</t>
+          <t>358</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>234.5662547700167</t>
+          <t>154.6608857258293</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>186.1802139647589</t>
+          <t>-284.8186440172012</t>
         </is>
       </c>
       <c r="BD22" t="n">
-        <v>8426</v>
+        <v>5976</v>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
@@ -9882,7 +9882,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2.60</t>
+          <t>3.12</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
@@ -9927,7 +9927,7 @@
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -9937,12 +9937,12 @@
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
         <is>
-          <t>4.74</t>
+          <t>4.66</t>
         </is>
       </c>
       <c r="BU22" t="inlineStr">
@@ -9952,7 +9952,7 @@
       </c>
       <c r="BV22" t="inlineStr">
         <is>
-          <t>12.57</t>
+          <t>12.78</t>
         </is>
       </c>
       <c r="BW22" t="inlineStr">
@@ -9967,12 +9967,12 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>47.65</t>
+          <t>48.44</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>10010</t>
+          <t>10177</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
@@ -9992,12 +9992,12 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>200.5</t>
+          <t>197.0</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>200.5</t>
+          <t>198.5</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
@@ -10007,7 +10007,7 @@
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>197.0</t>
+          <t>198.0</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -10039,12 +10039,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>-1.75</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>108.0</t>
+          <t>42.0</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -10054,7 +10054,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>200.5</t>
+          <t>197.0</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -10064,17 +10064,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>7.94</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-2.32</t>
+          <t>-0.79</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>11.96</t>
+          <t>16.90</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10094,7 +10094,7 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>2025-11-25 00:00:00</t>
+          <t>2025-11-26 00:00:00</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
@@ -10149,17 +10149,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>25.41</t>
+          <t>9.88</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>-0.74</t>
+          <t>-1.78</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10175,72 +10175,72 @@
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>128</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>46.15</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>82.83</t>
+          <t>70.94</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.60</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>2.72</t>
+          <t>2.8</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>196.9</t>
+          <t>197.5</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>196.0</t>
+          <t>196.32</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>190.81</t>
+          <t>190.97</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>189.91</t>
+          <t>189.94</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>-5.98</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>1.89</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10250,7 +10250,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-79.57</t>
+          <t>-79.87</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10260,46 +10260,46 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>28281.92324246772</t>
+          <t>28299.69197707737</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>21734.0</t>
+          <t>8426.0</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>13078.6</t>
+          <t>12937.0</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>11681.7</t>
+          <t>11067.0</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>9341.52</t>
+          <t>9335.32</t>
         </is>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>1396</t>
+          <t>1870</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>243.363716734609</t>
+          <t>234.5662547700167</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>589.8864320116754</t>
+          <t>186.1802139647589</t>
         </is>
       </c>
       <c r="BD23" t="n">
-        <v>21734</v>
+        <v>8426</v>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
@@ -10318,7 +10318,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>4.43</t>
+          <t>2.60</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
@@ -10363,7 +10363,7 @@
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -10373,12 +10373,12 @@
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
         <is>
-          <t>4.74</t>
+          <t>4.66</t>
         </is>
       </c>
       <c r="BU23" t="inlineStr">
@@ -10388,7 +10388,7 @@
       </c>
       <c r="BV23" t="inlineStr">
         <is>
-          <t>12.57</t>
+          <t>12.78</t>
         </is>
       </c>
       <c r="BW23" t="inlineStr">
@@ -10403,12 +10403,12 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>47.65</t>
+          <t>48.44</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>10010</t>
+          <t>10177</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
@@ -10428,22 +10428,22 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>203.5</t>
+          <t>200.5</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>203.5</t>
+          <t>200.5</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>199.0</t>
+          <t>197.0</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>200.5</t>
+          <t>197.0</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">

--- a/Result/checksun_type/HMI.xlsx
+++ b/Result/checksun_type/HMI.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>9.0</t>
+          <t>22.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>19.5</t>
+          <t>19.85</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-1.77</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-34.48</t>
+          <t>-25.82</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-10.76</t>
+          <t>-9.15</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,72 +1014,72 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>26.92</t>
+          <t>53.85</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>11.12</t>
+          <t>28.0</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>2.06</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-5.18</t>
+          <t>-4.02</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-5.44</t>
+          <t>-5.68</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-3.78</t>
+          <t>-3.92</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>19.31</t>
+          <t>19.45</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>20.36</t>
+          <t>20.26</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>21.54</t>
+          <t>21.48</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>22.38</t>
+          <t>22.36</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-10.91</t>
+          <t>-1.89</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-0.70</t>
+          <t>-0.64</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-109.53</t>
+          <t>-109.58</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1104,46 +1104,46 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>30418.92550143267</t>
+          <t>30376.36480686695</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>166.0</t>
+          <t>446.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>494.2</t>
+          <t>537.2</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>754.3</t>
+          <t>724.2</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>1394.4</t>
+          <t>1332.24</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-260</t>
+          <t>-187</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-142.3985018106445</t>
+          <t>-142.1892822709431</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-143.6359791514134</t>
+          <t>-141.0385748025855</t>
         </is>
       </c>
       <c r="BD2" t="n">
-        <v>166</v>
+        <v>446</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-17.55</t>
+          <t>-16.07</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
@@ -1207,17 +1207,17 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
@@ -1247,12 +1247,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>86.4</t>
+          <t>89.09</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>569</t>
+          <t>579</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1272,22 +1272,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>19.3</t>
+          <t>19.45</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>19.5</t>
+          <t>20.05</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>19.3</t>
+          <t>19.45</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>19.5</t>
+          <t>19.85</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1319,12 +1319,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>19.2</t>
+          <t>19.5</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1344,17 +1344,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-1.77</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-2.21</t>
+          <t>-34.48</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-12.13</t>
+          <t>-10.76</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1429,17 +1429,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1450,57 +1450,57 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>3.23</t>
+          <t>26.92</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>9.68</t>
+          <t>11.12</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-6.04</t>
+          <t>-5.18</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-5.2</t>
+          <t>-5.44</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-3.45</t>
+          <t>-3.78</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>19.25</t>
+          <t>19.31</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>20.49</t>
+          <t>20.36</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>21.61</t>
+          <t>21.54</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
@@ -1510,17 +1510,17 @@
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-17.72</t>
+          <t>-10.91</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>-0.70</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-0.63</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-109.27</t>
+          <t>-109.53</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1540,46 +1540,46 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>30418.92550143267</t>
+          <t>30376.36480686695</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>290.0</t>
+          <t>166.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>804.0</t>
+          <t>494.2</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>822.2</t>
+          <t>754.3</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>1439.06</t>
+          <t>1394.4</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-18</t>
+          <t>-260</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-142.1735059305047</t>
+          <t>-142.3985018106445</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-112.2167003943315</t>
+          <t>-143.6359791514134</t>
         </is>
       </c>
       <c r="BD3" t="n">
-        <v>290</v>
+        <v>166</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-18.82</t>
+          <t>-17.55</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1623,7 +1623,7 @@
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
@@ -1643,7 +1643,7 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1653,7 +1653,7 @@
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1683,12 +1683,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>86.4</t>
+          <t>89.09</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>569</t>
+          <t>579</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1708,22 +1708,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>19.2</t>
+          <t>19.3</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
+          <t>19.5</t>
+        </is>
+      </c>
+      <c r="CF3" t="inlineStr">
+        <is>
           <t>19.3</t>
         </is>
       </c>
-      <c r="CF3" t="inlineStr">
-        <is>
-          <t>19.2</t>
-        </is>
-      </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>19.2</t>
+          <t>19.5</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1755,12 +1755,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-1.53</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1780,17 +1780,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>3.27</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-1.77</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>3.85</t>
+          <t>-2.21</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1865,17 +1865,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1886,12 +1886,12 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
@@ -1901,62 +1901,62 @@
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>9.68</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-1.13</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-5.90</t>
+          <t>-6.04</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-4.83</t>
+          <t>-5.2</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-3.05</t>
+          <t>-3.45</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>19.42</t>
+          <t>19.25</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>20.64</t>
+          <t>20.49</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>21.68</t>
+          <t>21.61</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>22.37</t>
+          <t>22.38</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-21.10</t>
+          <t>-17.72</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-108.86</t>
+          <t>-109.27</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1976,46 +1976,46 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>30418.92550143267</t>
+          <t>30376.36480686695</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>1287.0</t>
+          <t>290.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>930.4</t>
+          <t>804.0</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>895.9</t>
+          <t>822.2</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>1833.62</t>
+          <t>1439.06</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>-18</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-147.6201978461726</t>
+          <t>-142.1735059305047</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-76.60999144155971</t>
+          <t>-112.2167003943315</t>
         </is>
       </c>
       <c r="BD4" t="n">
-        <v>1287</v>
+        <v>290</v>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2059,7 +2059,7 @@
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
@@ -2079,7 +2079,7 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>86.4</t>
+          <t>89.09</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>569</t>
+          <t>579</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2144,17 +2144,17 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>19.55</t>
+          <t>19.2</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>19.65</t>
+          <t>19.3</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>18.85</t>
+          <t>19.2</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>-1.53</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>26.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2206,7 +2206,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>19.5</t>
+          <t>19.2</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2216,17 +2216,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.27</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-1.77</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-4.04</t>
+          <t>3.85</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2291,7 +2291,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-10.76</t>
+          <t>-12.13</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2301,17 +2301,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>3.17</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2322,77 +2322,77 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>22.58</t>
+          <t>3.23</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>7.53</t>
+          <t>8.6</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>-1.13</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-5.39</t>
+          <t>-5.90</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-4.43</t>
+          <t>-4.83</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-2.68</t>
+          <t>-3.05</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>19.67</t>
+          <t>19.42</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>20.79</t>
+          <t>20.64</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>21.75</t>
+          <t>21.68</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>22.35</t>
+          <t>22.37</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-23.19</t>
+          <t>-21.10</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-0.68</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2402,7 +2402,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-108.40</t>
+          <t>-108.86</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2412,46 +2412,46 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>30418.92550143267</t>
+          <t>30376.36480686695</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>497.0</t>
+          <t>1287.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>738.2</t>
+          <t>930.4</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>769.3</t>
+          <t>895.9</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>1851.22</t>
+          <t>1833.62</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-31</t>
+          <t>34</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-160.5311444651931</t>
+          <t>-147.6201978461726</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-129.8286218146873</t>
+          <t>-76.60999144155971</t>
         </is>
       </c>
       <c r="BD5" t="n">
-        <v>497</v>
+        <v>1287</v>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-17.55</t>
+          <t>-18.82</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2495,7 +2495,7 @@
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2555,12 +2555,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>86.4</t>
+          <t>89.09</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>569</t>
+          <t>579</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2580,22 +2580,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
+          <t>19.55</t>
+        </is>
+      </c>
+      <c r="CE5" t="inlineStr">
+        <is>
+          <t>19.65</t>
+        </is>
+      </c>
+      <c r="CF5" t="inlineStr">
+        <is>
+          <t>18.85</t>
+        </is>
+      </c>
+      <c r="CG5" t="inlineStr">
+        <is>
           <t>19.2</t>
-        </is>
-      </c>
-      <c r="CE5" t="inlineStr">
-        <is>
-          <t>19.5</t>
-        </is>
-      </c>
-      <c r="CF5" t="inlineStr">
-        <is>
-          <t>18.9</t>
-        </is>
-      </c>
-      <c r="CG5" t="inlineStr">
-        <is>
-          <t>19.5</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>26.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2642,7 +2642,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>19.15</t>
+          <t>19.5</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2652,17 +2652,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-1.77</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>14.69</t>
+          <t>-4.04</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2727,7 +2727,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-12.36</t>
+          <t>-10.76</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2737,17 +2737,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>3.17</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2758,77 +2758,77 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>22.58</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.53</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-3.58</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-5.17</t>
+          <t>-5.39</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-3.97</t>
+          <t>-4.43</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-2.33</t>
+          <t>-2.68</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>19.86</t>
+          <t>19.67</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>20.94</t>
+          <t>20.79</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>21.81</t>
+          <t>21.75</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>22.33</t>
+          <t>22.35</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-28.42</t>
+          <t>-23.19</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-0.68</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-0.55</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2838,7 +2838,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-107.91</t>
+          <t>-108.40</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2848,46 +2848,46 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>30418.92550143267</t>
+          <t>30376.36480686695</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>231.0</t>
+          <t>497.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>911.2</t>
+          <t>738.2</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>794.5</t>
+          <t>769.3</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>1867.82</t>
+          <t>1851.22</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>116</t>
+          <t>-31</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-166.1134213107396</t>
+          <t>-160.5311444651931</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-116.5756429972018</t>
+          <t>-129.8286218146873</t>
         </is>
       </c>
       <c r="BD6" t="n">
-        <v>231</v>
+        <v>497</v>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-19.03</t>
+          <t>-17.55</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
@@ -2951,17 +2951,17 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2991,12 +2991,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>86.4</t>
+          <t>89.09</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>569</t>
+          <t>579</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -3016,22 +3016,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>18.85</t>
+          <t>19.2</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>19.15</t>
+          <t>19.5</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>18.85</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>19.15</t>
+          <t>19.5</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-4.24</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>19.2</t>
+          <t>19.15</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3088,17 +3088,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>3.53</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-1.77</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>21.51</t>
+          <t>14.69</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3163,7 +3163,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-12.13</t>
+          <t>-12.36</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3173,17 +3173,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>3.15</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-3.37</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3194,12 +3194,12 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -3209,62 +3209,62 @@
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>15.38</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-4.81</t>
+          <t>-3.58</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-4.41</t>
+          <t>-5.17</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-3.49</t>
+          <t>-3.97</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-2.01</t>
+          <t>-2.33</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>20.17</t>
+          <t>19.86</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>21.1</t>
+          <t>20.94</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>21.86</t>
+          <t>21.81</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>22.31</t>
+          <t>22.33</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-25.64</t>
+          <t>-28.42</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3274,7 +3274,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-107.35</t>
+          <t>-107.91</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3284,46 +3284,46 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>30418.92550143267</t>
+          <t>30376.36480686695</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>1715.0</t>
+          <t>231.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>1014.4</t>
+          <t>911.2</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>834.8</t>
+          <t>794.5</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>1896.36</t>
+          <t>1867.82</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>179</t>
+          <t>116</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-175.1202900950192</t>
+          <t>-166.1134213107396</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-64.97940029375127</t>
+          <t>-116.5756429972018</t>
         </is>
       </c>
       <c r="BD7" t="n">
-        <v>1715</v>
+        <v>231</v>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-18.82</t>
+          <t>-19.03</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3367,7 +3367,7 @@
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
@@ -3387,7 +3387,7 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3397,7 +3397,7 @@
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>86.4</t>
+          <t>89.09</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>569</t>
+          <t>579</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3452,22 +3452,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>20.05</t>
+          <t>18.85</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>20.05</t>
+          <t>19.15</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>19.0</t>
+          <t>18.85</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>19.2</t>
+          <t>19.15</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3499,12 +3499,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-2.0</t>
+          <t>-4.24</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>46.0</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>20.05</t>
+          <t>19.2</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3524,17 +3524,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-2.82</t>
+          <t>3.27</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-1.77</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>17.65</t>
+          <t>21.51</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-8.24</t>
+          <t>-12.13</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3609,17 +3609,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>3.15</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>-3.37</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3630,12 +3630,12 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
@@ -3645,62 +3645,62 @@
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>23.08</t>
+          <t>15.38</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-1.91</t>
+          <t>-4.81</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-3.90</t>
+          <t>-4.41</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-2.98</t>
+          <t>-3.49</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-1.65</t>
+          <t>-2.01</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>20.44</t>
+          <t>20.17</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>21.27</t>
+          <t>21.1</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>21.92</t>
+          <t>21.86</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>22.29</t>
+          <t>22.31</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-16.23</t>
+          <t>-25.64</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-106.88</t>
+          <t>-107.35</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3720,46 +3720,46 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>30418.92550143267</t>
+          <t>30376.36480686695</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>922.0</t>
+          <t>1715.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>840.4</t>
+          <t>1014.4</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>714.3</t>
+          <t>834.8</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>1889.2</t>
+          <t>1896.36</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>126</t>
+          <t>179</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-195.1459064225224</t>
+          <t>-175.1202900950192</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-147.9497892783307</t>
+          <t>-64.97940029375127</t>
         </is>
       </c>
       <c r="BD8" t="n">
-        <v>922</v>
+        <v>1715</v>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3778,7 +3778,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-15.22</t>
+          <t>-18.82</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3803,7 +3803,7 @@
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
@@ -3823,7 +3823,7 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -3833,7 +3833,7 @@
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>86.4</t>
+          <t>89.09</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>569</t>
+          <t>579</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3888,22 +3888,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>20.05</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>20.1</t>
+          <t>20.05</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>19.95</t>
+          <t>19.0</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>20.05</t>
+          <t>19.2</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3935,12 +3935,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-2.0</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>16.0</t>
+          <t>46.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3950,7 +3950,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>20.45</t>
+          <t>20.05</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3960,17 +3960,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-4.87</t>
+          <t>-1.01</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-1.77</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>22.57</t>
+          <t>17.65</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4035,7 +4035,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-6.41</t>
+          <t>-8.24</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4045,17 +4045,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4066,77 +4066,77 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>46.15</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>36.17</t>
+          <t>23.08</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-1.91</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-4.52</t>
+          <t>-3.90</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-2.41</t>
+          <t>-2.98</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-1.36</t>
+          <t>-1.65</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>20.46</t>
+          <t>20.44</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>21.43</t>
+          <t>21.27</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>21.96</t>
+          <t>21.92</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>22.26</t>
+          <t>22.29</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-15.32</t>
+          <t>-16.23</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.50</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-106.60</t>
+          <t>-106.88</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4156,46 +4156,46 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>30418.92550143267</t>
+          <t>30376.36480686695</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>326.0</t>
+          <t>922.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>861.4</t>
+          <t>840.4</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>702.8</t>
+          <t>714.3</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>2075.44</t>
+          <t>1889.2</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>158</t>
+          <t>126</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-203.7270186305573</t>
+          <t>-195.1459064225224</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-176.2307096392179</t>
+          <t>-147.9497892783307</t>
         </is>
       </c>
       <c r="BD9" t="n">
-        <v>326</v>
+        <v>922</v>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4214,7 +4214,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-13.53</t>
+          <t>-15.22</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
@@ -4259,7 +4259,7 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4269,7 +4269,7 @@
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4299,12 +4299,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>86.4</t>
+          <t>89.09</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>569</t>
+          <t>579</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4324,22 +4324,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>20.45</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>20.45</t>
+          <t>20.1</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>20.3</t>
+          <t>19.95</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>20.45</t>
+          <t>20.05</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4371,12 +4371,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-1.19</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4396,17 +4396,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-4.87</t>
+          <t>-3.02</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-1.77</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>22.57</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4481,17 +4481,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-1.95</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4502,67 +4502,67 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>23.08</t>
+          <t>46.15</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>28.41</t>
+          <t>36.17</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-4.33</t>
+          <t>-4.52</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-2.52</t>
+          <t>-2.41</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>-1.36</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>20.53</t>
+          <t>20.46</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>21.46</t>
+          <t>21.43</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>22.01</t>
+          <t>21.96</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>22.23</t>
+          <t>22.26</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-20.19</t>
+          <t>-15.32</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
@@ -4572,7 +4572,7 @@
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4582,7 +4582,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-106.34</t>
+          <t>-106.60</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4592,46 +4592,46 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>30418.92550143267</t>
+          <t>30376.36480686695</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>1362.0</t>
+          <t>326.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>800.4</t>
+          <t>861.4</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>791.6</t>
+          <t>702.8</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>2169.22</t>
+          <t>2075.44</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>158</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-208.7263475380736</t>
+          <t>-203.7270186305573</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-146.4809276676563</t>
+          <t>-176.2307096392179</t>
         </is>
       </c>
       <c r="BD10" t="n">
-        <v>1362</v>
+        <v>326</v>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4675,7 +4675,7 @@
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
@@ -4695,7 +4695,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4735,12 +4735,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>86.4</t>
+          <t>89.09</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>569</t>
+          <t>579</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4760,12 +4760,12 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>21.0</t>
+          <t>20.45</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>21.0</t>
+          <t>20.45</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
@@ -4807,12 +4807,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>-1.19</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>36.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4822,7 +4822,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>20.7</t>
+          <t>20.45</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4832,17 +4832,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-6.15</t>
+          <t>-3.02</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-1.77</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-32.18</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-5.26</t>
+          <t>-6.41</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4917,17 +4917,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>-1.95</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4938,67 +4938,67 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>39.29</t>
+          <t>23.08</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>20.71</t>
+          <t>28.41</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-4.13</t>
+          <t>-4.33</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-2.66</t>
+          <t>-2.52</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-0.54</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>20.6</t>
+          <t>20.53</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>21.49</t>
+          <t>21.46</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>22.08</t>
+          <t>22.01</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>22.19</t>
+          <t>22.23</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-25.12</t>
+          <t>-20.19</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
@@ -5008,7 +5008,7 @@
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -5018,7 +5018,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-106.02</t>
+          <t>-106.34</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -5028,46 +5028,46 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>30418.92550143267</t>
+          <t>30376.36480686695</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>747.0</t>
+          <t>1362.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>677.8</t>
+          <t>800.4</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>999.4</t>
+          <t>791.6</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>2614.76</t>
+          <t>2169.22</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-321</t>
+          <t>8</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-220.0436966054221</t>
+          <t>-208.7263475380736</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-209.7497774344375</t>
+          <t>-146.4809276676563</t>
         </is>
       </c>
       <c r="BD11" t="n">
-        <v>747</v>
+        <v>1362</v>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5086,7 +5086,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-12.47</t>
+          <t>-13.53</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5111,7 +5111,7 @@
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
@@ -5131,7 +5131,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5141,7 +5141,7 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5171,12 +5171,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>86.4</t>
+          <t>89.09</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>569</t>
+          <t>579</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5196,22 +5196,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>20.6</t>
+          <t>21.0</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>20.95</t>
+          <t>21.0</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>20.55</t>
+          <t>20.3</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>20.7</t>
+          <t>20.45</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5243,12 +5243,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>41.0</t>
+          <t>36.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5258,7 +5258,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>20.55</t>
+          <t>20.7</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5268,17 +5268,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-5.38</t>
+          <t>-4.28</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-1.77</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-33.22</t>
+          <t>-32.18</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5343,7 +5343,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-5.95</t>
+          <t>-5.26</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5353,17 +5353,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-4.11</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5374,77 +5374,77 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>22.86</t>
+          <t>39.29</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>19.66</t>
+          <t>20.71</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-4.71</t>
+          <t>-4.13</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-2.98</t>
+          <t>-2.66</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-0.54</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>20.49</t>
+          <t>20.6</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>21.5</t>
+          <t>21.49</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>22.16</t>
+          <t>22.08</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>22.16</t>
+          <t>22.19</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-36.40</t>
+          <t>-25.12</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>-0.50</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5454,7 +5454,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-105.65</t>
+          <t>-106.02</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5464,46 +5464,46 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>30418.92550143267</t>
+          <t>30376.36480686695</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>845.0</t>
+          <t>747.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>655.2</t>
+          <t>677.8</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>981.2</t>
+          <t>999.4</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>2840.22</t>
+          <t>2614.76</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-326</t>
+          <t>-321</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-221.9153182728739</t>
+          <t>-220.0436966054221</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-226.749927907181</t>
+          <t>-209.7497774344375</t>
         </is>
       </c>
       <c r="BD12" t="n">
-        <v>845</v>
+        <v>747</v>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5522,7 +5522,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-13.11</t>
+          <t>-12.47</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5547,7 +5547,7 @@
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
@@ -5567,7 +5567,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5577,7 +5577,7 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5607,12 +5607,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>86.4</t>
+          <t>89.09</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>569</t>
+          <t>579</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5632,22 +5632,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>20.2</t>
+          <t>20.6</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>21.75</t>
+          <t>20.95</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>20.2</t>
+          <t>20.55</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>20.55</t>
+          <t>20.7</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5679,12 +5679,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5709,12 +5709,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>7.97</t>
+          <t>13.06</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5734,7 +5734,7 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>2025-11-26 00:00:00</t>
+          <t>2025-11-27 00:00:00</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -5789,17 +5789,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>30.12</t>
+          <t>29.88</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5810,12 +5810,12 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>127</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
@@ -5830,57 +5830,57 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>3.18</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>3.54</t>
+          <t>4.44</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>3.07</t>
+          <t>3.16</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>207.4</t>
+          <t>210.0</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>200.3</t>
+          <t>201.08</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>194.34</t>
+          <t>194.92</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>191.84</t>
+          <t>192.22</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>43.78</t>
+          <t>43.25</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>4.06</t>
+          <t>4.54</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>2.83</t>
+          <t>3.17</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5890,7 +5890,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-71.78</t>
+          <t>-68.36</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5900,50 +5900,50 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>28299.69197707737</t>
+          <t>28317.34549356224</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>27123.0</t>
+          <t>27093.0</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>21655.6</t>
+          <t>25064.0</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>20056.7</t>
+          <t>22168.4</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>12284.3</t>
+          <t>12662.48</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>1598</t>
+          <t>2895</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>1393.334091030001</t>
+          <t>1554.494789995829</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>2293.457328001074</t>
+          <t>2440.878634307883</t>
         </is>
       </c>
       <c r="BD13" t="n">
-        <v>27123</v>
+        <v>27093</v>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="BF13" t="inlineStr">
@@ -6003,12 +6003,12 @@
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS13" t="inlineStr">
@@ -6043,7 +6043,7 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>48.44</t>
+          <t>49.24</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
@@ -6068,17 +6068,17 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
+          <t>215.0</t>
+        </is>
+      </c>
+      <c r="CE13" t="inlineStr">
+        <is>
+          <t>215.5</t>
+        </is>
+      </c>
+      <c r="CF13" t="inlineStr">
+        <is>
           <t>211.0</t>
-        </is>
-      </c>
-      <c r="CE13" t="inlineStr">
-        <is>
-          <t>214.0</t>
-        </is>
-      </c>
-      <c r="CF13" t="inlineStr">
-        <is>
-          <t>210.5</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
@@ -6115,12 +6115,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>105.0</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6130,7 +6130,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>210.5</t>
+          <t>214.0</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6140,17 +6140,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>13.00</t>
+          <t>7.97</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6170,7 +6170,7 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>2025-11-26 00:00:00</t>
+          <t>2025-11-27 00:00:00</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -6210,7 +6210,7 @@
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>4.47</t>
+          <t>6.20</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
@@ -6225,17 +6225,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>24.71</t>
+          <t>30.12</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6246,12 +6246,12 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>127</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
@@ -6266,57 +6266,57 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>2.93</t>
+          <t>3.18</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>2.52</t>
+          <t>3.54</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>2.93</t>
+          <t>3.07</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>204.5</t>
+          <t>207.4</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>199.48</t>
+          <t>200.3</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>193.8</t>
+          <t>194.34</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>191.47</t>
+          <t>191.84</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>34.99</t>
+          <t>43.78</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>4.06</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>2.52</t>
+          <t>2.83</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6326,7 +6326,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-74.87</t>
+          <t>-71.78</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6336,50 +6336,50 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>28299.69197707737</t>
+          <t>28317.34549356224</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>22122.0</t>
+          <t>27123.0</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>20551.2</t>
+          <t>21655.6</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>18187.0</t>
+          <t>20056.7</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>11819.44</t>
+          <t>12284.3</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>2364</t>
+          <t>1598</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>1229.675320671625</t>
+          <t>1393.334091030001</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>1997.731985848452</t>
+          <t>2293.457328001074</t>
         </is>
       </c>
       <c r="BD14" t="n">
-        <v>22122</v>
+        <v>27123</v>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="BF14" t="inlineStr">
@@ -6394,7 +6394,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>9.64</t>
+          <t>11.46</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -6439,7 +6439,7 @@
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
@@ -6449,7 +6449,7 @@
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
@@ -6479,7 +6479,7 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>48.44</t>
+          <t>49.24</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
@@ -6504,22 +6504,22 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>208.5</t>
+          <t>211.0</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>211.0</t>
+          <t>214.0</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>208.0</t>
+          <t>210.5</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>210.5</t>
+          <t>214.0</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -6551,12 +6551,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>105.0</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6566,7 +6566,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>207.0</t>
+          <t>210.5</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6576,17 +6576,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>3.27</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>19.04</t>
+          <t>13.00</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6606,7 +6606,7 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>2025-11-26 00:00:00</t>
+          <t>2025-11-27 00:00:00</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -6646,7 +6646,7 @@
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>2.73</t>
+          <t>4.47</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
@@ -6661,17 +6661,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>30.12</t>
+          <t>24.71</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6682,12 +6682,12 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>127</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
@@ -6697,62 +6697,62 @@
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>85.71</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>2.93</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>2.52</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>2.89</t>
+          <t>2.93</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>203.2</t>
+          <t>204.5</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>198.92</t>
+          <t>199.48</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>193.33</t>
+          <t>193.8</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>191.14</t>
+          <t>191.47</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>24.29</t>
+          <t>34.99</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>2.85</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>2.52</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6762,7 +6762,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-77.07</t>
+          <t>-74.87</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6772,50 +6772,50 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>28299.69197707737</t>
+          <t>28317.34549356224</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>26279.0</t>
+          <t>22122.0</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>21604.4</t>
+          <t>20551.2</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>18148.2</t>
+          <t>18187.0</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>11512.0</t>
+          <t>11819.44</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>3456</t>
+          <t>2364</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>1090.028654275838</t>
+          <t>1229.675320671625</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>2039.741068992971</t>
+          <t>1997.731985848452</t>
         </is>
       </c>
       <c r="BD15" t="n">
-        <v>26279</v>
+        <v>22122</v>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="BF15" t="inlineStr">
@@ -6830,7 +6830,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>7.81</t>
+          <t>9.64</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -6880,12 +6880,12 @@
       </c>
       <c r="BR15" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
@@ -6915,7 +6915,7 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>48.44</t>
+          <t>49.24</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
@@ -6940,22 +6940,22 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>203.5</t>
+          <t>208.5</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
+          <t>211.0</t>
+        </is>
+      </c>
+      <c r="CF15" t="inlineStr">
+        <is>
           <t>208.0</t>
         </is>
       </c>
-      <c r="CF15" t="inlineStr">
-        <is>
-          <t>202.0</t>
-        </is>
-      </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>207.0</t>
+          <t>210.5</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>112.0</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -7002,7 +7002,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>204.5</t>
+          <t>207.0</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -7012,17 +7012,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>4.44</t>
+          <t>3.27</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>40.09</t>
+          <t>19.04</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7042,7 +7042,7 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>2025-11-26 00:00:00</t>
+          <t>2025-11-27 00:00:00</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -7082,7 +7082,7 @@
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>2.73</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
@@ -7097,17 +7097,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>26.35</t>
+          <t>30.12</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7118,12 +7118,12 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>127</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
@@ -7133,62 +7133,62 @@
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>64.29</t>
+          <t>85.71</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>2.93</t>
+          <t>2.89</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>202.1</t>
+          <t>203.2</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>198.58</t>
+          <t>198.92</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>192.93</t>
+          <t>193.33</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>190.87</t>
+          <t>191.14</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>14.78</t>
+          <t>24.29</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>2.48</t>
+          <t>2.85</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7198,7 +7198,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-78.46</t>
+          <t>-77.07</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7208,50 +7208,50 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>28299.69197707737</t>
+          <t>28317.34549356224</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>22703.0</t>
+          <t>26279.0</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>23070.4</t>
+          <t>21604.4</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>16467.7</t>
+          <t>18148.2</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>11056.48</t>
+          <t>11512.0</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>6602</t>
+          <t>3456</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>917.3536697818137</t>
+          <t>1090.028654275838</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>1581.513292449679</t>
+          <t>2039.741068992971</t>
         </is>
       </c>
       <c r="BD16" t="n">
-        <v>22703</v>
+        <v>26279</v>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="BF16" t="inlineStr">
@@ -7266,7 +7266,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>6.51</t>
+          <t>7.81</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -7311,17 +7311,17 @@
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
@@ -7351,7 +7351,7 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>48.44</t>
+          <t>49.24</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
@@ -7376,22 +7376,22 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
+          <t>203.5</t>
+        </is>
+      </c>
+      <c r="CE16" t="inlineStr">
+        <is>
+          <t>208.0</t>
+        </is>
+      </c>
+      <c r="CF16" t="inlineStr">
+        <is>
           <t>202.0</t>
         </is>
       </c>
-      <c r="CE16" t="inlineStr">
-        <is>
-          <t>205.0</t>
-        </is>
-      </c>
-      <c r="CF16" t="inlineStr">
-        <is>
-          <t>202.0</t>
-        </is>
-      </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>204.5</t>
+          <t>207.0</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>112.0</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7438,7 +7438,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>201.0</t>
+          <t>204.5</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7448,17 +7448,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>6.07</t>
+          <t>4.44</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>28.98</t>
+          <t>40.09</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7478,7 +7478,7 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>2025-11-26 00:00:00</t>
+          <t>2025-11-27 00:00:00</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -7518,7 +7518,7 @@
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
@@ -7533,17 +7533,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11.76</t>
+          <t>26.35</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7554,17 +7554,17 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>127</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>57.14</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
@@ -7574,57 +7574,57 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>2.94</t>
+          <t>2.93</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>200.6</t>
+          <t>202.1</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>198.25</t>
+          <t>198.58</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>192.58</t>
+          <t>192.93</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>190.62</t>
+          <t>190.87</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>6.46</t>
+          <t>14.78</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>2.21</t>
+          <t>2.48</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>2.16</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7634,7 +7634,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-79.25</t>
+          <t>-78.46</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7644,50 +7644,50 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>28299.69197707737</t>
+          <t>28317.34549356224</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>10051.0</t>
+          <t>22703.0</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>19272.8</t>
+          <t>23070.4</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>14943.0</t>
+          <t>16467.7</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>10672.76</t>
+          <t>11056.48</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>4329</t>
+          <t>6602</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>796.5973747512926</t>
+          <t>917.3536697818137</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>1253.562422657489</t>
+          <t>1581.513292449679</t>
         </is>
       </c>
       <c r="BD17" t="n">
-        <v>10051</v>
+        <v>22703</v>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="BF17" t="inlineStr">
@@ -7702,7 +7702,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>4.69</t>
+          <t>6.51</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -7747,17 +7747,17 @@
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
@@ -7787,7 +7787,7 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>48.44</t>
+          <t>49.24</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
@@ -7812,22 +7812,22 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>199.5</t>
+          <t>202.0</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
+          <t>205.0</t>
+        </is>
+      </c>
+      <c r="CF17" t="inlineStr">
+        <is>
           <t>202.0</t>
         </is>
       </c>
-      <c r="CF17" t="inlineStr">
-        <is>
-          <t>198.5</t>
-        </is>
-      </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>201.0</t>
+          <t>204.5</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7859,12 +7859,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-2.2</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>107.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7874,7 +7874,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>199.5</t>
+          <t>201.0</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7884,17 +7884,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>6.78</t>
+          <t>6.07</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>17.59</t>
+          <t>28.98</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7914,7 +7914,7 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>2025-11-26 00:00:00</t>
+          <t>2025-11-27 00:00:00</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
@@ -7954,7 +7954,7 @@
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="W18" t="inlineStr">
@@ -7969,17 +7969,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>25.18</t>
+          <t>11.76</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>-2.00</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7990,77 +7990,77 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>127</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>35.71</t>
+          <t>57.14</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>78.57</t>
+          <t>64.29</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>2.96</t>
+          <t>2.94</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>200.0</t>
+          <t>200.6</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>197.98</t>
+          <t>198.25</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>192.28</t>
+          <t>192.58</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>190.44</t>
+          <t>190.62</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>7.56</t>
+          <t>6.46</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>2.21</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -8070,7 +8070,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-79.59</t>
+          <t>-79.25</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -8080,50 +8080,50 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>28299.69197707737</t>
+          <t>28317.34549356224</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>21601.0</t>
+          <t>10051.0</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>18457.8</t>
+          <t>19272.8</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>15697.4</t>
+          <t>14943.0</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>10622.98</t>
+          <t>10672.76</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>2760</t>
+          <t>4329</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>713.5128205865296</t>
+          <t>796.5973747512926</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>2095.862522145168</t>
+          <t>1253.562422657489</t>
         </is>
       </c>
       <c r="BD18" t="n">
-        <v>21601</v>
+        <v>10051</v>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="BF18" t="inlineStr">
@@ -8138,7 +8138,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>3.91</t>
+          <t>4.69</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -8183,17 +8183,17 @@
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>1.89</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
@@ -8223,7 +8223,7 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>48.44</t>
+          <t>49.24</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
@@ -8248,22 +8248,22 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>205.0</t>
+          <t>199.5</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>205.0</t>
+          <t>202.0</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>198.0</t>
+          <t>198.5</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>199.5</t>
+          <t>201.0</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -8295,12 +8295,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>-2.2</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>107.0</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8310,7 +8310,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>204.0</t>
+          <t>199.5</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8320,17 +8320,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>4.67</t>
+          <t>6.78</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>9.50</t>
+          <t>17.59</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8350,7 +8350,7 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>2025-11-26 00:00:00</t>
+          <t>2025-11-27 00:00:00</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
@@ -8390,7 +8390,7 @@
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">
@@ -8405,17 +8405,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>31.53</t>
+          <t>25.18</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>-2.00</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8426,32 +8426,32 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>127</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>35.71</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>82.05</t>
+          <t>78.57</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
@@ -8461,245 +8461,245 @@
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
+          <t>200.0</t>
+        </is>
+      </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>197.98</t>
+        </is>
+      </c>
+      <c r="AN19" t="inlineStr">
+        <is>
+          <t>192.28</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>190.44</t>
+        </is>
+      </c>
+      <c r="AP19" t="inlineStr">
+        <is>
+          <t>7.56</t>
+        </is>
+      </c>
+      <c r="AQ19" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="AR19" t="inlineStr">
+        <is>
+          <t>2.04</t>
+        </is>
+      </c>
+      <c r="AS19" t="inlineStr">
+        <is>
+          <t>10.01</t>
+        </is>
+      </c>
+      <c r="AT19" t="inlineStr">
+        <is>
+          <t>-79.59</t>
+        </is>
+      </c>
+      <c r="AU19" t="inlineStr">
+        <is>
+          <t>2025/11/14</t>
+        </is>
+      </c>
+      <c r="AV19" t="inlineStr">
+        <is>
+          <t>28317.34549356224</t>
+        </is>
+      </c>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>21601.0</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>18457.8</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>15697.4</t>
+        </is>
+      </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>10622.98</t>
+        </is>
+      </c>
+      <c r="BA19" t="inlineStr">
+        <is>
+          <t>2760</t>
+        </is>
+      </c>
+      <c r="BB19" t="inlineStr">
+        <is>
+          <t>713.5128205865296</t>
+        </is>
+      </c>
+      <c r="BC19" t="inlineStr">
+        <is>
+          <t>2095.862522145168</t>
+        </is>
+      </c>
+      <c r="BD19" t="n">
+        <v>21601</v>
+      </c>
+      <c r="BE19" t="inlineStr">
+        <is>
+          <t>2025-11-27</t>
+        </is>
+      </c>
+      <c r="BF19" t="inlineStr">
+        <is>
+          <t>192.0</t>
+        </is>
+      </c>
+      <c r="BG19" t="inlineStr">
+        <is>
+          <t>2025/10/14</t>
+        </is>
+      </c>
+      <c r="BH19" t="inlineStr">
+        <is>
+          <t>3.91</t>
+        </is>
+      </c>
+      <c r="BI19" t="inlineStr">
+        <is>
+          <t>鼎翰</t>
+        </is>
+      </c>
+      <c r="BJ19" t="inlineStr">
+        <is>
+          <t>鼎翰</t>
+        </is>
+      </c>
+      <c r="BK19" t="inlineStr">
+        <is>
+          <t>電腦及週邊設備業</t>
+        </is>
+      </c>
+      <c r="BL19" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BM19" t="inlineStr">
+        <is>
+          <t>0.56</t>
+        </is>
+      </c>
+      <c r="BN19" t="inlineStr">
+        <is>
+          <t>-11.45161899724185</t>
+        </is>
+      </c>
+      <c r="BO19" t="inlineStr">
+        <is>
+          <t>22.56717409239306</t>
+        </is>
+      </c>
+      <c r="BP19" t="inlineStr">
+        <is>
+          <t>38.82556207928187</t>
+        </is>
+      </c>
+      <c r="BQ19" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR19" t="inlineStr">
+        <is>
+          <t>價-量增</t>
+        </is>
+      </c>
+      <c r="BS19" t="inlineStr">
+        <is>
+          <t>1.89</t>
+        </is>
+      </c>
+      <c r="BT19" t="inlineStr">
+        <is>
+          <t>4.66</t>
+        </is>
+      </c>
+      <c r="BU19" t="inlineStr">
+        <is>
+          <t>57.78</t>
+        </is>
+      </c>
+      <c r="BV19" t="inlineStr">
+        <is>
+          <t>12.78</t>
+        </is>
+      </c>
+      <c r="BW19" t="inlineStr">
+        <is>
+          <t>33.69%</t>
+        </is>
+      </c>
+      <c r="BX19" t="inlineStr">
+        <is>
+          <t>11.08%</t>
+        </is>
+      </c>
+      <c r="BY19" t="inlineStr">
+        <is>
+          <t>49.24</t>
+        </is>
+      </c>
+      <c r="BZ19" t="inlineStr">
+        <is>
+          <t>10177</t>
+        </is>
+      </c>
+      <c r="CA19" t="inlineStr">
+        <is>
+          <t>條碼印表機及零配件52.71%、印表機各式標籤紙及其耗材41.09%、企業行動電腦6.20% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB19" t="inlineStr">
+        <is>
+          <t>鼎翰-電腦及週邊設備業-上櫃</t>
+        </is>
+      </c>
+      <c r="CC19" t="inlineStr">
+        <is>
+          <t>電腦及週邊設備業平上櫃</t>
+        </is>
+      </c>
+      <c r="CD19" t="inlineStr">
+        <is>
+          <t>205.0</t>
+        </is>
+      </c>
+      <c r="CE19" t="inlineStr">
+        <is>
+          <t>205.0</t>
+        </is>
+      </c>
+      <c r="CF19" t="inlineStr">
+        <is>
+          <t>198.0</t>
+        </is>
+      </c>
+      <c r="CG19" t="inlineStr">
+        <is>
           <t>199.5</t>
-        </is>
-      </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>197.7</t>
-        </is>
-      </c>
-      <c r="AN19" t="inlineStr">
-        <is>
-          <t>192.01</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>190.29</t>
-        </is>
-      </c>
-      <c r="AP19" t="inlineStr">
-        <is>
-          <t>14.82</t>
-        </is>
-      </c>
-      <c r="AQ19" t="inlineStr">
-        <is>
-          <t>2.30</t>
-        </is>
-      </c>
-      <c r="AR19" t="inlineStr">
-        <is>
-          <t>2.01</t>
-        </is>
-      </c>
-      <c r="AS19" t="inlineStr">
-        <is>
-          <t>10.01</t>
-        </is>
-      </c>
-      <c r="AT19" t="inlineStr">
-        <is>
-          <t>-79.98</t>
-        </is>
-      </c>
-      <c r="AU19" t="inlineStr">
-        <is>
-          <t>2025/11/14</t>
-        </is>
-      </c>
-      <c r="AV19" t="inlineStr">
-        <is>
-          <t>28299.69197707737</t>
-        </is>
-      </c>
-      <c r="AW19" t="inlineStr">
-        <is>
-          <t>27388.0</t>
-        </is>
-      </c>
-      <c r="AX19" t="inlineStr">
-        <is>
-          <t>15822.8</t>
-        </is>
-      </c>
-      <c r="AY19" t="inlineStr">
-        <is>
-          <t>14450.7</t>
-        </is>
-      </c>
-      <c r="AZ19" t="inlineStr">
-        <is>
-          <t>10277.46</t>
-        </is>
-      </c>
-      <c r="BA19" t="inlineStr">
-        <is>
-          <t>1372</t>
-        </is>
-      </c>
-      <c r="BB19" t="inlineStr">
-        <is>
-          <t>462.1765112122318</t>
-        </is>
-      </c>
-      <c r="BC19" t="inlineStr">
-        <is>
-          <t>1986.79614562238</t>
-        </is>
-      </c>
-      <c r="BD19" t="n">
-        <v>27388</v>
-      </c>
-      <c r="BE19" t="inlineStr">
-        <is>
-          <t>2025-11-26</t>
-        </is>
-      </c>
-      <c r="BF19" t="inlineStr">
-        <is>
-          <t>192.0</t>
-        </is>
-      </c>
-      <c r="BG19" t="inlineStr">
-        <is>
-          <t>2025/10/14</t>
-        </is>
-      </c>
-      <c r="BH19" t="inlineStr">
-        <is>
-          <t>6.25</t>
-        </is>
-      </c>
-      <c r="BI19" t="inlineStr">
-        <is>
-          <t>鼎翰</t>
-        </is>
-      </c>
-      <c r="BJ19" t="inlineStr">
-        <is>
-          <t>鼎翰</t>
-        </is>
-      </c>
-      <c r="BK19" t="inlineStr">
-        <is>
-          <t>電腦及週邊設備業</t>
-        </is>
-      </c>
-      <c r="BL19" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BM19" t="inlineStr">
-        <is>
-          <t>0.56</t>
-        </is>
-      </c>
-      <c r="BN19" t="inlineStr">
-        <is>
-          <t>-11.45161899724185</t>
-        </is>
-      </c>
-      <c r="BO19" t="inlineStr">
-        <is>
-          <t>22.56717409239306</t>
-        </is>
-      </c>
-      <c r="BP19" t="inlineStr">
-        <is>
-          <t>38.82556207928187</t>
-        </is>
-      </c>
-      <c r="BQ19" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR19" t="inlineStr">
-        <is>
-          <t>價-量增</t>
-        </is>
-      </c>
-      <c r="BS19" t="inlineStr">
-        <is>
-          <t>1.93</t>
-        </is>
-      </c>
-      <c r="BT19" t="inlineStr">
-        <is>
-          <t>4.66</t>
-        </is>
-      </c>
-      <c r="BU19" t="inlineStr">
-        <is>
-          <t>57.78</t>
-        </is>
-      </c>
-      <c r="BV19" t="inlineStr">
-        <is>
-          <t>12.78</t>
-        </is>
-      </c>
-      <c r="BW19" t="inlineStr">
-        <is>
-          <t>33.69%</t>
-        </is>
-      </c>
-      <c r="BX19" t="inlineStr">
-        <is>
-          <t>11.08%</t>
-        </is>
-      </c>
-      <c r="BY19" t="inlineStr">
-        <is>
-          <t>48.44</t>
-        </is>
-      </c>
-      <c r="BZ19" t="inlineStr">
-        <is>
-          <t>10177</t>
-        </is>
-      </c>
-      <c r="CA19" t="inlineStr">
-        <is>
-          <t>條碼印表機及零配件52.71%、印表機各式標籤紙及其耗材41.09%、企業行動電腦6.20% (2024年)</t>
-        </is>
-      </c>
-      <c r="CB19" t="inlineStr">
-        <is>
-          <t>鼎翰-電腦及週邊設備業-上櫃</t>
-        </is>
-      </c>
-      <c r="CC19" t="inlineStr">
-        <is>
-          <t>電腦及週邊設備業平上櫃</t>
-        </is>
-      </c>
-      <c r="CD19" t="inlineStr">
-        <is>
-          <t>201.5</t>
-        </is>
-      </c>
-      <c r="CE19" t="inlineStr">
-        <is>
-          <t>206.5</t>
-        </is>
-      </c>
-      <c r="CF19" t="inlineStr">
-        <is>
-          <t>201.5</t>
-        </is>
-      </c>
-      <c r="CG19" t="inlineStr">
-        <is>
-          <t>204.0</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8731,12 +8731,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>167.0</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8746,74 +8746,74 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
+          <t>204.0</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>4.67</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>-1.25</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>9.50</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>2025-11-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>2025-11-27 00:00:00</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>2025-10-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>2025-11-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
           <t>201.5</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>5.84</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>-0.79</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>21.03</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>2025-11-14</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>2025-11-14 00:00:00</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>2025-11-26 00:00:00</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>2025-10-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>2025-11-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q20" t="inlineStr">
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
         <is>
           <t>201.5</t>
         </is>
       </c>
-      <c r="R20" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>201.5</t>
-        </is>
-      </c>
       <c r="T20" t="inlineStr">
         <is>
           <t>195.5</t>
@@ -8826,7 +8826,7 @@
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
@@ -8841,17 +8841,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>39.29</t>
+          <t>31.53</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8862,12 +8862,12 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>127</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
@@ -8877,197 +8877,197 @@
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>69.23</t>
+          <t>82.05</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>2.87</t>
+          <t>2.96</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>198.8</t>
+          <t>199.5</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>197.15</t>
+          <t>197.7</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>191.65</t>
+          <t>192.01</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>190.08</t>
+          <t>190.29</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>14.82</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
+          <t>2.01</t>
+        </is>
+      </c>
+      <c r="AS20" t="inlineStr">
+        <is>
+          <t>10.01</t>
+        </is>
+      </c>
+      <c r="AT20" t="inlineStr">
+        <is>
+          <t>-79.98</t>
+        </is>
+      </c>
+      <c r="AU20" t="inlineStr">
+        <is>
+          <t>2025/11/14</t>
+        </is>
+      </c>
+      <c r="AV20" t="inlineStr">
+        <is>
+          <t>28317.34549356224</t>
+        </is>
+      </c>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>27388.0</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>15822.8</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>14450.7</t>
+        </is>
+      </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>10277.46</t>
+        </is>
+      </c>
+      <c r="BA20" t="inlineStr">
+        <is>
+          <t>1372</t>
+        </is>
+      </c>
+      <c r="BB20" t="inlineStr">
+        <is>
+          <t>462.1765112122318</t>
+        </is>
+      </c>
+      <c r="BC20" t="inlineStr">
+        <is>
+          <t>1986.79614562238</t>
+        </is>
+      </c>
+      <c r="BD20" t="n">
+        <v>27388</v>
+      </c>
+      <c r="BE20" t="inlineStr">
+        <is>
+          <t>2025-11-27</t>
+        </is>
+      </c>
+      <c r="BF20" t="inlineStr">
+        <is>
+          <t>192.0</t>
+        </is>
+      </c>
+      <c r="BG20" t="inlineStr">
+        <is>
+          <t>2025/10/14</t>
+        </is>
+      </c>
+      <c r="BH20" t="inlineStr">
+        <is>
+          <t>6.25</t>
+        </is>
+      </c>
+      <c r="BI20" t="inlineStr">
+        <is>
+          <t>鼎翰</t>
+        </is>
+      </c>
+      <c r="BJ20" t="inlineStr">
+        <is>
+          <t>鼎翰</t>
+        </is>
+      </c>
+      <c r="BK20" t="inlineStr">
+        <is>
+          <t>電腦及週邊設備業</t>
+        </is>
+      </c>
+      <c r="BL20" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BM20" t="inlineStr">
+        <is>
+          <t>0.56</t>
+        </is>
+      </c>
+      <c r="BN20" t="inlineStr">
+        <is>
+          <t>-11.45161899724185</t>
+        </is>
+      </c>
+      <c r="BO20" t="inlineStr">
+        <is>
+          <t>22.56717409239306</t>
+        </is>
+      </c>
+      <c r="BP20" t="inlineStr">
+        <is>
+          <t>38.82556207928187</t>
+        </is>
+      </c>
+      <c r="BQ20" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR20" t="inlineStr">
+        <is>
+          <t>價-量增</t>
+        </is>
+      </c>
+      <c r="BS20" t="inlineStr">
+        <is>
           <t>1.93</t>
         </is>
       </c>
-      <c r="AS20" t="inlineStr">
-        <is>
-          <t>10.01</t>
-        </is>
-      </c>
-      <c r="AT20" t="inlineStr">
-        <is>
-          <t>-80.72</t>
-        </is>
-      </c>
-      <c r="AU20" t="inlineStr">
-        <is>
-          <t>2025/11/14</t>
-        </is>
-      </c>
-      <c r="AV20" t="inlineStr">
-        <is>
-          <t>28299.69197707737</t>
-        </is>
-      </c>
-      <c r="AW20" t="inlineStr">
-        <is>
-          <t>33609.0</t>
-        </is>
-      </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>14692.0</t>
-        </is>
-      </c>
-      <c r="AY20" t="inlineStr">
-        <is>
-          <t>12138.8</t>
-        </is>
-      </c>
-      <c r="AZ20" t="inlineStr">
-        <is>
-          <t>9836.78</t>
-        </is>
-      </c>
-      <c r="BA20" t="inlineStr">
-        <is>
-          <t>2553</t>
-        </is>
-      </c>
-      <c r="BB20" t="inlineStr">
-        <is>
-          <t>184.9729413194776</t>
-        </is>
-      </c>
-      <c r="BC20" t="inlineStr">
-        <is>
-          <t>1139.994316817598</t>
-        </is>
-      </c>
-      <c r="BD20" t="n">
-        <v>33609</v>
-      </c>
-      <c r="BE20" t="inlineStr">
-        <is>
-          <t>2025-11-26</t>
-        </is>
-      </c>
-      <c r="BF20" t="inlineStr">
-        <is>
-          <t>192.0</t>
-        </is>
-      </c>
-      <c r="BG20" t="inlineStr">
-        <is>
-          <t>2025/10/14</t>
-        </is>
-      </c>
-      <c r="BH20" t="inlineStr">
-        <is>
-          <t>4.95</t>
-        </is>
-      </c>
-      <c r="BI20" t="inlineStr">
-        <is>
-          <t>鼎翰</t>
-        </is>
-      </c>
-      <c r="BJ20" t="inlineStr">
-        <is>
-          <t>鼎翰</t>
-        </is>
-      </c>
-      <c r="BK20" t="inlineStr">
-        <is>
-          <t>電腦及週邊設備業</t>
-        </is>
-      </c>
-      <c r="BL20" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BM20" t="inlineStr">
-        <is>
-          <t>0.56</t>
-        </is>
-      </c>
-      <c r="BN20" t="inlineStr">
-        <is>
-          <t>-11.45161899724185</t>
-        </is>
-      </c>
-      <c r="BO20" t="inlineStr">
-        <is>
-          <t>22.56717409239306</t>
-        </is>
-      </c>
-      <c r="BP20" t="inlineStr">
-        <is>
-          <t>38.82556207928187</t>
-        </is>
-      </c>
-      <c r="BQ20" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR20" t="inlineStr">
-        <is>
-          <t>價漲量增</t>
-        </is>
-      </c>
-      <c r="BS20" t="inlineStr">
-        <is>
-          <t>1.91</t>
-        </is>
-      </c>
       <c r="BT20" t="inlineStr">
         <is>
           <t>4.66</t>
@@ -9095,7 +9095,7 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>48.44</t>
+          <t>49.24</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
@@ -9120,22 +9120,22 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>199.0</t>
+          <t>201.5</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>202.5</t>
+          <t>206.5</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>198.5</t>
+          <t>201.5</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>201.5</t>
+          <t>204.0</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -9167,12 +9167,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>19.0</t>
+          <t>167.0</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9182,7 +9182,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>197.0</t>
+          <t>201.5</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9192,22 +9192,22 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>7.94</t>
+          <t>5.84</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>21.03</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -9222,7 +9222,7 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>2025-11-26 00:00:00</t>
+          <t>2025-11-27 00:00:00</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
@@ -9247,7 +9247,7 @@
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>201.5</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
@@ -9262,7 +9262,7 @@
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
@@ -9277,17 +9277,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>4.47</t>
+          <t>39.29</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>-1.27</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9298,72 +9298,72 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>127</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>46.15</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>51.28</t>
+          <t>69.23</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>2.84</t>
+          <t>2.87</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>197.9</t>
+          <t>198.8</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>196.78</t>
+          <t>197.15</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>191.34</t>
+          <t>191.65</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>190.02</t>
+          <t>190.08</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>-11.24</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
@@ -9378,7 +9378,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-80.75</t>
+          <t>-80.72</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9388,50 +9388,50 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>28299.69197707737</t>
+          <t>28317.34549356224</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>3715.0</t>
+          <t>33609.0</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>9865.0</t>
+          <t>14692.0</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>9864.3</t>
+          <t>12138.8</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>9269.96</t>
+          <t>9836.78</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2553</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>11.33269122891031</t>
+          <t>184.9729413194776</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>-776.9723785041442</t>
+          <t>1139.994316817598</t>
         </is>
       </c>
       <c r="BD21" t="n">
-        <v>3715</v>
+        <v>33609</v>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="BF21" t="inlineStr">
@@ -9446,7 +9446,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2.60</t>
+          <t>4.95</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
@@ -9491,7 +9491,7 @@
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
@@ -9501,7 +9501,7 @@
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
@@ -9531,7 +9531,7 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>48.44</t>
+          <t>49.24</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
@@ -9556,22 +9556,22 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>199.5</t>
+          <t>199.0</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>199.5</t>
+          <t>202.5</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>197.0</t>
+          <t>198.5</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>197.0</t>
+          <t>201.5</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -9603,12 +9603,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>19.0</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9618,7 +9618,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>198.0</t>
+          <t>197.0</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9628,17 +9628,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>7.48</t>
+          <t>7.94</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9658,7 +9658,7 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>2025-11-26 00:00:00</t>
+          <t>2025-11-27 00:00:00</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
@@ -9713,17 +9713,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>7.06</t>
+          <t>4.47</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>-1.27</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9734,77 +9734,77 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>127</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>61.54</t>
+          <t>46.15</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>69.23</t>
+          <t>51.28</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>0.80</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>2.85</t>
+          <t>2.84</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>0.62</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>198.2</t>
+          <t>197.9</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>196.62</t>
+          <t>196.78</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>191.17</t>
+          <t>191.34</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>189.99</t>
+          <t>190.02</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>-6.74</t>
+          <t>-11.24</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9814,7 +9814,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-80.21</t>
+          <t>-80.75</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9824,46 +9824,46 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>28299.69197707737</t>
+          <t>28317.34549356224</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>5976.0</t>
+          <t>3715.0</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>10613.2</t>
+          <t>9865.0</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>10254.6</t>
+          <t>9864.3</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>9315.64</t>
+          <t>9269.96</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>358</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>154.6608857258293</t>
+          <t>11.33269122891031</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>-284.8186440172012</t>
+          <t>-776.9723785041442</t>
         </is>
       </c>
       <c r="BD22" t="n">
-        <v>5976</v>
+        <v>3715</v>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
@@ -9882,7 +9882,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>3.12</t>
+          <t>2.60</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
@@ -9927,7 +9927,7 @@
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -9937,7 +9937,7 @@
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
@@ -9967,7 +9967,7 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>48.44</t>
+          <t>49.24</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
@@ -9992,22 +9992,22 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
+          <t>199.5</t>
+        </is>
+      </c>
+      <c r="CE22" t="inlineStr">
+        <is>
+          <t>199.5</t>
+        </is>
+      </c>
+      <c r="CF22" t="inlineStr">
+        <is>
           <t>197.0</t>
         </is>
       </c>
-      <c r="CE22" t="inlineStr">
-        <is>
-          <t>198.5</t>
-        </is>
-      </c>
-      <c r="CF22" t="inlineStr">
+      <c r="CG22" t="inlineStr">
         <is>
           <t>197.0</t>
-        </is>
-      </c>
-      <c r="CG22" t="inlineStr">
-        <is>
-          <t>198.0</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -10039,12 +10039,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-1.75</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>42.0</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -10054,7 +10054,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>197.0</t>
+          <t>198.0</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -10064,17 +10064,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>7.94</t>
+          <t>7.48</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>16.90</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10094,7 +10094,7 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>2025-11-26 00:00:00</t>
+          <t>2025-11-27 00:00:00</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
@@ -10149,17 +10149,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>9.88</t>
+          <t>7.06</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>-1.78</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10170,77 +10170,77 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>127</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>46.15</t>
+          <t>61.54</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>70.94</t>
+          <t>69.23</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>0.60</t>
+          <t>0.80</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>2.8</t>
+          <t>2.85</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>197.5</t>
+          <t>198.2</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>196.32</t>
+          <t>196.62</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>190.97</t>
+          <t>191.17</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>189.94</t>
+          <t>189.99</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>-5.98</t>
+          <t>-6.74</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>1.89</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10250,7 +10250,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-79.87</t>
+          <t>-80.21</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10260,46 +10260,46 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>28299.69197707737</t>
+          <t>28317.34549356224</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>8426.0</t>
+          <t>5976.0</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>12937.0</t>
+          <t>10613.2</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>11067.0</t>
+          <t>10254.6</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>9335.32</t>
+          <t>9315.64</t>
         </is>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>1870</t>
+          <t>358</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>234.5662547700167</t>
+          <t>154.6608857258293</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>186.1802139647589</t>
+          <t>-284.8186440172012</t>
         </is>
       </c>
       <c r="BD23" t="n">
-        <v>8426</v>
+        <v>5976</v>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
@@ -10318,7 +10318,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2.60</t>
+          <t>3.12</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
@@ -10363,7 +10363,7 @@
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -10373,7 +10373,7 @@
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
@@ -10403,7 +10403,7 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>48.44</t>
+          <t>49.24</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
@@ -10428,12 +10428,12 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>200.5</t>
+          <t>197.0</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>200.5</t>
+          <t>198.5</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
@@ -10443,7 +10443,7 @@
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>197.0</t>
+          <t>198.0</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">

--- a/Result/checksun_type/HMI.xlsx
+++ b/Result/checksun_type/HMI.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1057,15 +1057,11 @@
           <t>19.45</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>20.26</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>21.48</t>
-        </is>
+      <c r="AM2" t="n">
+        <v>20.26</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>21.48</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
@@ -1112,20 +1108,16 @@
           <t>446.0</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>537.2</t>
-        </is>
+      <c r="AX2" t="n">
+        <v>537.2</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
           <t>724.2</t>
         </is>
       </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>1332.24</t>
-        </is>
+      <c r="AZ2" t="n">
+        <v>1332.24</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
@@ -1142,8 +1134,10 @@
           <t>-141.0385748025855</t>
         </is>
       </c>
-      <c r="BD2" t="n">
-        <v>446</v>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>446.0</t>
+        </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1309,7 +1303,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1493,15 +1487,11 @@
           <t>19.31</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>20.36</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>21.54</t>
-        </is>
+      <c r="AM3" t="n">
+        <v>20.36</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>21.54</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
@@ -1548,20 +1538,16 @@
           <t>166.0</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>494.2</t>
-        </is>
+      <c r="AX3" t="n">
+        <v>494.2</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
           <t>754.3</t>
         </is>
       </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>1394.4</t>
-        </is>
+      <c r="AZ3" t="n">
+        <v>1394.4</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
@@ -1578,8 +1564,10 @@
           <t>-143.6359791514134</t>
         </is>
       </c>
-      <c r="BD3" t="n">
-        <v>166</v>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>166.0</t>
+        </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1745,7 +1733,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1929,15 +1917,11 @@
           <t>19.25</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>20.49</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>21.61</t>
-        </is>
+      <c r="AM4" t="n">
+        <v>20.49</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>21.61</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
@@ -1984,20 +1968,16 @@
           <t>290.0</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>804.0</t>
-        </is>
+      <c r="AX4" t="n">
+        <v>804</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
           <t>822.2</t>
         </is>
       </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>1439.06</t>
-        </is>
+      <c r="AZ4" t="n">
+        <v>1439.06</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
@@ -2014,8 +1994,10 @@
           <t>-112.2167003943315</t>
         </is>
       </c>
-      <c r="BD4" t="n">
-        <v>290</v>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>290.0</t>
+        </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2181,7 +2163,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2365,15 +2347,11 @@
           <t>19.42</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>20.64</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>21.68</t>
-        </is>
+      <c r="AM5" t="n">
+        <v>20.64</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>21.68</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
@@ -2420,20 +2398,16 @@
           <t>1287.0</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>930.4</t>
-        </is>
+      <c r="AX5" t="n">
+        <v>930.4</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
           <t>895.9</t>
         </is>
       </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>1833.62</t>
-        </is>
+      <c r="AZ5" t="n">
+        <v>1833.62</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
@@ -2450,8 +2424,10 @@
           <t>-76.60999144155971</t>
         </is>
       </c>
-      <c r="BD5" t="n">
-        <v>1287</v>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>1287.0</t>
+        </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2617,7 +2593,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2801,15 +2777,11 @@
           <t>19.67</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>20.79</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>21.75</t>
-        </is>
+      <c r="AM6" t="n">
+        <v>20.79</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>21.75</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
@@ -2856,20 +2828,16 @@
           <t>497.0</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>738.2</t>
-        </is>
+      <c r="AX6" t="n">
+        <v>738.2</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
           <t>769.3</t>
         </is>
       </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>1851.22</t>
-        </is>
+      <c r="AZ6" t="n">
+        <v>1851.22</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
@@ -2886,8 +2854,10 @@
           <t>-129.8286218146873</t>
         </is>
       </c>
-      <c r="BD6" t="n">
-        <v>497</v>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>497.0</t>
+        </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -3053,7 +3023,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3237,15 +3207,11 @@
           <t>19.86</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>20.94</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>21.81</t>
-        </is>
+      <c r="AM7" t="n">
+        <v>20.94</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>21.81</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
@@ -3292,20 +3258,16 @@
           <t>231.0</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>911.2</t>
-        </is>
+      <c r="AX7" t="n">
+        <v>911.2</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
           <t>794.5</t>
         </is>
       </c>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>1867.82</t>
-        </is>
+      <c r="AZ7" t="n">
+        <v>1867.82</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
@@ -3322,8 +3284,10 @@
           <t>-116.5756429972018</t>
         </is>
       </c>
-      <c r="BD7" t="n">
-        <v>231</v>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>231.0</t>
+        </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3489,7 +3453,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3673,15 +3637,11 @@
           <t>20.17</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>21.1</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>21.86</t>
-        </is>
+      <c r="AM8" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>21.86</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
@@ -3728,20 +3688,16 @@
           <t>1715.0</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>1014.4</t>
-        </is>
+      <c r="AX8" t="n">
+        <v>1014.4</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
           <t>834.8</t>
         </is>
       </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>1896.36</t>
-        </is>
+      <c r="AZ8" t="n">
+        <v>1896.36</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
@@ -3758,8 +3714,10 @@
           <t>-64.97940029375127</t>
         </is>
       </c>
-      <c r="BD8" t="n">
-        <v>1715</v>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>1715.0</t>
+        </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3925,7 +3883,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4109,15 +4067,11 @@
           <t>20.44</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>21.27</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>21.92</t>
-        </is>
+      <c r="AM9" t="n">
+        <v>21.27</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>21.92</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
@@ -4164,20 +4118,16 @@
           <t>922.0</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>840.4</t>
-        </is>
+      <c r="AX9" t="n">
+        <v>840.4</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
           <t>714.3</t>
         </is>
       </c>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>1889.2</t>
-        </is>
+      <c r="AZ9" t="n">
+        <v>1889.2</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
@@ -4194,8 +4144,10 @@
           <t>-147.9497892783307</t>
         </is>
       </c>
-      <c r="BD9" t="n">
-        <v>922</v>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>922.0</t>
+        </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4361,7 +4313,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4545,15 +4497,11 @@
           <t>20.46</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>21.43</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>21.96</t>
-        </is>
+      <c r="AM10" t="n">
+        <v>21.43</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>21.96</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
@@ -4600,20 +4548,16 @@
           <t>326.0</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>861.4</t>
-        </is>
+      <c r="AX10" t="n">
+        <v>861.4</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
           <t>702.8</t>
         </is>
       </c>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>2075.44</t>
-        </is>
+      <c r="AZ10" t="n">
+        <v>2075.44</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
@@ -4630,8 +4574,10 @@
           <t>-176.2307096392179</t>
         </is>
       </c>
-      <c r="BD10" t="n">
-        <v>326</v>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>326.0</t>
+        </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4797,7 +4743,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4981,15 +4927,11 @@
           <t>20.53</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>21.46</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>22.01</t>
-        </is>
+      <c r="AM11" t="n">
+        <v>21.46</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>22.01</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
@@ -5036,20 +4978,16 @@
           <t>1362.0</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>800.4</t>
-        </is>
+      <c r="AX11" t="n">
+        <v>800.4</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
           <t>791.6</t>
         </is>
       </c>
-      <c r="AZ11" t="inlineStr">
-        <is>
-          <t>2169.22</t>
-        </is>
+      <c r="AZ11" t="n">
+        <v>2169.22</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
@@ -5066,8 +5004,10 @@
           <t>-146.4809276676563</t>
         </is>
       </c>
-      <c r="BD11" t="n">
-        <v>1362</v>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>1362.0</t>
+        </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5233,7 +5173,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5417,15 +5357,11 @@
           <t>20.6</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>21.49</t>
-        </is>
-      </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>22.08</t>
-        </is>
+      <c r="AM12" t="n">
+        <v>21.49</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>22.08</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
@@ -5472,20 +5408,16 @@
           <t>747.0</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>677.8</t>
-        </is>
+      <c r="AX12" t="n">
+        <v>677.8</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
           <t>999.4</t>
         </is>
       </c>
-      <c r="AZ12" t="inlineStr">
-        <is>
-          <t>2614.76</t>
-        </is>
+      <c r="AZ12" t="n">
+        <v>2614.76</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
@@ -5502,8 +5434,10 @@
           <t>-209.7497774344375</t>
         </is>
       </c>
-      <c r="BD12" t="n">
-        <v>747</v>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>747.0</t>
+        </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5669,7 +5603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5853,15 +5787,11 @@
           <t>210.0</t>
         </is>
       </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>201.08</t>
-        </is>
-      </c>
-      <c r="AN13" t="inlineStr">
-        <is>
-          <t>194.92</t>
-        </is>
+      <c r="AM13" t="n">
+        <v>201.08</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>194.92</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
@@ -5908,20 +5838,16 @@
           <t>27093.0</t>
         </is>
       </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>25064.0</t>
-        </is>
+      <c r="AX13" t="n">
+        <v>25064</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
           <t>22168.4</t>
         </is>
       </c>
-      <c r="AZ13" t="inlineStr">
-        <is>
-          <t>12662.48</t>
-        </is>
+      <c r="AZ13" t="n">
+        <v>12662.48</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
@@ -5938,8 +5864,10 @@
           <t>2440.878634307883</t>
         </is>
       </c>
-      <c r="BD13" t="n">
-        <v>27093</v>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>27093.0</t>
+        </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
@@ -6105,7 +6033,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6289,15 +6217,11 @@
           <t>207.4</t>
         </is>
       </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>200.3</t>
-        </is>
-      </c>
-      <c r="AN14" t="inlineStr">
-        <is>
-          <t>194.34</t>
-        </is>
+      <c r="AM14" t="n">
+        <v>200.3</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>194.34</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
@@ -6344,20 +6268,16 @@
           <t>27123.0</t>
         </is>
       </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>21655.6</t>
-        </is>
+      <c r="AX14" t="n">
+        <v>21655.6</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
           <t>20056.7</t>
         </is>
       </c>
-      <c r="AZ14" t="inlineStr">
-        <is>
-          <t>12284.3</t>
-        </is>
+      <c r="AZ14" t="n">
+        <v>12284.3</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
@@ -6374,8 +6294,10 @@
           <t>2293.457328001074</t>
         </is>
       </c>
-      <c r="BD14" t="n">
-        <v>27123</v>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>27123.0</t>
+        </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
@@ -6541,7 +6463,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -6725,15 +6647,11 @@
           <t>204.5</t>
         </is>
       </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>199.48</t>
-        </is>
-      </c>
-      <c r="AN15" t="inlineStr">
-        <is>
-          <t>193.8</t>
-        </is>
+      <c r="AM15" t="n">
+        <v>199.48</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>193.8</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
@@ -6780,20 +6698,16 @@
           <t>22122.0</t>
         </is>
       </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>20551.2</t>
-        </is>
+      <c r="AX15" t="n">
+        <v>20551.2</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
           <t>18187.0</t>
         </is>
       </c>
-      <c r="AZ15" t="inlineStr">
-        <is>
-          <t>11819.44</t>
-        </is>
+      <c r="AZ15" t="n">
+        <v>11819.44</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
@@ -6810,8 +6724,10 @@
           <t>1997.731985848452</t>
         </is>
       </c>
-      <c r="BD15" t="n">
-        <v>22122</v>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>22122.0</t>
+        </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
@@ -6977,7 +6893,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -7161,15 +7077,11 @@
           <t>203.2</t>
         </is>
       </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>198.92</t>
-        </is>
-      </c>
-      <c r="AN16" t="inlineStr">
-        <is>
-          <t>193.33</t>
-        </is>
+      <c r="AM16" t="n">
+        <v>198.92</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>193.33</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
@@ -7216,20 +7128,16 @@
           <t>26279.0</t>
         </is>
       </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>21604.4</t>
-        </is>
+      <c r="AX16" t="n">
+        <v>21604.4</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
           <t>18148.2</t>
         </is>
       </c>
-      <c r="AZ16" t="inlineStr">
-        <is>
-          <t>11512.0</t>
-        </is>
+      <c r="AZ16" t="n">
+        <v>11512</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
@@ -7246,8 +7154,10 @@
           <t>2039.741068992971</t>
         </is>
       </c>
-      <c r="BD16" t="n">
-        <v>26279</v>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>26279.0</t>
+        </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
@@ -7413,7 +7323,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -7597,15 +7507,11 @@
           <t>202.1</t>
         </is>
       </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>198.58</t>
-        </is>
-      </c>
-      <c r="AN17" t="inlineStr">
-        <is>
-          <t>192.93</t>
-        </is>
+      <c r="AM17" t="n">
+        <v>198.58</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>192.93</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
@@ -7652,20 +7558,16 @@
           <t>22703.0</t>
         </is>
       </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>23070.4</t>
-        </is>
+      <c r="AX17" t="n">
+        <v>23070.4</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
           <t>16467.7</t>
         </is>
       </c>
-      <c r="AZ17" t="inlineStr">
-        <is>
-          <t>11056.48</t>
-        </is>
+      <c r="AZ17" t="n">
+        <v>11056.48</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
@@ -7682,8 +7584,10 @@
           <t>1581.513292449679</t>
         </is>
       </c>
-      <c r="BD17" t="n">
-        <v>22703</v>
+      <c r="BD17" t="inlineStr">
+        <is>
+          <t>22703.0</t>
+        </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
@@ -7849,7 +7753,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -8033,15 +7937,11 @@
           <t>200.6</t>
         </is>
       </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>198.25</t>
-        </is>
-      </c>
-      <c r="AN18" t="inlineStr">
-        <is>
-          <t>192.58</t>
-        </is>
+      <c r="AM18" t="n">
+        <v>198.25</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>192.58</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
@@ -8088,20 +7988,16 @@
           <t>10051.0</t>
         </is>
       </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>19272.8</t>
-        </is>
+      <c r="AX18" t="n">
+        <v>19272.8</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
           <t>14943.0</t>
         </is>
       </c>
-      <c r="AZ18" t="inlineStr">
-        <is>
-          <t>10672.76</t>
-        </is>
+      <c r="AZ18" t="n">
+        <v>10672.76</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
@@ -8118,8 +8014,10 @@
           <t>1253.562422657489</t>
         </is>
       </c>
-      <c r="BD18" t="n">
-        <v>10051</v>
+      <c r="BD18" t="inlineStr">
+        <is>
+          <t>10051.0</t>
+        </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
@@ -8285,7 +8183,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -8469,15 +8367,11 @@
           <t>200.0</t>
         </is>
       </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>197.98</t>
-        </is>
-      </c>
-      <c r="AN19" t="inlineStr">
-        <is>
-          <t>192.28</t>
-        </is>
+      <c r="AM19" t="n">
+        <v>197.98</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>192.28</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
@@ -8524,20 +8418,16 @@
           <t>21601.0</t>
         </is>
       </c>
-      <c r="AX19" t="inlineStr">
-        <is>
-          <t>18457.8</t>
-        </is>
+      <c r="AX19" t="n">
+        <v>18457.8</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
           <t>15697.4</t>
         </is>
       </c>
-      <c r="AZ19" t="inlineStr">
-        <is>
-          <t>10622.98</t>
-        </is>
+      <c r="AZ19" t="n">
+        <v>10622.98</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
@@ -8554,8 +8444,10 @@
           <t>2095.862522145168</t>
         </is>
       </c>
-      <c r="BD19" t="n">
-        <v>21601</v>
+      <c r="BD19" t="inlineStr">
+        <is>
+          <t>21601.0</t>
+        </is>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
@@ -8721,7 +8613,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -8905,15 +8797,11 @@
           <t>199.5</t>
         </is>
       </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>197.7</t>
-        </is>
-      </c>
-      <c r="AN20" t="inlineStr">
-        <is>
-          <t>192.01</t>
-        </is>
+      <c r="AM20" t="n">
+        <v>197.7</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>192.01</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
@@ -8960,20 +8848,16 @@
           <t>27388.0</t>
         </is>
       </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>15822.8</t>
-        </is>
+      <c r="AX20" t="n">
+        <v>15822.8</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
           <t>14450.7</t>
         </is>
       </c>
-      <c r="AZ20" t="inlineStr">
-        <is>
-          <t>10277.46</t>
-        </is>
+      <c r="AZ20" t="n">
+        <v>10277.46</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
@@ -8990,8 +8874,10 @@
           <t>1986.79614562238</t>
         </is>
       </c>
-      <c r="BD20" t="n">
-        <v>27388</v>
+      <c r="BD20" t="inlineStr">
+        <is>
+          <t>27388.0</t>
+        </is>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
@@ -9157,7 +9043,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -9341,15 +9227,11 @@
           <t>198.8</t>
         </is>
       </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>197.15</t>
-        </is>
-      </c>
-      <c r="AN21" t="inlineStr">
-        <is>
-          <t>191.65</t>
-        </is>
+      <c r="AM21" t="n">
+        <v>197.15</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>191.65</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
@@ -9396,20 +9278,16 @@
           <t>33609.0</t>
         </is>
       </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>14692.0</t>
-        </is>
+      <c r="AX21" t="n">
+        <v>14692</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
           <t>12138.8</t>
         </is>
       </c>
-      <c r="AZ21" t="inlineStr">
-        <is>
-          <t>9836.78</t>
-        </is>
+      <c r="AZ21" t="n">
+        <v>9836.780000000001</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
@@ -9426,8 +9304,10 @@
           <t>1139.994316817598</t>
         </is>
       </c>
-      <c r="BD21" t="n">
-        <v>33609</v>
+      <c r="BD21" t="inlineStr">
+        <is>
+          <t>33609.0</t>
+        </is>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
@@ -9593,7 +9473,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -9777,15 +9657,11 @@
           <t>197.9</t>
         </is>
       </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>196.78</t>
-        </is>
-      </c>
-      <c r="AN22" t="inlineStr">
-        <is>
-          <t>191.34</t>
-        </is>
+      <c r="AM22" t="n">
+        <v>196.78</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>191.34</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
@@ -9832,20 +9708,16 @@
           <t>3715.0</t>
         </is>
       </c>
-      <c r="AX22" t="inlineStr">
-        <is>
-          <t>9865.0</t>
-        </is>
+      <c r="AX22" t="n">
+        <v>9865</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
           <t>9864.3</t>
         </is>
       </c>
-      <c r="AZ22" t="inlineStr">
-        <is>
-          <t>9269.96</t>
-        </is>
+      <c r="AZ22" t="n">
+        <v>9269.959999999999</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
@@ -9862,8 +9734,10 @@
           <t>-776.9723785041442</t>
         </is>
       </c>
-      <c r="BD22" t="n">
-        <v>3715</v>
+      <c r="BD22" t="inlineStr">
+        <is>
+          <t>3715.0</t>
+        </is>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
@@ -10029,7 +9903,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -10213,15 +10087,11 @@
           <t>198.2</t>
         </is>
       </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>196.62</t>
-        </is>
-      </c>
-      <c r="AN23" t="inlineStr">
-        <is>
-          <t>191.17</t>
-        </is>
+      <c r="AM23" t="n">
+        <v>196.62</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>191.17</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
@@ -10268,20 +10138,16 @@
           <t>5976.0</t>
         </is>
       </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t>10613.2</t>
-        </is>
+      <c r="AX23" t="n">
+        <v>10613.2</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
           <t>10254.6</t>
         </is>
       </c>
-      <c r="AZ23" t="inlineStr">
-        <is>
-          <t>9315.64</t>
-        </is>
+      <c r="AZ23" t="n">
+        <v>9315.639999999999</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
@@ -10298,8 +10164,10 @@
           <t>-284.8186440172012</t>
         </is>
       </c>
-      <c r="BD23" t="n">
-        <v>5976</v>
+      <c r="BD23" t="inlineStr">
+        <is>
+          <t>5976.0</t>
+        </is>
       </c>
       <c r="BE23" t="inlineStr">
         <is>

--- a/Result/checksun_type/HMI.xlsx
+++ b/Result/checksun_type/HMI.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>22.0</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>19.85</t>
+          <t>19.75</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-25.82</t>
+          <t>-17.60</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-9.15</t>
+          <t>-9.61</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>-2.53</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,37 +1014,37 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>53.85</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>28.0</t>
+          <t>49.15</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-4.02</t>
+          <t>-3.26</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-5.68</t>
+          <t>-5.98</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
@@ -1054,28 +1054,28 @@
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>19.45</t>
+          <t>19.5</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>20.26</v>
+        <v>20.16</v>
       </c>
       <c r="AN2" t="n">
-        <v>21.48</v>
+        <v>21.44</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>22.36</t>
+          <t>22.31</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-1.89</t>
+          <t>3.76</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>-0.60</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
@@ -1090,53 +1090,53 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-109.58</t>
+          <t>-109.49</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
         <is>
-          <t>2025/10/21</t>
+          <t>2025/11/27</t>
         </is>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>30376.36480686695</t>
+          <t>30333.82071428571</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>446.0</t>
+          <t>397.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>537.2</v>
+        <v>517.2</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>724.2</t>
+          <t>627.7</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>1332.24</v>
+        <v>1309.6</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-187</t>
+          <t>-110</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-142.1892822709431</t>
+          <t>-141.7554584428505</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-141.0385748025855</t>
+          <t>-139.3694273883414</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>446.0</t>
+          <t>397.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-16.07</t>
+          <t>-16.49</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1201,17 +1201,17 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>89.09</t>
+          <t>89.61</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>579</t>
+          <t>576</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,22 +1266,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>19.45</t>
+          <t>20.3</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>20.05</t>
+          <t>20.3</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>19.45</t>
+          <t>19.7</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>19.85</t>
+          <t>19.75</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>9.0</t>
+          <t>22.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>19.5</t>
+          <t>19.85</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-34.48</t>
+          <t>-25.82</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-10.76</t>
+          <t>-9.15</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,68 +1444,68 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>26.92</t>
+          <t>53.85</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>11.12</t>
+          <t>28.0</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>2.06</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-5.18</t>
+          <t>-4.02</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-5.44</t>
+          <t>-5.68</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-3.78</t>
+          <t>-3.92</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>19.31</t>
+          <t>19.45</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>20.36</v>
+        <v>20.26</v>
       </c>
       <c r="AN3" t="n">
-        <v>21.54</v>
+        <v>21.48</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>22.38</t>
+          <t>22.36</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-10.91</t>
+          <t>-1.89</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-0.70</t>
+          <t>-0.64</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
@@ -1520,53 +1520,53 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-109.53</t>
+          <t>-109.58</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>2025/10/21</t>
+          <t>2025/11/27</t>
         </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>30376.36480686695</t>
+          <t>30333.82071428571</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>166.0</t>
+          <t>446.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>494.2</v>
+        <v>537.2</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>754.3</t>
+          <t>724.2</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>1394.4</v>
+        <v>1332.24</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-260</t>
+          <t>-187</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-142.3985018106445</t>
+          <t>-142.1892822709431</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-143.6359791514134</t>
+          <t>-141.0385748025855</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>166.0</t>
+          <t>446.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-17.55</t>
+          <t>-16.07</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1631,17 +1631,17 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>89.09</t>
+          <t>89.61</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>579</t>
+          <t>576</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,22 +1696,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>19.3</t>
+          <t>19.45</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>19.5</t>
+          <t>20.05</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>19.3</t>
+          <t>19.45</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>19.5</t>
+          <t>19.85</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>19.2</t>
+          <t>19.5</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>3.27</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-2.21</t>
+          <t>-34.48</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-12.13</t>
+          <t>-10.76</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,54 +1874,54 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>3.23</t>
+          <t>26.92</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>9.68</t>
+          <t>11.12</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-6.04</t>
+          <t>-5.18</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-5.2</t>
+          <t>-5.44</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-3.45</t>
+          <t>-3.78</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>19.25</t>
+          <t>19.31</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>20.49</v>
+        <v>20.36</v>
       </c>
       <c r="AN4" t="n">
-        <v>21.61</v>
+        <v>21.54</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
@@ -1930,17 +1930,17 @@
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-17.72</t>
+          <t>-10.91</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>-0.70</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-0.63</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,53 +1950,53 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-109.27</t>
+          <t>-109.53</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>2025/10/21</t>
+          <t>2025/11/27</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>30376.36480686695</t>
+          <t>30333.82071428571</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>290.0</t>
+          <t>166.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>804</v>
+        <v>494.2</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>822.2</t>
+          <t>754.3</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>1439.06</v>
+        <v>1394.4</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-18</t>
+          <t>-260</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-142.1735059305047</t>
+          <t>-142.3985018106445</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-112.2167003943315</t>
+          <t>-143.6359791514134</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>290.0</t>
+          <t>166.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-18.82</t>
+          <t>-17.55</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>89.09</t>
+          <t>89.61</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>579</t>
+          <t>576</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,22 +2126,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>19.2</t>
+          <t>19.3</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
+          <t>19.5</t>
+        </is>
+      </c>
+      <c r="CF4" t="inlineStr">
+        <is>
           <t>19.3</t>
         </is>
       </c>
-      <c r="CF4" t="inlineStr">
-        <is>
-          <t>19.2</t>
-        </is>
-      </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>19.2</t>
+          <t>19.5</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-1.53</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>3.27</t>
+          <t>2.78</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>3.85</t>
+          <t>-2.21</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,12 +2304,12 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -2319,58 +2319,58 @@
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>9.68</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-1.13</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-5.90</t>
+          <t>-6.04</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-4.83</t>
+          <t>-5.2</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-3.05</t>
+          <t>-3.45</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>19.42</t>
+          <t>19.25</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>20.64</v>
+        <v>20.49</v>
       </c>
       <c r="AN5" t="n">
-        <v>21.68</v>
+        <v>21.61</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>22.37</t>
+          <t>22.38</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-21.10</t>
+          <t>-17.72</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,53 +2380,53 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-108.86</t>
+          <t>-109.27</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>2025/10/21</t>
+          <t>2025/11/27</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>30376.36480686695</t>
+          <t>30333.82071428571</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>1287.0</t>
+          <t>290.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>930.4</v>
+        <v>804</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>895.9</t>
+          <t>822.2</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>1833.62</v>
+        <v>1439.06</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>-18</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-147.6201978461726</t>
+          <t>-142.1735059305047</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-76.60999144155971</t>
+          <t>-112.2167003943315</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>1287.0</t>
+          <t>290.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>89.09</t>
+          <t>89.61</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>579</t>
+          <t>576</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,17 +2556,17 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>19.55</t>
+          <t>19.2</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>19.65</t>
+          <t>19.3</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>18.85</t>
+          <t>19.2</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>-1.53</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>26.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>19.5</t>
+          <t>19.2</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>2.78</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-4.04</t>
+          <t>3.85</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-10.76</t>
+          <t>-12.13</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>3.17</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,73 +2734,73 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>22.58</t>
+          <t>3.23</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>7.53</t>
+          <t>8.6</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>-1.13</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-5.39</t>
+          <t>-5.90</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-4.43</t>
+          <t>-4.83</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-2.68</t>
+          <t>-3.05</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>19.67</t>
+          <t>19.42</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>20.79</v>
+        <v>20.64</v>
       </c>
       <c r="AN6" t="n">
-        <v>21.75</v>
+        <v>21.68</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>22.35</t>
+          <t>22.37</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-23.19</t>
+          <t>-21.10</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.68</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,53 +2810,53 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-108.40</t>
+          <t>-108.86</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>2025/10/21</t>
+          <t>2025/11/27</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>30376.36480686695</t>
+          <t>30333.82071428571</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>497.0</t>
+          <t>1287.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>738.2</v>
+        <v>930.4</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>769.3</t>
+          <t>895.9</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>1851.22</v>
+        <v>1833.62</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-31</t>
+          <t>34</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-160.5311444651931</t>
+          <t>-147.6201978461726</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-129.8286218146873</t>
+          <t>-76.60999144155971</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>497.0</t>
+          <t>1287.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-17.55</t>
+          <t>-18.82</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>89.09</t>
+          <t>89.61</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>579</t>
+          <t>576</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
+          <t>19.55</t>
+        </is>
+      </c>
+      <c r="CE6" t="inlineStr">
+        <is>
+          <t>19.65</t>
+        </is>
+      </c>
+      <c r="CF6" t="inlineStr">
+        <is>
+          <t>18.85</t>
+        </is>
+      </c>
+      <c r="CG6" t="inlineStr">
+        <is>
           <t>19.2</t>
-        </is>
-      </c>
-      <c r="CE6" t="inlineStr">
-        <is>
-          <t>19.5</t>
-        </is>
-      </c>
-      <c r="CF6" t="inlineStr">
-        <is>
-          <t>18.9</t>
-        </is>
-      </c>
-      <c r="CG6" t="inlineStr">
-        <is>
-          <t>19.5</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>26.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>19.15</t>
+          <t>19.5</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>3.53</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>14.69</t>
+          <t>-4.04</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-12.36</t>
+          <t>-10.76</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>3.17</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,73 +3164,73 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>22.58</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.53</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-3.58</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-5.17</t>
+          <t>-5.39</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-3.97</t>
+          <t>-4.43</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-2.33</t>
+          <t>-2.68</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>19.86</t>
+          <t>19.67</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>20.94</v>
+        <v>20.79</v>
       </c>
       <c r="AN7" t="n">
-        <v>21.81</v>
+        <v>21.75</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>22.33</t>
+          <t>22.35</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-28.42</t>
+          <t>-23.19</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-0.68</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-0.55</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,53 +3240,53 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-107.91</t>
+          <t>-108.40</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>2025/10/21</t>
+          <t>2025/11/27</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>30376.36480686695</t>
+          <t>30333.82071428571</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>231.0</t>
+          <t>497.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>911.2</v>
+        <v>738.2</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>794.5</t>
+          <t>769.3</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>1867.82</v>
+        <v>1851.22</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>116</t>
+          <t>-31</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-166.1134213107396</t>
+          <t>-160.5311444651931</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-116.5756429972018</t>
+          <t>-129.8286218146873</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>231.0</t>
+          <t>497.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-19.03</t>
+          <t>-17.55</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3351,17 +3351,17 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>89.09</t>
+          <t>89.61</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>579</t>
+          <t>576</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,22 +3416,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>18.85</t>
+          <t>19.2</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>19.15</t>
+          <t>19.5</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>18.85</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>19.15</t>
+          <t>19.5</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-4.24</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>19.2</t>
+          <t>19.15</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>3.27</t>
+          <t>3.04</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>21.51</t>
+          <t>14.69</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-12.13</t>
+          <t>-12.36</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>3.15</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-3.37</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,12 +3594,12 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
@@ -3609,58 +3609,58 @@
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>15.38</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-4.81</t>
+          <t>-3.58</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-4.41</t>
+          <t>-5.17</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-3.49</t>
+          <t>-3.97</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-2.01</t>
+          <t>-2.33</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>20.17</t>
+          <t>19.86</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>21.1</v>
+        <v>20.94</v>
       </c>
       <c r="AN8" t="n">
-        <v>21.86</v>
+        <v>21.81</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>22.31</t>
+          <t>22.33</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-25.64</t>
+          <t>-28.42</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,53 +3670,53 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-107.35</t>
+          <t>-107.91</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>2025/10/21</t>
+          <t>2025/11/27</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>30376.36480686695</t>
+          <t>30333.82071428571</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>1715.0</t>
+          <t>231.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>1014.4</v>
+        <v>911.2</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>834.8</t>
+          <t>794.5</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>1896.36</v>
+        <v>1867.82</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>179</t>
+          <t>116</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-175.1202900950192</t>
+          <t>-166.1134213107396</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-64.97940029375127</t>
+          <t>-116.5756429972018</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>1715.0</t>
+          <t>231.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-18.82</t>
+          <t>-19.03</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3781,7 +3781,7 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -3791,7 +3791,7 @@
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>89.09</t>
+          <t>89.61</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>579</t>
+          <t>576</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,22 +3846,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>20.05</t>
+          <t>18.85</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>20.05</t>
+          <t>19.15</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>19.0</t>
+          <t>18.85</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>19.2</t>
+          <t>19.15</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-2.0</t>
+          <t>-4.24</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>46.0</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>20.05</t>
+          <t>19.2</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-1.01</t>
+          <t>2.78</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>17.65</t>
+          <t>21.51</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-8.24</t>
+          <t>-12.13</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>3.15</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>-3.37</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,12 +4024,12 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
@@ -4039,58 +4039,58 @@
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>23.08</t>
+          <t>15.38</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-1.91</t>
+          <t>-4.81</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-3.90</t>
+          <t>-4.41</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-2.98</t>
+          <t>-3.49</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-1.65</t>
+          <t>-2.01</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>20.44</t>
+          <t>20.17</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>21.27</v>
+        <v>21.1</v>
       </c>
       <c r="AN9" t="n">
-        <v>21.92</v>
+        <v>21.86</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>22.29</t>
+          <t>22.31</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-16.23</t>
+          <t>-25.64</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,53 +4100,53 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-106.88</t>
+          <t>-107.35</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>2025/10/21</t>
+          <t>2025/11/27</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>30376.36480686695</t>
+          <t>30333.82071428571</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>922.0</t>
+          <t>1715.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>840.4</v>
+        <v>1014.4</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>714.3</t>
+          <t>834.8</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>1889.2</v>
+        <v>1896.36</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>126</t>
+          <t>179</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-195.1459064225224</t>
+          <t>-175.1202900950192</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-147.9497892783307</t>
+          <t>-64.97940029375127</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>922.0</t>
+          <t>1715.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-15.22</t>
+          <t>-18.82</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4211,7 +4211,7 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4221,7 +4221,7 @@
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>89.09</t>
+          <t>89.61</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>579</t>
+          <t>576</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,22 +4276,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>20.05</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>20.1</t>
+          <t>20.05</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>19.95</t>
+          <t>19.0</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>20.05</t>
+          <t>19.2</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-2.0</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>16.0</t>
+          <t>46.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>20.45</t>
+          <t>20.05</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-3.02</t>
+          <t>-1.52</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>22.57</t>
+          <t>17.65</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-6.41</t>
+          <t>-8.24</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,73 +4454,73 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>46.15</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>36.17</t>
+          <t>23.08</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-1.91</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-4.52</t>
+          <t>-3.90</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-2.41</t>
+          <t>-2.98</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-1.36</t>
+          <t>-1.65</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>20.46</t>
+          <t>20.44</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>21.43</v>
+        <v>21.27</v>
       </c>
       <c r="AN10" t="n">
-        <v>21.96</v>
+        <v>21.92</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>22.26</t>
+          <t>22.29</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-15.32</t>
+          <t>-16.23</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.50</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,53 +4530,53 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-106.60</t>
+          <t>-106.88</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>2025/10/21</t>
+          <t>2025/11/27</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>30376.36480686695</t>
+          <t>30333.82071428571</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>326.0</t>
+          <t>922.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>861.4</v>
+        <v>840.4</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>702.8</t>
+          <t>714.3</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>2075.44</v>
+        <v>1889.2</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>158</t>
+          <t>126</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-203.7270186305573</t>
+          <t>-195.1459064225224</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-176.2307096392179</t>
+          <t>-147.9497892783307</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>326.0</t>
+          <t>922.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-13.53</t>
+          <t>-15.22</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4641,7 +4641,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>89.09</t>
+          <t>89.61</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>579</t>
+          <t>576</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>20.45</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>20.45</t>
+          <t>20.1</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>20.3</t>
+          <t>19.95</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>20.45</t>
+          <t>20.05</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-1.19</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4778,17 +4778,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-3.02</t>
+          <t>-3.54</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>22.57</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-1.95</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,63 +4884,63 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>23.08</t>
+          <t>46.15</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>28.41</t>
+          <t>36.17</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-4.33</t>
+          <t>-4.52</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-2.52</t>
+          <t>-2.41</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>-1.36</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>20.53</t>
+          <t>20.46</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>21.46</v>
+        <v>21.43</v>
       </c>
       <c r="AN11" t="n">
-        <v>22.01</v>
+        <v>21.96</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>22.23</t>
+          <t>22.26</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-20.19</t>
+          <t>-15.32</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
@@ -4950,7 +4950,7 @@
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,53 +4960,53 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-106.34</t>
+          <t>-106.60</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>2025/10/21</t>
+          <t>2025/11/27</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>30376.36480686695</t>
+          <t>30333.82071428571</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>1362.0</t>
+          <t>326.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>800.4</v>
+        <v>861.4</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>791.6</t>
+          <t>702.8</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>2169.22</v>
+        <v>2075.44</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>158</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-208.7263475380736</t>
+          <t>-203.7270186305573</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-146.4809276676563</t>
+          <t>-176.2307096392179</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>1362.0</t>
+          <t>326.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>89.09</t>
+          <t>89.61</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>579</t>
+          <t>576</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,12 +5136,12 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>21.0</t>
+          <t>20.45</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>21.0</t>
+          <t>20.45</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>-1.19</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>36.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>20.7</t>
+          <t>20.45</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5208,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-4.28</t>
+          <t>-3.54</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-32.18</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-5.26</t>
+          <t>-6.41</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>-1.95</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,63 +5314,63 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>39.29</t>
+          <t>23.08</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>20.71</t>
+          <t>28.41</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-4.13</t>
+          <t>-4.33</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-2.66</t>
+          <t>-2.52</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-0.54</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>20.6</t>
+          <t>20.53</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>21.49</v>
+        <v>21.46</v>
       </c>
       <c r="AN12" t="n">
-        <v>22.08</v>
+        <v>22.01</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>22.19</t>
+          <t>22.23</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-25.12</t>
+          <t>-20.19</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
@@ -5380,7 +5380,7 @@
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,53 +5390,53 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-106.02</t>
+          <t>-106.34</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>2025/10/21</t>
+          <t>2025/11/27</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>30376.36480686695</t>
+          <t>30333.82071428571</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>747.0</t>
+          <t>1362.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>677.8</v>
+        <v>800.4</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>999.4</t>
+          <t>791.6</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>2614.76</v>
+        <v>2169.22</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-321</t>
+          <t>8</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-220.0436966054221</t>
+          <t>-208.7263475380736</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-209.7497774344375</t>
+          <t>-146.4809276676563</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>747.0</t>
+          <t>1362.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-12.47</t>
+          <t>-13.53</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,7 +5511,7 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>89.09</t>
+          <t>89.61</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>579</t>
+          <t>576</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,22 +5566,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>20.6</t>
+          <t>21.0</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>20.95</t>
+          <t>21.0</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>20.55</t>
+          <t>20.3</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>20.7</t>
+          <t>20.45</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5613,42 +5613,42 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
+          <t>0.23</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>214.5</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>127.0</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>214.0</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>13.06</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5668,7 +5668,7 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>2025-11-27 00:00:00</t>
+          <t>2025-11-28 00:00:00</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -5708,7 +5708,7 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>6.20</t>
+          <t>6.45</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
@@ -5723,17 +5723,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>29.88</t>
+          <t>19.06</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5744,12 +5744,12 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>127</t>
+          <t>81</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
@@ -5764,53 +5764,53 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>4.44</t>
+          <t>4.99</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>3.16</t>
+          <t>3.29</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>210.0</t>
+          <t>212.0</t>
         </is>
       </c>
       <c r="AM13" t="n">
-        <v>201.08</v>
+        <v>201.92</v>
       </c>
       <c r="AN13" t="n">
-        <v>194.92</v>
+        <v>195.5</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>192.22</t>
+          <t>192.61</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>43.25</t>
+          <t>39.40</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>4.54</t>
+          <t>4.90</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>3.17</t>
+          <t>3.51</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5820,7 +5820,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-68.36</t>
+          <t>-64.90</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5830,48 +5830,48 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>28317.34549356224</t>
+          <t>28313.90571428571</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>27093.0</t>
+          <t>17273.0</t>
         </is>
       </c>
       <c r="AX13" t="n">
-        <v>25064</v>
+        <v>23978</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>22168.4</t>
+          <t>23524.2</t>
         </is>
       </c>
       <c r="AZ13" t="n">
-        <v>12662.48</v>
+        <v>12876.32</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>2895</t>
+          <t>453</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>1554.494789995829</t>
+          <t>1584.041988898771</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>2440.878634307883</t>
+          <t>1746.551582864951</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>27093.0</t>
+          <t>17273.0</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="BF13" t="inlineStr">
@@ -5886,7 +5886,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>11.46</t>
+          <t>11.72</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -5931,7 +5931,7 @@
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
@@ -5941,12 +5941,12 @@
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
         <is>
-          <t>4.66</t>
+          <t>4.65</t>
         </is>
       </c>
       <c r="BU13" t="inlineStr">
@@ -5956,7 +5956,7 @@
       </c>
       <c r="BV13" t="inlineStr">
         <is>
-          <t>12.78</t>
+          <t>12.81</t>
         </is>
       </c>
       <c r="BW13" t="inlineStr">
@@ -5971,12 +5971,12 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>49.24</t>
+          <t>49.59</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>10177</t>
+          <t>10201</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -5996,7 +5996,7 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>215.0</t>
+          <t>214.5</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
@@ -6006,12 +6006,12 @@
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>211.0</t>
+          <t>213.0</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>214.0</t>
+          <t>214.5</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6068,17 +6068,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>7.97</t>
+          <t>13.06</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6098,7 +6098,7 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>2025-11-27 00:00:00</t>
+          <t>2025-11-28 00:00:00</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -6153,17 +6153,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>30.12</t>
+          <t>29.88</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6174,12 +6174,12 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>127</t>
+          <t>81</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
@@ -6194,53 +6194,53 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>3.18</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>3.54</t>
+          <t>4.44</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>3.07</t>
+          <t>3.16</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>207.4</t>
+          <t>210.0</t>
         </is>
       </c>
       <c r="AM14" t="n">
-        <v>200.3</v>
+        <v>201.08</v>
       </c>
       <c r="AN14" t="n">
-        <v>194.34</v>
+        <v>194.92</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>191.84</t>
+          <t>192.22</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>43.78</t>
+          <t>43.25</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>4.06</t>
+          <t>4.54</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>2.83</t>
+          <t>3.17</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6250,7 +6250,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-71.78</t>
+          <t>-68.36</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6260,48 +6260,48 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>28317.34549356224</t>
+          <t>28313.90571428571</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>27123.0</t>
+          <t>27093.0</t>
         </is>
       </c>
       <c r="AX14" t="n">
-        <v>21655.6</v>
+        <v>25064</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>20056.7</t>
+          <t>22168.4</t>
         </is>
       </c>
       <c r="AZ14" t="n">
-        <v>12284.3</v>
+        <v>12662.48</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>1598</t>
+          <t>2895</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>1393.334091030001</t>
+          <t>1554.494789995829</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>2293.457328001074</t>
+          <t>2440.878634307883</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>27123.0</t>
+          <t>27093.0</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="BF14" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS14" t="inlineStr">
@@ -6376,7 +6376,7 @@
       </c>
       <c r="BT14" t="inlineStr">
         <is>
-          <t>4.66</t>
+          <t>4.65</t>
         </is>
       </c>
       <c r="BU14" t="inlineStr">
@@ -6386,7 +6386,7 @@
       </c>
       <c r="BV14" t="inlineStr">
         <is>
-          <t>12.78</t>
+          <t>12.81</t>
         </is>
       </c>
       <c r="BW14" t="inlineStr">
@@ -6401,12 +6401,12 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>49.24</t>
+          <t>49.59</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>10177</t>
+          <t>10201</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -6426,17 +6426,17 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
+          <t>215.0</t>
+        </is>
+      </c>
+      <c r="CE14" t="inlineStr">
+        <is>
+          <t>215.5</t>
+        </is>
+      </c>
+      <c r="CF14" t="inlineStr">
+        <is>
           <t>211.0</t>
-        </is>
-      </c>
-      <c r="CE14" t="inlineStr">
-        <is>
-          <t>214.0</t>
-        </is>
-      </c>
-      <c r="CF14" t="inlineStr">
-        <is>
-          <t>210.5</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
@@ -6473,12 +6473,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>105.0</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6488,7 +6488,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>210.5</t>
+          <t>214.0</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6498,17 +6498,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>13.00</t>
+          <t>7.97</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6528,7 +6528,7 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>2025-11-27 00:00:00</t>
+          <t>2025-11-28 00:00:00</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -6568,7 +6568,7 @@
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>4.47</t>
+          <t>6.20</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
@@ -6583,17 +6583,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>24.71</t>
+          <t>30.12</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6604,12 +6604,12 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>127</t>
+          <t>81</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
@@ -6624,53 +6624,53 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>2.93</t>
+          <t>3.18</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>2.52</t>
+          <t>3.54</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>2.93</t>
+          <t>3.07</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>204.5</t>
+          <t>207.4</t>
         </is>
       </c>
       <c r="AM15" t="n">
-        <v>199.48</v>
+        <v>200.3</v>
       </c>
       <c r="AN15" t="n">
-        <v>193.8</v>
+        <v>194.34</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>191.47</t>
+          <t>191.84</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>34.99</t>
+          <t>43.78</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>4.06</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>2.52</t>
+          <t>2.83</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6680,7 +6680,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-74.87</t>
+          <t>-71.78</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6690,48 +6690,48 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>28317.34549356224</t>
+          <t>28313.90571428571</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>22122.0</t>
+          <t>27123.0</t>
         </is>
       </c>
       <c r="AX15" t="n">
-        <v>20551.2</v>
+        <v>21655.6</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>18187.0</t>
+          <t>20056.7</t>
         </is>
       </c>
       <c r="AZ15" t="n">
-        <v>11819.44</v>
+        <v>12284.3</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>2364</t>
+          <t>1598</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>1229.675320671625</t>
+          <t>1393.334091030001</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>1997.731985848452</t>
+          <t>2293.457328001074</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>22122.0</t>
+          <t>27123.0</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="BF15" t="inlineStr">
@@ -6746,7 +6746,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>9.64</t>
+          <t>11.46</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -6791,7 +6791,7 @@
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
@@ -6801,12 +6801,12 @@
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
         <is>
-          <t>4.66</t>
+          <t>4.65</t>
         </is>
       </c>
       <c r="BU15" t="inlineStr">
@@ -6816,7 +6816,7 @@
       </c>
       <c r="BV15" t="inlineStr">
         <is>
-          <t>12.78</t>
+          <t>12.81</t>
         </is>
       </c>
       <c r="BW15" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>49.24</t>
+          <t>49.59</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>10177</t>
+          <t>10201</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -6856,22 +6856,22 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>208.5</t>
+          <t>211.0</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>211.0</t>
+          <t>214.0</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>208.0</t>
+          <t>210.5</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>210.5</t>
+          <t>214.0</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -6903,12 +6903,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>105.0</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6918,7 +6918,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>207.0</t>
+          <t>210.5</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6928,17 +6928,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>3.27</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>19.04</t>
+          <t>13.00</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -6958,7 +6958,7 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>2025-11-27 00:00:00</t>
+          <t>2025-11-28 00:00:00</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -6998,7 +6998,7 @@
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>2.73</t>
+          <t>4.47</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
@@ -7013,17 +7013,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>30.12</t>
+          <t>24.71</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7034,12 +7034,12 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>127</t>
+          <t>81</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
@@ -7049,58 +7049,58 @@
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>85.71</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>2.93</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>2.52</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>2.89</t>
+          <t>2.93</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>203.2</t>
+          <t>204.5</t>
         </is>
       </c>
       <c r="AM16" t="n">
-        <v>198.92</v>
+        <v>199.48</v>
       </c>
       <c r="AN16" t="n">
-        <v>193.33</v>
+        <v>193.8</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>191.14</t>
+          <t>191.47</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>24.29</t>
+          <t>34.99</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>2.85</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>2.52</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7110,7 +7110,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-77.07</t>
+          <t>-74.87</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7120,48 +7120,48 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>28317.34549356224</t>
+          <t>28313.90571428571</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>26279.0</t>
+          <t>22122.0</t>
         </is>
       </c>
       <c r="AX16" t="n">
-        <v>21604.4</v>
+        <v>20551.2</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>18148.2</t>
+          <t>18187.0</t>
         </is>
       </c>
       <c r="AZ16" t="n">
-        <v>11512</v>
+        <v>11819.44</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>3456</t>
+          <t>2364</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>1090.028654275838</t>
+          <t>1229.675320671625</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>2039.741068992971</t>
+          <t>1997.731985848452</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>26279.0</t>
+          <t>22122.0</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="BF16" t="inlineStr">
@@ -7176,7 +7176,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>7.81</t>
+          <t>9.64</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -7226,17 +7226,17 @@
       </c>
       <c r="BR16" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
         <is>
-          <t>4.66</t>
+          <t>4.65</t>
         </is>
       </c>
       <c r="BU16" t="inlineStr">
@@ -7246,7 +7246,7 @@
       </c>
       <c r="BV16" t="inlineStr">
         <is>
-          <t>12.78</t>
+          <t>12.81</t>
         </is>
       </c>
       <c r="BW16" t="inlineStr">
@@ -7261,12 +7261,12 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>49.24</t>
+          <t>49.59</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>10177</t>
+          <t>10201</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -7286,22 +7286,22 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>203.5</t>
+          <t>208.5</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
+          <t>211.0</t>
+        </is>
+      </c>
+      <c r="CF16" t="inlineStr">
+        <is>
           <t>208.0</t>
         </is>
       </c>
-      <c r="CF16" t="inlineStr">
-        <is>
-          <t>202.0</t>
-        </is>
-      </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>207.0</t>
+          <t>210.5</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -7333,12 +7333,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>112.0</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7348,7 +7348,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>204.5</t>
+          <t>207.0</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7358,17 +7358,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>4.44</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>40.09</t>
+          <t>19.04</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7388,7 +7388,7 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>2025-11-27 00:00:00</t>
+          <t>2025-11-28 00:00:00</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -7428,7 +7428,7 @@
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>2.73</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
@@ -7443,17 +7443,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>26.35</t>
+          <t>30.12</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7464,12 +7464,12 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>127</t>
+          <t>81</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
@@ -7479,58 +7479,58 @@
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>64.29</t>
+          <t>85.71</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>2.93</t>
+          <t>2.89</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>202.1</t>
+          <t>203.2</t>
         </is>
       </c>
       <c r="AM17" t="n">
-        <v>198.58</v>
+        <v>198.92</v>
       </c>
       <c r="AN17" t="n">
-        <v>192.93</v>
+        <v>193.33</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>190.87</t>
+          <t>191.14</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>14.78</t>
+          <t>24.29</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>2.48</t>
+          <t>2.85</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7540,7 +7540,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-78.46</t>
+          <t>-77.07</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7550,48 +7550,48 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>28317.34549356224</t>
+          <t>28313.90571428571</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>22703.0</t>
+          <t>26279.0</t>
         </is>
       </c>
       <c r="AX17" t="n">
-        <v>23070.4</v>
+        <v>21604.4</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>16467.7</t>
+          <t>18148.2</t>
         </is>
       </c>
       <c r="AZ17" t="n">
-        <v>11056.48</v>
+        <v>11512</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>6602</t>
+          <t>3456</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>917.3536697818137</t>
+          <t>1090.028654275838</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>1581.513292449679</t>
+          <t>2039.741068992971</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>22703.0</t>
+          <t>26279.0</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="BF17" t="inlineStr">
@@ -7606,7 +7606,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>6.51</t>
+          <t>7.81</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -7651,22 +7651,22 @@
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
         <is>
-          <t>4.66</t>
+          <t>4.65</t>
         </is>
       </c>
       <c r="BU17" t="inlineStr">
@@ -7676,7 +7676,7 @@
       </c>
       <c r="BV17" t="inlineStr">
         <is>
-          <t>12.78</t>
+          <t>12.81</t>
         </is>
       </c>
       <c r="BW17" t="inlineStr">
@@ -7691,12 +7691,12 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>49.24</t>
+          <t>49.59</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>10177</t>
+          <t>10201</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -7716,22 +7716,22 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
+          <t>203.5</t>
+        </is>
+      </c>
+      <c r="CE17" t="inlineStr">
+        <is>
+          <t>208.0</t>
+        </is>
+      </c>
+      <c r="CF17" t="inlineStr">
+        <is>
           <t>202.0</t>
         </is>
       </c>
-      <c r="CE17" t="inlineStr">
-        <is>
-          <t>205.0</t>
-        </is>
-      </c>
-      <c r="CF17" t="inlineStr">
-        <is>
-          <t>202.0</t>
-        </is>
-      </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>204.5</t>
+          <t>207.0</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7763,12 +7763,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>112.0</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7778,7 +7778,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>201.0</t>
+          <t>204.5</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7788,17 +7788,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>6.07</t>
+          <t>4.66</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>28.98</t>
+          <t>40.09</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7818,7 +7818,7 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>2025-11-27 00:00:00</t>
+          <t>2025-11-28 00:00:00</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
@@ -7858,7 +7858,7 @@
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="W18" t="inlineStr">
@@ -7873,17 +7873,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11.76</t>
+          <t>26.35</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7894,17 +7894,17 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>127</t>
+          <t>81</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>57.14</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
@@ -7914,53 +7914,53 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>2.94</t>
+          <t>2.93</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>200.6</t>
+          <t>202.1</t>
         </is>
       </c>
       <c r="AM18" t="n">
-        <v>198.25</v>
+        <v>198.58</v>
       </c>
       <c r="AN18" t="n">
-        <v>192.58</v>
+        <v>192.93</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>190.62</t>
+          <t>190.87</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>6.46</t>
+          <t>14.78</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>2.21</t>
+          <t>2.48</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>2.16</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -7970,7 +7970,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-79.25</t>
+          <t>-78.46</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7980,48 +7980,48 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>28317.34549356224</t>
+          <t>28313.90571428571</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>10051.0</t>
+          <t>22703.0</t>
         </is>
       </c>
       <c r="AX18" t="n">
-        <v>19272.8</v>
+        <v>23070.4</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>14943.0</t>
+          <t>16467.7</t>
         </is>
       </c>
       <c r="AZ18" t="n">
-        <v>10672.76</v>
+        <v>11056.48</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>4329</t>
+          <t>6602</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>796.5973747512926</t>
+          <t>917.3536697818137</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>1253.562422657489</t>
+          <t>1581.513292449679</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>10051.0</t>
+          <t>22703.0</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="BF18" t="inlineStr">
@@ -8036,7 +8036,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>4.69</t>
+          <t>6.51</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -8081,22 +8081,22 @@
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
         <is>
-          <t>4.66</t>
+          <t>4.65</t>
         </is>
       </c>
       <c r="BU18" t="inlineStr">
@@ -8106,7 +8106,7 @@
       </c>
       <c r="BV18" t="inlineStr">
         <is>
-          <t>12.78</t>
+          <t>12.81</t>
         </is>
       </c>
       <c r="BW18" t="inlineStr">
@@ -8121,12 +8121,12 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>49.24</t>
+          <t>49.59</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>10177</t>
+          <t>10201</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -8146,22 +8146,22 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>199.5</t>
+          <t>202.0</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
+          <t>205.0</t>
+        </is>
+      </c>
+      <c r="CF18" t="inlineStr">
+        <is>
           <t>202.0</t>
         </is>
       </c>
-      <c r="CF18" t="inlineStr">
-        <is>
-          <t>198.5</t>
-        </is>
-      </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>201.0</t>
+          <t>204.5</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-2.2</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>107.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8208,7 +8208,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>199.5</t>
+          <t>201.0</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8218,17 +8218,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>6.78</t>
+          <t>6.29</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>17.59</t>
+          <t>28.98</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8248,7 +8248,7 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>2025-11-27 00:00:00</t>
+          <t>2025-11-28 00:00:00</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
@@ -8288,7 +8288,7 @@
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">
@@ -8303,17 +8303,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>25.18</t>
+          <t>11.76</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>-2.00</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8324,73 +8324,73 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>127</t>
+          <t>81</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>35.71</t>
+          <t>57.14</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>78.57</t>
+          <t>64.29</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>2.96</t>
+          <t>2.94</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>200.0</t>
+          <t>200.6</t>
         </is>
       </c>
       <c r="AM19" t="n">
-        <v>197.98</v>
+        <v>198.25</v>
       </c>
       <c r="AN19" t="n">
-        <v>192.28</v>
+        <v>192.58</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>190.44</t>
+          <t>190.62</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>7.56</t>
+          <t>6.46</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>2.21</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8400,7 +8400,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-79.59</t>
+          <t>-79.25</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8410,48 +8410,48 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>28317.34549356224</t>
+          <t>28313.90571428571</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>21601.0</t>
+          <t>10051.0</t>
         </is>
       </c>
       <c r="AX19" t="n">
-        <v>18457.8</v>
+        <v>19272.8</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>15697.4</t>
+          <t>14943.0</t>
         </is>
       </c>
       <c r="AZ19" t="n">
-        <v>10622.98</v>
+        <v>10672.76</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>2760</t>
+          <t>4329</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>713.5128205865296</t>
+          <t>796.5973747512926</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>2095.862522145168</t>
+          <t>1253.562422657489</t>
         </is>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
-          <t>21601.0</t>
+          <t>10051.0</t>
         </is>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="BF19" t="inlineStr">
@@ -8466,7 +8466,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>3.91</t>
+          <t>4.69</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -8511,22 +8511,22 @@
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>1.89</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
         <is>
-          <t>4.66</t>
+          <t>4.65</t>
         </is>
       </c>
       <c r="BU19" t="inlineStr">
@@ -8536,7 +8536,7 @@
       </c>
       <c r="BV19" t="inlineStr">
         <is>
-          <t>12.78</t>
+          <t>12.81</t>
         </is>
       </c>
       <c r="BW19" t="inlineStr">
@@ -8551,12 +8551,12 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>49.24</t>
+          <t>49.59</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>10177</t>
+          <t>10201</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -8576,22 +8576,22 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>205.0</t>
+          <t>199.5</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>205.0</t>
+          <t>202.0</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>198.0</t>
+          <t>198.5</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>199.5</t>
+          <t>201.0</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8623,12 +8623,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>-2.2</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>107.0</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8638,7 +8638,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>204.0</t>
+          <t>199.5</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8648,17 +8648,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>4.67</t>
+          <t>6.99</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>9.50</t>
+          <t>17.59</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8678,7 +8678,7 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>2025-11-27 00:00:00</t>
+          <t>2025-11-28 00:00:00</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
@@ -8718,7 +8718,7 @@
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
@@ -8733,17 +8733,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>31.53</t>
+          <t>25.18</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>-2.00</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8754,32 +8754,32 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>127</t>
+          <t>81</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>35.71</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>82.05</t>
+          <t>78.57</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
@@ -8789,239 +8789,239 @@
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
+          <t>200.0</t>
+        </is>
+      </c>
+      <c r="AM20" t="n">
+        <v>197.98</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>192.28</v>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>190.44</t>
+        </is>
+      </c>
+      <c r="AP20" t="inlineStr">
+        <is>
+          <t>7.56</t>
+        </is>
+      </c>
+      <c r="AQ20" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="AR20" t="inlineStr">
+        <is>
+          <t>2.04</t>
+        </is>
+      </c>
+      <c r="AS20" t="inlineStr">
+        <is>
+          <t>10.01</t>
+        </is>
+      </c>
+      <c r="AT20" t="inlineStr">
+        <is>
+          <t>-79.59</t>
+        </is>
+      </c>
+      <c r="AU20" t="inlineStr">
+        <is>
+          <t>2025/11/14</t>
+        </is>
+      </c>
+      <c r="AV20" t="inlineStr">
+        <is>
+          <t>28313.90571428571</t>
+        </is>
+      </c>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>21601.0</t>
+        </is>
+      </c>
+      <c r="AX20" t="n">
+        <v>18457.8</v>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>15697.4</t>
+        </is>
+      </c>
+      <c r="AZ20" t="n">
+        <v>10622.98</v>
+      </c>
+      <c r="BA20" t="inlineStr">
+        <is>
+          <t>2760</t>
+        </is>
+      </c>
+      <c r="BB20" t="inlineStr">
+        <is>
+          <t>713.5128205865296</t>
+        </is>
+      </c>
+      <c r="BC20" t="inlineStr">
+        <is>
+          <t>2095.862522145168</t>
+        </is>
+      </c>
+      <c r="BD20" t="inlineStr">
+        <is>
+          <t>21601.0</t>
+        </is>
+      </c>
+      <c r="BE20" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="BF20" t="inlineStr">
+        <is>
+          <t>192.0</t>
+        </is>
+      </c>
+      <c r="BG20" t="inlineStr">
+        <is>
+          <t>2025/10/14</t>
+        </is>
+      </c>
+      <c r="BH20" t="inlineStr">
+        <is>
+          <t>3.91</t>
+        </is>
+      </c>
+      <c r="BI20" t="inlineStr">
+        <is>
+          <t>鼎翰</t>
+        </is>
+      </c>
+      <c r="BJ20" t="inlineStr">
+        <is>
+          <t>鼎翰</t>
+        </is>
+      </c>
+      <c r="BK20" t="inlineStr">
+        <is>
+          <t>電腦及週邊設備業</t>
+        </is>
+      </c>
+      <c r="BL20" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BM20" t="inlineStr">
+        <is>
+          <t>0.56</t>
+        </is>
+      </c>
+      <c r="BN20" t="inlineStr">
+        <is>
+          <t>-11.45161899724185</t>
+        </is>
+      </c>
+      <c r="BO20" t="inlineStr">
+        <is>
+          <t>22.56717409239306</t>
+        </is>
+      </c>
+      <c r="BP20" t="inlineStr">
+        <is>
+          <t>38.82556207928187</t>
+        </is>
+      </c>
+      <c r="BQ20" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR20" t="inlineStr">
+        <is>
+          <t>價-量增</t>
+        </is>
+      </c>
+      <c r="BS20" t="inlineStr">
+        <is>
+          <t>1.89</t>
+        </is>
+      </c>
+      <c r="BT20" t="inlineStr">
+        <is>
+          <t>4.65</t>
+        </is>
+      </c>
+      <c r="BU20" t="inlineStr">
+        <is>
+          <t>57.78</t>
+        </is>
+      </c>
+      <c r="BV20" t="inlineStr">
+        <is>
+          <t>12.81</t>
+        </is>
+      </c>
+      <c r="BW20" t="inlineStr">
+        <is>
+          <t>33.69%</t>
+        </is>
+      </c>
+      <c r="BX20" t="inlineStr">
+        <is>
+          <t>11.08%</t>
+        </is>
+      </c>
+      <c r="BY20" t="inlineStr">
+        <is>
+          <t>49.59</t>
+        </is>
+      </c>
+      <c r="BZ20" t="inlineStr">
+        <is>
+          <t>10201</t>
+        </is>
+      </c>
+      <c r="CA20" t="inlineStr">
+        <is>
+          <t>條碼印表機及零配件52.71%、印表機各式標籤紙及其耗材41.09%、企業行動電腦6.20% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB20" t="inlineStr">
+        <is>
+          <t>鼎翰-電腦及週邊設備業-上櫃</t>
+        </is>
+      </c>
+      <c r="CC20" t="inlineStr">
+        <is>
+          <t>電腦及週邊設備業平上櫃</t>
+        </is>
+      </c>
+      <c r="CD20" t="inlineStr">
+        <is>
+          <t>205.0</t>
+        </is>
+      </c>
+      <c r="CE20" t="inlineStr">
+        <is>
+          <t>205.0</t>
+        </is>
+      </c>
+      <c r="CF20" t="inlineStr">
+        <is>
+          <t>198.0</t>
+        </is>
+      </c>
+      <c r="CG20" t="inlineStr">
+        <is>
           <t>199.5</t>
-        </is>
-      </c>
-      <c r="AM20" t="n">
-        <v>197.7</v>
-      </c>
-      <c r="AN20" t="n">
-        <v>192.01</v>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>190.29</t>
-        </is>
-      </c>
-      <c r="AP20" t="inlineStr">
-        <is>
-          <t>14.82</t>
-        </is>
-      </c>
-      <c r="AQ20" t="inlineStr">
-        <is>
-          <t>2.30</t>
-        </is>
-      </c>
-      <c r="AR20" t="inlineStr">
-        <is>
-          <t>2.01</t>
-        </is>
-      </c>
-      <c r="AS20" t="inlineStr">
-        <is>
-          <t>10.01</t>
-        </is>
-      </c>
-      <c r="AT20" t="inlineStr">
-        <is>
-          <t>-79.98</t>
-        </is>
-      </c>
-      <c r="AU20" t="inlineStr">
-        <is>
-          <t>2025/11/14</t>
-        </is>
-      </c>
-      <c r="AV20" t="inlineStr">
-        <is>
-          <t>28317.34549356224</t>
-        </is>
-      </c>
-      <c r="AW20" t="inlineStr">
-        <is>
-          <t>27388.0</t>
-        </is>
-      </c>
-      <c r="AX20" t="n">
-        <v>15822.8</v>
-      </c>
-      <c r="AY20" t="inlineStr">
-        <is>
-          <t>14450.7</t>
-        </is>
-      </c>
-      <c r="AZ20" t="n">
-        <v>10277.46</v>
-      </c>
-      <c r="BA20" t="inlineStr">
-        <is>
-          <t>1372</t>
-        </is>
-      </c>
-      <c r="BB20" t="inlineStr">
-        <is>
-          <t>462.1765112122318</t>
-        </is>
-      </c>
-      <c r="BC20" t="inlineStr">
-        <is>
-          <t>1986.79614562238</t>
-        </is>
-      </c>
-      <c r="BD20" t="inlineStr">
-        <is>
-          <t>27388.0</t>
-        </is>
-      </c>
-      <c r="BE20" t="inlineStr">
-        <is>
-          <t>2025-11-27</t>
-        </is>
-      </c>
-      <c r="BF20" t="inlineStr">
-        <is>
-          <t>192.0</t>
-        </is>
-      </c>
-      <c r="BG20" t="inlineStr">
-        <is>
-          <t>2025/10/14</t>
-        </is>
-      </c>
-      <c r="BH20" t="inlineStr">
-        <is>
-          <t>6.25</t>
-        </is>
-      </c>
-      <c r="BI20" t="inlineStr">
-        <is>
-          <t>鼎翰</t>
-        </is>
-      </c>
-      <c r="BJ20" t="inlineStr">
-        <is>
-          <t>鼎翰</t>
-        </is>
-      </c>
-      <c r="BK20" t="inlineStr">
-        <is>
-          <t>電腦及週邊設備業</t>
-        </is>
-      </c>
-      <c r="BL20" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BM20" t="inlineStr">
-        <is>
-          <t>0.56</t>
-        </is>
-      </c>
-      <c r="BN20" t="inlineStr">
-        <is>
-          <t>-11.45161899724185</t>
-        </is>
-      </c>
-      <c r="BO20" t="inlineStr">
-        <is>
-          <t>22.56717409239306</t>
-        </is>
-      </c>
-      <c r="BP20" t="inlineStr">
-        <is>
-          <t>38.82556207928187</t>
-        </is>
-      </c>
-      <c r="BQ20" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR20" t="inlineStr">
-        <is>
-          <t>價-量增</t>
-        </is>
-      </c>
-      <c r="BS20" t="inlineStr">
-        <is>
-          <t>1.93</t>
-        </is>
-      </c>
-      <c r="BT20" t="inlineStr">
-        <is>
-          <t>4.66</t>
-        </is>
-      </c>
-      <c r="BU20" t="inlineStr">
-        <is>
-          <t>57.78</t>
-        </is>
-      </c>
-      <c r="BV20" t="inlineStr">
-        <is>
-          <t>12.78</t>
-        </is>
-      </c>
-      <c r="BW20" t="inlineStr">
-        <is>
-          <t>33.69%</t>
-        </is>
-      </c>
-      <c r="BX20" t="inlineStr">
-        <is>
-          <t>11.08%</t>
-        </is>
-      </c>
-      <c r="BY20" t="inlineStr">
-        <is>
-          <t>49.24</t>
-        </is>
-      </c>
-      <c r="BZ20" t="inlineStr">
-        <is>
-          <t>10177</t>
-        </is>
-      </c>
-      <c r="CA20" t="inlineStr">
-        <is>
-          <t>條碼印表機及零配件52.71%、印表機各式標籤紙及其耗材41.09%、企業行動電腦6.20% (2024年)</t>
-        </is>
-      </c>
-      <c r="CB20" t="inlineStr">
-        <is>
-          <t>鼎翰-電腦及週邊設備業-上櫃</t>
-        </is>
-      </c>
-      <c r="CC20" t="inlineStr">
-        <is>
-          <t>電腦及週邊設備業平上櫃</t>
-        </is>
-      </c>
-      <c r="CD20" t="inlineStr">
-        <is>
-          <t>201.5</t>
-        </is>
-      </c>
-      <c r="CE20" t="inlineStr">
-        <is>
-          <t>206.5</t>
-        </is>
-      </c>
-      <c r="CF20" t="inlineStr">
-        <is>
-          <t>201.5</t>
-        </is>
-      </c>
-      <c r="CG20" t="inlineStr">
-        <is>
-          <t>204.0</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -9053,12 +9053,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>167.0</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9068,74 +9068,74 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
+          <t>204.0</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>4.9</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>-0.91</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>9.50</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>2025-11-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>2025-11-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>2025-10-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>2025-11-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
           <t>201.5</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>5.84</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>-1.25</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>21.03</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>2025-11-14</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>2025-11-14 00:00:00</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>2025-11-27 00:00:00</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>2025-10-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>2025-11-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q21" t="inlineStr">
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
         <is>
           <t>201.5</t>
         </is>
       </c>
-      <c r="R21" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>201.5</t>
-        </is>
-      </c>
       <c r="T21" t="inlineStr">
         <is>
           <t>195.5</t>
@@ -9148,7 +9148,7 @@
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
@@ -9163,17 +9163,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>39.29</t>
+          <t>31.53</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9184,12 +9184,12 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>127</t>
+          <t>81</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
@@ -9199,194 +9199,194 @@
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>69.23</t>
+          <t>82.05</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>2.87</t>
+          <t>2.96</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>198.8</t>
+          <t>199.5</t>
         </is>
       </c>
       <c r="AM21" t="n">
-        <v>197.15</v>
+        <v>197.7</v>
       </c>
       <c r="AN21" t="n">
-        <v>191.65</v>
+        <v>192.01</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>190.08</t>
+          <t>190.29</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>14.82</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
+          <t>2.01</t>
+        </is>
+      </c>
+      <c r="AS21" t="inlineStr">
+        <is>
+          <t>10.01</t>
+        </is>
+      </c>
+      <c r="AT21" t="inlineStr">
+        <is>
+          <t>-79.98</t>
+        </is>
+      </c>
+      <c r="AU21" t="inlineStr">
+        <is>
+          <t>2025/11/14</t>
+        </is>
+      </c>
+      <c r="AV21" t="inlineStr">
+        <is>
+          <t>28313.90571428571</t>
+        </is>
+      </c>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>27388.0</t>
+        </is>
+      </c>
+      <c r="AX21" t="n">
+        <v>15822.8</v>
+      </c>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>14450.7</t>
+        </is>
+      </c>
+      <c r="AZ21" t="n">
+        <v>10277.46</v>
+      </c>
+      <c r="BA21" t="inlineStr">
+        <is>
+          <t>1372</t>
+        </is>
+      </c>
+      <c r="BB21" t="inlineStr">
+        <is>
+          <t>462.1765112122318</t>
+        </is>
+      </c>
+      <c r="BC21" t="inlineStr">
+        <is>
+          <t>1986.79614562238</t>
+        </is>
+      </c>
+      <c r="BD21" t="inlineStr">
+        <is>
+          <t>27388.0</t>
+        </is>
+      </c>
+      <c r="BE21" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="BF21" t="inlineStr">
+        <is>
+          <t>192.0</t>
+        </is>
+      </c>
+      <c r="BG21" t="inlineStr">
+        <is>
+          <t>2025/10/14</t>
+        </is>
+      </c>
+      <c r="BH21" t="inlineStr">
+        <is>
+          <t>6.25</t>
+        </is>
+      </c>
+      <c r="BI21" t="inlineStr">
+        <is>
+          <t>鼎翰</t>
+        </is>
+      </c>
+      <c r="BJ21" t="inlineStr">
+        <is>
+          <t>鼎翰</t>
+        </is>
+      </c>
+      <c r="BK21" t="inlineStr">
+        <is>
+          <t>電腦及週邊設備業</t>
+        </is>
+      </c>
+      <c r="BL21" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BM21" t="inlineStr">
+        <is>
+          <t>0.56</t>
+        </is>
+      </c>
+      <c r="BN21" t="inlineStr">
+        <is>
+          <t>-11.45161899724185</t>
+        </is>
+      </c>
+      <c r="BO21" t="inlineStr">
+        <is>
+          <t>22.56717409239306</t>
+        </is>
+      </c>
+      <c r="BP21" t="inlineStr">
+        <is>
+          <t>38.82556207928187</t>
+        </is>
+      </c>
+      <c r="BQ21" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR21" t="inlineStr">
+        <is>
+          <t>價漲量增</t>
+        </is>
+      </c>
+      <c r="BS21" t="inlineStr">
+        <is>
           <t>1.93</t>
         </is>
       </c>
-      <c r="AS21" t="inlineStr">
-        <is>
-          <t>10.01</t>
-        </is>
-      </c>
-      <c r="AT21" t="inlineStr">
-        <is>
-          <t>-80.72</t>
-        </is>
-      </c>
-      <c r="AU21" t="inlineStr">
-        <is>
-          <t>2025/11/14</t>
-        </is>
-      </c>
-      <c r="AV21" t="inlineStr">
-        <is>
-          <t>28317.34549356224</t>
-        </is>
-      </c>
-      <c r="AW21" t="inlineStr">
-        <is>
-          <t>33609.0</t>
-        </is>
-      </c>
-      <c r="AX21" t="n">
-        <v>14692</v>
-      </c>
-      <c r="AY21" t="inlineStr">
-        <is>
-          <t>12138.8</t>
-        </is>
-      </c>
-      <c r="AZ21" t="n">
-        <v>9836.780000000001</v>
-      </c>
-      <c r="BA21" t="inlineStr">
-        <is>
-          <t>2553</t>
-        </is>
-      </c>
-      <c r="BB21" t="inlineStr">
-        <is>
-          <t>184.9729413194776</t>
-        </is>
-      </c>
-      <c r="BC21" t="inlineStr">
-        <is>
-          <t>1139.994316817598</t>
-        </is>
-      </c>
-      <c r="BD21" t="inlineStr">
-        <is>
-          <t>33609.0</t>
-        </is>
-      </c>
-      <c r="BE21" t="inlineStr">
-        <is>
-          <t>2025-11-27</t>
-        </is>
-      </c>
-      <c r="BF21" t="inlineStr">
-        <is>
-          <t>192.0</t>
-        </is>
-      </c>
-      <c r="BG21" t="inlineStr">
-        <is>
-          <t>2025/10/14</t>
-        </is>
-      </c>
-      <c r="BH21" t="inlineStr">
-        <is>
-          <t>4.95</t>
-        </is>
-      </c>
-      <c r="BI21" t="inlineStr">
-        <is>
-          <t>鼎翰</t>
-        </is>
-      </c>
-      <c r="BJ21" t="inlineStr">
-        <is>
-          <t>鼎翰</t>
-        </is>
-      </c>
-      <c r="BK21" t="inlineStr">
-        <is>
-          <t>電腦及週邊設備業</t>
-        </is>
-      </c>
-      <c r="BL21" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BM21" t="inlineStr">
-        <is>
-          <t>0.56</t>
-        </is>
-      </c>
-      <c r="BN21" t="inlineStr">
-        <is>
-          <t>-11.45161899724185</t>
-        </is>
-      </c>
-      <c r="BO21" t="inlineStr">
-        <is>
-          <t>22.56717409239306</t>
-        </is>
-      </c>
-      <c r="BP21" t="inlineStr">
-        <is>
-          <t>38.82556207928187</t>
-        </is>
-      </c>
-      <c r="BQ21" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR21" t="inlineStr">
-        <is>
-          <t>價-量增</t>
-        </is>
-      </c>
-      <c r="BS21" t="inlineStr">
-        <is>
-          <t>1.91</t>
-        </is>
-      </c>
       <c r="BT21" t="inlineStr">
         <is>
-          <t>4.66</t>
+          <t>4.65</t>
         </is>
       </c>
       <c r="BU21" t="inlineStr">
@@ -9396,7 +9396,7 @@
       </c>
       <c r="BV21" t="inlineStr">
         <is>
-          <t>12.78</t>
+          <t>12.81</t>
         </is>
       </c>
       <c r="BW21" t="inlineStr">
@@ -9411,12 +9411,12 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>49.24</t>
+          <t>49.59</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>10177</t>
+          <t>10201</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
@@ -9436,22 +9436,22 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>199.0</t>
+          <t>201.5</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>202.5</t>
+          <t>206.5</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>198.5</t>
+          <t>201.5</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>201.5</t>
+          <t>204.0</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -9473,7 +9473,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>【c】</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -9483,12 +9483,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>19.0</t>
+          <t>167.0</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9498,7 +9498,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>197.0</t>
+          <t>201.5</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9508,22 +9508,22 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>7.94</t>
+          <t>6.06</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>21.03</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -9538,7 +9538,7 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>2025-11-27 00:00:00</t>
+          <t>2025-11-28 00:00:00</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
@@ -9563,7 +9563,7 @@
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>201.5</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
@@ -9578,7 +9578,7 @@
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W22" t="inlineStr">
@@ -9593,17 +9593,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>4.47</t>
+          <t>39.29</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>-1.27</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9614,68 +9614,68 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>127</t>
+          <t>81</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>46.15</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>51.28</t>
+          <t>69.23</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>2.84</t>
+          <t>2.87</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>197.9</t>
+          <t>198.8</t>
         </is>
       </c>
       <c r="AM22" t="n">
-        <v>196.78</v>
+        <v>197.15</v>
       </c>
       <c r="AN22" t="n">
-        <v>191.34</v>
+        <v>191.65</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>190.02</t>
+          <t>190.08</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>-11.24</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
@@ -9690,7 +9690,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-80.75</t>
+          <t>-80.72</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9700,48 +9700,48 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>28317.34549356224</t>
+          <t>28313.90571428571</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>3715.0</t>
+          <t>33609.0</t>
         </is>
       </c>
       <c r="AX22" t="n">
-        <v>9865</v>
+        <v>14692</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>9864.3</t>
+          <t>12138.8</t>
         </is>
       </c>
       <c r="AZ22" t="n">
-        <v>9269.959999999999</v>
+        <v>9836.780000000001</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2553</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>11.33269122891031</t>
+          <t>184.9729413194776</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>-776.9723785041442</t>
+          <t>1139.994316817598</t>
         </is>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
-          <t>3715.0</t>
+          <t>33609.0</t>
         </is>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="BF22" t="inlineStr">
@@ -9756,7 +9756,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2.60</t>
+          <t>4.95</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
@@ -9801,7 +9801,7 @@
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -9811,12 +9811,12 @@
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
         <is>
-          <t>4.66</t>
+          <t>4.65</t>
         </is>
       </c>
       <c r="BU22" t="inlineStr">
@@ -9826,7 +9826,7 @@
       </c>
       <c r="BV22" t="inlineStr">
         <is>
-          <t>12.78</t>
+          <t>12.81</t>
         </is>
       </c>
       <c r="BW22" t="inlineStr">
@@ -9841,12 +9841,12 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>49.24</t>
+          <t>49.59</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>10177</t>
+          <t>10201</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
@@ -9866,22 +9866,22 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>199.5</t>
+          <t>199.0</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>199.5</t>
+          <t>202.5</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>197.0</t>
+          <t>198.5</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>197.0</t>
+          <t>201.5</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -9913,12 +9913,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>19.0</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9928,7 +9928,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>198.0</t>
+          <t>197.0</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9938,17 +9938,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>7.48</t>
+          <t>8.16</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -9968,7 +9968,7 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>2025-11-27 00:00:00</t>
+          <t>2025-11-28 00:00:00</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
@@ -10023,17 +10023,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>7.06</t>
+          <t>4.47</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>-1.27</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10044,73 +10044,73 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>127</t>
+          <t>81</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>61.54</t>
+          <t>46.15</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>69.23</t>
+          <t>51.28</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>0.80</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>2.85</t>
+          <t>2.84</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>0.62</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>198.2</t>
+          <t>197.9</t>
         </is>
       </c>
       <c r="AM23" t="n">
-        <v>196.62</v>
+        <v>196.78</v>
       </c>
       <c r="AN23" t="n">
-        <v>191.17</v>
+        <v>191.34</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>189.99</t>
+          <t>190.02</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>-6.74</t>
+          <t>-11.24</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10120,7 +10120,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-80.21</t>
+          <t>-80.75</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10130,43 +10130,43 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>28317.34549356224</t>
+          <t>28313.90571428571</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>5976.0</t>
+          <t>3715.0</t>
         </is>
       </c>
       <c r="AX23" t="n">
-        <v>10613.2</v>
+        <v>9865</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>10254.6</t>
+          <t>9864.3</t>
         </is>
       </c>
       <c r="AZ23" t="n">
-        <v>9315.639999999999</v>
+        <v>9269.959999999999</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>358</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>154.6608857258293</t>
+          <t>11.33269122891031</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>-284.8186440172012</t>
+          <t>-776.9723785041442</t>
         </is>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
-          <t>5976.0</t>
+          <t>3715.0</t>
         </is>
       </c>
       <c r="BE23" t="inlineStr">
@@ -10186,7 +10186,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>3.12</t>
+          <t>2.60</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
@@ -10231,7 +10231,7 @@
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -10241,12 +10241,12 @@
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
         <is>
-          <t>4.66</t>
+          <t>4.65</t>
         </is>
       </c>
       <c r="BU23" t="inlineStr">
@@ -10256,7 +10256,7 @@
       </c>
       <c r="BV23" t="inlineStr">
         <is>
-          <t>12.78</t>
+          <t>12.81</t>
         </is>
       </c>
       <c r="BW23" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>49.24</t>
+          <t>49.59</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>10177</t>
+          <t>10201</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
@@ -10296,22 +10296,22 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
+          <t>199.5</t>
+        </is>
+      </c>
+      <c r="CE23" t="inlineStr">
+        <is>
+          <t>199.5</t>
+        </is>
+      </c>
+      <c r="CF23" t="inlineStr">
+        <is>
           <t>197.0</t>
         </is>
       </c>
-      <c r="CE23" t="inlineStr">
-        <is>
-          <t>198.5</t>
-        </is>
-      </c>
-      <c r="CF23" t="inlineStr">
+      <c r="CG23" t="inlineStr">
         <is>
           <t>197.0</t>
-        </is>
-      </c>
-      <c r="CG23" t="inlineStr">
-        <is>
-          <t>198.0</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">

--- a/Result/checksun_type/HMI.xlsx
+++ b/Result/checksun_type/HMI.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>22.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>19.75</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>-1.44</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-17.60</t>
+          <t>-45.47</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-9.61</t>
+          <t>-8.92</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-2.53</t>
+          <t>-1.01</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,73 +1014,73 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>49.15</t>
+          <t>73.5</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-3.26</t>
+          <t>-2.17</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-5.98</t>
+          <t>-6.24</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-3.92</t>
+          <t>-3.82</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>19.5</t>
+          <t>19.64</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>20.16</v>
+        <v>20.08</v>
       </c>
       <c r="AN2" t="n">
-        <v>21.44</v>
+        <v>21.41</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>22.31</t>
+          <t>22.26</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>3.76</t>
+          <t>9.79</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-0.60</t>
+          <t>-0.55</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-0.63</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-109.49</t>
+          <t>-109.26</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1100,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>30333.82071428571</t>
+          <t>30291.50071326676</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>397.0</t>
+          <t>445.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>517.2</v>
+        <v>348.8</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>627.7</t>
+          <t>639.6</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>1309.6</v>
+        <v>1276.44</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-110</t>
+          <t>-290</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-141.7554584428505</t>
+          <t>-140.1187399922061</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-139.3694273883414</t>
+          <t>-131.1167885136618</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>397.0</t>
+          <t>445.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-16.49</t>
+          <t>-15.86</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
@@ -1201,7 +1201,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1211,7 +1211,7 @@
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>89.61</t>
+          <t>89.32</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>576</t>
+          <t>581</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,22 +1266,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>20.3</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>20.3</t>
+          <t>20.1</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>19.7</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>19.75</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1303,7 +1303,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>22.0</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>19.85</t>
+          <t>19.75</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>-1.44</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-25.82</t>
+          <t>-17.60</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-9.15</t>
+          <t>-9.61</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>-2.53</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,37 +1444,37 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>53.85</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>28.0</t>
+          <t>49.15</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-4.02</t>
+          <t>-3.26</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-5.68</t>
+          <t>-5.98</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1484,28 +1484,28 @@
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>19.45</t>
+          <t>19.5</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>20.26</v>
+        <v>20.16</v>
       </c>
       <c r="AN3" t="n">
-        <v>21.48</v>
+        <v>21.44</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>22.36</t>
+          <t>22.31</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-1.89</t>
+          <t>3.76</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>-0.60</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-109.58</t>
+          <t>-109.49</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1530,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>30333.82071428571</t>
+          <t>30291.50071326676</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>446.0</t>
+          <t>397.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>537.2</v>
+        <v>517.2</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>724.2</t>
+          <t>627.7</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>1332.24</v>
+        <v>1309.6</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-187</t>
+          <t>-110</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-142.1892822709431</t>
+          <t>-141.7554584428505</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-141.0385748025855</t>
+          <t>-139.3694273883414</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>446.0</t>
+          <t>397.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-16.07</t>
+          <t>-16.49</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
@@ -1631,17 +1631,17 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>89.61</t>
+          <t>89.32</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>576</t>
+          <t>581</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,22 +1696,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>19.45</t>
+          <t>20.3</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>20.05</t>
+          <t>20.3</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>19.45</t>
+          <t>19.7</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>19.85</t>
+          <t>19.75</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>9.0</t>
+          <t>22.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>19.5</t>
+          <t>19.85</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>-1.44</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-34.48</t>
+          <t>-25.82</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-10.76</t>
+          <t>-9.15</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,68 +1874,68 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>26.92</t>
+          <t>53.85</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>11.12</t>
+          <t>28.0</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>2.06</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-5.18</t>
+          <t>-4.02</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-5.44</t>
+          <t>-5.68</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-3.78</t>
+          <t>-3.92</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>19.31</t>
+          <t>19.45</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>20.36</v>
+        <v>20.26</v>
       </c>
       <c r="AN4" t="n">
-        <v>21.54</v>
+        <v>21.48</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>22.38</t>
+          <t>22.36</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-10.91</t>
+          <t>-1.89</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-0.70</t>
+          <t>-0.64</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-109.53</t>
+          <t>-109.58</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1960,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>30333.82071428571</t>
+          <t>30291.50071326676</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>166.0</t>
+          <t>446.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>494.2</v>
+        <v>537.2</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>754.3</t>
+          <t>724.2</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>1394.4</v>
+        <v>1332.24</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-260</t>
+          <t>-187</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-142.3985018106445</t>
+          <t>-142.1892822709431</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-143.6359791514134</t>
+          <t>-141.0385748025855</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>166.0</t>
+          <t>446.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-17.55</t>
+          <t>-16.07</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2041,7 +2041,7 @@
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
@@ -2061,17 +2061,17 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>89.61</t>
+          <t>89.32</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>576</t>
+          <t>581</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,22 +2126,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>19.3</t>
+          <t>19.45</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>19.5</t>
+          <t>20.05</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>19.3</t>
+          <t>19.45</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>19.5</t>
+          <t>19.85</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>19.2</t>
+          <t>19.5</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2.78</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>-1.44</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-2.21</t>
+          <t>-34.48</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-12.13</t>
+          <t>-10.76</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,54 +2304,54 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>3.23</t>
+          <t>26.92</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>9.68</t>
+          <t>11.12</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-6.04</t>
+          <t>-5.18</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-5.2</t>
+          <t>-5.44</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-3.45</t>
+          <t>-3.78</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>19.25</t>
+          <t>19.31</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>20.49</v>
+        <v>20.36</v>
       </c>
       <c r="AN5" t="n">
-        <v>21.61</v>
+        <v>21.54</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
@@ -2360,17 +2360,17 @@
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-17.72</t>
+          <t>-10.91</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>-0.70</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-0.63</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-109.27</t>
+          <t>-109.53</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>30333.82071428571</t>
+          <t>30291.50071326676</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>290.0</t>
+          <t>166.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>804</v>
+        <v>494.2</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>822.2</t>
+          <t>754.3</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>1439.06</v>
+        <v>1394.4</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-18</t>
+          <t>-260</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-142.1735059305047</t>
+          <t>-142.3985018106445</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-112.2167003943315</t>
+          <t>-143.6359791514134</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>290.0</t>
+          <t>166.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-18.82</t>
+          <t>-17.55</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2501,7 +2501,7 @@
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>89.61</t>
+          <t>89.32</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>576</t>
+          <t>581</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,22 +2556,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>19.2</t>
+          <t>19.3</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
+          <t>19.5</t>
+        </is>
+      </c>
+      <c r="CF5" t="inlineStr">
+        <is>
           <t>19.3</t>
         </is>
       </c>
-      <c r="CF5" t="inlineStr">
-        <is>
-          <t>19.2</t>
-        </is>
-      </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>19.2</t>
+          <t>19.5</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-1.53</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2.78</t>
+          <t>3.52</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>-1.44</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>3.85</t>
+          <t>-2.21</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,12 +2734,12 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -2749,58 +2749,58 @@
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>9.68</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-1.13</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-5.90</t>
+          <t>-6.04</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-4.83</t>
+          <t>-5.2</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-3.05</t>
+          <t>-3.45</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>19.42</t>
+          <t>19.25</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>20.64</v>
+        <v>20.49</v>
       </c>
       <c r="AN6" t="n">
-        <v>21.68</v>
+        <v>21.61</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>22.37</t>
+          <t>22.38</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-21.10</t>
+          <t>-17.72</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-108.86</t>
+          <t>-109.27</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>30333.82071428571</t>
+          <t>30291.50071326676</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>1287.0</t>
+          <t>290.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>930.4</v>
+        <v>804</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>895.9</t>
+          <t>822.2</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>1833.62</v>
+        <v>1439.06</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>-18</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-147.6201978461726</t>
+          <t>-142.1735059305047</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-76.60999144155971</t>
+          <t>-112.2167003943315</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>1287.0</t>
+          <t>290.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>89.61</t>
+          <t>89.32</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>576</t>
+          <t>581</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,17 +2986,17 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>19.55</t>
+          <t>19.2</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>19.65</t>
+          <t>19.3</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>18.85</t>
+          <t>19.2</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>-1.53</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>26.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>19.5</t>
+          <t>19.2</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>3.52</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>-1.44</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-4.04</t>
+          <t>3.85</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-10.76</t>
+          <t>-12.13</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>3.17</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,73 +3164,73 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>22.58</t>
+          <t>3.23</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>7.53</t>
+          <t>8.6</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>-1.13</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-5.39</t>
+          <t>-5.90</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-4.43</t>
+          <t>-4.83</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-2.68</t>
+          <t>-3.05</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>19.67</t>
+          <t>19.42</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>20.79</v>
+        <v>20.64</v>
       </c>
       <c r="AN7" t="n">
-        <v>21.75</v>
+        <v>21.68</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>22.35</t>
+          <t>22.37</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-23.19</t>
+          <t>-21.10</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.68</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-108.40</t>
+          <t>-108.86</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>30333.82071428571</t>
+          <t>30291.50071326676</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>497.0</t>
+          <t>1287.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>738.2</v>
+        <v>930.4</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>769.3</t>
+          <t>895.9</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>1851.22</v>
+        <v>1833.62</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-31</t>
+          <t>34</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-160.5311444651931</t>
+          <t>-147.6201978461726</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-129.8286218146873</t>
+          <t>-76.60999144155971</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>497.0</t>
+          <t>1287.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-17.55</t>
+          <t>-18.82</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
@@ -3356,12 +3356,12 @@
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>89.61</t>
+          <t>89.32</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>576</t>
+          <t>581</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,22 +3416,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
+          <t>19.55</t>
+        </is>
+      </c>
+      <c r="CE7" t="inlineStr">
+        <is>
+          <t>19.65</t>
+        </is>
+      </c>
+      <c r="CF7" t="inlineStr">
+        <is>
+          <t>18.85</t>
+        </is>
+      </c>
+      <c r="CG7" t="inlineStr">
+        <is>
           <t>19.2</t>
-        </is>
-      </c>
-      <c r="CE7" t="inlineStr">
-        <is>
-          <t>19.5</t>
-        </is>
-      </c>
-      <c r="CF7" t="inlineStr">
-        <is>
-          <t>18.9</t>
-        </is>
-      </c>
-      <c r="CG7" t="inlineStr">
-        <is>
-          <t>19.5</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>26.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>19.15</t>
+          <t>19.5</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>-1.44</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>14.69</t>
+          <t>-4.04</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-12.36</t>
+          <t>-10.76</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>3.17</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,73 +3594,73 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>22.58</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.53</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-3.58</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-5.17</t>
+          <t>-5.39</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-3.97</t>
+          <t>-4.43</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-2.33</t>
+          <t>-2.68</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>19.86</t>
+          <t>19.67</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>20.94</v>
+        <v>20.79</v>
       </c>
       <c r="AN8" t="n">
-        <v>21.81</v>
+        <v>21.75</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>22.33</t>
+          <t>22.35</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-28.42</t>
+          <t>-23.19</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-0.68</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-0.55</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-107.91</t>
+          <t>-108.40</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>30333.82071428571</t>
+          <t>30291.50071326676</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>231.0</t>
+          <t>497.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>911.2</v>
+        <v>738.2</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>794.5</t>
+          <t>769.3</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>1867.82</v>
+        <v>1851.22</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>116</t>
+          <t>-31</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-166.1134213107396</t>
+          <t>-160.5311444651931</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-116.5756429972018</t>
+          <t>-129.8286218146873</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>231.0</t>
+          <t>497.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-19.03</t>
+          <t>-17.55</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3761,7 +3761,7 @@
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
@@ -3781,17 +3781,17 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>89.61</t>
+          <t>89.32</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>576</t>
+          <t>581</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,22 +3846,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>18.85</t>
+          <t>19.2</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>19.15</t>
+          <t>19.5</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>18.85</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>19.15</t>
+          <t>19.5</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-4.24</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>19.2</t>
+          <t>19.15</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2.78</t>
+          <t>3.77</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>-1.44</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>21.51</t>
+          <t>14.69</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-12.13</t>
+          <t>-12.36</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>3.15</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-3.37</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,12 +4024,12 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
@@ -4039,58 +4039,58 @@
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>15.38</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-4.81</t>
+          <t>-3.58</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-4.41</t>
+          <t>-5.17</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-3.49</t>
+          <t>-3.97</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-2.01</t>
+          <t>-2.33</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>20.17</t>
+          <t>19.86</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>21.1</v>
+        <v>20.94</v>
       </c>
       <c r="AN9" t="n">
-        <v>21.86</v>
+        <v>21.81</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>22.31</t>
+          <t>22.33</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-25.64</t>
+          <t>-28.42</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-107.35</t>
+          <t>-107.91</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>30333.82071428571</t>
+          <t>30291.50071326676</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>1715.0</t>
+          <t>231.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>1014.4</v>
+        <v>911.2</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>834.8</t>
+          <t>794.5</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>1896.36</v>
+        <v>1867.82</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>179</t>
+          <t>116</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-175.1202900950192</t>
+          <t>-166.1134213107396</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-64.97940029375127</t>
+          <t>-116.5756429972018</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>1715.0</t>
+          <t>231.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-18.82</t>
+          <t>-19.03</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4191,7 +4191,7 @@
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
@@ -4211,7 +4211,7 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4221,7 +4221,7 @@
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>89.61</t>
+          <t>89.32</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>576</t>
+          <t>581</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,22 +4276,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>20.05</t>
+          <t>18.85</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>20.05</t>
+          <t>19.15</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>19.0</t>
+          <t>18.85</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>19.2</t>
+          <t>19.15</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-2.0</t>
+          <t>-4.24</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>46.0</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>20.05</t>
+          <t>19.2</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-1.52</t>
+          <t>3.52</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>-1.44</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>17.65</t>
+          <t>21.51</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-8.24</t>
+          <t>-12.13</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>3.15</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>-3.37</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,12 +4454,12 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
@@ -4469,58 +4469,58 @@
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>23.08</t>
+          <t>15.38</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-1.91</t>
+          <t>-4.81</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-3.90</t>
+          <t>-4.41</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-2.98</t>
+          <t>-3.49</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-1.65</t>
+          <t>-2.01</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>20.44</t>
+          <t>20.17</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>21.27</v>
+        <v>21.1</v>
       </c>
       <c r="AN10" t="n">
-        <v>21.92</v>
+        <v>21.86</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>22.29</t>
+          <t>22.31</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-16.23</t>
+          <t>-25.64</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-106.88</t>
+          <t>-107.35</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>30333.82071428571</t>
+          <t>30291.50071326676</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>922.0</t>
+          <t>1715.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>840.4</v>
+        <v>1014.4</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>714.3</t>
+          <t>834.8</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>1889.2</v>
+        <v>1896.36</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>126</t>
+          <t>179</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-195.1459064225224</t>
+          <t>-175.1202900950192</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-147.9497892783307</t>
+          <t>-64.97940029375127</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>922.0</t>
+          <t>1715.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-15.22</t>
+          <t>-18.82</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4621,7 +4621,7 @@
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
@@ -4641,17 +4641,17 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>89.61</t>
+          <t>89.32</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>576</t>
+          <t>581</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>20.05</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>20.1</t>
+          <t>20.05</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>19.95</t>
+          <t>19.0</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>20.05</t>
+          <t>19.2</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-2.0</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>16.0</t>
+          <t>46.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>20.45</t>
+          <t>20.05</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4778,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-3.54</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>-1.44</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>22.57</t>
+          <t>17.65</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-6.41</t>
+          <t>-8.24</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,73 +4884,73 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>46.15</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>36.17</t>
+          <t>23.08</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-1.91</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-4.52</t>
+          <t>-3.90</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-2.41</t>
+          <t>-2.98</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-1.36</t>
+          <t>-1.65</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>20.46</t>
+          <t>20.44</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>21.43</v>
+        <v>21.27</v>
       </c>
       <c r="AN11" t="n">
-        <v>21.96</v>
+        <v>21.92</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>22.26</t>
+          <t>22.29</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-15.32</t>
+          <t>-16.23</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.50</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-106.60</t>
+          <t>-106.88</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>30333.82071428571</t>
+          <t>30291.50071326676</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>326.0</t>
+          <t>922.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>861.4</v>
+        <v>840.4</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>702.8</t>
+          <t>714.3</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>2075.44</v>
+        <v>1889.2</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>158</t>
+          <t>126</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-203.7270186305573</t>
+          <t>-195.1459064225224</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-176.2307096392179</t>
+          <t>-147.9497892783307</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>326.0</t>
+          <t>922.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-13.53</t>
+          <t>-15.22</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5051,7 +5051,7 @@
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>89.61</t>
+          <t>89.32</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>576</t>
+          <t>581</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>20.45</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>20.45</t>
+          <t>20.1</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>20.3</t>
+          <t>19.95</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>20.45</t>
+          <t>20.05</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-1.19</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5208,17 +5208,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-3.54</t>
+          <t>-2.76</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>-1.44</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>22.57</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-1.95</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,63 +5314,63 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>23.08</t>
+          <t>46.15</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>28.41</t>
+          <t>36.17</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-4.33</t>
+          <t>-4.52</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-2.52</t>
+          <t>-2.41</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>-1.36</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>20.53</t>
+          <t>20.46</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>21.46</v>
+        <v>21.43</v>
       </c>
       <c r="AN12" t="n">
-        <v>22.01</v>
+        <v>21.96</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>22.23</t>
+          <t>22.26</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-20.19</t>
+          <t>-15.32</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
@@ -5380,7 +5380,7 @@
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-106.34</t>
+          <t>-106.60</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5400,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>30333.82071428571</t>
+          <t>30291.50071326676</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>1362.0</t>
+          <t>326.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>800.4</v>
+        <v>861.4</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>791.6</t>
+          <t>702.8</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>2169.22</v>
+        <v>2075.44</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>158</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-208.7263475380736</t>
+          <t>-203.7270186305573</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-146.4809276676563</t>
+          <t>-176.2307096392179</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>1362.0</t>
+          <t>326.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>89.61</t>
+          <t>89.32</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>576</t>
+          <t>581</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,12 +5566,12 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>21.0</t>
+          <t>20.45</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>21.0</t>
+          <t>20.45</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
@@ -5613,12 +5613,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5628,7 +5628,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>214.5</t>
+          <t>215.5</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5643,12 +5643,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-1.06</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5668,7 +5668,7 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>2025-11-28 00:00:00</t>
+          <t>2025-11-29 00:00:00</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -5708,7 +5708,7 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>6.45</t>
+          <t>6.95</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
@@ -5723,17 +5723,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>19.06</t>
+          <t>17.18</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5749,7 +5749,7 @@
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>73</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
@@ -5764,53 +5764,53 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>4.99</t>
+          <t>5.31</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>3.29</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>212.0</t>
+          <t>213.7</t>
         </is>
       </c>
       <c r="AM13" t="n">
-        <v>201.92</v>
+        <v>202.92</v>
       </c>
       <c r="AN13" t="n">
-        <v>195.5</v>
+        <v>196.07</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>192.61</t>
+          <t>193.0</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>39.40</t>
+          <t>35.12</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>4.90</t>
+          <t>5.21</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>3.51</t>
+          <t>3.85</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5820,7 +5820,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-64.90</t>
+          <t>-61.52</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5830,48 +5830,48 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>28313.90571428571</t>
+          <t>28307.18473609129</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>17273.0</t>
+          <t>15735.0</t>
         </is>
       </c>
       <c r="AX13" t="n">
-        <v>23978</v>
+        <v>21869.2</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>23524.2</t>
+          <t>21736.8</t>
         </is>
       </c>
       <c r="AZ13" t="n">
-        <v>12876.32</v>
+        <v>12717.58</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>453</t>
+          <t>132</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>1584.041988898771</t>
+          <t>1509.806122496388</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>1746.551582864951</t>
+          <t>1101.508857283279</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>17273.0</t>
+          <t>15735.0</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-11-29</t>
         </is>
       </c>
       <c r="BF13" t="inlineStr">
@@ -5886,7 +5886,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>11.72</t>
+          <t>12.24</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -5931,22 +5931,22 @@
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
         <is>
-          <t>4.65</t>
+          <t>4.63</t>
         </is>
       </c>
       <c r="BU13" t="inlineStr">
@@ -5956,7 +5956,7 @@
       </c>
       <c r="BV13" t="inlineStr">
         <is>
-          <t>12.81</t>
+          <t>12.87</t>
         </is>
       </c>
       <c r="BW13" t="inlineStr">
@@ -5971,12 +5971,12 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>49.59</t>
+          <t>49.8</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>10201</t>
+          <t>10248</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -5996,7 +5996,7 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>214.5</t>
+          <t>215.0</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
@@ -6006,12 +6006,12 @@
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>213.0</t>
+          <t>213.5</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>214.5</t>
+          <t>215.5</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6058,7 +6058,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>214.0</t>
+          <t>214.5</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6068,17 +6068,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-1.06</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>13.06</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6098,7 +6098,7 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>2025-11-28 00:00:00</t>
+          <t>2025-11-29 00:00:00</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -6138,7 +6138,7 @@
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>6.20</t>
+          <t>6.45</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
@@ -6153,17 +6153,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>29.88</t>
+          <t>19.06</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6179,7 +6179,7 @@
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>73</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
@@ -6194,53 +6194,53 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>4.44</t>
+          <t>4.99</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>3.16</t>
+          <t>3.29</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>210.0</t>
+          <t>212.0</t>
         </is>
       </c>
       <c r="AM14" t="n">
-        <v>201.08</v>
+        <v>201.92</v>
       </c>
       <c r="AN14" t="n">
-        <v>194.92</v>
+        <v>195.5</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>192.22</t>
+          <t>192.61</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>43.25</t>
+          <t>39.40</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>4.54</t>
+          <t>4.90</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>3.17</t>
+          <t>3.51</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6250,7 +6250,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-68.36</t>
+          <t>-64.90</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6260,48 +6260,48 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>28313.90571428571</t>
+          <t>28307.18473609129</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>27093.0</t>
+          <t>17273.0</t>
         </is>
       </c>
       <c r="AX14" t="n">
-        <v>25064</v>
+        <v>23978</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>22168.4</t>
+          <t>23524.2</t>
         </is>
       </c>
       <c r="AZ14" t="n">
-        <v>12662.48</v>
+        <v>12876.32</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>2895</t>
+          <t>453</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>1554.494789995829</t>
+          <t>1584.041988898771</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>2440.878634307883</t>
+          <t>1746.551582864951</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>27093.0</t>
+          <t>17273.0</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-11-29</t>
         </is>
       </c>
       <c r="BF14" t="inlineStr">
@@ -6316,7 +6316,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>11.46</t>
+          <t>11.72</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -6361,7 +6361,7 @@
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
@@ -6371,12 +6371,12 @@
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
         <is>
-          <t>4.65</t>
+          <t>4.63</t>
         </is>
       </c>
       <c r="BU14" t="inlineStr">
@@ -6386,7 +6386,7 @@
       </c>
       <c r="BV14" t="inlineStr">
         <is>
-          <t>12.81</t>
+          <t>12.87</t>
         </is>
       </c>
       <c r="BW14" t="inlineStr">
@@ -6401,12 +6401,12 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>49.59</t>
+          <t>49.8</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>10201</t>
+          <t>10248</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -6426,7 +6426,7 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>215.0</t>
+          <t>214.5</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
@@ -6436,12 +6436,12 @@
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>211.0</t>
+          <t>213.0</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>214.0</t>
+          <t>214.5</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -6473,12 +6473,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6498,17 +6498,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-1.06</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>7.97</t>
+          <t>13.06</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6528,7 +6528,7 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>2025-11-28 00:00:00</t>
+          <t>2025-11-29 00:00:00</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -6583,17 +6583,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>30.12</t>
+          <t>29.88</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6609,7 +6609,7 @@
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>73</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
@@ -6624,53 +6624,53 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>3.18</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>3.54</t>
+          <t>4.44</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>3.07</t>
+          <t>3.16</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>207.4</t>
+          <t>210.0</t>
         </is>
       </c>
       <c r="AM15" t="n">
-        <v>200.3</v>
+        <v>201.08</v>
       </c>
       <c r="AN15" t="n">
-        <v>194.34</v>
+        <v>194.92</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>191.84</t>
+          <t>192.22</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>43.78</t>
+          <t>43.25</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>4.06</t>
+          <t>4.54</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>2.83</t>
+          <t>3.17</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6680,7 +6680,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-71.78</t>
+          <t>-68.36</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6690,48 +6690,48 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>28313.90571428571</t>
+          <t>28307.18473609129</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>27123.0</t>
+          <t>27093.0</t>
         </is>
       </c>
       <c r="AX15" t="n">
-        <v>21655.6</v>
+        <v>25064</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>20056.7</t>
+          <t>22168.4</t>
         </is>
       </c>
       <c r="AZ15" t="n">
-        <v>12284.3</v>
+        <v>12662.48</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>1598</t>
+          <t>2895</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>1393.334091030001</t>
+          <t>1554.494789995829</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>2293.457328001074</t>
+          <t>2440.878634307883</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>27123.0</t>
+          <t>27093.0</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-11-29</t>
         </is>
       </c>
       <c r="BF15" t="inlineStr">
@@ -6791,12 +6791,12 @@
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS15" t="inlineStr">
@@ -6806,7 +6806,7 @@
       </c>
       <c r="BT15" t="inlineStr">
         <is>
-          <t>4.65</t>
+          <t>4.63</t>
         </is>
       </c>
       <c r="BU15" t="inlineStr">
@@ -6816,7 +6816,7 @@
       </c>
       <c r="BV15" t="inlineStr">
         <is>
-          <t>12.81</t>
+          <t>12.87</t>
         </is>
       </c>
       <c r="BW15" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>49.59</t>
+          <t>49.8</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>10201</t>
+          <t>10248</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -6856,17 +6856,17 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
+          <t>215.0</t>
+        </is>
+      </c>
+      <c r="CE15" t="inlineStr">
+        <is>
+          <t>215.5</t>
+        </is>
+      </c>
+      <c r="CF15" t="inlineStr">
+        <is>
           <t>211.0</t>
-        </is>
-      </c>
-      <c r="CE15" t="inlineStr">
-        <is>
-          <t>214.0</t>
-        </is>
-      </c>
-      <c r="CF15" t="inlineStr">
-        <is>
-          <t>210.5</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
@@ -6903,12 +6903,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>105.0</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6918,7 +6918,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>210.5</t>
+          <t>214.0</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6928,17 +6928,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-1.06</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>13.00</t>
+          <t>7.97</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -6958,7 +6958,7 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>2025-11-28 00:00:00</t>
+          <t>2025-11-29 00:00:00</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -6998,7 +6998,7 @@
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>4.47</t>
+          <t>6.20</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
@@ -7013,17 +7013,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>24.71</t>
+          <t>30.12</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7039,7 +7039,7 @@
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>73</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
@@ -7054,53 +7054,53 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>2.93</t>
+          <t>3.18</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>2.52</t>
+          <t>3.54</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>2.93</t>
+          <t>3.07</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>204.5</t>
+          <t>207.4</t>
         </is>
       </c>
       <c r="AM16" t="n">
-        <v>199.48</v>
+        <v>200.3</v>
       </c>
       <c r="AN16" t="n">
-        <v>193.8</v>
+        <v>194.34</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>191.47</t>
+          <t>191.84</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>34.99</t>
+          <t>43.78</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>4.06</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>2.52</t>
+          <t>2.83</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7110,7 +7110,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-74.87</t>
+          <t>-71.78</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7120,48 +7120,48 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>28313.90571428571</t>
+          <t>28307.18473609129</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>22122.0</t>
+          <t>27123.0</t>
         </is>
       </c>
       <c r="AX16" t="n">
-        <v>20551.2</v>
+        <v>21655.6</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>18187.0</t>
+          <t>20056.7</t>
         </is>
       </c>
       <c r="AZ16" t="n">
-        <v>11819.44</v>
+        <v>12284.3</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>2364</t>
+          <t>1598</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>1229.675320671625</t>
+          <t>1393.334091030001</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>1997.731985848452</t>
+          <t>2293.457328001074</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>22122.0</t>
+          <t>27123.0</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-11-29</t>
         </is>
       </c>
       <c r="BF16" t="inlineStr">
@@ -7176,7 +7176,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>9.64</t>
+          <t>11.46</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -7221,7 +7221,7 @@
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
@@ -7231,12 +7231,12 @@
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
         <is>
-          <t>4.65</t>
+          <t>4.63</t>
         </is>
       </c>
       <c r="BU16" t="inlineStr">
@@ -7246,7 +7246,7 @@
       </c>
       <c r="BV16" t="inlineStr">
         <is>
-          <t>12.81</t>
+          <t>12.87</t>
         </is>
       </c>
       <c r="BW16" t="inlineStr">
@@ -7261,12 +7261,12 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>49.59</t>
+          <t>49.8</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>10201</t>
+          <t>10248</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -7286,22 +7286,22 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>208.5</t>
+          <t>211.0</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>211.0</t>
+          <t>214.0</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>208.0</t>
+          <t>210.5</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>210.5</t>
+          <t>214.0</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -7333,12 +7333,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>105.0</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7348,7 +7348,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>207.0</t>
+          <t>210.5</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7358,17 +7358,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-1.06</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>19.04</t>
+          <t>13.00</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7388,7 +7388,7 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>2025-11-28 00:00:00</t>
+          <t>2025-11-29 00:00:00</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -7428,7 +7428,7 @@
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>2.73</t>
+          <t>4.47</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
@@ -7443,17 +7443,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>30.12</t>
+          <t>24.71</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7469,7 +7469,7 @@
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>73</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
@@ -7479,58 +7479,58 @@
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>85.71</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>2.93</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>2.52</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>2.89</t>
+          <t>2.93</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>203.2</t>
+          <t>204.5</t>
         </is>
       </c>
       <c r="AM17" t="n">
-        <v>198.92</v>
+        <v>199.48</v>
       </c>
       <c r="AN17" t="n">
-        <v>193.33</v>
+        <v>193.8</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>191.14</t>
+          <t>191.47</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>24.29</t>
+          <t>34.99</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>2.85</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>2.52</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7540,7 +7540,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-77.07</t>
+          <t>-74.87</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7550,48 +7550,48 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>28313.90571428571</t>
+          <t>28307.18473609129</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>26279.0</t>
+          <t>22122.0</t>
         </is>
       </c>
       <c r="AX17" t="n">
-        <v>21604.4</v>
+        <v>20551.2</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>18148.2</t>
+          <t>18187.0</t>
         </is>
       </c>
       <c r="AZ17" t="n">
-        <v>11512</v>
+        <v>11819.44</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>3456</t>
+          <t>2364</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>1090.028654275838</t>
+          <t>1229.675320671625</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>2039.741068992971</t>
+          <t>1997.731985848452</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>26279.0</t>
+          <t>22122.0</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-11-29</t>
         </is>
       </c>
       <c r="BF17" t="inlineStr">
@@ -7606,7 +7606,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>7.81</t>
+          <t>9.64</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -7656,17 +7656,17 @@
       </c>
       <c r="BR17" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
         <is>
-          <t>4.65</t>
+          <t>4.63</t>
         </is>
       </c>
       <c r="BU17" t="inlineStr">
@@ -7676,7 +7676,7 @@
       </c>
       <c r="BV17" t="inlineStr">
         <is>
-          <t>12.81</t>
+          <t>12.87</t>
         </is>
       </c>
       <c r="BW17" t="inlineStr">
@@ -7691,12 +7691,12 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>49.59</t>
+          <t>49.8</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>10201</t>
+          <t>10248</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -7716,22 +7716,22 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>203.5</t>
+          <t>208.5</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
+          <t>211.0</t>
+        </is>
+      </c>
+      <c r="CF17" t="inlineStr">
+        <is>
           <t>208.0</t>
         </is>
       </c>
-      <c r="CF17" t="inlineStr">
-        <is>
-          <t>202.0</t>
-        </is>
-      </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>207.0</t>
+          <t>210.5</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7763,12 +7763,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>112.0</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7778,7 +7778,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>204.5</t>
+          <t>207.0</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7788,17 +7788,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>4.66</t>
+          <t>3.94</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-1.06</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>40.09</t>
+          <t>19.04</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7818,7 +7818,7 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>2025-11-28 00:00:00</t>
+          <t>2025-11-29 00:00:00</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
@@ -7858,7 +7858,7 @@
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>2.73</t>
         </is>
       </c>
       <c r="W18" t="inlineStr">
@@ -7873,17 +7873,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>26.35</t>
+          <t>30.12</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7899,7 +7899,7 @@
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>73</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
@@ -7909,58 +7909,58 @@
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>64.29</t>
+          <t>85.71</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>2.93</t>
+          <t>2.89</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>202.1</t>
+          <t>203.2</t>
         </is>
       </c>
       <c r="AM18" t="n">
-        <v>198.58</v>
+        <v>198.92</v>
       </c>
       <c r="AN18" t="n">
-        <v>192.93</v>
+        <v>193.33</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>190.87</t>
+          <t>191.14</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>14.78</t>
+          <t>24.29</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>2.48</t>
+          <t>2.85</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -7970,7 +7970,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-78.46</t>
+          <t>-77.07</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7980,48 +7980,48 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>28313.90571428571</t>
+          <t>28307.18473609129</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>22703.0</t>
+          <t>26279.0</t>
         </is>
       </c>
       <c r="AX18" t="n">
-        <v>23070.4</v>
+        <v>21604.4</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>16467.7</t>
+          <t>18148.2</t>
         </is>
       </c>
       <c r="AZ18" t="n">
-        <v>11056.48</v>
+        <v>11512</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>6602</t>
+          <t>3456</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>917.3536697818137</t>
+          <t>1090.028654275838</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>1581.513292449679</t>
+          <t>2039.741068992971</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>22703.0</t>
+          <t>26279.0</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-11-29</t>
         </is>
       </c>
       <c r="BF18" t="inlineStr">
@@ -8036,7 +8036,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>6.51</t>
+          <t>7.81</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -8081,22 +8081,22 @@
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
         <is>
-          <t>4.65</t>
+          <t>4.63</t>
         </is>
       </c>
       <c r="BU18" t="inlineStr">
@@ -8106,7 +8106,7 @@
       </c>
       <c r="BV18" t="inlineStr">
         <is>
-          <t>12.81</t>
+          <t>12.87</t>
         </is>
       </c>
       <c r="BW18" t="inlineStr">
@@ -8121,12 +8121,12 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>49.59</t>
+          <t>49.8</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>10201</t>
+          <t>10248</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -8146,22 +8146,22 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
+          <t>203.5</t>
+        </is>
+      </c>
+      <c r="CE18" t="inlineStr">
+        <is>
+          <t>208.0</t>
+        </is>
+      </c>
+      <c r="CF18" t="inlineStr">
+        <is>
           <t>202.0</t>
         </is>
       </c>
-      <c r="CE18" t="inlineStr">
-        <is>
-          <t>205.0</t>
-        </is>
-      </c>
-      <c r="CF18" t="inlineStr">
-        <is>
-          <t>202.0</t>
-        </is>
-      </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>204.5</t>
+          <t>207.0</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>112.0</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8208,7 +8208,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>201.0</t>
+          <t>204.5</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8218,17 +8218,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>6.29</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-1.06</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>28.98</t>
+          <t>40.09</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8248,7 +8248,7 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>2025-11-28 00:00:00</t>
+          <t>2025-11-29 00:00:00</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
@@ -8288,7 +8288,7 @@
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">
@@ -8303,17 +8303,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11.76</t>
+          <t>26.35</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8329,12 +8329,12 @@
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>73</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>57.14</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
@@ -8344,53 +8344,53 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>2.94</t>
+          <t>2.93</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>200.6</t>
+          <t>202.1</t>
         </is>
       </c>
       <c r="AM19" t="n">
-        <v>198.25</v>
+        <v>198.58</v>
       </c>
       <c r="AN19" t="n">
-        <v>192.58</v>
+        <v>192.93</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>190.62</t>
+          <t>190.87</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>6.46</t>
+          <t>14.78</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>2.21</t>
+          <t>2.48</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>2.16</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8400,7 +8400,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-79.25</t>
+          <t>-78.46</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8410,48 +8410,48 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>28313.90571428571</t>
+          <t>28307.18473609129</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>10051.0</t>
+          <t>22703.0</t>
         </is>
       </c>
       <c r="AX19" t="n">
-        <v>19272.8</v>
+        <v>23070.4</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>14943.0</t>
+          <t>16467.7</t>
         </is>
       </c>
       <c r="AZ19" t="n">
-        <v>10672.76</v>
+        <v>11056.48</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>4329</t>
+          <t>6602</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>796.5973747512926</t>
+          <t>917.3536697818137</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>1253.562422657489</t>
+          <t>1581.513292449679</t>
         </is>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
-          <t>10051.0</t>
+          <t>22703.0</t>
         </is>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-11-29</t>
         </is>
       </c>
       <c r="BF19" t="inlineStr">
@@ -8466,7 +8466,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>4.69</t>
+          <t>6.51</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -8511,22 +8511,22 @@
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
         <is>
-          <t>4.65</t>
+          <t>4.63</t>
         </is>
       </c>
       <c r="BU19" t="inlineStr">
@@ -8536,7 +8536,7 @@
       </c>
       <c r="BV19" t="inlineStr">
         <is>
-          <t>12.81</t>
+          <t>12.87</t>
         </is>
       </c>
       <c r="BW19" t="inlineStr">
@@ -8551,12 +8551,12 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>49.59</t>
+          <t>49.8</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>10201</t>
+          <t>10248</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -8576,22 +8576,22 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>199.5</t>
+          <t>202.0</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
+          <t>205.0</t>
+        </is>
+      </c>
+      <c r="CF19" t="inlineStr">
+        <is>
           <t>202.0</t>
         </is>
       </c>
-      <c r="CF19" t="inlineStr">
-        <is>
-          <t>198.5</t>
-        </is>
-      </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>201.0</t>
+          <t>204.5</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8623,12 +8623,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-2.2</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>107.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8638,7 +8638,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>199.5</t>
+          <t>201.0</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8648,17 +8648,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>6.99</t>
+          <t>6.73</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-1.06</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>17.59</t>
+          <t>28.98</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8678,7 +8678,7 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>2025-11-28 00:00:00</t>
+          <t>2025-11-29 00:00:00</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
@@ -8718,7 +8718,7 @@
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
@@ -8733,17 +8733,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>25.18</t>
+          <t>11.76</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>-2.00</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8759,68 +8759,68 @@
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>73</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>35.71</t>
+          <t>57.14</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>78.57</t>
+          <t>64.29</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>2.96</t>
+          <t>2.94</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>200.0</t>
+          <t>200.6</t>
         </is>
       </c>
       <c r="AM20" t="n">
-        <v>197.98</v>
+        <v>198.25</v>
       </c>
       <c r="AN20" t="n">
-        <v>192.28</v>
+        <v>192.58</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>190.44</t>
+          <t>190.62</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>7.56</t>
+          <t>6.46</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>2.21</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-79.59</t>
+          <t>-79.25</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8840,48 +8840,48 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>28313.90571428571</t>
+          <t>28307.18473609129</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>21601.0</t>
+          <t>10051.0</t>
         </is>
       </c>
       <c r="AX20" t="n">
-        <v>18457.8</v>
+        <v>19272.8</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>15697.4</t>
+          <t>14943.0</t>
         </is>
       </c>
       <c r="AZ20" t="n">
-        <v>10622.98</v>
+        <v>10672.76</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>2760</t>
+          <t>4329</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>713.5128205865296</t>
+          <t>796.5973747512926</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>2095.862522145168</t>
+          <t>1253.562422657489</t>
         </is>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
-          <t>21601.0</t>
+          <t>10051.0</t>
         </is>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-11-29</t>
         </is>
       </c>
       <c r="BF20" t="inlineStr">
@@ -8896,7 +8896,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>3.91</t>
+          <t>4.69</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -8941,22 +8941,22 @@
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>1.89</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
         <is>
-          <t>4.65</t>
+          <t>4.63</t>
         </is>
       </c>
       <c r="BU20" t="inlineStr">
@@ -8966,7 +8966,7 @@
       </c>
       <c r="BV20" t="inlineStr">
         <is>
-          <t>12.81</t>
+          <t>12.87</t>
         </is>
       </c>
       <c r="BW20" t="inlineStr">
@@ -8981,12 +8981,12 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>49.59</t>
+          <t>49.8</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>10201</t>
+          <t>10248</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
@@ -9006,22 +9006,22 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>205.0</t>
+          <t>199.5</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>205.0</t>
+          <t>202.0</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>198.0</t>
+          <t>198.5</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>199.5</t>
+          <t>201.0</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -9053,12 +9053,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>-2.2</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>107.0</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9068,7 +9068,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>204.0</t>
+          <t>199.5</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9078,17 +9078,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>7.42</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-1.06</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>9.50</t>
+          <t>17.59</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9108,7 +9108,7 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>2025-11-28 00:00:00</t>
+          <t>2025-11-29 00:00:00</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
@@ -9148,7 +9148,7 @@
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
@@ -9163,17 +9163,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>31.53</t>
+          <t>25.18</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>-2.00</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9189,27 +9189,27 @@
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>73</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>35.71</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>82.05</t>
+          <t>78.57</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
@@ -9219,239 +9219,239 @@
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
+          <t>200.0</t>
+        </is>
+      </c>
+      <c r="AM21" t="n">
+        <v>197.98</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>192.28</v>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>190.44</t>
+        </is>
+      </c>
+      <c r="AP21" t="inlineStr">
+        <is>
+          <t>7.56</t>
+        </is>
+      </c>
+      <c r="AQ21" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="AR21" t="inlineStr">
+        <is>
+          <t>2.04</t>
+        </is>
+      </c>
+      <c r="AS21" t="inlineStr">
+        <is>
+          <t>10.01</t>
+        </is>
+      </c>
+      <c r="AT21" t="inlineStr">
+        <is>
+          <t>-79.59</t>
+        </is>
+      </c>
+      <c r="AU21" t="inlineStr">
+        <is>
+          <t>2025/11/14</t>
+        </is>
+      </c>
+      <c r="AV21" t="inlineStr">
+        <is>
+          <t>28307.18473609129</t>
+        </is>
+      </c>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>21601.0</t>
+        </is>
+      </c>
+      <c r="AX21" t="n">
+        <v>18457.8</v>
+      </c>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>15697.4</t>
+        </is>
+      </c>
+      <c r="AZ21" t="n">
+        <v>10622.98</v>
+      </c>
+      <c r="BA21" t="inlineStr">
+        <is>
+          <t>2760</t>
+        </is>
+      </c>
+      <c r="BB21" t="inlineStr">
+        <is>
+          <t>713.5128205865296</t>
+        </is>
+      </c>
+      <c r="BC21" t="inlineStr">
+        <is>
+          <t>2095.862522145168</t>
+        </is>
+      </c>
+      <c r="BD21" t="inlineStr">
+        <is>
+          <t>21601.0</t>
+        </is>
+      </c>
+      <c r="BE21" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="BF21" t="inlineStr">
+        <is>
+          <t>192.0</t>
+        </is>
+      </c>
+      <c r="BG21" t="inlineStr">
+        <is>
+          <t>2025/10/14</t>
+        </is>
+      </c>
+      <c r="BH21" t="inlineStr">
+        <is>
+          <t>3.91</t>
+        </is>
+      </c>
+      <c r="BI21" t="inlineStr">
+        <is>
+          <t>鼎翰</t>
+        </is>
+      </c>
+      <c r="BJ21" t="inlineStr">
+        <is>
+          <t>鼎翰</t>
+        </is>
+      </c>
+      <c r="BK21" t="inlineStr">
+        <is>
+          <t>電腦及週邊設備業</t>
+        </is>
+      </c>
+      <c r="BL21" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BM21" t="inlineStr">
+        <is>
+          <t>0.56</t>
+        </is>
+      </c>
+      <c r="BN21" t="inlineStr">
+        <is>
+          <t>-11.45161899724185</t>
+        </is>
+      </c>
+      <c r="BO21" t="inlineStr">
+        <is>
+          <t>22.56717409239306</t>
+        </is>
+      </c>
+      <c r="BP21" t="inlineStr">
+        <is>
+          <t>38.82556207928187</t>
+        </is>
+      </c>
+      <c r="BQ21" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR21" t="inlineStr">
+        <is>
+          <t>價-量增</t>
+        </is>
+      </c>
+      <c r="BS21" t="inlineStr">
+        <is>
+          <t>1.89</t>
+        </is>
+      </c>
+      <c r="BT21" t="inlineStr">
+        <is>
+          <t>4.63</t>
+        </is>
+      </c>
+      <c r="BU21" t="inlineStr">
+        <is>
+          <t>57.78</t>
+        </is>
+      </c>
+      <c r="BV21" t="inlineStr">
+        <is>
+          <t>12.87</t>
+        </is>
+      </c>
+      <c r="BW21" t="inlineStr">
+        <is>
+          <t>33.69%</t>
+        </is>
+      </c>
+      <c r="BX21" t="inlineStr">
+        <is>
+          <t>11.08%</t>
+        </is>
+      </c>
+      <c r="BY21" t="inlineStr">
+        <is>
+          <t>49.8</t>
+        </is>
+      </c>
+      <c r="BZ21" t="inlineStr">
+        <is>
+          <t>10248</t>
+        </is>
+      </c>
+      <c r="CA21" t="inlineStr">
+        <is>
+          <t>條碼印表機及零配件52.71%、印表機各式標籤紙及其耗材41.09%、企業行動電腦6.20% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB21" t="inlineStr">
+        <is>
+          <t>鼎翰-電腦及週邊設備業-上櫃</t>
+        </is>
+      </c>
+      <c r="CC21" t="inlineStr">
+        <is>
+          <t>電腦及週邊設備業平上櫃</t>
+        </is>
+      </c>
+      <c r="CD21" t="inlineStr">
+        <is>
+          <t>205.0</t>
+        </is>
+      </c>
+      <c r="CE21" t="inlineStr">
+        <is>
+          <t>205.0</t>
+        </is>
+      </c>
+      <c r="CF21" t="inlineStr">
+        <is>
+          <t>198.0</t>
+        </is>
+      </c>
+      <c r="CG21" t="inlineStr">
+        <is>
           <t>199.5</t>
-        </is>
-      </c>
-      <c r="AM21" t="n">
-        <v>197.7</v>
-      </c>
-      <c r="AN21" t="n">
-        <v>192.01</v>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>190.29</t>
-        </is>
-      </c>
-      <c r="AP21" t="inlineStr">
-        <is>
-          <t>14.82</t>
-        </is>
-      </c>
-      <c r="AQ21" t="inlineStr">
-        <is>
-          <t>2.30</t>
-        </is>
-      </c>
-      <c r="AR21" t="inlineStr">
-        <is>
-          <t>2.01</t>
-        </is>
-      </c>
-      <c r="AS21" t="inlineStr">
-        <is>
-          <t>10.01</t>
-        </is>
-      </c>
-      <c r="AT21" t="inlineStr">
-        <is>
-          <t>-79.98</t>
-        </is>
-      </c>
-      <c r="AU21" t="inlineStr">
-        <is>
-          <t>2025/11/14</t>
-        </is>
-      </c>
-      <c r="AV21" t="inlineStr">
-        <is>
-          <t>28313.90571428571</t>
-        </is>
-      </c>
-      <c r="AW21" t="inlineStr">
-        <is>
-          <t>27388.0</t>
-        </is>
-      </c>
-      <c r="AX21" t="n">
-        <v>15822.8</v>
-      </c>
-      <c r="AY21" t="inlineStr">
-        <is>
-          <t>14450.7</t>
-        </is>
-      </c>
-      <c r="AZ21" t="n">
-        <v>10277.46</v>
-      </c>
-      <c r="BA21" t="inlineStr">
-        <is>
-          <t>1372</t>
-        </is>
-      </c>
-      <c r="BB21" t="inlineStr">
-        <is>
-          <t>462.1765112122318</t>
-        </is>
-      </c>
-      <c r="BC21" t="inlineStr">
-        <is>
-          <t>1986.79614562238</t>
-        </is>
-      </c>
-      <c r="BD21" t="inlineStr">
-        <is>
-          <t>27388.0</t>
-        </is>
-      </c>
-      <c r="BE21" t="inlineStr">
-        <is>
-          <t>2025-11-28</t>
-        </is>
-      </c>
-      <c r="BF21" t="inlineStr">
-        <is>
-          <t>192.0</t>
-        </is>
-      </c>
-      <c r="BG21" t="inlineStr">
-        <is>
-          <t>2025/10/14</t>
-        </is>
-      </c>
-      <c r="BH21" t="inlineStr">
-        <is>
-          <t>6.25</t>
-        </is>
-      </c>
-      <c r="BI21" t="inlineStr">
-        <is>
-          <t>鼎翰</t>
-        </is>
-      </c>
-      <c r="BJ21" t="inlineStr">
-        <is>
-          <t>鼎翰</t>
-        </is>
-      </c>
-      <c r="BK21" t="inlineStr">
-        <is>
-          <t>電腦及週邊設備業</t>
-        </is>
-      </c>
-      <c r="BL21" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BM21" t="inlineStr">
-        <is>
-          <t>0.56</t>
-        </is>
-      </c>
-      <c r="BN21" t="inlineStr">
-        <is>
-          <t>-11.45161899724185</t>
-        </is>
-      </c>
-      <c r="BO21" t="inlineStr">
-        <is>
-          <t>22.56717409239306</t>
-        </is>
-      </c>
-      <c r="BP21" t="inlineStr">
-        <is>
-          <t>38.82556207928187</t>
-        </is>
-      </c>
-      <c r="BQ21" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR21" t="inlineStr">
-        <is>
-          <t>價漲量增</t>
-        </is>
-      </c>
-      <c r="BS21" t="inlineStr">
-        <is>
-          <t>1.93</t>
-        </is>
-      </c>
-      <c r="BT21" t="inlineStr">
-        <is>
-          <t>4.65</t>
-        </is>
-      </c>
-      <c r="BU21" t="inlineStr">
-        <is>
-          <t>57.78</t>
-        </is>
-      </c>
-      <c r="BV21" t="inlineStr">
-        <is>
-          <t>12.81</t>
-        </is>
-      </c>
-      <c r="BW21" t="inlineStr">
-        <is>
-          <t>33.69%</t>
-        </is>
-      </c>
-      <c r="BX21" t="inlineStr">
-        <is>
-          <t>11.08%</t>
-        </is>
-      </c>
-      <c r="BY21" t="inlineStr">
-        <is>
-          <t>49.59</t>
-        </is>
-      </c>
-      <c r="BZ21" t="inlineStr">
-        <is>
-          <t>10201</t>
-        </is>
-      </c>
-      <c r="CA21" t="inlineStr">
-        <is>
-          <t>條碼印表機及零配件52.71%、印表機各式標籤紙及其耗材41.09%、企業行動電腦6.20% (2024年)</t>
-        </is>
-      </c>
-      <c r="CB21" t="inlineStr">
-        <is>
-          <t>鼎翰-電腦及週邊設備業-上櫃</t>
-        </is>
-      </c>
-      <c r="CC21" t="inlineStr">
-        <is>
-          <t>電腦及週邊設備業平上櫃</t>
-        </is>
-      </c>
-      <c r="CD21" t="inlineStr">
-        <is>
-          <t>201.5</t>
-        </is>
-      </c>
-      <c r="CE21" t="inlineStr">
-        <is>
-          <t>206.5</t>
-        </is>
-      </c>
-      <c r="CF21" t="inlineStr">
-        <is>
-          <t>201.5</t>
-        </is>
-      </c>
-      <c r="CG21" t="inlineStr">
-        <is>
-          <t>204.0</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -9483,12 +9483,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>167.0</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9498,74 +9498,74 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
+          <t>204.0</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>5.34</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>-1.06</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>9.50</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>2025-11-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>2025-11-29 00:00:00</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>2025-10-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>2025-11-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
           <t>201.5</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>6.06</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>-0.91</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>21.03</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>2025-11-14</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>2025-11-14 00:00:00</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>2025-11-28 00:00:00</t>
-        </is>
-      </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>2025-10-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>2025-11-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q22" t="inlineStr">
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
         <is>
           <t>201.5</t>
         </is>
       </c>
-      <c r="R22" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S22" t="inlineStr">
-        <is>
-          <t>201.5</t>
-        </is>
-      </c>
       <c r="T22" t="inlineStr">
         <is>
           <t>195.5</t>
@@ -9578,7 +9578,7 @@
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="W22" t="inlineStr">
@@ -9593,17 +9593,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>39.29</t>
+          <t>31.53</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9619,7 +9619,7 @@
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>73</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
@@ -9629,194 +9629,194 @@
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>69.23</t>
+          <t>82.05</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>2.87</t>
+          <t>2.96</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>198.8</t>
+          <t>199.5</t>
         </is>
       </c>
       <c r="AM22" t="n">
-        <v>197.15</v>
+        <v>197.7</v>
       </c>
       <c r="AN22" t="n">
-        <v>191.65</v>
+        <v>192.01</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>190.08</t>
+          <t>190.29</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>14.82</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
+          <t>2.01</t>
+        </is>
+      </c>
+      <c r="AS22" t="inlineStr">
+        <is>
+          <t>10.01</t>
+        </is>
+      </c>
+      <c r="AT22" t="inlineStr">
+        <is>
+          <t>-79.98</t>
+        </is>
+      </c>
+      <c r="AU22" t="inlineStr">
+        <is>
+          <t>2025/11/14</t>
+        </is>
+      </c>
+      <c r="AV22" t="inlineStr">
+        <is>
+          <t>28307.18473609129</t>
+        </is>
+      </c>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>27388.0</t>
+        </is>
+      </c>
+      <c r="AX22" t="n">
+        <v>15822.8</v>
+      </c>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>14450.7</t>
+        </is>
+      </c>
+      <c r="AZ22" t="n">
+        <v>10277.46</v>
+      </c>
+      <c r="BA22" t="inlineStr">
+        <is>
+          <t>1372</t>
+        </is>
+      </c>
+      <c r="BB22" t="inlineStr">
+        <is>
+          <t>462.1765112122318</t>
+        </is>
+      </c>
+      <c r="BC22" t="inlineStr">
+        <is>
+          <t>1986.79614562238</t>
+        </is>
+      </c>
+      <c r="BD22" t="inlineStr">
+        <is>
+          <t>27388.0</t>
+        </is>
+      </c>
+      <c r="BE22" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="BF22" t="inlineStr">
+        <is>
+          <t>192.0</t>
+        </is>
+      </c>
+      <c r="BG22" t="inlineStr">
+        <is>
+          <t>2025/10/14</t>
+        </is>
+      </c>
+      <c r="BH22" t="inlineStr">
+        <is>
+          <t>6.25</t>
+        </is>
+      </c>
+      <c r="BI22" t="inlineStr">
+        <is>
+          <t>鼎翰</t>
+        </is>
+      </c>
+      <c r="BJ22" t="inlineStr">
+        <is>
+          <t>鼎翰</t>
+        </is>
+      </c>
+      <c r="BK22" t="inlineStr">
+        <is>
+          <t>電腦及週邊設備業</t>
+        </is>
+      </c>
+      <c r="BL22" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BM22" t="inlineStr">
+        <is>
+          <t>0.56</t>
+        </is>
+      </c>
+      <c r="BN22" t="inlineStr">
+        <is>
+          <t>-11.45161899724185</t>
+        </is>
+      </c>
+      <c r="BO22" t="inlineStr">
+        <is>
+          <t>22.56717409239306</t>
+        </is>
+      </c>
+      <c r="BP22" t="inlineStr">
+        <is>
+          <t>38.82556207928187</t>
+        </is>
+      </c>
+      <c r="BQ22" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR22" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS22" t="inlineStr">
+        <is>
           <t>1.93</t>
         </is>
       </c>
-      <c r="AS22" t="inlineStr">
-        <is>
-          <t>10.01</t>
-        </is>
-      </c>
-      <c r="AT22" t="inlineStr">
-        <is>
-          <t>-80.72</t>
-        </is>
-      </c>
-      <c r="AU22" t="inlineStr">
-        <is>
-          <t>2025/11/14</t>
-        </is>
-      </c>
-      <c r="AV22" t="inlineStr">
-        <is>
-          <t>28313.90571428571</t>
-        </is>
-      </c>
-      <c r="AW22" t="inlineStr">
-        <is>
-          <t>33609.0</t>
-        </is>
-      </c>
-      <c r="AX22" t="n">
-        <v>14692</v>
-      </c>
-      <c r="AY22" t="inlineStr">
-        <is>
-          <t>12138.8</t>
-        </is>
-      </c>
-      <c r="AZ22" t="n">
-        <v>9836.780000000001</v>
-      </c>
-      <c r="BA22" t="inlineStr">
-        <is>
-          <t>2553</t>
-        </is>
-      </c>
-      <c r="BB22" t="inlineStr">
-        <is>
-          <t>184.9729413194776</t>
-        </is>
-      </c>
-      <c r="BC22" t="inlineStr">
-        <is>
-          <t>1139.994316817598</t>
-        </is>
-      </c>
-      <c r="BD22" t="inlineStr">
-        <is>
-          <t>33609.0</t>
-        </is>
-      </c>
-      <c r="BE22" t="inlineStr">
-        <is>
-          <t>2025-11-28</t>
-        </is>
-      </c>
-      <c r="BF22" t="inlineStr">
-        <is>
-          <t>192.0</t>
-        </is>
-      </c>
-      <c r="BG22" t="inlineStr">
-        <is>
-          <t>2025/10/14</t>
-        </is>
-      </c>
-      <c r="BH22" t="inlineStr">
-        <is>
-          <t>4.95</t>
-        </is>
-      </c>
-      <c r="BI22" t="inlineStr">
-        <is>
-          <t>鼎翰</t>
-        </is>
-      </c>
-      <c r="BJ22" t="inlineStr">
-        <is>
-          <t>鼎翰</t>
-        </is>
-      </c>
-      <c r="BK22" t="inlineStr">
-        <is>
-          <t>電腦及週邊設備業</t>
-        </is>
-      </c>
-      <c r="BL22" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BM22" t="inlineStr">
-        <is>
-          <t>0.56</t>
-        </is>
-      </c>
-      <c r="BN22" t="inlineStr">
-        <is>
-          <t>-11.45161899724185</t>
-        </is>
-      </c>
-      <c r="BO22" t="inlineStr">
-        <is>
-          <t>22.56717409239306</t>
-        </is>
-      </c>
-      <c r="BP22" t="inlineStr">
-        <is>
-          <t>38.82556207928187</t>
-        </is>
-      </c>
-      <c r="BQ22" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR22" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BS22" t="inlineStr">
-        <is>
-          <t>1.91</t>
-        </is>
-      </c>
       <c r="BT22" t="inlineStr">
         <is>
-          <t>4.65</t>
+          <t>4.63</t>
         </is>
       </c>
       <c r="BU22" t="inlineStr">
@@ -9826,7 +9826,7 @@
       </c>
       <c r="BV22" t="inlineStr">
         <is>
-          <t>12.81</t>
+          <t>12.87</t>
         </is>
       </c>
       <c r="BW22" t="inlineStr">
@@ -9841,12 +9841,12 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>49.59</t>
+          <t>49.8</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>10201</t>
+          <t>10248</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
@@ -9866,22 +9866,22 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>199.0</t>
+          <t>201.5</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>202.5</t>
+          <t>206.5</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>198.5</t>
+          <t>201.5</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>201.5</t>
+          <t>204.0</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -9903,7 +9903,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>【c】</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -9913,12 +9913,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>19.0</t>
+          <t>167.0</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9928,7 +9928,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>197.0</t>
+          <t>201.5</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9938,22 +9938,22 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>8.16</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-1.06</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>21.03</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -9968,7 +9968,7 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>2025-11-28 00:00:00</t>
+          <t>2025-11-29 00:00:00</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
@@ -9993,7 +9993,7 @@
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>201.5</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
@@ -10008,7 +10008,7 @@
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W23" t="inlineStr">
@@ -10023,17 +10023,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>4.47</t>
+          <t>39.29</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>-1.27</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10049,63 +10049,63 @@
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>73</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>46.15</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>51.28</t>
+          <t>69.23</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>2.84</t>
+          <t>2.87</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>197.9</t>
+          <t>198.8</t>
         </is>
       </c>
       <c r="AM23" t="n">
-        <v>196.78</v>
+        <v>197.15</v>
       </c>
       <c r="AN23" t="n">
-        <v>191.34</v>
+        <v>191.65</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>190.02</t>
+          <t>190.08</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>-11.24</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
@@ -10120,7 +10120,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-80.75</t>
+          <t>-80.72</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10130,48 +10130,48 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>28313.90571428571</t>
+          <t>28307.18473609129</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>3715.0</t>
+          <t>33609.0</t>
         </is>
       </c>
       <c r="AX23" t="n">
-        <v>9865</v>
+        <v>14692</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>9864.3</t>
+          <t>12138.8</t>
         </is>
       </c>
       <c r="AZ23" t="n">
-        <v>9269.959999999999</v>
+        <v>9836.780000000001</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2553</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>11.33269122891031</t>
+          <t>184.9729413194776</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>-776.9723785041442</t>
+          <t>1139.994316817598</t>
         </is>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
-          <t>3715.0</t>
+          <t>33609.0</t>
         </is>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-29</t>
         </is>
       </c>
       <c r="BF23" t="inlineStr">
@@ -10186,7 +10186,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2.60</t>
+          <t>4.95</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
@@ -10231,7 +10231,7 @@
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -10241,12 +10241,12 @@
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
         <is>
-          <t>4.65</t>
+          <t>4.63</t>
         </is>
       </c>
       <c r="BU23" t="inlineStr">
@@ -10256,7 +10256,7 @@
       </c>
       <c r="BV23" t="inlineStr">
         <is>
-          <t>12.81</t>
+          <t>12.87</t>
         </is>
       </c>
       <c r="BW23" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>49.59</t>
+          <t>49.8</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>10201</t>
+          <t>10248</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
@@ -10296,22 +10296,22 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>199.5</t>
+          <t>199.0</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>199.5</t>
+          <t>202.5</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>197.0</t>
+          <t>198.5</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>197.0</t>
+          <t>201.5</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">

--- a/Result/checksun_type/HMI.xlsx
+++ b/Result/checksun_type/HMI.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>22.0</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>20.3</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,97 +913,97 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
+          <t>-1.03</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>-38.48</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>-50.0</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>2025-10-23 00:00:00</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>2025-10-29 00:00:00</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>2025-09-24 00:00:00</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>2025-10-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>22.25</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>21.85</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>23.4</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>22.5</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>-7.09</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>-1.11</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>2025-12-01</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>0.57</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
           <t>-1.44</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>-45.47</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>-50.0</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>2025-10-23 00:00:00</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>2025-10-29 00:00:00</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>2025-09-24 00:00:00</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>2025-10-08 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>22.25</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>21.85</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>23.4</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>22.5</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>-8.92</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>-1.11</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>2025-11-28</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>0.78</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>-1.01</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,12 +1014,12 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -1029,58 +1029,58 @@
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>73.5</t>
+          <t>88.89</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-2.17</t>
+          <t>-0.79</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-6.24</t>
+          <t>-6.4</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-3.82</t>
+          <t>-3.70</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>19.64</t>
+          <t>19.86</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>20.08</v>
+        <v>20.02</v>
       </c>
       <c r="AN2" t="n">
-        <v>21.41</v>
+        <v>21.39</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>22.26</t>
+          <t>22.21</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>9.79</t>
+          <t>18.96</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>-0.47</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-109.26</t>
+          <t>-108.84</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1100,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>30291.50071326676</t>
+          <t>30249.05982905983</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>445.0</t>
+          <t>332.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>348.8</v>
+        <v>357.2</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>639.6</t>
+          <t>580.6</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>1276.44</v>
+        <v>1257.56</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-290</t>
+          <t>-223</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-140.1187399922061</t>
+          <t>-138.6446294685659</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-131.1167885136618</t>
+          <t>-130.5370215885447</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>445.0</t>
+          <t>332.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-15.86</t>
+          <t>-14.16</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1201,7 +1201,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1211,7 +1211,7 @@
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>89.32</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>581</t>
+          <t>592</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1271,7 +1271,7 @@
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>20.1</t>
+          <t>21.0</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
@@ -1281,7 +1281,7 @@
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>20.3</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>22.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>19.75</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-1.44</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-17.60</t>
+          <t>-45.47</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-9.61</t>
+          <t>-8.92</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-2.53</t>
+          <t>-1.01</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,73 +1444,73 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>49.15</t>
+          <t>73.5</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-3.26</t>
+          <t>-2.17</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-5.98</t>
+          <t>-6.24</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-3.92</t>
+          <t>-3.82</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>19.5</t>
+          <t>19.64</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>20.16</v>
+        <v>20.08</v>
       </c>
       <c r="AN3" t="n">
-        <v>21.44</v>
+        <v>21.41</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>22.31</t>
+          <t>22.26</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>3.76</t>
+          <t>9.79</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-0.60</t>
+          <t>-0.55</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.63</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-109.49</t>
+          <t>-109.26</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1530,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>30291.50071326676</t>
+          <t>30249.05982905983</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>397.0</t>
+          <t>445.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>517.2</v>
+        <v>348.8</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>627.7</t>
+          <t>639.6</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>1309.6</v>
+        <v>1276.44</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-110</t>
+          <t>-290</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-141.7554584428505</t>
+          <t>-140.1187399922061</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-139.3694273883414</t>
+          <t>-131.1167885136618</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>397.0</t>
+          <t>445.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-16.49</t>
+          <t>-15.86</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>89.32</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>581</t>
+          <t>592</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,22 +1696,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>20.3</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>20.3</t>
+          <t>20.1</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>19.7</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>19.75</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1733,7 +1733,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>22.0</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>19.85</t>
+          <t>19.75</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>2.71</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-1.44</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-25.82</t>
+          <t>-17.60</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-9.15</t>
+          <t>-9.61</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>-2.53</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,37 +1874,37 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>53.85</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>28.0</t>
+          <t>49.15</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-4.02</t>
+          <t>-3.26</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-5.68</t>
+          <t>-5.98</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
@@ -1914,28 +1914,28 @@
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>19.45</t>
+          <t>19.5</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>20.26</v>
+        <v>20.16</v>
       </c>
       <c r="AN4" t="n">
-        <v>21.48</v>
+        <v>21.44</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>22.36</t>
+          <t>22.31</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-1.89</t>
+          <t>3.76</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>-0.60</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-109.58</t>
+          <t>-109.49</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1960,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>30291.50071326676</t>
+          <t>30249.05982905983</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>446.0</t>
+          <t>397.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>537.2</v>
+        <v>517.2</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>724.2</t>
+          <t>627.7</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>1332.24</v>
+        <v>1309.6</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-187</t>
+          <t>-110</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-142.1892822709431</t>
+          <t>-141.7554584428505</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-141.0385748025855</t>
+          <t>-139.3694273883414</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>446.0</t>
+          <t>397.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-16.07</t>
+          <t>-16.49</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2061,17 +2061,17 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>89.32</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>581</t>
+          <t>592</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,22 +2126,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>19.45</t>
+          <t>20.3</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>20.05</t>
+          <t>20.3</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>19.45</t>
+          <t>19.7</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>19.85</t>
+          <t>19.75</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>9.0</t>
+          <t>22.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>19.5</t>
+          <t>19.85</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-1.44</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-34.48</t>
+          <t>-25.82</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-10.76</t>
+          <t>-9.15</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,68 +2304,68 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>26.92</t>
+          <t>53.85</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>11.12</t>
+          <t>28.0</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>2.06</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-5.18</t>
+          <t>-4.02</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-5.44</t>
+          <t>-5.68</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-3.78</t>
+          <t>-3.92</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>19.31</t>
+          <t>19.45</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>20.36</v>
+        <v>20.26</v>
       </c>
       <c r="AN5" t="n">
-        <v>21.54</v>
+        <v>21.48</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>22.38</t>
+          <t>22.36</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-10.91</t>
+          <t>-1.89</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-0.70</t>
+          <t>-0.64</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-109.53</t>
+          <t>-109.58</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>30291.50071326676</t>
+          <t>30249.05982905983</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>166.0</t>
+          <t>446.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>494.2</v>
+        <v>537.2</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>754.3</t>
+          <t>724.2</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>1394.4</v>
+        <v>1332.24</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-260</t>
+          <t>-187</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-142.3985018106445</t>
+          <t>-142.1892822709431</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-143.6359791514134</t>
+          <t>-141.0385748025855</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>166.0</t>
+          <t>446.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-17.55</t>
+          <t>-16.07</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2491,17 +2491,17 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>89.32</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>581</t>
+          <t>592</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,22 +2556,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>19.3</t>
+          <t>19.45</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>19.5</t>
+          <t>20.05</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>19.3</t>
+          <t>19.45</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>19.5</t>
+          <t>19.85</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>19.2</t>
+          <t>19.5</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>3.52</t>
+          <t>3.94</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-1.44</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-2.21</t>
+          <t>-34.48</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-12.13</t>
+          <t>-10.76</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,54 +2734,54 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>3.23</t>
+          <t>26.92</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>9.68</t>
+          <t>11.12</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-6.04</t>
+          <t>-5.18</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-5.2</t>
+          <t>-5.44</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-3.45</t>
+          <t>-3.78</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>19.25</t>
+          <t>19.31</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>20.49</v>
+        <v>20.36</v>
       </c>
       <c r="AN6" t="n">
-        <v>21.61</v>
+        <v>21.54</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
@@ -2790,17 +2790,17 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-17.72</t>
+          <t>-10.91</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>-0.70</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-0.63</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-109.27</t>
+          <t>-109.53</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>30291.50071326676</t>
+          <t>30249.05982905983</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>290.0</t>
+          <t>166.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>804</v>
+        <v>494.2</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>822.2</t>
+          <t>754.3</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>1439.06</v>
+        <v>1394.4</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-18</t>
+          <t>-260</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-142.1735059305047</t>
+          <t>-142.3985018106445</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-112.2167003943315</t>
+          <t>-143.6359791514134</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>290.0</t>
+          <t>166.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-18.82</t>
+          <t>-17.55</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>89.32</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>581</t>
+          <t>592</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>19.2</t>
+          <t>19.3</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
+          <t>19.5</t>
+        </is>
+      </c>
+      <c r="CF6" t="inlineStr">
+        <is>
           <t>19.3</t>
         </is>
       </c>
-      <c r="CF6" t="inlineStr">
-        <is>
-          <t>19.2</t>
-        </is>
-      </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>19.2</t>
+          <t>19.5</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-1.53</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>3.52</t>
+          <t>5.42</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-1.44</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>3.85</t>
+          <t>-2.21</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,12 +3164,12 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -3179,58 +3179,58 @@
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>9.68</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-1.13</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-5.90</t>
+          <t>-6.04</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-4.83</t>
+          <t>-5.2</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-3.05</t>
+          <t>-3.45</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>19.42</t>
+          <t>19.25</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>20.64</v>
+        <v>20.49</v>
       </c>
       <c r="AN7" t="n">
-        <v>21.68</v>
+        <v>21.61</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>22.37</t>
+          <t>22.38</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-21.10</t>
+          <t>-17.72</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-108.86</t>
+          <t>-109.27</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>30291.50071326676</t>
+          <t>30249.05982905983</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>1287.0</t>
+          <t>290.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>930.4</v>
+        <v>804</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>895.9</t>
+          <t>822.2</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>1833.62</v>
+        <v>1439.06</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>-18</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-147.6201978461726</t>
+          <t>-142.1735059305047</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-76.60999144155971</t>
+          <t>-112.2167003943315</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>1287.0</t>
+          <t>290.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3351,7 +3351,7 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>89.32</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>581</t>
+          <t>592</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,17 +3416,17 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>19.55</t>
+          <t>19.2</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>19.65</t>
+          <t>19.3</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>18.85</t>
+          <t>19.2</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>-1.53</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>26.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>19.5</t>
+          <t>19.2</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>5.42</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-1.44</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-4.04</t>
+          <t>3.85</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-10.76</t>
+          <t>-12.13</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>3.17</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,73 +3594,73 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>22.58</t>
+          <t>3.23</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>7.53</t>
+          <t>8.6</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>-1.13</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-5.39</t>
+          <t>-5.90</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-4.43</t>
+          <t>-4.83</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-2.68</t>
+          <t>-3.05</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>19.67</t>
+          <t>19.42</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>20.79</v>
+        <v>20.64</v>
       </c>
       <c r="AN8" t="n">
-        <v>21.75</v>
+        <v>21.68</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>22.35</t>
+          <t>22.37</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-23.19</t>
+          <t>-21.10</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.68</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-108.40</t>
+          <t>-108.86</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>30291.50071326676</t>
+          <t>30249.05982905983</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>497.0</t>
+          <t>1287.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>738.2</v>
+        <v>930.4</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>769.3</t>
+          <t>895.9</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>1851.22</v>
+        <v>1833.62</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-31</t>
+          <t>34</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-160.5311444651931</t>
+          <t>-147.6201978461726</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-129.8286218146873</t>
+          <t>-76.60999144155971</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>497.0</t>
+          <t>1287.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-17.55</t>
+          <t>-18.82</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3786,12 +3786,12 @@
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>89.32</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>581</t>
+          <t>592</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,22 +3846,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
+          <t>19.55</t>
+        </is>
+      </c>
+      <c r="CE8" t="inlineStr">
+        <is>
+          <t>19.65</t>
+        </is>
+      </c>
+      <c r="CF8" t="inlineStr">
+        <is>
+          <t>18.85</t>
+        </is>
+      </c>
+      <c r="CG8" t="inlineStr">
+        <is>
           <t>19.2</t>
-        </is>
-      </c>
-      <c r="CE8" t="inlineStr">
-        <is>
-          <t>19.5</t>
-        </is>
-      </c>
-      <c r="CF8" t="inlineStr">
-        <is>
-          <t>18.9</t>
-        </is>
-      </c>
-      <c r="CG8" t="inlineStr">
-        <is>
-          <t>19.5</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>26.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>19.15</t>
+          <t>19.5</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>3.77</t>
+          <t>3.94</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-1.44</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>14.69</t>
+          <t>-4.04</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-12.36</t>
+          <t>-10.76</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>3.17</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,73 +4024,73 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>22.58</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.53</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-3.58</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-5.17</t>
+          <t>-5.39</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-3.97</t>
+          <t>-4.43</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-2.33</t>
+          <t>-2.68</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>19.86</t>
+          <t>19.67</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>20.94</v>
+        <v>20.79</v>
       </c>
       <c r="AN9" t="n">
-        <v>21.81</v>
+        <v>21.75</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>22.33</t>
+          <t>22.35</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-28.42</t>
+          <t>-23.19</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-0.68</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-0.55</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-107.91</t>
+          <t>-108.40</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>30291.50071326676</t>
+          <t>30249.05982905983</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>231.0</t>
+          <t>497.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>911.2</v>
+        <v>738.2</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>794.5</t>
+          <t>769.3</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>1867.82</v>
+        <v>1851.22</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>116</t>
+          <t>-31</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-166.1134213107396</t>
+          <t>-160.5311444651931</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-116.5756429972018</t>
+          <t>-129.8286218146873</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>231.0</t>
+          <t>497.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-19.03</t>
+          <t>-17.55</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4211,17 +4211,17 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>89.32</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>581</t>
+          <t>592</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,22 +4276,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>18.85</t>
+          <t>19.2</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>19.15</t>
+          <t>19.5</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>18.85</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>19.15</t>
+          <t>19.5</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-4.24</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>19.2</t>
+          <t>19.15</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>3.52</t>
+          <t>5.67</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-1.44</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>21.51</t>
+          <t>14.69</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-12.13</t>
+          <t>-12.36</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>3.15</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-3.37</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,12 +4454,12 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
@@ -4469,58 +4469,58 @@
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>15.38</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-4.81</t>
+          <t>-3.58</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-4.41</t>
+          <t>-5.17</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-3.49</t>
+          <t>-3.97</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-2.01</t>
+          <t>-2.33</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>20.17</t>
+          <t>19.86</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>21.1</v>
+        <v>20.94</v>
       </c>
       <c r="AN10" t="n">
-        <v>21.86</v>
+        <v>21.81</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>22.31</t>
+          <t>22.33</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-25.64</t>
+          <t>-28.42</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-107.35</t>
+          <t>-107.91</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>30291.50071326676</t>
+          <t>30249.05982905983</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>1715.0</t>
+          <t>231.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>1014.4</v>
+        <v>911.2</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>834.8</t>
+          <t>794.5</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>1896.36</v>
+        <v>1867.82</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>179</t>
+          <t>116</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-175.1202900950192</t>
+          <t>-166.1134213107396</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-64.97940029375127</t>
+          <t>-116.5756429972018</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>1715.0</t>
+          <t>231.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-18.82</t>
+          <t>-19.03</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4641,7 +4641,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>89.32</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>581</t>
+          <t>592</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>20.05</t>
+          <t>18.85</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>20.05</t>
+          <t>19.15</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>19.0</t>
+          <t>18.85</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>19.2</t>
+          <t>19.15</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-2.0</t>
+          <t>-4.24</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>46.0</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>20.05</t>
+          <t>19.2</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4778,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>5.42</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-1.44</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>17.65</t>
+          <t>21.51</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-8.24</t>
+          <t>-12.13</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>3.15</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>-3.37</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,12 +4884,12 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
@@ -4899,58 +4899,58 @@
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>23.08</t>
+          <t>15.38</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-1.91</t>
+          <t>-4.81</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-3.90</t>
+          <t>-4.41</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-2.98</t>
+          <t>-3.49</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-1.65</t>
+          <t>-2.01</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>20.44</t>
+          <t>20.17</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>21.27</v>
+        <v>21.1</v>
       </c>
       <c r="AN11" t="n">
-        <v>21.92</v>
+        <v>21.86</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>22.29</t>
+          <t>22.31</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-16.23</t>
+          <t>-25.64</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-106.88</t>
+          <t>-107.35</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>30291.50071326676</t>
+          <t>30249.05982905983</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>922.0</t>
+          <t>1715.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>840.4</v>
+        <v>1014.4</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>714.3</t>
+          <t>834.8</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>1889.2</v>
+        <v>1896.36</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>126</t>
+          <t>179</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-195.1459064225224</t>
+          <t>-175.1202900950192</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-147.9497892783307</t>
+          <t>-64.97940029375127</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>922.0</t>
+          <t>1715.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-15.22</t>
+          <t>-18.82</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>89.32</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>581</t>
+          <t>592</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>20.05</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>20.1</t>
+          <t>20.05</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>19.95</t>
+          <t>19.0</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>20.05</t>
+          <t>19.2</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-2.0</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>16.0</t>
+          <t>46.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>20.45</t>
+          <t>20.05</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5208,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-2.76</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-1.44</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>22.57</t>
+          <t>17.65</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-6.41</t>
+          <t>-8.24</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,73 +5314,73 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>46.15</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>36.17</t>
+          <t>23.08</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-1.91</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-4.52</t>
+          <t>-3.90</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-2.41</t>
+          <t>-2.98</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-1.36</t>
+          <t>-1.65</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>20.46</t>
+          <t>20.44</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>21.43</v>
+        <v>21.27</v>
       </c>
       <c r="AN12" t="n">
-        <v>21.96</v>
+        <v>21.92</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>22.26</t>
+          <t>22.29</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-15.32</t>
+          <t>-16.23</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.50</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-106.60</t>
+          <t>-106.88</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5400,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>30291.50071326676</t>
+          <t>30249.05982905983</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>326.0</t>
+          <t>922.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>861.4</v>
+        <v>840.4</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>702.8</t>
+          <t>714.3</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>2075.44</v>
+        <v>1889.2</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>158</t>
+          <t>126</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-203.7270186305573</t>
+          <t>-195.1459064225224</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-176.2307096392179</t>
+          <t>-147.9497892783307</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>326.0</t>
+          <t>922.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-13.53</t>
+          <t>-15.22</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,7 +5511,7 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>89.32</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>581</t>
+          <t>592</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,22 +5566,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>20.45</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>20.45</t>
+          <t>20.1</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>20.3</t>
+          <t>19.95</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>20.45</t>
+          <t>20.05</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5613,12 +5613,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>56.0</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5628,7 +5628,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>215.5</t>
+          <t>213.5</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5643,12 +5643,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-1.06</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>-1.69</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5668,7 +5668,7 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>2025-11-29 00:00:00</t>
+          <t>2025-12-02 00:00:00</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -5708,7 +5708,7 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>6.95</t>
+          <t>5.96</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
@@ -5723,17 +5723,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>17.18</t>
+          <t>13.18</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>-1.17</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5744,73 +5744,73 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>56</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>86.21</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>95.4</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>-0.37</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>5.31</t>
+          <t>5.15</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>3.66</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>213.7</t>
+          <t>214.3</t>
         </is>
       </c>
       <c r="AM13" t="n">
-        <v>202.92</v>
+        <v>203.8</v>
       </c>
       <c r="AN13" t="n">
-        <v>196.07</v>
+        <v>196.6</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>193.0</t>
+          <t>193.37</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>35.12</t>
+          <t>26.64</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>5.21</t>
+          <t>5.23</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>3.85</t>
+          <t>4.13</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5820,7 +5820,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-61.52</t>
+          <t>-58.78</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5830,48 +5830,48 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>28307.18473609129</t>
+          <t>28292.75427350427</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>15735.0</t>
+          <t>12118.0</t>
         </is>
       </c>
       <c r="AX13" t="n">
-        <v>21869.2</v>
+        <v>19868.4</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>21736.8</t>
+          <t>20209.8</t>
         </is>
       </c>
       <c r="AZ13" t="n">
-        <v>12717.58</v>
+        <v>12862.38</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>132</t>
+          <t>-341</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>1509.806122496388</t>
+          <t>1331.553831026793</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>1101.508857283279</t>
+          <t>351.1662279440243</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>15735.0</t>
+          <t>12118.0</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
-          <t>2025-11-29</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="BF13" t="inlineStr">
@@ -5886,7 +5886,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>12.24</t>
+          <t>11.20</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -5911,7 +5911,7 @@
       </c>
       <c r="BM13" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="BN13" t="inlineStr">
@@ -5931,7 +5931,7 @@
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
@@ -5941,12 +5941,12 @@
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
         <is>
-          <t>4.63</t>
+          <t>4.67</t>
         </is>
       </c>
       <c r="BU13" t="inlineStr">
@@ -5956,7 +5956,7 @@
       </c>
       <c r="BV13" t="inlineStr">
         <is>
-          <t>12.87</t>
+          <t>12.75</t>
         </is>
       </c>
       <c r="BW13" t="inlineStr">
@@ -5971,12 +5971,12 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>49.44</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>10248</t>
+          <t>10153</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -5996,22 +5996,22 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>215.0</t>
+          <t>215.5</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>215.5</t>
+          <t>217.0</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
+          <t>212.5</t>
+        </is>
+      </c>
+      <c r="CG13" t="inlineStr">
+        <is>
           <t>213.5</t>
-        </is>
-      </c>
-      <c r="CG13" t="inlineStr">
-        <is>
-          <t>215.5</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6058,7 +6058,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>214.5</t>
+          <t>215.5</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6068,17 +6068,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>-0.94</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-1.06</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6098,7 +6098,7 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>2025-11-29 00:00:00</t>
+          <t>2025-12-02 00:00:00</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -6138,7 +6138,7 @@
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>6.45</t>
+          <t>6.95</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
@@ -6153,17 +6153,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>19.06</t>
+          <t>17.18</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6174,12 +6174,12 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>56</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
@@ -6194,53 +6194,53 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>4.99</t>
+          <t>5.31</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>3.29</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>212.0</t>
+          <t>213.7</t>
         </is>
       </c>
       <c r="AM14" t="n">
-        <v>201.92</v>
+        <v>202.92</v>
       </c>
       <c r="AN14" t="n">
-        <v>195.5</v>
+        <v>196.07</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>192.61</t>
+          <t>193.0</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>39.40</t>
+          <t>35.12</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>4.90</t>
+          <t>5.21</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>3.51</t>
+          <t>3.85</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6250,7 +6250,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-64.90</t>
+          <t>-61.52</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6260,48 +6260,48 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>28307.18473609129</t>
+          <t>28292.75427350427</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>17273.0</t>
+          <t>15735.0</t>
         </is>
       </c>
       <c r="AX14" t="n">
-        <v>23978</v>
+        <v>21869.2</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>23524.2</t>
+          <t>21736.8</t>
         </is>
       </c>
       <c r="AZ14" t="n">
-        <v>12876.32</v>
+        <v>12717.58</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>453</t>
+          <t>132</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>1584.041988898771</t>
+          <t>1509.806122496388</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>1746.551582864951</t>
+          <t>1101.508857283279</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>17273.0</t>
+          <t>15735.0</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
-          <t>2025-11-29</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="BF14" t="inlineStr">
@@ -6316,7 +6316,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>11.72</t>
+          <t>12.24</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -6341,7 +6341,7 @@
       </c>
       <c r="BM14" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="BN14" t="inlineStr">
@@ -6361,22 +6361,22 @@
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
         <is>
-          <t>4.63</t>
+          <t>4.67</t>
         </is>
       </c>
       <c r="BU14" t="inlineStr">
@@ -6386,7 +6386,7 @@
       </c>
       <c r="BV14" t="inlineStr">
         <is>
-          <t>12.87</t>
+          <t>12.75</t>
         </is>
       </c>
       <c r="BW14" t="inlineStr">
@@ -6401,12 +6401,12 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>49.44</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>10248</t>
+          <t>10153</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -6426,7 +6426,7 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>214.5</t>
+          <t>215.0</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
@@ -6436,12 +6436,12 @@
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>213.0</t>
+          <t>213.5</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>214.5</t>
+          <t>215.5</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -6473,12 +6473,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6488,7 +6488,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>214.0</t>
+          <t>214.5</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6498,17 +6498,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>-0.47</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-1.06</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>13.06</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6528,7 +6528,7 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>2025-11-29 00:00:00</t>
+          <t>2025-12-02 00:00:00</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -6568,7 +6568,7 @@
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>6.20</t>
+          <t>6.45</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
@@ -6583,17 +6583,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>29.88</t>
+          <t>19.06</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6604,12 +6604,12 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>56</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
@@ -6624,53 +6624,53 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>4.44</t>
+          <t>4.99</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>3.16</t>
+          <t>3.29</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>210.0</t>
+          <t>212.0</t>
         </is>
       </c>
       <c r="AM15" t="n">
-        <v>201.08</v>
+        <v>201.92</v>
       </c>
       <c r="AN15" t="n">
-        <v>194.92</v>
+        <v>195.5</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>192.22</t>
+          <t>192.61</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>43.25</t>
+          <t>39.40</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>4.54</t>
+          <t>4.90</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>3.17</t>
+          <t>3.51</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6680,7 +6680,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-68.36</t>
+          <t>-64.90</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6690,48 +6690,48 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>28307.18473609129</t>
+          <t>28292.75427350427</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>27093.0</t>
+          <t>17273.0</t>
         </is>
       </c>
       <c r="AX15" t="n">
-        <v>25064</v>
+        <v>23978</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>22168.4</t>
+          <t>23524.2</t>
         </is>
       </c>
       <c r="AZ15" t="n">
-        <v>12662.48</v>
+        <v>12876.32</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>2895</t>
+          <t>453</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>1554.494789995829</t>
+          <t>1584.041988898771</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>2440.878634307883</t>
+          <t>1746.551582864951</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>27093.0</t>
+          <t>17273.0</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
-          <t>2025-11-29</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="BF15" t="inlineStr">
@@ -6746,7 +6746,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>11.46</t>
+          <t>11.72</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -6771,7 +6771,7 @@
       </c>
       <c r="BM15" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="BN15" t="inlineStr">
@@ -6791,7 +6791,7 @@
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
@@ -6801,12 +6801,12 @@
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
         <is>
-          <t>4.63</t>
+          <t>4.67</t>
         </is>
       </c>
       <c r="BU15" t="inlineStr">
@@ -6816,7 +6816,7 @@
       </c>
       <c r="BV15" t="inlineStr">
         <is>
-          <t>12.87</t>
+          <t>12.75</t>
         </is>
       </c>
       <c r="BW15" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>49.44</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>10248</t>
+          <t>10153</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -6856,7 +6856,7 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>215.0</t>
+          <t>214.5</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
@@ -6866,12 +6866,12 @@
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>211.0</t>
+          <t>213.0</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>214.0</t>
+          <t>214.5</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -6903,12 +6903,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6928,17 +6928,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-1.06</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>7.97</t>
+          <t>13.06</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -6958,7 +6958,7 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>2025-11-29 00:00:00</t>
+          <t>2025-12-02 00:00:00</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -7013,17 +7013,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>30.12</t>
+          <t>29.88</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7034,12 +7034,12 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>56</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
@@ -7054,53 +7054,53 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>3.18</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>3.54</t>
+          <t>4.44</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>3.07</t>
+          <t>3.16</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>207.4</t>
+          <t>210.0</t>
         </is>
       </c>
       <c r="AM16" t="n">
-        <v>200.3</v>
+        <v>201.08</v>
       </c>
       <c r="AN16" t="n">
-        <v>194.34</v>
+        <v>194.92</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>191.84</t>
+          <t>192.22</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>43.78</t>
+          <t>43.25</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>4.06</t>
+          <t>4.54</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>2.83</t>
+          <t>3.17</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7110,7 +7110,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-71.78</t>
+          <t>-68.36</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7120,48 +7120,48 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>28307.18473609129</t>
+          <t>28292.75427350427</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>27123.0</t>
+          <t>27093.0</t>
         </is>
       </c>
       <c r="AX16" t="n">
-        <v>21655.6</v>
+        <v>25064</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>20056.7</t>
+          <t>22168.4</t>
         </is>
       </c>
       <c r="AZ16" t="n">
-        <v>12284.3</v>
+        <v>12662.48</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>1598</t>
+          <t>2895</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>1393.334091030001</t>
+          <t>1554.494789995829</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>2293.457328001074</t>
+          <t>2440.878634307883</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>27123.0</t>
+          <t>27093.0</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
-          <t>2025-11-29</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="BF16" t="inlineStr">
@@ -7201,7 +7201,7 @@
       </c>
       <c r="BM16" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="BN16" t="inlineStr">
@@ -7221,12 +7221,12 @@
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS16" t="inlineStr">
@@ -7236,7 +7236,7 @@
       </c>
       <c r="BT16" t="inlineStr">
         <is>
-          <t>4.63</t>
+          <t>4.67</t>
         </is>
       </c>
       <c r="BU16" t="inlineStr">
@@ -7246,7 +7246,7 @@
       </c>
       <c r="BV16" t="inlineStr">
         <is>
-          <t>12.87</t>
+          <t>12.75</t>
         </is>
       </c>
       <c r="BW16" t="inlineStr">
@@ -7261,12 +7261,12 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>49.44</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>10248</t>
+          <t>10153</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -7286,17 +7286,17 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
+          <t>215.0</t>
+        </is>
+      </c>
+      <c r="CE16" t="inlineStr">
+        <is>
+          <t>215.5</t>
+        </is>
+      </c>
+      <c r="CF16" t="inlineStr">
+        <is>
           <t>211.0</t>
-        </is>
-      </c>
-      <c r="CE16" t="inlineStr">
-        <is>
-          <t>214.0</t>
-        </is>
-      </c>
-      <c r="CF16" t="inlineStr">
-        <is>
-          <t>210.5</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
@@ -7333,12 +7333,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>105.0</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7348,7 +7348,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>210.5</t>
+          <t>214.0</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7358,17 +7358,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2.32</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-1.06</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>13.00</t>
+          <t>7.97</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7388,7 +7388,7 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>2025-11-29 00:00:00</t>
+          <t>2025-12-02 00:00:00</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -7428,7 +7428,7 @@
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>4.47</t>
+          <t>6.20</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
@@ -7443,17 +7443,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>24.71</t>
+          <t>30.12</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7464,12 +7464,12 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>56</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
@@ -7484,53 +7484,53 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>2.93</t>
+          <t>3.18</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>2.52</t>
+          <t>3.54</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>2.93</t>
+          <t>3.07</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>204.5</t>
+          <t>207.4</t>
         </is>
       </c>
       <c r="AM17" t="n">
-        <v>199.48</v>
+        <v>200.3</v>
       </c>
       <c r="AN17" t="n">
-        <v>193.8</v>
+        <v>194.34</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>191.47</t>
+          <t>191.84</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>34.99</t>
+          <t>43.78</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>4.06</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>2.52</t>
+          <t>2.83</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7540,7 +7540,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-74.87</t>
+          <t>-71.78</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7550,48 +7550,48 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>28307.18473609129</t>
+          <t>28292.75427350427</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>22122.0</t>
+          <t>27123.0</t>
         </is>
       </c>
       <c r="AX17" t="n">
-        <v>20551.2</v>
+        <v>21655.6</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>18187.0</t>
+          <t>20056.7</t>
         </is>
       </c>
       <c r="AZ17" t="n">
-        <v>11819.44</v>
+        <v>12284.3</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>2364</t>
+          <t>1598</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>1229.675320671625</t>
+          <t>1393.334091030001</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>1997.731985848452</t>
+          <t>2293.457328001074</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>22122.0</t>
+          <t>27123.0</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
-          <t>2025-11-29</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="BF17" t="inlineStr">
@@ -7606,7 +7606,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>9.64</t>
+          <t>11.46</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -7631,7 +7631,7 @@
       </c>
       <c r="BM17" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="BN17" t="inlineStr">
@@ -7651,7 +7651,7 @@
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
@@ -7661,12 +7661,12 @@
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
         <is>
-          <t>4.63</t>
+          <t>4.67</t>
         </is>
       </c>
       <c r="BU17" t="inlineStr">
@@ -7676,7 +7676,7 @@
       </c>
       <c r="BV17" t="inlineStr">
         <is>
-          <t>12.87</t>
+          <t>12.75</t>
         </is>
       </c>
       <c r="BW17" t="inlineStr">
@@ -7691,12 +7691,12 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>49.44</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>10248</t>
+          <t>10153</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -7716,22 +7716,22 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>208.5</t>
+          <t>211.0</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>211.0</t>
+          <t>214.0</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>208.0</t>
+          <t>210.5</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>210.5</t>
+          <t>214.0</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7763,12 +7763,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>105.0</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7778,7 +7778,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>207.0</t>
+          <t>210.5</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7788,17 +7788,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>3.94</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-1.06</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>19.04</t>
+          <t>13.00</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7818,7 +7818,7 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>2025-11-29 00:00:00</t>
+          <t>2025-12-02 00:00:00</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
@@ -7858,7 +7858,7 @@
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>2.73</t>
+          <t>4.47</t>
         </is>
       </c>
       <c r="W18" t="inlineStr">
@@ -7873,17 +7873,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>30.12</t>
+          <t>24.71</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7894,12 +7894,12 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>56</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
@@ -7909,58 +7909,58 @@
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>85.71</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>2.93</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>2.52</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>2.89</t>
+          <t>2.93</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>203.2</t>
+          <t>204.5</t>
         </is>
       </c>
       <c r="AM18" t="n">
-        <v>198.92</v>
+        <v>199.48</v>
       </c>
       <c r="AN18" t="n">
-        <v>193.33</v>
+        <v>193.8</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>191.14</t>
+          <t>191.47</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>24.29</t>
+          <t>34.99</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>2.85</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>2.52</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -7970,7 +7970,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-77.07</t>
+          <t>-74.87</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7980,48 +7980,48 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>28307.18473609129</t>
+          <t>28292.75427350427</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>26279.0</t>
+          <t>22122.0</t>
         </is>
       </c>
       <c r="AX18" t="n">
-        <v>21604.4</v>
+        <v>20551.2</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>18148.2</t>
+          <t>18187.0</t>
         </is>
       </c>
       <c r="AZ18" t="n">
-        <v>11512</v>
+        <v>11819.44</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>3456</t>
+          <t>2364</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>1090.028654275838</t>
+          <t>1229.675320671625</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>2039.741068992971</t>
+          <t>1997.731985848452</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>26279.0</t>
+          <t>22122.0</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
-          <t>2025-11-29</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="BF18" t="inlineStr">
@@ -8036,7 +8036,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>7.81</t>
+          <t>9.64</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -8061,7 +8061,7 @@
       </c>
       <c r="BM18" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="BN18" t="inlineStr">
@@ -8086,17 +8086,17 @@
       </c>
       <c r="BR18" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
         <is>
-          <t>4.63</t>
+          <t>4.67</t>
         </is>
       </c>
       <c r="BU18" t="inlineStr">
@@ -8106,7 +8106,7 @@
       </c>
       <c r="BV18" t="inlineStr">
         <is>
-          <t>12.87</t>
+          <t>12.75</t>
         </is>
       </c>
       <c r="BW18" t="inlineStr">
@@ -8121,12 +8121,12 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>49.44</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>10248</t>
+          <t>10153</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -8146,22 +8146,22 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>203.5</t>
+          <t>208.5</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
+          <t>211.0</t>
+        </is>
+      </c>
+      <c r="CF18" t="inlineStr">
+        <is>
           <t>208.0</t>
         </is>
       </c>
-      <c r="CF18" t="inlineStr">
-        <is>
-          <t>202.0</t>
-        </is>
-      </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>207.0</t>
+          <t>210.5</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>112.0</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8208,7 +8208,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>204.5</t>
+          <t>207.0</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8218,17 +8218,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>5.1</t>
+          <t>3.04</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-1.06</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>40.09</t>
+          <t>19.04</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8248,7 +8248,7 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>2025-11-29 00:00:00</t>
+          <t>2025-12-02 00:00:00</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
@@ -8288,7 +8288,7 @@
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>2.73</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">
@@ -8303,17 +8303,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>26.35</t>
+          <t>30.12</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8324,12 +8324,12 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>56</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
@@ -8339,58 +8339,58 @@
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>64.29</t>
+          <t>85.71</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>2.93</t>
+          <t>2.89</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>202.1</t>
+          <t>203.2</t>
         </is>
       </c>
       <c r="AM19" t="n">
-        <v>198.58</v>
+        <v>198.92</v>
       </c>
       <c r="AN19" t="n">
-        <v>192.93</v>
+        <v>193.33</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>190.87</t>
+          <t>191.14</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>14.78</t>
+          <t>24.29</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>2.48</t>
+          <t>2.85</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8400,7 +8400,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-78.46</t>
+          <t>-77.07</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8410,48 +8410,48 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>28307.18473609129</t>
+          <t>28292.75427350427</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>22703.0</t>
+          <t>26279.0</t>
         </is>
       </c>
       <c r="AX19" t="n">
-        <v>23070.4</v>
+        <v>21604.4</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>16467.7</t>
+          <t>18148.2</t>
         </is>
       </c>
       <c r="AZ19" t="n">
-        <v>11056.48</v>
+        <v>11512</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>6602</t>
+          <t>3456</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>917.3536697818137</t>
+          <t>1090.028654275838</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>1581.513292449679</t>
+          <t>2039.741068992971</t>
         </is>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
-          <t>22703.0</t>
+          <t>26279.0</t>
         </is>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
-          <t>2025-11-29</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="BF19" t="inlineStr">
@@ -8466,7 +8466,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>6.51</t>
+          <t>7.81</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -8491,7 +8491,7 @@
       </c>
       <c r="BM19" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="BN19" t="inlineStr">
@@ -8511,22 +8511,22 @@
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
         <is>
-          <t>4.63</t>
+          <t>4.67</t>
         </is>
       </c>
       <c r="BU19" t="inlineStr">
@@ -8536,7 +8536,7 @@
       </c>
       <c r="BV19" t="inlineStr">
         <is>
-          <t>12.87</t>
+          <t>12.75</t>
         </is>
       </c>
       <c r="BW19" t="inlineStr">
@@ -8551,12 +8551,12 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>49.44</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>10248</t>
+          <t>10153</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -8576,22 +8576,22 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
+          <t>203.5</t>
+        </is>
+      </c>
+      <c r="CE19" t="inlineStr">
+        <is>
+          <t>208.0</t>
+        </is>
+      </c>
+      <c r="CF19" t="inlineStr">
+        <is>
           <t>202.0</t>
         </is>
       </c>
-      <c r="CE19" t="inlineStr">
-        <is>
-          <t>205.0</t>
-        </is>
-      </c>
-      <c r="CF19" t="inlineStr">
-        <is>
-          <t>202.0</t>
-        </is>
-      </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>204.5</t>
+          <t>207.0</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8623,12 +8623,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>112.0</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8638,7 +8638,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>201.0</t>
+          <t>204.5</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8648,17 +8648,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>6.73</t>
+          <t>4.22</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-1.06</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>28.98</t>
+          <t>40.09</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8678,7 +8678,7 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>2025-11-29 00:00:00</t>
+          <t>2025-12-02 00:00:00</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
@@ -8718,7 +8718,7 @@
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
@@ -8733,17 +8733,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11.76</t>
+          <t>26.35</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8754,17 +8754,17 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>56</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>57.14</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
@@ -8774,53 +8774,53 @@
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>2.94</t>
+          <t>2.93</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>200.6</t>
+          <t>202.1</t>
         </is>
       </c>
       <c r="AM20" t="n">
-        <v>198.25</v>
+        <v>198.58</v>
       </c>
       <c r="AN20" t="n">
-        <v>192.58</v>
+        <v>192.93</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>190.62</t>
+          <t>190.87</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>6.46</t>
+          <t>14.78</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>2.21</t>
+          <t>2.48</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>2.16</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-79.25</t>
+          <t>-78.46</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8840,48 +8840,48 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>28307.18473609129</t>
+          <t>28292.75427350427</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>10051.0</t>
+          <t>22703.0</t>
         </is>
       </c>
       <c r="AX20" t="n">
-        <v>19272.8</v>
+        <v>23070.4</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>14943.0</t>
+          <t>16467.7</t>
         </is>
       </c>
       <c r="AZ20" t="n">
-        <v>10672.76</v>
+        <v>11056.48</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>4329</t>
+          <t>6602</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>796.5973747512926</t>
+          <t>917.3536697818137</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>1253.562422657489</t>
+          <t>1581.513292449679</t>
         </is>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
-          <t>10051.0</t>
+          <t>22703.0</t>
         </is>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
-          <t>2025-11-29</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="BF20" t="inlineStr">
@@ -8896,7 +8896,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>4.69</t>
+          <t>6.51</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -8921,7 +8921,7 @@
       </c>
       <c r="BM20" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="BN20" t="inlineStr">
@@ -8941,22 +8941,22 @@
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
         <is>
-          <t>4.63</t>
+          <t>4.67</t>
         </is>
       </c>
       <c r="BU20" t="inlineStr">
@@ -8966,7 +8966,7 @@
       </c>
       <c r="BV20" t="inlineStr">
         <is>
-          <t>12.87</t>
+          <t>12.75</t>
         </is>
       </c>
       <c r="BW20" t="inlineStr">
@@ -8981,12 +8981,12 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>49.44</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>10248</t>
+          <t>10153</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
@@ -9006,22 +9006,22 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>199.5</t>
+          <t>202.0</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
+          <t>205.0</t>
+        </is>
+      </c>
+      <c r="CF20" t="inlineStr">
+        <is>
           <t>202.0</t>
         </is>
       </c>
-      <c r="CF20" t="inlineStr">
-        <is>
-          <t>198.5</t>
-        </is>
-      </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>201.0</t>
+          <t>204.5</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -9053,12 +9053,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-2.2</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>107.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9068,7 +9068,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>199.5</t>
+          <t>201.0</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9078,17 +9078,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>7.42</t>
+          <t>5.85</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-1.06</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>17.59</t>
+          <t>28.98</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9108,7 +9108,7 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>2025-11-29 00:00:00</t>
+          <t>2025-12-02 00:00:00</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
@@ -9148,7 +9148,7 @@
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
@@ -9163,17 +9163,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>25.18</t>
+          <t>11.76</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>-2.00</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9184,73 +9184,73 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>56</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>35.71</t>
+          <t>57.14</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>78.57</t>
+          <t>64.29</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>2.96</t>
+          <t>2.94</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>200.0</t>
+          <t>200.6</t>
         </is>
       </c>
       <c r="AM21" t="n">
-        <v>197.98</v>
+        <v>198.25</v>
       </c>
       <c r="AN21" t="n">
-        <v>192.28</v>
+        <v>192.58</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>190.44</t>
+          <t>190.62</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>7.56</t>
+          <t>6.46</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>2.21</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9260,7 +9260,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-79.59</t>
+          <t>-79.25</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9270,48 +9270,48 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>28307.18473609129</t>
+          <t>28292.75427350427</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>21601.0</t>
+          <t>10051.0</t>
         </is>
       </c>
       <c r="AX21" t="n">
-        <v>18457.8</v>
+        <v>19272.8</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>15697.4</t>
+          <t>14943.0</t>
         </is>
       </c>
       <c r="AZ21" t="n">
-        <v>10622.98</v>
+        <v>10672.76</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>2760</t>
+          <t>4329</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>713.5128205865296</t>
+          <t>796.5973747512926</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>2095.862522145168</t>
+          <t>1253.562422657489</t>
         </is>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
-          <t>21601.0</t>
+          <t>10051.0</t>
         </is>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
-          <t>2025-11-29</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="BF21" t="inlineStr">
@@ -9326,7 +9326,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>3.91</t>
+          <t>4.69</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
@@ -9351,7 +9351,7 @@
       </c>
       <c r="BM21" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="BN21" t="inlineStr">
@@ -9371,7 +9371,7 @@
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
@@ -9381,12 +9381,12 @@
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>1.89</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
         <is>
-          <t>4.63</t>
+          <t>4.67</t>
         </is>
       </c>
       <c r="BU21" t="inlineStr">
@@ -9396,7 +9396,7 @@
       </c>
       <c r="BV21" t="inlineStr">
         <is>
-          <t>12.87</t>
+          <t>12.75</t>
         </is>
       </c>
       <c r="BW21" t="inlineStr">
@@ -9411,12 +9411,12 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>49.44</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>10248</t>
+          <t>10153</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
@@ -9436,22 +9436,22 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>205.0</t>
+          <t>199.5</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>205.0</t>
+          <t>202.0</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>198.0</t>
+          <t>198.5</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>199.5</t>
+          <t>201.0</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -9483,12 +9483,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>-2.2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>107.0</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9498,7 +9498,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>204.0</t>
+          <t>199.5</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9508,17 +9508,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>5.34</t>
+          <t>6.56</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-1.06</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>9.50</t>
+          <t>17.59</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9538,7 +9538,7 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>2025-11-29 00:00:00</t>
+          <t>2025-12-02 00:00:00</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
@@ -9578,7 +9578,7 @@
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="W22" t="inlineStr">
@@ -9593,17 +9593,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>31.53</t>
+          <t>25.18</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>-2.00</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9614,32 +9614,32 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>56</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>35.71</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>82.05</t>
+          <t>78.57</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
@@ -9649,239 +9649,239 @@
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
+          <t>200.0</t>
+        </is>
+      </c>
+      <c r="AM22" t="n">
+        <v>197.98</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>192.28</v>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>190.44</t>
+        </is>
+      </c>
+      <c r="AP22" t="inlineStr">
+        <is>
+          <t>7.56</t>
+        </is>
+      </c>
+      <c r="AQ22" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="AR22" t="inlineStr">
+        <is>
+          <t>2.04</t>
+        </is>
+      </c>
+      <c r="AS22" t="inlineStr">
+        <is>
+          <t>10.01</t>
+        </is>
+      </c>
+      <c r="AT22" t="inlineStr">
+        <is>
+          <t>-79.59</t>
+        </is>
+      </c>
+      <c r="AU22" t="inlineStr">
+        <is>
+          <t>2025/11/14</t>
+        </is>
+      </c>
+      <c r="AV22" t="inlineStr">
+        <is>
+          <t>28292.75427350427</t>
+        </is>
+      </c>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>21601.0</t>
+        </is>
+      </c>
+      <c r="AX22" t="n">
+        <v>18457.8</v>
+      </c>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>15697.4</t>
+        </is>
+      </c>
+      <c r="AZ22" t="n">
+        <v>10622.98</v>
+      </c>
+      <c r="BA22" t="inlineStr">
+        <is>
+          <t>2760</t>
+        </is>
+      </c>
+      <c r="BB22" t="inlineStr">
+        <is>
+          <t>713.5128205865296</t>
+        </is>
+      </c>
+      <c r="BC22" t="inlineStr">
+        <is>
+          <t>2095.862522145168</t>
+        </is>
+      </c>
+      <c r="BD22" t="inlineStr">
+        <is>
+          <t>21601.0</t>
+        </is>
+      </c>
+      <c r="BE22" t="inlineStr">
+        <is>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="BF22" t="inlineStr">
+        <is>
+          <t>192.0</t>
+        </is>
+      </c>
+      <c r="BG22" t="inlineStr">
+        <is>
+          <t>2025/10/14</t>
+        </is>
+      </c>
+      <c r="BH22" t="inlineStr">
+        <is>
+          <t>3.91</t>
+        </is>
+      </c>
+      <c r="BI22" t="inlineStr">
+        <is>
+          <t>鼎翰</t>
+        </is>
+      </c>
+      <c r="BJ22" t="inlineStr">
+        <is>
+          <t>鼎翰</t>
+        </is>
+      </c>
+      <c r="BK22" t="inlineStr">
+        <is>
+          <t>電腦及週邊設備業</t>
+        </is>
+      </c>
+      <c r="BL22" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BM22" t="inlineStr">
+        <is>
+          <t>0.57</t>
+        </is>
+      </c>
+      <c r="BN22" t="inlineStr">
+        <is>
+          <t>-11.45161899724185</t>
+        </is>
+      </c>
+      <c r="BO22" t="inlineStr">
+        <is>
+          <t>22.56717409239306</t>
+        </is>
+      </c>
+      <c r="BP22" t="inlineStr">
+        <is>
+          <t>38.82556207928187</t>
+        </is>
+      </c>
+      <c r="BQ22" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR22" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS22" t="inlineStr">
+        <is>
+          <t>1.89</t>
+        </is>
+      </c>
+      <c r="BT22" t="inlineStr">
+        <is>
+          <t>4.67</t>
+        </is>
+      </c>
+      <c r="BU22" t="inlineStr">
+        <is>
+          <t>57.78</t>
+        </is>
+      </c>
+      <c r="BV22" t="inlineStr">
+        <is>
+          <t>12.75</t>
+        </is>
+      </c>
+      <c r="BW22" t="inlineStr">
+        <is>
+          <t>33.69%</t>
+        </is>
+      </c>
+      <c r="BX22" t="inlineStr">
+        <is>
+          <t>11.08%</t>
+        </is>
+      </c>
+      <c r="BY22" t="inlineStr">
+        <is>
+          <t>49.44</t>
+        </is>
+      </c>
+      <c r="BZ22" t="inlineStr">
+        <is>
+          <t>10153</t>
+        </is>
+      </c>
+      <c r="CA22" t="inlineStr">
+        <is>
+          <t>條碼印表機及零配件52.71%、印表機各式標籤紙及其耗材41.09%、企業行動電腦6.20% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB22" t="inlineStr">
+        <is>
+          <t>鼎翰-電腦及週邊設備業-上櫃</t>
+        </is>
+      </c>
+      <c r="CC22" t="inlineStr">
+        <is>
+          <t>電腦及週邊設備業平上櫃</t>
+        </is>
+      </c>
+      <c r="CD22" t="inlineStr">
+        <is>
+          <t>205.0</t>
+        </is>
+      </c>
+      <c r="CE22" t="inlineStr">
+        <is>
+          <t>205.0</t>
+        </is>
+      </c>
+      <c r="CF22" t="inlineStr">
+        <is>
+          <t>198.0</t>
+        </is>
+      </c>
+      <c r="CG22" t="inlineStr">
+        <is>
           <t>199.5</t>
-        </is>
-      </c>
-      <c r="AM22" t="n">
-        <v>197.7</v>
-      </c>
-      <c r="AN22" t="n">
-        <v>192.01</v>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>190.29</t>
-        </is>
-      </c>
-      <c r="AP22" t="inlineStr">
-        <is>
-          <t>14.82</t>
-        </is>
-      </c>
-      <c r="AQ22" t="inlineStr">
-        <is>
-          <t>2.30</t>
-        </is>
-      </c>
-      <c r="AR22" t="inlineStr">
-        <is>
-          <t>2.01</t>
-        </is>
-      </c>
-      <c r="AS22" t="inlineStr">
-        <is>
-          <t>10.01</t>
-        </is>
-      </c>
-      <c r="AT22" t="inlineStr">
-        <is>
-          <t>-79.98</t>
-        </is>
-      </c>
-      <c r="AU22" t="inlineStr">
-        <is>
-          <t>2025/11/14</t>
-        </is>
-      </c>
-      <c r="AV22" t="inlineStr">
-        <is>
-          <t>28307.18473609129</t>
-        </is>
-      </c>
-      <c r="AW22" t="inlineStr">
-        <is>
-          <t>27388.0</t>
-        </is>
-      </c>
-      <c r="AX22" t="n">
-        <v>15822.8</v>
-      </c>
-      <c r="AY22" t="inlineStr">
-        <is>
-          <t>14450.7</t>
-        </is>
-      </c>
-      <c r="AZ22" t="n">
-        <v>10277.46</v>
-      </c>
-      <c r="BA22" t="inlineStr">
-        <is>
-          <t>1372</t>
-        </is>
-      </c>
-      <c r="BB22" t="inlineStr">
-        <is>
-          <t>462.1765112122318</t>
-        </is>
-      </c>
-      <c r="BC22" t="inlineStr">
-        <is>
-          <t>1986.79614562238</t>
-        </is>
-      </c>
-      <c r="BD22" t="inlineStr">
-        <is>
-          <t>27388.0</t>
-        </is>
-      </c>
-      <c r="BE22" t="inlineStr">
-        <is>
-          <t>2025-11-29</t>
-        </is>
-      </c>
-      <c r="BF22" t="inlineStr">
-        <is>
-          <t>192.0</t>
-        </is>
-      </c>
-      <c r="BG22" t="inlineStr">
-        <is>
-          <t>2025/10/14</t>
-        </is>
-      </c>
-      <c r="BH22" t="inlineStr">
-        <is>
-          <t>6.25</t>
-        </is>
-      </c>
-      <c r="BI22" t="inlineStr">
-        <is>
-          <t>鼎翰</t>
-        </is>
-      </c>
-      <c r="BJ22" t="inlineStr">
-        <is>
-          <t>鼎翰</t>
-        </is>
-      </c>
-      <c r="BK22" t="inlineStr">
-        <is>
-          <t>電腦及週邊設備業</t>
-        </is>
-      </c>
-      <c r="BL22" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BM22" t="inlineStr">
-        <is>
-          <t>0.56</t>
-        </is>
-      </c>
-      <c r="BN22" t="inlineStr">
-        <is>
-          <t>-11.45161899724185</t>
-        </is>
-      </c>
-      <c r="BO22" t="inlineStr">
-        <is>
-          <t>22.56717409239306</t>
-        </is>
-      </c>
-      <c r="BP22" t="inlineStr">
-        <is>
-          <t>38.82556207928187</t>
-        </is>
-      </c>
-      <c r="BQ22" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR22" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BS22" t="inlineStr">
-        <is>
-          <t>1.93</t>
-        </is>
-      </c>
-      <c r="BT22" t="inlineStr">
-        <is>
-          <t>4.63</t>
-        </is>
-      </c>
-      <c r="BU22" t="inlineStr">
-        <is>
-          <t>57.78</t>
-        </is>
-      </c>
-      <c r="BV22" t="inlineStr">
-        <is>
-          <t>12.87</t>
-        </is>
-      </c>
-      <c r="BW22" t="inlineStr">
-        <is>
-          <t>33.69%</t>
-        </is>
-      </c>
-      <c r="BX22" t="inlineStr">
-        <is>
-          <t>11.08%</t>
-        </is>
-      </c>
-      <c r="BY22" t="inlineStr">
-        <is>
-          <t>49.8</t>
-        </is>
-      </c>
-      <c r="BZ22" t="inlineStr">
-        <is>
-          <t>10248</t>
-        </is>
-      </c>
-      <c r="CA22" t="inlineStr">
-        <is>
-          <t>條碼印表機及零配件52.71%、印表機各式標籤紙及其耗材41.09%、企業行動電腦6.20% (2024年)</t>
-        </is>
-      </c>
-      <c r="CB22" t="inlineStr">
-        <is>
-          <t>鼎翰-電腦及週邊設備業-上櫃</t>
-        </is>
-      </c>
-      <c r="CC22" t="inlineStr">
-        <is>
-          <t>電腦及週邊設備業平上櫃</t>
-        </is>
-      </c>
-      <c r="CD22" t="inlineStr">
-        <is>
-          <t>201.5</t>
-        </is>
-      </c>
-      <c r="CE22" t="inlineStr">
-        <is>
-          <t>206.5</t>
-        </is>
-      </c>
-      <c r="CF22" t="inlineStr">
-        <is>
-          <t>201.5</t>
-        </is>
-      </c>
-      <c r="CG22" t="inlineStr">
-        <is>
-          <t>204.0</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -9913,12 +9913,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>167.0</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9928,74 +9928,74 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
+          <t>204.0</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>4.45</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>-0.78</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>9.50</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>2025-11-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>2025-12-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>2025-10-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>2025-11-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
           <t>201.5</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>6.5</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>-1.06</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>21.03</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>2025-11-14</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>2025-11-14 00:00:00</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>2025-11-29 00:00:00</t>
-        </is>
-      </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>2025-10-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>2025-11-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q23" t="inlineStr">
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
         <is>
           <t>201.5</t>
         </is>
       </c>
-      <c r="R23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S23" t="inlineStr">
-        <is>
-          <t>201.5</t>
-        </is>
-      </c>
       <c r="T23" t="inlineStr">
         <is>
           <t>195.5</t>
@@ -10008,7 +10008,7 @@
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="W23" t="inlineStr">
@@ -10023,17 +10023,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>39.29</t>
+          <t>31.53</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10044,12 +10044,12 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>56</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
@@ -10059,194 +10059,194 @@
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>69.23</t>
+          <t>82.05</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>2.87</t>
+          <t>2.96</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>198.8</t>
+          <t>199.5</t>
         </is>
       </c>
       <c r="AM23" t="n">
-        <v>197.15</v>
+        <v>197.7</v>
       </c>
       <c r="AN23" t="n">
-        <v>191.65</v>
+        <v>192.01</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>190.08</t>
+          <t>190.29</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>14.82</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
+          <t>2.01</t>
+        </is>
+      </c>
+      <c r="AS23" t="inlineStr">
+        <is>
+          <t>10.01</t>
+        </is>
+      </c>
+      <c r="AT23" t="inlineStr">
+        <is>
+          <t>-79.98</t>
+        </is>
+      </c>
+      <c r="AU23" t="inlineStr">
+        <is>
+          <t>2025/11/14</t>
+        </is>
+      </c>
+      <c r="AV23" t="inlineStr">
+        <is>
+          <t>28292.75427350427</t>
+        </is>
+      </c>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>27388.0</t>
+        </is>
+      </c>
+      <c r="AX23" t="n">
+        <v>15822.8</v>
+      </c>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>14450.7</t>
+        </is>
+      </c>
+      <c r="AZ23" t="n">
+        <v>10277.46</v>
+      </c>
+      <c r="BA23" t="inlineStr">
+        <is>
+          <t>1372</t>
+        </is>
+      </c>
+      <c r="BB23" t="inlineStr">
+        <is>
+          <t>462.1765112122318</t>
+        </is>
+      </c>
+      <c r="BC23" t="inlineStr">
+        <is>
+          <t>1986.79614562238</t>
+        </is>
+      </c>
+      <c r="BD23" t="inlineStr">
+        <is>
+          <t>27388.0</t>
+        </is>
+      </c>
+      <c r="BE23" t="inlineStr">
+        <is>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="BF23" t="inlineStr">
+        <is>
+          <t>192.0</t>
+        </is>
+      </c>
+      <c r="BG23" t="inlineStr">
+        <is>
+          <t>2025/10/14</t>
+        </is>
+      </c>
+      <c r="BH23" t="inlineStr">
+        <is>
+          <t>6.25</t>
+        </is>
+      </c>
+      <c r="BI23" t="inlineStr">
+        <is>
+          <t>鼎翰</t>
+        </is>
+      </c>
+      <c r="BJ23" t="inlineStr">
+        <is>
+          <t>鼎翰</t>
+        </is>
+      </c>
+      <c r="BK23" t="inlineStr">
+        <is>
+          <t>電腦及週邊設備業</t>
+        </is>
+      </c>
+      <c r="BL23" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BM23" t="inlineStr">
+        <is>
+          <t>0.57</t>
+        </is>
+      </c>
+      <c r="BN23" t="inlineStr">
+        <is>
+          <t>-11.45161899724185</t>
+        </is>
+      </c>
+      <c r="BO23" t="inlineStr">
+        <is>
+          <t>22.56717409239306</t>
+        </is>
+      </c>
+      <c r="BP23" t="inlineStr">
+        <is>
+          <t>38.82556207928187</t>
+        </is>
+      </c>
+      <c r="BQ23" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR23" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS23" t="inlineStr">
+        <is>
           <t>1.93</t>
         </is>
       </c>
-      <c r="AS23" t="inlineStr">
-        <is>
-          <t>10.01</t>
-        </is>
-      </c>
-      <c r="AT23" t="inlineStr">
-        <is>
-          <t>-80.72</t>
-        </is>
-      </c>
-      <c r="AU23" t="inlineStr">
-        <is>
-          <t>2025/11/14</t>
-        </is>
-      </c>
-      <c r="AV23" t="inlineStr">
-        <is>
-          <t>28307.18473609129</t>
-        </is>
-      </c>
-      <c r="AW23" t="inlineStr">
-        <is>
-          <t>33609.0</t>
-        </is>
-      </c>
-      <c r="AX23" t="n">
-        <v>14692</v>
-      </c>
-      <c r="AY23" t="inlineStr">
-        <is>
-          <t>12138.8</t>
-        </is>
-      </c>
-      <c r="AZ23" t="n">
-        <v>9836.780000000001</v>
-      </c>
-      <c r="BA23" t="inlineStr">
-        <is>
-          <t>2553</t>
-        </is>
-      </c>
-      <c r="BB23" t="inlineStr">
-        <is>
-          <t>184.9729413194776</t>
-        </is>
-      </c>
-      <c r="BC23" t="inlineStr">
-        <is>
-          <t>1139.994316817598</t>
-        </is>
-      </c>
-      <c r="BD23" t="inlineStr">
-        <is>
-          <t>33609.0</t>
-        </is>
-      </c>
-      <c r="BE23" t="inlineStr">
-        <is>
-          <t>2025-11-29</t>
-        </is>
-      </c>
-      <c r="BF23" t="inlineStr">
-        <is>
-          <t>192.0</t>
-        </is>
-      </c>
-      <c r="BG23" t="inlineStr">
-        <is>
-          <t>2025/10/14</t>
-        </is>
-      </c>
-      <c r="BH23" t="inlineStr">
-        <is>
-          <t>4.95</t>
-        </is>
-      </c>
-      <c r="BI23" t="inlineStr">
-        <is>
-          <t>鼎翰</t>
-        </is>
-      </c>
-      <c r="BJ23" t="inlineStr">
-        <is>
-          <t>鼎翰</t>
-        </is>
-      </c>
-      <c r="BK23" t="inlineStr">
-        <is>
-          <t>電腦及週邊設備業</t>
-        </is>
-      </c>
-      <c r="BL23" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BM23" t="inlineStr">
-        <is>
-          <t>0.56</t>
-        </is>
-      </c>
-      <c r="BN23" t="inlineStr">
-        <is>
-          <t>-11.45161899724185</t>
-        </is>
-      </c>
-      <c r="BO23" t="inlineStr">
-        <is>
-          <t>22.56717409239306</t>
-        </is>
-      </c>
-      <c r="BP23" t="inlineStr">
-        <is>
-          <t>38.82556207928187</t>
-        </is>
-      </c>
-      <c r="BQ23" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR23" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BS23" t="inlineStr">
-        <is>
-          <t>1.91</t>
-        </is>
-      </c>
       <c r="BT23" t="inlineStr">
         <is>
-          <t>4.63</t>
+          <t>4.67</t>
         </is>
       </c>
       <c r="BU23" t="inlineStr">
@@ -10256,7 +10256,7 @@
       </c>
       <c r="BV23" t="inlineStr">
         <is>
-          <t>12.87</t>
+          <t>12.75</t>
         </is>
       </c>
       <c r="BW23" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>49.44</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>10248</t>
+          <t>10153</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
@@ -10296,22 +10296,22 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>199.0</t>
+          <t>201.5</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>202.5</t>
+          <t>206.5</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>198.5</t>
+          <t>201.5</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>201.5</t>
+          <t>204.0</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">

--- a/Result/checksun_type/HMI.xlsx
+++ b/Result/checksun_type/HMI.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>16.0</t>
+          <t>29.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>20.3</t>
+          <t>20.25</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>-1.3</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-38.48</t>
+          <t>-5.42</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-7.09</t>
+          <t>-7.32</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-1.44</t>
+          <t>-1.23</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,73 +1014,73 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>95.45</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>88.89</t>
+          <t>98.48</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-6.4</t>
+          <t>-6.38</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-3.70</t>
+          <t>-3.59</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>19.86</t>
+          <t>20.01</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>20.02</v>
+        <v>20</v>
       </c>
       <c r="AN2" t="n">
-        <v>21.39</v>
+        <v>21.36</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>22.21</t>
+          <t>22.15</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>18.96</t>
+          <t>25.28</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-0.47</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-0.55</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-108.84</t>
+          <t>-108.32</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1100,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>30249.05982905983</t>
+          <t>30207.30512091039</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>332.0</t>
+          <t>597.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>357.2</v>
+        <v>443.4</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>580.6</t>
+          <t>468.8</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>1257.56</v>
+        <v>1250.78</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-223</t>
+          <t>-25</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-138.6446294685659</t>
+          <t>-133.7751109659018</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-130.5370215885447</t>
+          <t>-106.9927592012491</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>332.0</t>
+          <t>597.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-14.16</t>
+          <t>-14.38</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1201,7 +1201,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>88.59</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>592</t>
+          <t>591</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,22 +1266,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>20.5</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>21.0</t>
+          <t>20.5</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>20.25</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>20.3</t>
+          <t>20.25</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>22.0</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>20.3</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>-1.3</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-45.47</t>
+          <t>-38.48</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-8.92</t>
+          <t>-7.09</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-1.01</t>
+          <t>-1.44</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,12 +1444,12 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
@@ -1459,58 +1459,58 @@
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>73.5</t>
+          <t>88.89</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-2.17</t>
+          <t>-0.79</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-6.24</t>
+          <t>-6.4</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-3.82</t>
+          <t>-3.70</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>19.64</t>
+          <t>19.86</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>20.08</v>
+        <v>20.02</v>
       </c>
       <c r="AN3" t="n">
-        <v>21.41</v>
+        <v>21.39</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>22.26</t>
+          <t>22.21</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>9.79</t>
+          <t>18.96</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>-0.47</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-109.26</t>
+          <t>-108.84</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1530,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>30249.05982905983</t>
+          <t>30207.30512091039</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>445.0</t>
+          <t>332.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>348.8</v>
+        <v>357.2</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>639.6</t>
+          <t>580.6</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>1276.44</v>
+        <v>1257.56</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-290</t>
+          <t>-223</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-140.1187399922061</t>
+          <t>-138.6446294685659</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-131.1167885136618</t>
+          <t>-130.5370215885447</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>445.0</t>
+          <t>332.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-15.86</t>
+          <t>-14.16</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>88.59</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>592</t>
+          <t>591</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1701,7 +1701,7 @@
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>20.1</t>
+          <t>21.0</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>20.3</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>22.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>19.75</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2.71</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>-1.3</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-17.60</t>
+          <t>-45.47</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-9.61</t>
+          <t>-8.92</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-2.53</t>
+          <t>-1.01</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,73 +1874,73 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>49.15</t>
+          <t>73.5</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-3.26</t>
+          <t>-2.17</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-5.98</t>
+          <t>-6.24</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-3.92</t>
+          <t>-3.82</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>19.5</t>
+          <t>19.64</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>20.16</v>
+        <v>20.08</v>
       </c>
       <c r="AN4" t="n">
-        <v>21.44</v>
+        <v>21.41</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>22.31</t>
+          <t>22.26</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>3.76</t>
+          <t>9.79</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-0.60</t>
+          <t>-0.55</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.63</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-109.49</t>
+          <t>-109.26</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1960,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>30249.05982905983</t>
+          <t>30207.30512091039</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>397.0</t>
+          <t>445.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>517.2</v>
+        <v>348.8</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>627.7</t>
+          <t>639.6</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>1309.6</v>
+        <v>1276.44</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-110</t>
+          <t>-290</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-141.7554584428505</t>
+          <t>-140.1187399922061</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-139.3694273883414</t>
+          <t>-131.1167885136618</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>397.0</t>
+          <t>445.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-16.49</t>
+          <t>-15.86</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>88.59</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>592</t>
+          <t>591</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,22 +2126,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>20.3</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>20.3</t>
+          <t>20.1</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>19.7</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>19.75</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2163,7 +2163,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>22.0</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>19.85</t>
+          <t>19.75</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>-1.3</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-25.82</t>
+          <t>-17.60</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-9.15</t>
+          <t>-9.61</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>-2.53</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,37 +2304,37 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>53.85</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>28.0</t>
+          <t>49.15</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-4.02</t>
+          <t>-3.26</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-5.68</t>
+          <t>-5.98</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -2344,28 +2344,28 @@
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>19.45</t>
+          <t>19.5</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>20.26</v>
+        <v>20.16</v>
       </c>
       <c r="AN5" t="n">
-        <v>21.48</v>
+        <v>21.44</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>22.36</t>
+          <t>22.31</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-1.89</t>
+          <t>3.76</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>-0.60</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-109.58</t>
+          <t>-109.49</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>30249.05982905983</t>
+          <t>30207.30512091039</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>446.0</t>
+          <t>397.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>537.2</v>
+        <v>517.2</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>724.2</t>
+          <t>627.7</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>1332.24</v>
+        <v>1309.6</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-187</t>
+          <t>-110</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-142.1892822709431</t>
+          <t>-141.7554584428505</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-141.0385748025855</t>
+          <t>-139.3694273883414</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>446.0</t>
+          <t>397.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-16.07</t>
+          <t>-16.49</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2491,17 +2491,17 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>88.59</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>592</t>
+          <t>591</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,22 +2556,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>19.45</t>
+          <t>20.3</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>20.05</t>
+          <t>20.3</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>19.45</t>
+          <t>19.7</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>19.85</t>
+          <t>19.75</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>9.0</t>
+          <t>22.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>19.5</t>
+          <t>19.85</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>3.94</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>-1.3</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-34.48</t>
+          <t>-25.82</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-10.76</t>
+          <t>-9.15</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,68 +2734,68 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>26.92</t>
+          <t>53.85</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>11.12</t>
+          <t>28.0</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>2.06</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-5.18</t>
+          <t>-4.02</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-5.44</t>
+          <t>-5.68</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-3.78</t>
+          <t>-3.92</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>19.31</t>
+          <t>19.45</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>20.36</v>
+        <v>20.26</v>
       </c>
       <c r="AN6" t="n">
-        <v>21.54</v>
+        <v>21.48</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>22.38</t>
+          <t>22.36</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-10.91</t>
+          <t>-1.89</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.70</t>
+          <t>-0.64</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-109.53</t>
+          <t>-109.58</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>30249.05982905983</t>
+          <t>30207.30512091039</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>166.0</t>
+          <t>446.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>494.2</v>
+        <v>537.2</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>754.3</t>
+          <t>724.2</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>1394.4</v>
+        <v>1332.24</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-260</t>
+          <t>-187</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-142.3985018106445</t>
+          <t>-142.1892822709431</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-143.6359791514134</t>
+          <t>-141.0385748025855</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>166.0</t>
+          <t>446.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-17.55</t>
+          <t>-16.07</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2921,17 +2921,17 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>88.59</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>592</t>
+          <t>591</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>19.3</t>
+          <t>19.45</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>19.5</t>
+          <t>20.05</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>19.3</t>
+          <t>19.45</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>19.5</t>
+          <t>19.85</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>19.2</t>
+          <t>19.5</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>5.42</t>
+          <t>3.7</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>-1.3</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-2.21</t>
+          <t>-34.48</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-12.13</t>
+          <t>-10.76</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,54 +3164,54 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>3.23</t>
+          <t>26.92</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>9.68</t>
+          <t>11.12</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-6.04</t>
+          <t>-5.18</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-5.2</t>
+          <t>-5.44</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-3.45</t>
+          <t>-3.78</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>19.25</t>
+          <t>19.31</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>20.49</v>
+        <v>20.36</v>
       </c>
       <c r="AN7" t="n">
-        <v>21.61</v>
+        <v>21.54</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
@@ -3220,17 +3220,17 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-17.72</t>
+          <t>-10.91</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>-0.70</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-0.63</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-109.27</t>
+          <t>-109.53</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>30249.05982905983</t>
+          <t>30207.30512091039</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>290.0</t>
+          <t>166.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>804</v>
+        <v>494.2</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>822.2</t>
+          <t>754.3</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>1439.06</v>
+        <v>1394.4</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-18</t>
+          <t>-260</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-142.1735059305047</t>
+          <t>-142.3985018106445</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-112.2167003943315</t>
+          <t>-143.6359791514134</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>290.0</t>
+          <t>166.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-18.82</t>
+          <t>-17.55</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3351,7 +3351,7 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3361,7 +3361,7 @@
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>88.59</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>592</t>
+          <t>591</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,22 +3416,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>19.2</t>
+          <t>19.3</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
+          <t>19.5</t>
+        </is>
+      </c>
+      <c r="CF7" t="inlineStr">
+        <is>
           <t>19.3</t>
         </is>
       </c>
-      <c r="CF7" t="inlineStr">
-        <is>
-          <t>19.2</t>
-        </is>
-      </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>19.2</t>
+          <t>19.5</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-1.53</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>5.42</t>
+          <t>5.19</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>-1.3</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>3.85</t>
+          <t>-2.21</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,12 +3594,12 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
@@ -3609,58 +3609,58 @@
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>9.68</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-1.13</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-5.90</t>
+          <t>-6.04</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-4.83</t>
+          <t>-5.2</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-3.05</t>
+          <t>-3.45</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>19.42</t>
+          <t>19.25</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>20.64</v>
+        <v>20.49</v>
       </c>
       <c r="AN8" t="n">
-        <v>21.68</v>
+        <v>21.61</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>22.37</t>
+          <t>22.38</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-21.10</t>
+          <t>-17.72</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-108.86</t>
+          <t>-109.27</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>30249.05982905983</t>
+          <t>30207.30512091039</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>1287.0</t>
+          <t>290.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>930.4</v>
+        <v>804</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>895.9</t>
+          <t>822.2</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>1833.62</v>
+        <v>1439.06</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>-18</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-147.6201978461726</t>
+          <t>-142.1735059305047</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-76.60999144155971</t>
+          <t>-112.2167003943315</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>1287.0</t>
+          <t>290.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3781,7 +3781,7 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>88.59</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>592</t>
+          <t>591</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,17 +3846,17 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>19.55</t>
+          <t>19.2</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>19.65</t>
+          <t>19.3</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>18.85</t>
+          <t>19.2</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>-1.53</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>26.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>19.5</t>
+          <t>19.2</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>3.94</t>
+          <t>5.19</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>-1.3</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-4.04</t>
+          <t>3.85</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-10.76</t>
+          <t>-12.13</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>3.17</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,73 +4024,73 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>22.58</t>
+          <t>3.23</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>7.53</t>
+          <t>8.6</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>-1.13</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-5.39</t>
+          <t>-5.90</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-4.43</t>
+          <t>-4.83</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-2.68</t>
+          <t>-3.05</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>19.67</t>
+          <t>19.42</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>20.79</v>
+        <v>20.64</v>
       </c>
       <c r="AN9" t="n">
-        <v>21.75</v>
+        <v>21.68</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>22.35</t>
+          <t>22.37</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-23.19</t>
+          <t>-21.10</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.68</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-108.40</t>
+          <t>-108.86</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>30249.05982905983</t>
+          <t>30207.30512091039</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>497.0</t>
+          <t>1287.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>738.2</v>
+        <v>930.4</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>769.3</t>
+          <t>895.9</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>1851.22</v>
+        <v>1833.62</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-31</t>
+          <t>34</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-160.5311444651931</t>
+          <t>-147.6201978461726</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-129.8286218146873</t>
+          <t>-76.60999144155971</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>497.0</t>
+          <t>1287.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-17.55</t>
+          <t>-18.82</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4216,12 +4216,12 @@
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>88.59</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>592</t>
+          <t>591</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,22 +4276,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
+          <t>19.55</t>
+        </is>
+      </c>
+      <c r="CE9" t="inlineStr">
+        <is>
+          <t>19.65</t>
+        </is>
+      </c>
+      <c r="CF9" t="inlineStr">
+        <is>
+          <t>18.85</t>
+        </is>
+      </c>
+      <c r="CG9" t="inlineStr">
+        <is>
           <t>19.2</t>
-        </is>
-      </c>
-      <c r="CE9" t="inlineStr">
-        <is>
-          <t>19.5</t>
-        </is>
-      </c>
-      <c r="CF9" t="inlineStr">
-        <is>
-          <t>18.9</t>
-        </is>
-      </c>
-      <c r="CG9" t="inlineStr">
-        <is>
-          <t>19.5</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>26.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>19.15</t>
+          <t>19.5</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>5.67</t>
+          <t>3.7</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>-1.3</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>14.69</t>
+          <t>-4.04</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-12.36</t>
+          <t>-10.76</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>3.17</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,73 +4454,73 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>22.58</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.53</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-3.58</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-5.17</t>
+          <t>-5.39</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-3.97</t>
+          <t>-4.43</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-2.33</t>
+          <t>-2.68</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>19.86</t>
+          <t>19.67</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>20.94</v>
+        <v>20.79</v>
       </c>
       <c r="AN10" t="n">
-        <v>21.81</v>
+        <v>21.75</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>22.33</t>
+          <t>22.35</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-28.42</t>
+          <t>-23.19</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-0.68</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-0.55</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-107.91</t>
+          <t>-108.40</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>30249.05982905983</t>
+          <t>30207.30512091039</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>231.0</t>
+          <t>497.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>911.2</v>
+        <v>738.2</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>794.5</t>
+          <t>769.3</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>1867.82</v>
+        <v>1851.22</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>116</t>
+          <t>-31</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-166.1134213107396</t>
+          <t>-160.5311444651931</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-116.5756429972018</t>
+          <t>-129.8286218146873</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>231.0</t>
+          <t>497.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-19.03</t>
+          <t>-17.55</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4641,17 +4641,17 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>88.59</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>592</t>
+          <t>591</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>18.85</t>
+          <t>19.2</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>19.15</t>
+          <t>19.5</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>18.85</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>19.15</t>
+          <t>19.5</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-4.24</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>19.2</t>
+          <t>19.15</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4778,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>5.42</t>
+          <t>5.43</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>-1.3</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>21.51</t>
+          <t>14.69</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-12.13</t>
+          <t>-12.36</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>3.15</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-3.37</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,12 +4884,12 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
@@ -4899,58 +4899,58 @@
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>15.38</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-4.81</t>
+          <t>-3.58</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-4.41</t>
+          <t>-5.17</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-3.49</t>
+          <t>-3.97</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-2.01</t>
+          <t>-2.33</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>20.17</t>
+          <t>19.86</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>21.1</v>
+        <v>20.94</v>
       </c>
       <c r="AN11" t="n">
-        <v>21.86</v>
+        <v>21.81</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>22.31</t>
+          <t>22.33</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-25.64</t>
+          <t>-28.42</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-107.35</t>
+          <t>-107.91</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>30249.05982905983</t>
+          <t>30207.30512091039</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>1715.0</t>
+          <t>231.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>1014.4</v>
+        <v>911.2</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>834.8</t>
+          <t>794.5</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>1896.36</v>
+        <v>1867.82</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>179</t>
+          <t>116</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-175.1202900950192</t>
+          <t>-166.1134213107396</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-64.97940029375127</t>
+          <t>-116.5756429972018</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>1715.0</t>
+          <t>231.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-18.82</t>
+          <t>-19.03</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>88.59</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>592</t>
+          <t>591</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>20.05</t>
+          <t>18.85</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>20.05</t>
+          <t>19.15</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>19.0</t>
+          <t>18.85</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>19.2</t>
+          <t>19.15</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-2.0</t>
+          <t>-4.24</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>46.0</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>20.05</t>
+          <t>19.2</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5208,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>5.19</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>-1.3</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>17.65</t>
+          <t>21.51</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-8.24</t>
+          <t>-12.13</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>3.15</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>-3.37</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,12 +5314,12 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -5329,58 +5329,58 @@
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>23.08</t>
+          <t>15.38</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-1.91</t>
+          <t>-4.81</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-3.90</t>
+          <t>-4.41</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-2.98</t>
+          <t>-3.49</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-1.65</t>
+          <t>-2.01</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>20.44</t>
+          <t>20.17</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>21.27</v>
+        <v>21.1</v>
       </c>
       <c r="AN12" t="n">
-        <v>21.92</v>
+        <v>21.86</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>22.29</t>
+          <t>22.31</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-16.23</t>
+          <t>-25.64</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-106.88</t>
+          <t>-107.35</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5400,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>30249.05982905983</t>
+          <t>30207.30512091039</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>922.0</t>
+          <t>1715.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>840.4</v>
+        <v>1014.4</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>714.3</t>
+          <t>834.8</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>1889.2</v>
+        <v>1896.36</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>126</t>
+          <t>179</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-195.1459064225224</t>
+          <t>-175.1202900950192</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-147.9497892783307</t>
+          <t>-64.97940029375127</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>922.0</t>
+          <t>1715.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-15.22</t>
+          <t>-18.82</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,7 +5511,7 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>88.59</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>592</t>
+          <t>591</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,22 +5566,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>20.05</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>20.1</t>
+          <t>20.05</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>19.95</t>
+          <t>19.0</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>20.05</t>
+          <t>19.2</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5613,12 +5613,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>56.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5628,7 +5628,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>213.5</t>
+          <t>214.0</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5643,12 +5643,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-1.69</t>
+          <t>-14.56</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5668,7 +5668,7 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>2025-12-02 00:00:00</t>
+          <t>2025-12-03 00:00:00</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -5708,7 +5708,7 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>5.96</t>
+          <t>6.20</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
@@ -5723,17 +5723,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13.18</t>
+          <t>9.41</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>-1.17</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5749,37 +5749,37 @@
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>40</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>86.21</t>
+          <t>86.36</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>95.4</t>
+          <t>90.86</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>5.15</t>
+          <t>4.64</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>3.66</t>
+          <t>3.89</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
@@ -5788,29 +5788,29 @@
         </is>
       </c>
       <c r="AM13" t="n">
-        <v>203.8</v>
+        <v>204.8</v>
       </c>
       <c r="AN13" t="n">
-        <v>196.6</v>
+        <v>197.13</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>193.37</t>
+          <t>193.75</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>26.64</t>
+          <t>20.18</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>5.23</t>
+          <t>5.22</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>4.13</t>
+          <t>4.35</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5820,7 +5820,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-58.78</t>
+          <t>-56.59</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5830,48 +5830,48 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>28292.75427350427</t>
+          <t>28270.70697012803</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>12118.0</t>
+          <t>8529.0</t>
         </is>
       </c>
       <c r="AX13" t="n">
-        <v>19868.4</v>
+        <v>16149.6</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>20209.8</t>
+          <t>18902.6</t>
         </is>
       </c>
       <c r="AZ13" t="n">
-        <v>12862.38</v>
+        <v>12813</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>-341</t>
+          <t>-2752</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>1331.553831026793</t>
+          <t>1057.156661900817</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>351.1662279440243</t>
+          <t>-452.0277682920532</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>12118.0</t>
+          <t>8529.0</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="BF13" t="inlineStr">
@@ -5886,7 +5886,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>11.20</t>
+          <t>11.46</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -5936,7 +5936,7 @@
       </c>
       <c r="BR13" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS13" t="inlineStr">
@@ -5946,7 +5946,7 @@
       </c>
       <c r="BT13" t="inlineStr">
         <is>
-          <t>4.67</t>
+          <t>4.66</t>
         </is>
       </c>
       <c r="BU13" t="inlineStr">
@@ -5956,7 +5956,7 @@
       </c>
       <c r="BV13" t="inlineStr">
         <is>
-          <t>12.75</t>
+          <t>12.78</t>
         </is>
       </c>
       <c r="BW13" t="inlineStr">
@@ -5971,12 +5971,12 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>49.44</t>
+          <t>49.06</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>10153</t>
+          <t>10177</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -6001,7 +6001,7 @@
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>217.0</t>
+          <t>215.5</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
@@ -6011,7 +6011,7 @@
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>213.5</t>
+          <t>214.0</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>56.0</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6058,7 +6058,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>215.5</t>
+          <t>213.5</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6068,17 +6068,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>-1.69</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6098,7 +6098,7 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>2025-12-02 00:00:00</t>
+          <t>2025-12-03 00:00:00</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -6138,7 +6138,7 @@
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>6.95</t>
+          <t>5.96</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
@@ -6153,17 +6153,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>17.18</t>
+          <t>13.18</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>-1.17</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6179,68 +6179,68 @@
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>40</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>86.21</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>95.4</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>-0.37</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>5.31</t>
+          <t>5.15</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>3.66</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>213.7</t>
+          <t>214.3</t>
         </is>
       </c>
       <c r="AM14" t="n">
-        <v>202.92</v>
+        <v>203.8</v>
       </c>
       <c r="AN14" t="n">
-        <v>196.07</v>
+        <v>196.6</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>193.0</t>
+          <t>193.37</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>35.12</t>
+          <t>26.64</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>5.21</t>
+          <t>5.23</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>3.85</t>
+          <t>4.13</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6250,7 +6250,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-61.52</t>
+          <t>-58.78</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6260,48 +6260,48 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>28292.75427350427</t>
+          <t>28270.70697012803</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>15735.0</t>
+          <t>12118.0</t>
         </is>
       </c>
       <c r="AX14" t="n">
-        <v>21869.2</v>
+        <v>19868.4</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>21736.8</t>
+          <t>20209.8</t>
         </is>
       </c>
       <c r="AZ14" t="n">
-        <v>12717.58</v>
+        <v>12862.38</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>132</t>
+          <t>-341</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>1509.806122496388</t>
+          <t>1331.553831026793</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>1101.508857283279</t>
+          <t>351.1662279440243</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>15735.0</t>
+          <t>12118.0</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="BF14" t="inlineStr">
@@ -6316,7 +6316,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>12.24</t>
+          <t>11.20</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -6361,7 +6361,7 @@
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
@@ -6371,12 +6371,12 @@
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
         <is>
-          <t>4.67</t>
+          <t>4.66</t>
         </is>
       </c>
       <c r="BU14" t="inlineStr">
@@ -6386,7 +6386,7 @@
       </c>
       <c r="BV14" t="inlineStr">
         <is>
-          <t>12.75</t>
+          <t>12.78</t>
         </is>
       </c>
       <c r="BW14" t="inlineStr">
@@ -6401,12 +6401,12 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>49.44</t>
+          <t>49.06</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>10153</t>
+          <t>10177</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -6426,22 +6426,22 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>215.0</t>
+          <t>215.5</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>215.5</t>
+          <t>217.0</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
+          <t>212.5</t>
+        </is>
+      </c>
+      <c r="CG14" t="inlineStr">
+        <is>
           <t>213.5</t>
-        </is>
-      </c>
-      <c r="CG14" t="inlineStr">
-        <is>
-          <t>215.5</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -6473,12 +6473,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6488,7 +6488,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>214.5</t>
+          <t>215.5</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6498,17 +6498,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-0.47</t>
+          <t>-0.7</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6528,7 +6528,7 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>2025-12-02 00:00:00</t>
+          <t>2025-12-03 00:00:00</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -6568,7 +6568,7 @@
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>6.45</t>
+          <t>6.95</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
@@ -6583,17 +6583,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>19.06</t>
+          <t>17.18</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6609,7 +6609,7 @@
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>40</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
@@ -6624,53 +6624,53 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>4.99</t>
+          <t>5.31</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>3.29</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>212.0</t>
+          <t>213.7</t>
         </is>
       </c>
       <c r="AM15" t="n">
-        <v>201.92</v>
+        <v>202.92</v>
       </c>
       <c r="AN15" t="n">
-        <v>195.5</v>
+        <v>196.07</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>192.61</t>
+          <t>193.0</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>39.40</t>
+          <t>35.12</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>4.90</t>
+          <t>5.21</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>3.51</t>
+          <t>3.85</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6680,7 +6680,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-64.90</t>
+          <t>-61.52</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6690,48 +6690,48 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>28292.75427350427</t>
+          <t>28270.70697012803</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>17273.0</t>
+          <t>15735.0</t>
         </is>
       </c>
       <c r="AX15" t="n">
-        <v>23978</v>
+        <v>21869.2</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>23524.2</t>
+          <t>21736.8</t>
         </is>
       </c>
       <c r="AZ15" t="n">
-        <v>12876.32</v>
+        <v>12717.58</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>453</t>
+          <t>132</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>1584.041988898771</t>
+          <t>1509.806122496388</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>1746.551582864951</t>
+          <t>1101.508857283279</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>17273.0</t>
+          <t>15735.0</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="BF15" t="inlineStr">
@@ -6746,7 +6746,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>11.72</t>
+          <t>12.24</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -6791,22 +6791,22 @@
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
         <is>
-          <t>4.67</t>
+          <t>4.66</t>
         </is>
       </c>
       <c r="BU15" t="inlineStr">
@@ -6816,7 +6816,7 @@
       </c>
       <c r="BV15" t="inlineStr">
         <is>
-          <t>12.75</t>
+          <t>12.78</t>
         </is>
       </c>
       <c r="BW15" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>49.44</t>
+          <t>49.06</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>10153</t>
+          <t>10177</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -6856,7 +6856,7 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>214.5</t>
+          <t>215.0</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
@@ -6866,12 +6866,12 @@
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>213.0</t>
+          <t>213.5</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>214.5</t>
+          <t>215.5</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -6903,12 +6903,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6918,7 +6918,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>214.0</t>
+          <t>214.5</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6933,12 +6933,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>13.06</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -6958,7 +6958,7 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>2025-12-02 00:00:00</t>
+          <t>2025-12-03 00:00:00</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -6998,7 +6998,7 @@
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>6.20</t>
+          <t>6.45</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
@@ -7013,17 +7013,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>29.88</t>
+          <t>19.06</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7039,7 +7039,7 @@
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>40</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
@@ -7054,53 +7054,53 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>4.44</t>
+          <t>4.99</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>3.16</t>
+          <t>3.29</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>210.0</t>
+          <t>212.0</t>
         </is>
       </c>
       <c r="AM16" t="n">
-        <v>201.08</v>
+        <v>201.92</v>
       </c>
       <c r="AN16" t="n">
-        <v>194.92</v>
+        <v>195.5</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>192.22</t>
+          <t>192.61</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>43.25</t>
+          <t>39.40</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>4.54</t>
+          <t>4.90</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>3.17</t>
+          <t>3.51</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7110,7 +7110,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-68.36</t>
+          <t>-64.90</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7120,48 +7120,48 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>28292.75427350427</t>
+          <t>28270.70697012803</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>27093.0</t>
+          <t>17273.0</t>
         </is>
       </c>
       <c r="AX16" t="n">
-        <v>25064</v>
+        <v>23978</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>22168.4</t>
+          <t>23524.2</t>
         </is>
       </c>
       <c r="AZ16" t="n">
-        <v>12662.48</v>
+        <v>12876.32</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>2895</t>
+          <t>453</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>1554.494789995829</t>
+          <t>1584.041988898771</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>2440.878634307883</t>
+          <t>1746.551582864951</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>27093.0</t>
+          <t>17273.0</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="BF16" t="inlineStr">
@@ -7176,7 +7176,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>11.46</t>
+          <t>11.72</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -7221,7 +7221,7 @@
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
@@ -7231,12 +7231,12 @@
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
         <is>
-          <t>4.67</t>
+          <t>4.66</t>
         </is>
       </c>
       <c r="BU16" t="inlineStr">
@@ -7246,7 +7246,7 @@
       </c>
       <c r="BV16" t="inlineStr">
         <is>
-          <t>12.75</t>
+          <t>12.78</t>
         </is>
       </c>
       <c r="BW16" t="inlineStr">
@@ -7261,12 +7261,12 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>49.44</t>
+          <t>49.06</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>10153</t>
+          <t>10177</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -7286,7 +7286,7 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>215.0</t>
+          <t>214.5</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
@@ -7296,12 +7296,12 @@
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>211.0</t>
+          <t>213.0</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>214.0</t>
+          <t>214.5</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -7333,12 +7333,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7358,17 +7358,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>7.97</t>
+          <t>13.06</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7388,7 +7388,7 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>2025-12-02 00:00:00</t>
+          <t>2025-12-03 00:00:00</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -7443,17 +7443,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>30.12</t>
+          <t>29.88</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7469,7 +7469,7 @@
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>40</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
@@ -7484,53 +7484,53 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>3.18</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>3.54</t>
+          <t>4.44</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>3.07</t>
+          <t>3.16</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>207.4</t>
+          <t>210.0</t>
         </is>
       </c>
       <c r="AM17" t="n">
-        <v>200.3</v>
+        <v>201.08</v>
       </c>
       <c r="AN17" t="n">
-        <v>194.34</v>
+        <v>194.92</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>191.84</t>
+          <t>192.22</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>43.78</t>
+          <t>43.25</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>4.06</t>
+          <t>4.54</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>2.83</t>
+          <t>3.17</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7540,7 +7540,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-71.78</t>
+          <t>-68.36</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7550,48 +7550,48 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>28292.75427350427</t>
+          <t>28270.70697012803</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>27123.0</t>
+          <t>27093.0</t>
         </is>
       </c>
       <c r="AX17" t="n">
-        <v>21655.6</v>
+        <v>25064</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>20056.7</t>
+          <t>22168.4</t>
         </is>
       </c>
       <c r="AZ17" t="n">
-        <v>12284.3</v>
+        <v>12662.48</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>1598</t>
+          <t>2895</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>1393.334091030001</t>
+          <t>1554.494789995829</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>2293.457328001074</t>
+          <t>2440.878634307883</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>27123.0</t>
+          <t>27093.0</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="BF17" t="inlineStr">
@@ -7651,12 +7651,12 @@
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS17" t="inlineStr">
@@ -7666,7 +7666,7 @@
       </c>
       <c r="BT17" t="inlineStr">
         <is>
-          <t>4.67</t>
+          <t>4.66</t>
         </is>
       </c>
       <c r="BU17" t="inlineStr">
@@ -7676,7 +7676,7 @@
       </c>
       <c r="BV17" t="inlineStr">
         <is>
-          <t>12.75</t>
+          <t>12.78</t>
         </is>
       </c>
       <c r="BW17" t="inlineStr">
@@ -7691,12 +7691,12 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>49.44</t>
+          <t>49.06</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>10153</t>
+          <t>10177</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -7716,17 +7716,17 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
+          <t>215.0</t>
+        </is>
+      </c>
+      <c r="CE17" t="inlineStr">
+        <is>
+          <t>215.5</t>
+        </is>
+      </c>
+      <c r="CF17" t="inlineStr">
+        <is>
           <t>211.0</t>
-        </is>
-      </c>
-      <c r="CE17" t="inlineStr">
-        <is>
-          <t>214.0</t>
-        </is>
-      </c>
-      <c r="CF17" t="inlineStr">
-        <is>
-          <t>210.5</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
@@ -7763,12 +7763,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>105.0</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7778,7 +7778,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>210.5</t>
+          <t>214.0</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7788,17 +7788,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>13.00</t>
+          <t>7.97</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7818,7 +7818,7 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>2025-12-02 00:00:00</t>
+          <t>2025-12-03 00:00:00</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
@@ -7858,7 +7858,7 @@
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>4.47</t>
+          <t>6.20</t>
         </is>
       </c>
       <c r="W18" t="inlineStr">
@@ -7873,17 +7873,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>24.71</t>
+          <t>30.12</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7899,7 +7899,7 @@
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>40</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
@@ -7914,53 +7914,53 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>2.93</t>
+          <t>3.18</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>2.52</t>
+          <t>3.54</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>2.93</t>
+          <t>3.07</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>204.5</t>
+          <t>207.4</t>
         </is>
       </c>
       <c r="AM18" t="n">
-        <v>199.48</v>
+        <v>200.3</v>
       </c>
       <c r="AN18" t="n">
-        <v>193.8</v>
+        <v>194.34</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>191.47</t>
+          <t>191.84</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>34.99</t>
+          <t>43.78</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>4.06</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>2.52</t>
+          <t>2.83</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -7970,7 +7970,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-74.87</t>
+          <t>-71.78</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7980,48 +7980,48 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>28292.75427350427</t>
+          <t>28270.70697012803</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>22122.0</t>
+          <t>27123.0</t>
         </is>
       </c>
       <c r="AX18" t="n">
-        <v>20551.2</v>
+        <v>21655.6</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>18187.0</t>
+          <t>20056.7</t>
         </is>
       </c>
       <c r="AZ18" t="n">
-        <v>11819.44</v>
+        <v>12284.3</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>2364</t>
+          <t>1598</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>1229.675320671625</t>
+          <t>1393.334091030001</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>1997.731985848452</t>
+          <t>2293.457328001074</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>22122.0</t>
+          <t>27123.0</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="BF18" t="inlineStr">
@@ -8036,7 +8036,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>9.64</t>
+          <t>11.46</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -8081,7 +8081,7 @@
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
@@ -8091,12 +8091,12 @@
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
         <is>
-          <t>4.67</t>
+          <t>4.66</t>
         </is>
       </c>
       <c r="BU18" t="inlineStr">
@@ -8106,7 +8106,7 @@
       </c>
       <c r="BV18" t="inlineStr">
         <is>
-          <t>12.75</t>
+          <t>12.78</t>
         </is>
       </c>
       <c r="BW18" t="inlineStr">
@@ -8121,12 +8121,12 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>49.44</t>
+          <t>49.06</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>10153</t>
+          <t>10177</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -8146,22 +8146,22 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>208.5</t>
+          <t>211.0</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>211.0</t>
+          <t>214.0</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>208.0</t>
+          <t>210.5</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>210.5</t>
+          <t>214.0</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>105.0</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8208,7 +8208,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>207.0</t>
+          <t>210.5</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8218,17 +8218,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>19.04</t>
+          <t>13.00</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8248,7 +8248,7 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>2025-12-02 00:00:00</t>
+          <t>2025-12-03 00:00:00</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
@@ -8288,7 +8288,7 @@
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>2.73</t>
+          <t>4.47</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">
@@ -8303,17 +8303,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>30.12</t>
+          <t>24.71</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8329,7 +8329,7 @@
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>40</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
@@ -8339,58 +8339,58 @@
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>85.71</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>2.93</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>2.52</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>2.89</t>
+          <t>2.93</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>203.2</t>
+          <t>204.5</t>
         </is>
       </c>
       <c r="AM19" t="n">
-        <v>198.92</v>
+        <v>199.48</v>
       </c>
       <c r="AN19" t="n">
-        <v>193.33</v>
+        <v>193.8</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>191.14</t>
+          <t>191.47</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>24.29</t>
+          <t>34.99</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>2.85</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>2.52</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8400,7 +8400,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-77.07</t>
+          <t>-74.87</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8410,48 +8410,48 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>28292.75427350427</t>
+          <t>28270.70697012803</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>26279.0</t>
+          <t>22122.0</t>
         </is>
       </c>
       <c r="AX19" t="n">
-        <v>21604.4</v>
+        <v>20551.2</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>18148.2</t>
+          <t>18187.0</t>
         </is>
       </c>
       <c r="AZ19" t="n">
-        <v>11512</v>
+        <v>11819.44</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>3456</t>
+          <t>2364</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>1090.028654275838</t>
+          <t>1229.675320671625</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>2039.741068992971</t>
+          <t>1997.731985848452</t>
         </is>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
-          <t>26279.0</t>
+          <t>22122.0</t>
         </is>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="BF19" t="inlineStr">
@@ -8466,7 +8466,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>7.81</t>
+          <t>9.64</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -8516,17 +8516,17 @@
       </c>
       <c r="BR19" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
         <is>
-          <t>4.67</t>
+          <t>4.66</t>
         </is>
       </c>
       <c r="BU19" t="inlineStr">
@@ -8536,7 +8536,7 @@
       </c>
       <c r="BV19" t="inlineStr">
         <is>
-          <t>12.75</t>
+          <t>12.78</t>
         </is>
       </c>
       <c r="BW19" t="inlineStr">
@@ -8551,12 +8551,12 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>49.44</t>
+          <t>49.06</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>10153</t>
+          <t>10177</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -8576,22 +8576,22 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>203.5</t>
+          <t>208.5</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
+          <t>211.0</t>
+        </is>
+      </c>
+      <c r="CF19" t="inlineStr">
+        <is>
           <t>208.0</t>
         </is>
       </c>
-      <c r="CF19" t="inlineStr">
-        <is>
-          <t>202.0</t>
-        </is>
-      </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>207.0</t>
+          <t>210.5</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8623,12 +8623,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>112.0</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8638,7 +8638,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>204.5</t>
+          <t>207.0</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8648,17 +8648,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>4.22</t>
+          <t>3.27</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>40.09</t>
+          <t>19.04</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8678,7 +8678,7 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>2025-12-02 00:00:00</t>
+          <t>2025-12-03 00:00:00</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
@@ -8718,7 +8718,7 @@
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>2.73</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
@@ -8733,17 +8733,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>26.35</t>
+          <t>30.12</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8759,7 +8759,7 @@
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>40</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
@@ -8769,58 +8769,58 @@
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>64.29</t>
+          <t>85.71</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>2.93</t>
+          <t>2.89</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>202.1</t>
+          <t>203.2</t>
         </is>
       </c>
       <c r="AM20" t="n">
-        <v>198.58</v>
+        <v>198.92</v>
       </c>
       <c r="AN20" t="n">
-        <v>192.93</v>
+        <v>193.33</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>190.87</t>
+          <t>191.14</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>14.78</t>
+          <t>24.29</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>2.48</t>
+          <t>2.85</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-78.46</t>
+          <t>-77.07</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8840,48 +8840,48 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>28292.75427350427</t>
+          <t>28270.70697012803</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>22703.0</t>
+          <t>26279.0</t>
         </is>
       </c>
       <c r="AX20" t="n">
-        <v>23070.4</v>
+        <v>21604.4</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>16467.7</t>
+          <t>18148.2</t>
         </is>
       </c>
       <c r="AZ20" t="n">
-        <v>11056.48</v>
+        <v>11512</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>6602</t>
+          <t>3456</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>917.3536697818137</t>
+          <t>1090.028654275838</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>1581.513292449679</t>
+          <t>2039.741068992971</t>
         </is>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
-          <t>22703.0</t>
+          <t>26279.0</t>
         </is>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="BF20" t="inlineStr">
@@ -8896,7 +8896,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>6.51</t>
+          <t>7.81</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -8941,22 +8941,22 @@
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
         <is>
-          <t>4.67</t>
+          <t>4.66</t>
         </is>
       </c>
       <c r="BU20" t="inlineStr">
@@ -8966,7 +8966,7 @@
       </c>
       <c r="BV20" t="inlineStr">
         <is>
-          <t>12.75</t>
+          <t>12.78</t>
         </is>
       </c>
       <c r="BW20" t="inlineStr">
@@ -8981,12 +8981,12 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>49.44</t>
+          <t>49.06</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>10153</t>
+          <t>10177</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
@@ -9006,22 +9006,22 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
+          <t>203.5</t>
+        </is>
+      </c>
+      <c r="CE20" t="inlineStr">
+        <is>
+          <t>208.0</t>
+        </is>
+      </c>
+      <c r="CF20" t="inlineStr">
+        <is>
           <t>202.0</t>
         </is>
       </c>
-      <c r="CE20" t="inlineStr">
-        <is>
-          <t>205.0</t>
-        </is>
-      </c>
-      <c r="CF20" t="inlineStr">
-        <is>
-          <t>202.0</t>
-        </is>
-      </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>204.5</t>
+          <t>207.0</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -9053,12 +9053,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>112.0</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9068,7 +9068,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>201.0</t>
+          <t>204.5</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9078,17 +9078,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>5.85</t>
+          <t>4.44</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>28.98</t>
+          <t>40.09</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9108,7 +9108,7 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>2025-12-02 00:00:00</t>
+          <t>2025-12-03 00:00:00</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
@@ -9148,7 +9148,7 @@
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
@@ -9163,17 +9163,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11.76</t>
+          <t>26.35</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9189,12 +9189,12 @@
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>40</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>57.14</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
@@ -9204,53 +9204,53 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>2.94</t>
+          <t>2.93</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>200.6</t>
+          <t>202.1</t>
         </is>
       </c>
       <c r="AM21" t="n">
-        <v>198.25</v>
+        <v>198.58</v>
       </c>
       <c r="AN21" t="n">
-        <v>192.58</v>
+        <v>192.93</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>190.62</t>
+          <t>190.87</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>6.46</t>
+          <t>14.78</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>2.21</t>
+          <t>2.48</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>2.16</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9260,7 +9260,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-79.25</t>
+          <t>-78.46</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9270,48 +9270,48 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>28292.75427350427</t>
+          <t>28270.70697012803</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>10051.0</t>
+          <t>22703.0</t>
         </is>
       </c>
       <c r="AX21" t="n">
-        <v>19272.8</v>
+        <v>23070.4</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>14943.0</t>
+          <t>16467.7</t>
         </is>
       </c>
       <c r="AZ21" t="n">
-        <v>10672.76</v>
+        <v>11056.48</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>4329</t>
+          <t>6602</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>796.5973747512926</t>
+          <t>917.3536697818137</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>1253.562422657489</t>
+          <t>1581.513292449679</t>
         </is>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
-          <t>10051.0</t>
+          <t>22703.0</t>
         </is>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="BF21" t="inlineStr">
@@ -9326,7 +9326,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>4.69</t>
+          <t>6.51</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
@@ -9371,7 +9371,7 @@
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
@@ -9381,12 +9381,12 @@
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
         <is>
-          <t>4.67</t>
+          <t>4.66</t>
         </is>
       </c>
       <c r="BU21" t="inlineStr">
@@ -9396,7 +9396,7 @@
       </c>
       <c r="BV21" t="inlineStr">
         <is>
-          <t>12.75</t>
+          <t>12.78</t>
         </is>
       </c>
       <c r="BW21" t="inlineStr">
@@ -9411,12 +9411,12 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>49.44</t>
+          <t>49.06</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>10153</t>
+          <t>10177</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
@@ -9436,22 +9436,22 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>199.5</t>
+          <t>202.0</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
+          <t>205.0</t>
+        </is>
+      </c>
+      <c r="CF21" t="inlineStr">
+        <is>
           <t>202.0</t>
         </is>
       </c>
-      <c r="CF21" t="inlineStr">
-        <is>
-          <t>198.5</t>
-        </is>
-      </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>201.0</t>
+          <t>204.5</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -9483,12 +9483,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-2.2</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>107.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9498,7 +9498,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>199.5</t>
+          <t>201.0</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9508,17 +9508,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>6.56</t>
+          <t>6.07</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>17.59</t>
+          <t>28.98</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9538,7 +9538,7 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>2025-12-02 00:00:00</t>
+          <t>2025-12-03 00:00:00</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
@@ -9578,7 +9578,7 @@
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="W22" t="inlineStr">
@@ -9593,17 +9593,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>25.18</t>
+          <t>11.76</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>-2.00</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9619,68 +9619,68 @@
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>40</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>35.71</t>
+          <t>57.14</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>78.57</t>
+          <t>64.29</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>2.96</t>
+          <t>2.94</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>200.0</t>
+          <t>200.6</t>
         </is>
       </c>
       <c r="AM22" t="n">
-        <v>197.98</v>
+        <v>198.25</v>
       </c>
       <c r="AN22" t="n">
-        <v>192.28</v>
+        <v>192.58</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>190.44</t>
+          <t>190.62</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>7.56</t>
+          <t>6.46</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>2.21</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9690,7 +9690,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-79.59</t>
+          <t>-79.25</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9700,48 +9700,48 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>28292.75427350427</t>
+          <t>28270.70697012803</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>21601.0</t>
+          <t>10051.0</t>
         </is>
       </c>
       <c r="AX22" t="n">
-        <v>18457.8</v>
+        <v>19272.8</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>15697.4</t>
+          <t>14943.0</t>
         </is>
       </c>
       <c r="AZ22" t="n">
-        <v>10622.98</v>
+        <v>10672.76</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>2760</t>
+          <t>4329</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>713.5128205865296</t>
+          <t>796.5973747512926</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>2095.862522145168</t>
+          <t>1253.562422657489</t>
         </is>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
-          <t>21601.0</t>
+          <t>10051.0</t>
         </is>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="BF22" t="inlineStr">
@@ -9756,7 +9756,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>3.91</t>
+          <t>4.69</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
@@ -9801,7 +9801,7 @@
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -9811,12 +9811,12 @@
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>1.89</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
         <is>
-          <t>4.67</t>
+          <t>4.66</t>
         </is>
       </c>
       <c r="BU22" t="inlineStr">
@@ -9826,7 +9826,7 @@
       </c>
       <c r="BV22" t="inlineStr">
         <is>
-          <t>12.75</t>
+          <t>12.78</t>
         </is>
       </c>
       <c r="BW22" t="inlineStr">
@@ -9841,12 +9841,12 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>49.44</t>
+          <t>49.06</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>10153</t>
+          <t>10177</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
@@ -9866,22 +9866,22 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>205.0</t>
+          <t>199.5</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>205.0</t>
+          <t>202.0</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>198.0</t>
+          <t>198.5</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>199.5</t>
+          <t>201.0</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -9913,12 +9913,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>-2.2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>107.0</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9928,7 +9928,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>204.0</t>
+          <t>199.5</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9938,17 +9938,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>4.45</t>
+          <t>6.78</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>9.50</t>
+          <t>17.59</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -9968,7 +9968,7 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>2025-12-02 00:00:00</t>
+          <t>2025-12-03 00:00:00</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
@@ -10008,7 +10008,7 @@
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="W23" t="inlineStr">
@@ -10023,17 +10023,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>31.53</t>
+          <t>25.18</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>-2.00</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10049,27 +10049,27 @@
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>40</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>35.71</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>82.05</t>
+          <t>78.57</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
@@ -10079,239 +10079,239 @@
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
+          <t>200.0</t>
+        </is>
+      </c>
+      <c r="AM23" t="n">
+        <v>197.98</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>192.28</v>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>190.44</t>
+        </is>
+      </c>
+      <c r="AP23" t="inlineStr">
+        <is>
+          <t>7.56</t>
+        </is>
+      </c>
+      <c r="AQ23" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="AR23" t="inlineStr">
+        <is>
+          <t>2.04</t>
+        </is>
+      </c>
+      <c r="AS23" t="inlineStr">
+        <is>
+          <t>10.01</t>
+        </is>
+      </c>
+      <c r="AT23" t="inlineStr">
+        <is>
+          <t>-79.59</t>
+        </is>
+      </c>
+      <c r="AU23" t="inlineStr">
+        <is>
+          <t>2025/11/14</t>
+        </is>
+      </c>
+      <c r="AV23" t="inlineStr">
+        <is>
+          <t>28270.70697012803</t>
+        </is>
+      </c>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>21601.0</t>
+        </is>
+      </c>
+      <c r="AX23" t="n">
+        <v>18457.8</v>
+      </c>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>15697.4</t>
+        </is>
+      </c>
+      <c r="AZ23" t="n">
+        <v>10622.98</v>
+      </c>
+      <c r="BA23" t="inlineStr">
+        <is>
+          <t>2760</t>
+        </is>
+      </c>
+      <c r="BB23" t="inlineStr">
+        <is>
+          <t>713.5128205865296</t>
+        </is>
+      </c>
+      <c r="BC23" t="inlineStr">
+        <is>
+          <t>2095.862522145168</t>
+        </is>
+      </c>
+      <c r="BD23" t="inlineStr">
+        <is>
+          <t>21601.0</t>
+        </is>
+      </c>
+      <c r="BE23" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="BF23" t="inlineStr">
+        <is>
+          <t>192.0</t>
+        </is>
+      </c>
+      <c r="BG23" t="inlineStr">
+        <is>
+          <t>2025/10/14</t>
+        </is>
+      </c>
+      <c r="BH23" t="inlineStr">
+        <is>
+          <t>3.91</t>
+        </is>
+      </c>
+      <c r="BI23" t="inlineStr">
+        <is>
+          <t>鼎翰</t>
+        </is>
+      </c>
+      <c r="BJ23" t="inlineStr">
+        <is>
+          <t>鼎翰</t>
+        </is>
+      </c>
+      <c r="BK23" t="inlineStr">
+        <is>
+          <t>電腦及週邊設備業</t>
+        </is>
+      </c>
+      <c r="BL23" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BM23" t="inlineStr">
+        <is>
+          <t>0.57</t>
+        </is>
+      </c>
+      <c r="BN23" t="inlineStr">
+        <is>
+          <t>-11.45161899724185</t>
+        </is>
+      </c>
+      <c r="BO23" t="inlineStr">
+        <is>
+          <t>22.56717409239306</t>
+        </is>
+      </c>
+      <c r="BP23" t="inlineStr">
+        <is>
+          <t>38.82556207928187</t>
+        </is>
+      </c>
+      <c r="BQ23" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR23" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS23" t="inlineStr">
+        <is>
+          <t>1.89</t>
+        </is>
+      </c>
+      <c r="BT23" t="inlineStr">
+        <is>
+          <t>4.66</t>
+        </is>
+      </c>
+      <c r="BU23" t="inlineStr">
+        <is>
+          <t>57.78</t>
+        </is>
+      </c>
+      <c r="BV23" t="inlineStr">
+        <is>
+          <t>12.78</t>
+        </is>
+      </c>
+      <c r="BW23" t="inlineStr">
+        <is>
+          <t>33.69%</t>
+        </is>
+      </c>
+      <c r="BX23" t="inlineStr">
+        <is>
+          <t>11.08%</t>
+        </is>
+      </c>
+      <c r="BY23" t="inlineStr">
+        <is>
+          <t>49.06</t>
+        </is>
+      </c>
+      <c r="BZ23" t="inlineStr">
+        <is>
+          <t>10177</t>
+        </is>
+      </c>
+      <c r="CA23" t="inlineStr">
+        <is>
+          <t>條碼印表機及零配件52.71%、印表機各式標籤紙及其耗材41.09%、企業行動電腦6.20% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB23" t="inlineStr">
+        <is>
+          <t>鼎翰-電腦及週邊設備業-上櫃</t>
+        </is>
+      </c>
+      <c r="CC23" t="inlineStr">
+        <is>
+          <t>電腦及週邊設備業平上櫃</t>
+        </is>
+      </c>
+      <c r="CD23" t="inlineStr">
+        <is>
+          <t>205.0</t>
+        </is>
+      </c>
+      <c r="CE23" t="inlineStr">
+        <is>
+          <t>205.0</t>
+        </is>
+      </c>
+      <c r="CF23" t="inlineStr">
+        <is>
+          <t>198.0</t>
+        </is>
+      </c>
+      <c r="CG23" t="inlineStr">
+        <is>
           <t>199.5</t>
-        </is>
-      </c>
-      <c r="AM23" t="n">
-        <v>197.7</v>
-      </c>
-      <c r="AN23" t="n">
-        <v>192.01</v>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>190.29</t>
-        </is>
-      </c>
-      <c r="AP23" t="inlineStr">
-        <is>
-          <t>14.82</t>
-        </is>
-      </c>
-      <c r="AQ23" t="inlineStr">
-        <is>
-          <t>2.30</t>
-        </is>
-      </c>
-      <c r="AR23" t="inlineStr">
-        <is>
-          <t>2.01</t>
-        </is>
-      </c>
-      <c r="AS23" t="inlineStr">
-        <is>
-          <t>10.01</t>
-        </is>
-      </c>
-      <c r="AT23" t="inlineStr">
-        <is>
-          <t>-79.98</t>
-        </is>
-      </c>
-      <c r="AU23" t="inlineStr">
-        <is>
-          <t>2025/11/14</t>
-        </is>
-      </c>
-      <c r="AV23" t="inlineStr">
-        <is>
-          <t>28292.75427350427</t>
-        </is>
-      </c>
-      <c r="AW23" t="inlineStr">
-        <is>
-          <t>27388.0</t>
-        </is>
-      </c>
-      <c r="AX23" t="n">
-        <v>15822.8</v>
-      </c>
-      <c r="AY23" t="inlineStr">
-        <is>
-          <t>14450.7</t>
-        </is>
-      </c>
-      <c r="AZ23" t="n">
-        <v>10277.46</v>
-      </c>
-      <c r="BA23" t="inlineStr">
-        <is>
-          <t>1372</t>
-        </is>
-      </c>
-      <c r="BB23" t="inlineStr">
-        <is>
-          <t>462.1765112122318</t>
-        </is>
-      </c>
-      <c r="BC23" t="inlineStr">
-        <is>
-          <t>1986.79614562238</t>
-        </is>
-      </c>
-      <c r="BD23" t="inlineStr">
-        <is>
-          <t>27388.0</t>
-        </is>
-      </c>
-      <c r="BE23" t="inlineStr">
-        <is>
-          <t>2025-12-02</t>
-        </is>
-      </c>
-      <c r="BF23" t="inlineStr">
-        <is>
-          <t>192.0</t>
-        </is>
-      </c>
-      <c r="BG23" t="inlineStr">
-        <is>
-          <t>2025/10/14</t>
-        </is>
-      </c>
-      <c r="BH23" t="inlineStr">
-        <is>
-          <t>6.25</t>
-        </is>
-      </c>
-      <c r="BI23" t="inlineStr">
-        <is>
-          <t>鼎翰</t>
-        </is>
-      </c>
-      <c r="BJ23" t="inlineStr">
-        <is>
-          <t>鼎翰</t>
-        </is>
-      </c>
-      <c r="BK23" t="inlineStr">
-        <is>
-          <t>電腦及週邊設備業</t>
-        </is>
-      </c>
-      <c r="BL23" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BM23" t="inlineStr">
-        <is>
-          <t>0.57</t>
-        </is>
-      </c>
-      <c r="BN23" t="inlineStr">
-        <is>
-          <t>-11.45161899724185</t>
-        </is>
-      </c>
-      <c r="BO23" t="inlineStr">
-        <is>
-          <t>22.56717409239306</t>
-        </is>
-      </c>
-      <c r="BP23" t="inlineStr">
-        <is>
-          <t>38.82556207928187</t>
-        </is>
-      </c>
-      <c r="BQ23" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR23" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BS23" t="inlineStr">
-        <is>
-          <t>1.93</t>
-        </is>
-      </c>
-      <c r="BT23" t="inlineStr">
-        <is>
-          <t>4.67</t>
-        </is>
-      </c>
-      <c r="BU23" t="inlineStr">
-        <is>
-          <t>57.78</t>
-        </is>
-      </c>
-      <c r="BV23" t="inlineStr">
-        <is>
-          <t>12.75</t>
-        </is>
-      </c>
-      <c r="BW23" t="inlineStr">
-        <is>
-          <t>33.69%</t>
-        </is>
-      </c>
-      <c r="BX23" t="inlineStr">
-        <is>
-          <t>11.08%</t>
-        </is>
-      </c>
-      <c r="BY23" t="inlineStr">
-        <is>
-          <t>49.44</t>
-        </is>
-      </c>
-      <c r="BZ23" t="inlineStr">
-        <is>
-          <t>10153</t>
-        </is>
-      </c>
-      <c r="CA23" t="inlineStr">
-        <is>
-          <t>條碼印表機及零配件52.71%、印表機各式標籤紙及其耗材41.09%、企業行動電腦6.20% (2024年)</t>
-        </is>
-      </c>
-      <c r="CB23" t="inlineStr">
-        <is>
-          <t>鼎翰-電腦及週邊設備業-上櫃</t>
-        </is>
-      </c>
-      <c r="CC23" t="inlineStr">
-        <is>
-          <t>電腦及週邊設備業平上櫃</t>
-        </is>
-      </c>
-      <c r="CD23" t="inlineStr">
-        <is>
-          <t>201.5</t>
-        </is>
-      </c>
-      <c r="CE23" t="inlineStr">
-        <is>
-          <t>206.5</t>
-        </is>
-      </c>
-      <c r="CF23" t="inlineStr">
-        <is>
-          <t>201.5</t>
-        </is>
-      </c>
-      <c r="CG23" t="inlineStr">
-        <is>
-          <t>204.0</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">

--- a/Result/checksun_type/HMI.xlsx
+++ b/Result/checksun_type/HMI.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>【d】</t>
+          <t>【d1】;【d2】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>-1.73</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>21.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>20.6</t>
+          <t>20.25</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-6.97</t>
+          <t>8.11</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-5.72</t>
+          <t>-7.32</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,74 +1014,66 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>68.18</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>98.48</t>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>1.63</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>1.39</t>
-        </is>
+          <t>89.39</t>
+        </is>
+      </c>
+      <c r="AH2" t="n">
+        <v>-0.44</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>1.88</v>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-6.16</t>
+          <t>-5.99</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-3.35</t>
+          <t>-3.43</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>20.27</t>
+          <t>20.34</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>19.99</v>
+        <v>19.96</v>
       </c>
       <c r="AN2" t="n">
-        <v>21.3</v>
+        <v>21.24</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>22.04</t>
+          <t>21.99</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>39.82</t>
-        </is>
-      </c>
-      <c r="AQ2" t="inlineStr">
-        <is>
-          <t>-0.28</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>-0.46</t>
-        </is>
+          <t>41.38</t>
+        </is>
+      </c>
+      <c r="AQ2" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>-0.42</v>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
@@ -1090,7 +1082,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-107.02</t>
+          <t>-106.36</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1092,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>30123.47234042553</t>
+          <t>30081.33144475921</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>431.0</t>
+          <t>248.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>449.8</v>
+        <v>410.4</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>483.5</t>
+          <t>379.6</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>1229.92</v>
+        <v>1080.7</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-33</t>
+          <t>30</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-122.9276269897701</t>
+          <t>-119.2499695063228</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-92.42759578056138</t>
+          <t>-99.02285334736263</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>431.0</t>
+          <t>248.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1148,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-12.90</t>
+          <t>-14.38</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1201,7 +1193,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1211,7 +1203,7 @@
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
@@ -1241,12 +1233,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>90.83</t>
+          <t>90.14</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>601</t>
+          <t>591</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1261,27 +1253,27 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>光電業平上櫃</t>
+          <t>光電業右下上櫃</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>20.3</t>
+          <t>20.2</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>20.6</t>
+          <t>20.4</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
+          <t>20.0</t>
+        </is>
+      </c>
+      <c r="CG2" t="inlineStr">
+        <is>
           <t>20.25</t>
-        </is>
-      </c>
-      <c r="CG2" t="inlineStr">
-        <is>
-          <t>20.6</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1303,7 +1295,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>【d】</t>
+          <t>【d1】;【d2】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1313,12 +1305,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>22.0</t>
+          <t>21.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1320,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>20.3</t>
+          <t>20.6</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,7 +1330,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>-1.73</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -1348,7 +1340,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-9.61</t>
+          <t>-6.97</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1358,7 +1350,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -1413,7 +1405,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-7.09</t>
+          <t>-5.72</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,17 +1415,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,12 +1436,12 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
@@ -1462,56 +1454,48 @@
           <t>98.48</t>
         </is>
       </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>1.00</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>0.49</t>
-        </is>
+      <c r="AH3" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>1.39</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-6.21</t>
+          <t>-6.16</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-3.47</t>
+          <t>-3.35</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>20.1</t>
+          <t>20.27</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>20</v>
+        <v>19.99</v>
       </c>
       <c r="AN3" t="n">
-        <v>21.33</v>
+        <v>21.3</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>22.1</t>
+          <t>22.04</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>30.88</t>
-        </is>
-      </c>
-      <c r="AQ3" t="inlineStr">
-        <is>
-          <t>-0.35</t>
-        </is>
-      </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>-0.51</t>
-        </is>
+          <t>39.82</t>
+        </is>
+      </c>
+      <c r="AQ3" t="n">
+        <v>-0.28</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>-0.46</v>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
@@ -1520,7 +1504,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-107.72</t>
+          <t>-107.02</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1514,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>30123.47234042553</t>
+          <t>30081.33144475921</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>444.0</t>
+          <t>431.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>443</v>
+        <v>449.8</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>490.1</t>
+          <t>483.5</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>1239.7</v>
+        <v>1229.92</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-47</t>
+          <t>-33</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-128.4730872096262</t>
+          <t>-122.9276269897701</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-99.31195655011089</t>
+          <t>-92.42759578056138</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>444.0</t>
+          <t>431.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1570,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-14.16</t>
+          <t>-12.90</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1631,7 +1615,7 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1641,7 +1625,7 @@
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1671,12 +1655,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>90.83</t>
+          <t>90.14</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>601</t>
+          <t>591</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1691,27 +1675,27 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>光電業平上櫃</t>
+          <t>光電業右下上櫃</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>19.95</t>
+          <t>20.3</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>20.3</t>
+          <t>20.6</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>20.25</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>20.3</t>
+          <t>20.6</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1733,7 +1717,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>【d】</t>
+          <t>【d1】;【d2】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1743,12 +1727,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>29.0</t>
+          <t>22.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1742,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>20.25</t>
+          <t>20.3</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,7 +1752,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1778,7 +1762,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-5.42</t>
+          <t>-9.61</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1788,7 +1772,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -1843,7 +1827,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-7.32</t>
+          <t>-7.09</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1837,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-1.23</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,17 +1858,17 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>95.45</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
@@ -1892,56 +1876,48 @@
           <t>98.48</t>
         </is>
       </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>1.20</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>0.08</t>
-        </is>
+      <c r="AH4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>0.49</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-6.38</t>
+          <t>-6.21</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-3.59</t>
+          <t>-3.47</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>20.01</t>
+          <t>20.1</t>
         </is>
       </c>
       <c r="AM4" t="n">
         <v>20</v>
       </c>
       <c r="AN4" t="n">
-        <v>21.36</v>
+        <v>21.33</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>22.15</t>
+          <t>22.1</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>25.28</t>
-        </is>
-      </c>
-      <c r="AQ4" t="inlineStr">
-        <is>
-          <t>-0.41</t>
-        </is>
-      </c>
-      <c r="AR4" t="inlineStr">
-        <is>
-          <t>-0.55</t>
-        </is>
+          <t>30.88</t>
+        </is>
+      </c>
+      <c r="AQ4" t="n">
+        <v>-0.35</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>-0.51</v>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
@@ -1950,7 +1926,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-108.32</t>
+          <t>-107.72</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1936,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>30123.47234042553</t>
+          <t>30081.33144475921</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>597.0</t>
+          <t>444.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>443.4</v>
+        <v>443</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>468.8</t>
+          <t>490.1</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>1250.78</v>
+        <v>1239.7</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-25</t>
+          <t>-47</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-133.7751109659018</t>
+          <t>-128.4730872096262</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-106.9927592012491</t>
+          <t>-99.31195655011089</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>597.0</t>
+          <t>444.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +1992,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-14.38</t>
+          <t>-14.16</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2061,7 +2037,7 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2101,12 +2077,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>90.83</t>
+          <t>90.14</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>601</t>
+          <t>591</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2121,27 +2097,27 @@
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>光電業平上櫃</t>
+          <t>光電業右下上櫃</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>20.5</t>
+          <t>19.95</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>20.5</t>
+          <t>20.3</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>20.25</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>20.25</t>
+          <t>20.3</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2163,7 +2139,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>【d】</t>
+          <t>【d1】;【d2】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2173,12 +2149,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>16.0</t>
+          <t>29.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2164,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>20.3</t>
+          <t>20.25</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,7 +2174,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -2208,7 +2184,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-38.48</t>
+          <t>-5.42</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2218,7 +2194,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -2273,7 +2249,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-7.09</t>
+          <t>-7.32</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2259,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-1.44</t>
+          <t>-1.23</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,74 +2280,66 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>95.45</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>88.89</t>
-        </is>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>2.22</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>-0.79</t>
-        </is>
+          <t>98.48</t>
+        </is>
+      </c>
+      <c r="AH5" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>0.08</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-6.4</t>
+          <t>-6.38</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-3.70</t>
+          <t>-3.59</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>19.86</t>
+          <t>20.01</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>20.02</v>
+        <v>20</v>
       </c>
       <c r="AN5" t="n">
-        <v>21.39</v>
+        <v>21.36</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>22.21</t>
+          <t>22.15</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>18.96</t>
-        </is>
-      </c>
-      <c r="AQ5" t="inlineStr">
-        <is>
-          <t>-0.47</t>
-        </is>
-      </c>
-      <c r="AR5" t="inlineStr">
-        <is>
-          <t>-0.58</t>
-        </is>
+          <t>25.28</t>
+        </is>
+      </c>
+      <c r="AQ5" t="n">
+        <v>-0.41</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>-0.55</v>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
@@ -2380,7 +2348,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-108.84</t>
+          <t>-108.32</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2358,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>30123.47234042553</t>
+          <t>30081.33144475921</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>332.0</t>
+          <t>597.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>357.2</v>
+        <v>443.4</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>580.6</t>
+          <t>468.8</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>1257.56</v>
+        <v>1250.78</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-223</t>
+          <t>-25</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-138.6446294685659</t>
+          <t>-133.7751109659018</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-130.5370215885447</t>
+          <t>-106.9927592012491</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>332.0</t>
+          <t>597.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2414,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-14.16</t>
+          <t>-14.38</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2491,7 +2459,7 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2531,12 +2499,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>90.83</t>
+          <t>90.14</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>601</t>
+          <t>591</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2551,27 +2519,27 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>光電業平上櫃</t>
+          <t>光電業右下上櫃</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>20.5</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>21.0</t>
+          <t>20.5</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>20.25</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>20.3</t>
+          <t>20.25</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2591,11 +2559,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>【d】</t>
-        </is>
-      </c>
+      <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr">
         <is>
           <t>3623</t>
@@ -2603,12 +2567,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>22.0</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2582,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>20.3</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,7 +2592,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>3.4</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -2638,7 +2602,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-45.47</t>
+          <t>-38.48</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2648,7 +2612,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -2703,7 +2667,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-8.92</t>
+          <t>-7.09</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2677,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-1.01</t>
+          <t>-1.44</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,12 +2698,12 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -2749,59 +2713,51 @@
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>73.5</t>
-        </is>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>1.32</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>-2.17</t>
-        </is>
+          <t>88.89</t>
+        </is>
+      </c>
+      <c r="AH6" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>-0.79</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-6.24</t>
+          <t>-6.4</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-3.82</t>
+          <t>-3.70</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>19.64</t>
+          <t>19.86</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>20.08</v>
+        <v>20.02</v>
       </c>
       <c r="AN6" t="n">
-        <v>21.41</v>
+        <v>21.39</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>22.26</t>
+          <t>22.21</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>9.79</t>
-        </is>
-      </c>
-      <c r="AQ6" t="inlineStr">
-        <is>
-          <t>-0.55</t>
-        </is>
-      </c>
-      <c r="AR6" t="inlineStr">
-        <is>
-          <t>-0.61</t>
-        </is>
+          <t>18.96</t>
+        </is>
+      </c>
+      <c r="AQ6" t="n">
+        <v>-0.47</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>-0.58</v>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
@@ -2810,7 +2766,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-109.26</t>
+          <t>-108.84</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2776,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>30123.47234042553</t>
+          <t>30081.33144475921</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>445.0</t>
+          <t>332.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>348.8</v>
+        <v>357.2</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>639.6</t>
+          <t>580.6</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>1276.44</v>
+        <v>1257.56</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-290</t>
+          <t>-223</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-140.1187399922061</t>
+          <t>-138.6446294685659</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-131.1167885136618</t>
+          <t>-130.5370215885447</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>445.0</t>
+          <t>332.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2832,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-15.86</t>
+          <t>-14.16</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2921,7 +2877,7 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -2931,7 +2887,7 @@
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2961,12 +2917,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>90.83</t>
+          <t>90.14</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>601</t>
+          <t>591</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2981,7 +2937,7 @@
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>光電業平上櫃</t>
+          <t>光電業右下上櫃</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
@@ -2991,7 +2947,7 @@
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>20.1</t>
+          <t>21.0</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
@@ -3001,7 +2957,7 @@
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>20.3</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3021,11 +2977,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>【d】</t>
-        </is>
-      </c>
+      <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr">
         <is>
           <t>3623</t>
@@ -3033,12 +2985,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>22.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3000,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>19.75</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,7 +3010,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>4.13</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -3068,7 +3020,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-17.60</t>
+          <t>-45.47</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3078,7 +3030,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -3133,7 +3085,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-9.61</t>
+          <t>-8.92</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3095,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-2.53</t>
+          <t>-1.01</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,74 +3116,66 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>49.15</t>
-        </is>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>1.28</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>-3.26</t>
-        </is>
+          <t>73.5</t>
+        </is>
+      </c>
+      <c r="AH7" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>-2.17</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-5.98</t>
+          <t>-6.24</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-3.92</t>
+          <t>-3.82</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>19.5</t>
+          <t>19.64</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>20.16</v>
+        <v>20.08</v>
       </c>
       <c r="AN7" t="n">
-        <v>21.44</v>
+        <v>21.41</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>22.31</t>
+          <t>22.26</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>3.76</t>
-        </is>
-      </c>
-      <c r="AQ7" t="inlineStr">
-        <is>
-          <t>-0.60</t>
-        </is>
-      </c>
-      <c r="AR7" t="inlineStr">
-        <is>
-          <t>-0.63</t>
-        </is>
+          <t>9.79</t>
+        </is>
+      </c>
+      <c r="AQ7" t="n">
+        <v>-0.55</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>-0.61</v>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
@@ -3240,7 +3184,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-109.49</t>
+          <t>-109.26</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3194,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>30123.47234042553</t>
+          <t>30081.33144475921</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>397.0</t>
+          <t>445.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>517.2</v>
+        <v>348.8</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>627.7</t>
+          <t>639.6</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>1309.6</v>
+        <v>1276.44</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-110</t>
+          <t>-290</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-141.7554584428505</t>
+          <t>-140.1187399922061</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-139.3694273883414</t>
+          <t>-131.1167885136618</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>397.0</t>
+          <t>445.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3250,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-16.49</t>
+          <t>-15.86</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3351,7 +3295,7 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3361,7 +3305,7 @@
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3391,12 +3335,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>90.83</t>
+          <t>90.14</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>601</t>
+          <t>591</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3411,27 +3355,27 @@
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>光電業平上櫃</t>
+          <t>光電業右下上櫃</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>20.3</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>20.3</t>
+          <t>20.1</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>19.7</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>19.75</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3451,11 +3395,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>【e】</t>
-        </is>
-      </c>
+      <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr">
         <is>
           <t>3623</t>
@@ -3463,12 +3403,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>22.0</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3418,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>19.85</t>
+          <t>19.75</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,7 +3428,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>3.64</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -3498,7 +3438,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-25.82</t>
+          <t>-17.60</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3508,7 +3448,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -3563,7 +3503,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-9.15</t>
+          <t>-9.61</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3513,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>-2.53</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,37 +3534,33 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>53.85</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>28.0</t>
-        </is>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>2.06</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>-4.02</t>
-        </is>
+          <t>49.15</t>
+        </is>
+      </c>
+      <c r="AH8" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>-3.26</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-5.68</t>
+          <t>-5.98</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
@@ -3634,34 +3570,30 @@
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>19.45</t>
+          <t>19.5</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>20.26</v>
+        <v>20.16</v>
       </c>
       <c r="AN8" t="n">
-        <v>21.48</v>
+        <v>21.44</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>22.36</t>
+          <t>22.31</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-1.89</t>
-        </is>
-      </c>
-      <c r="AQ8" t="inlineStr">
-        <is>
-          <t>-0.64</t>
-        </is>
-      </c>
-      <c r="AR8" t="inlineStr">
-        <is>
-          <t>-0.63</t>
-        </is>
+          <t>3.76</t>
+        </is>
+      </c>
+      <c r="AQ8" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>-0.63</v>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
@@ -3670,7 +3602,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-109.58</t>
+          <t>-109.49</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3612,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>30123.47234042553</t>
+          <t>30081.33144475921</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>446.0</t>
+          <t>397.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>537.2</v>
+        <v>517.2</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>724.2</t>
+          <t>627.7</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>1332.24</v>
+        <v>1309.6</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-187</t>
+          <t>-110</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-142.1892822709431</t>
+          <t>-141.7554584428505</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-141.0385748025855</t>
+          <t>-139.3694273883414</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>446.0</t>
+          <t>397.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3668,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-16.07</t>
+          <t>-16.49</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3781,17 +3713,17 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3821,12 +3753,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>90.83</t>
+          <t>90.14</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>601</t>
+          <t>591</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3841,27 +3773,27 @@
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>光電業平上櫃</t>
+          <t>光電業右下上櫃</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>19.45</t>
+          <t>20.3</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>20.05</t>
+          <t>20.3</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>19.45</t>
+          <t>19.7</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>19.85</t>
+          <t>19.75</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3825,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>9.0</t>
+          <t>22.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3840,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>19.5</t>
+          <t>19.85</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,7 +3850,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>5.34</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -3928,7 +3860,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-34.48</t>
+          <t>-25.82</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3938,7 +3870,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -3993,7 +3925,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-10.76</t>
+          <t>-9.15</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +3935,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,74 +3956,66 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>26.92</t>
+          <t>53.85</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>11.12</t>
-        </is>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>0.98</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>-5.18</t>
-        </is>
+          <t>28.0</t>
+        </is>
+      </c>
+      <c r="AH9" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>-4.02</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-5.44</t>
+          <t>-5.68</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-3.78</t>
+          <t>-3.92</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>19.31</t>
+          <t>19.45</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>20.36</v>
+        <v>20.26</v>
       </c>
       <c r="AN9" t="n">
-        <v>21.54</v>
+        <v>21.48</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>22.38</t>
+          <t>22.36</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-10.91</t>
-        </is>
-      </c>
-      <c r="AQ9" t="inlineStr">
-        <is>
-          <t>-0.70</t>
-        </is>
-      </c>
-      <c r="AR9" t="inlineStr">
-        <is>
-          <t>-0.63</t>
-        </is>
+          <t>-1.89</t>
+        </is>
+      </c>
+      <c r="AQ9" t="n">
+        <v>-0.64</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>-0.63</v>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
@@ -4100,7 +4024,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-109.53</t>
+          <t>-109.58</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4034,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>30123.47234042553</t>
+          <t>30081.33144475921</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>166.0</t>
+          <t>446.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>494.2</v>
+        <v>537.2</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>754.3</t>
+          <t>724.2</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>1394.4</v>
+        <v>1332.24</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-260</t>
+          <t>-187</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-142.3985018106445</t>
+          <t>-142.1892822709431</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-143.6359791514134</t>
+          <t>-141.0385748025855</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>166.0</t>
+          <t>446.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4090,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-17.55</t>
+          <t>-16.07</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4211,17 +4135,17 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4251,12 +4175,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>90.83</t>
+          <t>90.14</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>601</t>
+          <t>591</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4271,27 +4195,27 @@
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>光電業平上櫃</t>
+          <t>光電業右下上櫃</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>19.3</t>
+          <t>19.45</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>19.5</t>
+          <t>20.05</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>19.3</t>
+          <t>19.45</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>19.5</t>
+          <t>19.85</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,42 +4247,42 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>9.0</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>19.5</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>3.7</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>15.0</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>19.2</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>6.8</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-2.21</t>
+          <t>-34.48</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4368,7 +4292,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -4423,7 +4347,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-12.13</t>
+          <t>-10.76</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4357,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,54 +4378,50 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>3.23</t>
+          <t>26.92</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>9.68</t>
-        </is>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>-0.26</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>-6.04</t>
-        </is>
+          <t>11.12</t>
+        </is>
+      </c>
+      <c r="AH10" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>-5.18</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-5.2</t>
+          <t>-5.44</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-3.45</t>
+          <t>-3.78</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>19.25</t>
+          <t>19.31</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>20.49</v>
+        <v>20.36</v>
       </c>
       <c r="AN10" t="n">
-        <v>21.61</v>
+        <v>21.54</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
@@ -4510,18 +4430,14 @@
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-17.72</t>
-        </is>
-      </c>
-      <c r="AQ10" t="inlineStr">
-        <is>
-          <t>-0.72</t>
-        </is>
-      </c>
-      <c r="AR10" t="inlineStr">
-        <is>
-          <t>-0.61</t>
-        </is>
+          <t>-10.91</t>
+        </is>
+      </c>
+      <c r="AQ10" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>-0.63</v>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
@@ -4530,7 +4446,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-109.27</t>
+          <t>-109.53</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4456,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>30123.47234042553</t>
+          <t>30081.33144475921</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>290.0</t>
+          <t>166.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>804</v>
+        <v>494.2</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>822.2</t>
+          <t>754.3</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>1439.06</v>
+        <v>1394.4</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-18</t>
+          <t>-260</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-142.1735059305047</t>
+          <t>-142.3985018106445</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-112.2167003943315</t>
+          <t>-143.6359791514134</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>290.0</t>
+          <t>166.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4512,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-18.82</t>
+          <t>-17.55</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4641,7 +4557,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4651,7 +4567,7 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4681,12 +4597,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>90.83</t>
+          <t>90.14</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>601</t>
+          <t>591</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4701,27 +4617,27 @@
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>光電業平上櫃</t>
+          <t>光電業右下上櫃</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>19.2</t>
+          <t>19.3</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
+          <t>19.5</t>
+        </is>
+      </c>
+      <c r="CF10" t="inlineStr">
+        <is>
           <t>19.3</t>
         </is>
       </c>
-      <c r="CF10" t="inlineStr">
-        <is>
-          <t>19.2</t>
-        </is>
-      </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>19.2</t>
+          <t>19.5</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4669,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-1.53</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4778,7 +4694,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>6.8</t>
+          <t>5.19</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -4788,7 +4704,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>3.85</t>
+          <t>-2.21</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4798,7 +4714,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -4863,17 +4779,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,12 +4800,12 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
@@ -4899,59 +4815,51 @@
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>8.6</t>
-        </is>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>-1.13</t>
-        </is>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>-5.90</t>
-        </is>
+          <t>9.68</t>
+        </is>
+      </c>
+      <c r="AH11" t="n">
+        <v>-0.26</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>-6.04</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-4.83</t>
+          <t>-5.2</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-3.05</t>
+          <t>-3.45</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>19.42</t>
+          <t>19.25</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>20.64</v>
+        <v>20.49</v>
       </c>
       <c r="AN11" t="n">
-        <v>21.68</v>
+        <v>21.61</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>22.37</t>
+          <t>22.38</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-21.10</t>
-        </is>
-      </c>
-      <c r="AQ11" t="inlineStr">
-        <is>
-          <t>-0.71</t>
-        </is>
-      </c>
-      <c r="AR11" t="inlineStr">
-        <is>
-          <t>-0.58</t>
-        </is>
+          <t>-17.72</t>
+        </is>
+      </c>
+      <c r="AQ11" t="n">
+        <v>-0.72</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>-0.61</v>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
@@ -4960,7 +4868,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-108.86</t>
+          <t>-109.27</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4878,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>30123.47234042553</t>
+          <t>30081.33144475921</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>1287.0</t>
+          <t>290.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>930.4</v>
+        <v>804</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>895.9</t>
+          <t>822.2</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>1833.62</v>
+        <v>1439.06</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>-18</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-147.6201978461726</t>
+          <t>-142.1735059305047</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-76.60999144155971</t>
+          <t>-112.2167003943315</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>1287.0</t>
+          <t>290.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5071,7 +4979,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5111,12 +5019,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>90.83</t>
+          <t>90.14</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>601</t>
+          <t>591</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5131,22 +5039,22 @@
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>光電業平上櫃</t>
+          <t>光電業右下上櫃</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>19.55</t>
+          <t>19.2</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>19.65</t>
+          <t>19.3</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>18.85</t>
+          <t>19.2</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5183,12 +5091,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>-1.53</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>26.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5106,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>19.5</t>
+          <t>19.2</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,7 +5116,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>5.34</t>
+          <t>5.19</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -5218,7 +5126,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-4.04</t>
+          <t>3.85</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5228,7 +5136,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -5283,7 +5191,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-10.76</t>
+          <t>-12.13</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5201,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>3.17</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,74 +5222,66 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>22.58</t>
+          <t>3.23</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>7.53</t>
-        </is>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>-0.86</t>
-        </is>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>-5.39</t>
-        </is>
+          <t>8.6</t>
+        </is>
+      </c>
+      <c r="AH12" t="n">
+        <v>-1.13</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>-5.9</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-4.43</t>
+          <t>-4.83</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-2.68</t>
+          <t>-3.05</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>19.67</t>
+          <t>19.42</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>20.79</v>
+        <v>20.64</v>
       </c>
       <c r="AN12" t="n">
-        <v>21.75</v>
+        <v>21.68</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>22.35</t>
+          <t>22.37</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-23.19</t>
-        </is>
-      </c>
-      <c r="AQ12" t="inlineStr">
-        <is>
-          <t>-0.68</t>
-        </is>
-      </c>
-      <c r="AR12" t="inlineStr">
-        <is>
-          <t>-0.55</t>
-        </is>
+          <t>-21.10</t>
+        </is>
+      </c>
+      <c r="AQ12" t="n">
+        <v>-0.71</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>-0.58</v>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
@@ -5390,7 +5290,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-108.40</t>
+          <t>-108.86</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5300,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>30123.47234042553</t>
+          <t>30081.33144475921</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>497.0</t>
+          <t>1287.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>738.2</v>
+        <v>930.4</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>769.3</t>
+          <t>895.9</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>1851.22</v>
+        <v>1833.62</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-31</t>
+          <t>34</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-160.5311444651931</t>
+          <t>-147.6201978461726</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-129.8286218146873</t>
+          <t>-76.60999144155971</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>497.0</t>
+          <t>1287.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5356,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-17.55</t>
+          <t>-18.82</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5511,7 +5411,7 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5541,12 +5441,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>90.83</t>
+          <t>90.14</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>601</t>
+          <t>591</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5561,27 +5461,27 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>光電業平上櫃</t>
+          <t>光電業右下上櫃</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
         <is>
+          <t>19.55</t>
+        </is>
+      </c>
+      <c r="CE12" t="inlineStr">
+        <is>
+          <t>19.65</t>
+        </is>
+      </c>
+      <c r="CF12" t="inlineStr">
+        <is>
+          <t>18.85</t>
+        </is>
+      </c>
+      <c r="CG12" t="inlineStr">
+        <is>
           <t>19.2</t>
-        </is>
-      </c>
-      <c r="CE12" t="inlineStr">
-        <is>
-          <t>19.5</t>
-        </is>
-      </c>
-      <c r="CF12" t="inlineStr">
-        <is>
-          <t>18.9</t>
-        </is>
-      </c>
-      <c r="CG12" t="inlineStr">
-        <is>
-          <t>19.5</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5603,7 +5503,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>【b】</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5613,42 +5513,42 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
+          <t>-1.19</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>43.0</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>208.5</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>24.0</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>211.0</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-38.92</t>
+          <t>-40.81</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5688,7 +5588,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>208.5</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -5708,12 +5608,12 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>4.71</t>
+          <t>3.47</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5723,17 +5623,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>5.65</t>
+          <t>10.12</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.96</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5749,69 +5649,61 @@
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>43</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>47.81</t>
-        </is>
-      </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>-0.94</t>
-        </is>
-      </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>3.27</t>
-        </is>
+          <t>19.02</t>
+        </is>
+      </c>
+      <c r="AH13" t="n">
+        <v>-1.47</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>2.31</v>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>4.11</t>
+          <t>4.17</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>213.0</t>
+          <t>211.6</t>
         </is>
       </c>
       <c r="AM13" t="n">
-        <v>206.25</v>
+        <v>206.82</v>
       </c>
       <c r="AN13" t="n">
-        <v>198.1</v>
+        <v>198.55</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>194.35</t>
+          <t>194.48</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>3.00</t>
-        </is>
-      </c>
-      <c r="AQ13" t="inlineStr">
-        <is>
-          <t>4.63</t>
-        </is>
-      </c>
-      <c r="AR13" t="inlineStr">
-        <is>
-          <t>4.50</t>
-        </is>
+          <t>-6.26</t>
+        </is>
+      </c>
+      <c r="AQ13" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>4.43</v>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
@@ -5820,7 +5712,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-55.10</t>
+          <t>-55.79</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5830,43 +5722,43 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>28225.24042553192</t>
+          <t>28204.36402266289</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>5024.0</t>
+          <t>8991.0</t>
         </is>
       </c>
       <c r="AX13" t="n">
-        <v>10541.4</v>
+        <v>9192.6</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>17259.7</t>
+          <t>15530.9</t>
         </is>
       </c>
       <c r="AZ13" t="n">
-        <v>12942.1</v>
+        <v>13076.72</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>-6718</t>
+          <t>-6338</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>424.7712440790905</t>
+          <t>107.8641564708477</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>-1486.085871874324</t>
+          <t>-1635.124825374487</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>5024.0</t>
+          <t>8991.0</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
@@ -5886,7 +5778,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>9.90</t>
+          <t>8.59</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -5941,12 +5833,12 @@
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
         <is>
-          <t>4.73</t>
+          <t>4.79</t>
         </is>
       </c>
       <c r="BU13" t="inlineStr">
@@ -5956,7 +5848,7 @@
       </c>
       <c r="BV13" t="inlineStr">
         <is>
-          <t>12.6</t>
+          <t>12.45</t>
         </is>
       </c>
       <c r="BW13" t="inlineStr">
@@ -5971,12 +5863,12 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>49.79</t>
+          <t>50.05</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>10034</t>
+          <t>9915</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -5996,22 +5888,22 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>210.0</t>
+          <t>210.5</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>213.0</t>
+          <t>210.5</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>209.5</t>
+          <t>208.5</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>211.0</t>
+          <t>208.5</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6033,7 +5925,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>【b】</t>
+          <t>【b1】</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6043,12 +5935,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-1.4</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>53.0</t>
+          <t>24.0</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6068,17 +5960,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
+          <t>-1.2</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-31.72</t>
+          <t>-38.92</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6118,7 +6010,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>208.5</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -6143,7 +6035,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6153,17 +6045,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12.47</t>
+          <t>5.65</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6179,69 +6071,61 @@
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>43</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>47.06</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>73.21</t>
-        </is>
-      </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>-1.26</t>
-        </is>
-      </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>3.93</t>
-        </is>
+          <t>47.81</t>
+        </is>
+      </c>
+      <c r="AH14" t="n">
+        <v>-0.9399999999999999</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>3.27</v>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>4.06</t>
+          <t>4.11</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>213.7</t>
+          <t>213.0</t>
         </is>
       </c>
       <c r="AM14" t="n">
-        <v>205.62</v>
+        <v>206.25</v>
       </c>
       <c r="AN14" t="n">
-        <v>197.6</v>
+        <v>198.1</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>194.07</t>
+          <t>194.35</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>10.33</t>
-        </is>
-      </c>
-      <c r="AQ14" t="inlineStr">
-        <is>
-          <t>4.92</t>
-        </is>
-      </c>
-      <c r="AR14" t="inlineStr">
-        <is>
-          <t>4.46</t>
-        </is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="AQ14" t="n">
+        <v>4.63</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>4.5</v>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
@@ -6250,7 +6134,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-55.44</t>
+          <t>-55.10</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6260,43 +6144,43 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>28225.24042553192</t>
+          <t>28204.36402266289</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>11301.0</t>
+          <t>5024.0</t>
         </is>
       </c>
       <c r="AX14" t="n">
-        <v>12991.2</v>
+        <v>10541.4</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>19027.6</t>
+          <t>17259.7</t>
         </is>
       </c>
       <c r="AZ14" t="n">
-        <v>12958.32</v>
+        <v>12942.1</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>-6036</t>
+          <t>-6718</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>772.1998106160748</t>
+          <t>424.7712440790905</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>-795.0628714500053</t>
+          <t>-1486.085871874324</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>11301.0</t>
+          <t>5024.0</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
@@ -6361,7 +6245,7 @@
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
@@ -6376,7 +6260,7 @@
       </c>
       <c r="BT14" t="inlineStr">
         <is>
-          <t>4.73</t>
+          <t>4.79</t>
         </is>
       </c>
       <c r="BU14" t="inlineStr">
@@ -6386,7 +6270,7 @@
       </c>
       <c r="BV14" t="inlineStr">
         <is>
-          <t>12.6</t>
+          <t>12.45</t>
         </is>
       </c>
       <c r="BW14" t="inlineStr">
@@ -6401,12 +6285,12 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>49.79</t>
+          <t>50.05</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>10034</t>
+          <t>9915</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -6426,12 +6310,12 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>214.0</t>
+          <t>210.0</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>214.0</t>
+          <t>213.0</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
@@ -6463,7 +6347,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>【b】</t>
+          <t>【b1】</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -6473,12 +6357,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>-1.4</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>53.0</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6488,7 +6372,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>214.0</t>
+          <t>211.0</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6498,7 +6382,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>-1.2</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -6508,7 +6392,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-14.56</t>
+          <t>-31.72</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6548,7 +6432,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>208.5</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -6568,12 +6452,12 @@
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>6.20</t>
+          <t>4.71</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6583,17 +6467,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>9.41</t>
+          <t>12.47</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6609,69 +6493,61 @@
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>43</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>86.36</t>
+          <t>47.06</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>90.86</t>
-        </is>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>-0.14</t>
-        </is>
-      </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>4.64</t>
-        </is>
+          <t>73.21</t>
+        </is>
+      </c>
+      <c r="AH15" t="n">
+        <v>-1.26</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>3.93</v>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>3.89</t>
+          <t>4.06</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>214.3</t>
+          <t>213.7</t>
         </is>
       </c>
       <c r="AM15" t="n">
-        <v>204.8</v>
+        <v>205.62</v>
       </c>
       <c r="AN15" t="n">
-        <v>197.13</v>
+        <v>197.6</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>193.75</t>
+          <t>194.07</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>20.18</t>
-        </is>
-      </c>
-      <c r="AQ15" t="inlineStr">
-        <is>
-          <t>5.22</t>
-        </is>
-      </c>
-      <c r="AR15" t="inlineStr">
-        <is>
-          <t>4.35</t>
-        </is>
+          <t>10.33</t>
+        </is>
+      </c>
+      <c r="AQ15" t="n">
+        <v>4.92</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>4.46</v>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
@@ -6680,7 +6556,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-56.59</t>
+          <t>-55.44</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6690,43 +6566,43 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>28225.24042553192</t>
+          <t>28204.36402266289</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>8529.0</t>
+          <t>11301.0</t>
         </is>
       </c>
       <c r="AX15" t="n">
-        <v>16149.6</v>
+        <v>12991.2</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>18902.6</t>
+          <t>19027.6</t>
         </is>
       </c>
       <c r="AZ15" t="n">
-        <v>12813</v>
+        <v>12958.32</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>-2752</t>
+          <t>-6036</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>1057.156661900817</t>
+          <t>772.1998106160748</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>-452.0277682920532</t>
+          <t>-795.0628714500053</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>8529.0</t>
+          <t>11301.0</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
@@ -6746,7 +6622,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>11.46</t>
+          <t>9.90</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -6801,12 +6677,12 @@
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
         <is>
-          <t>4.73</t>
+          <t>4.79</t>
         </is>
       </c>
       <c r="BU15" t="inlineStr">
@@ -6816,7 +6692,7 @@
       </c>
       <c r="BV15" t="inlineStr">
         <is>
-          <t>12.6</t>
+          <t>12.45</t>
         </is>
       </c>
       <c r="BW15" t="inlineStr">
@@ -6831,12 +6707,12 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>49.79</t>
+          <t>50.05</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>10034</t>
+          <t>9915</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -6856,22 +6732,22 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>215.5</t>
+          <t>214.0</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>215.5</t>
+          <t>214.0</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>212.5</t>
+          <t>209.5</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>214.0</t>
+          <t>211.0</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -6893,7 +6769,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>【b】</t>
+          <t>【b1】</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -6903,12 +6779,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>56.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6918,7 +6794,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>213.5</t>
+          <t>214.0</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6928,7 +6804,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-1.18</t>
+          <t>-2.64</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -6938,7 +6814,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-1.69</t>
+          <t>-14.56</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -6978,7 +6854,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>208.5</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -6998,12 +6874,12 @@
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>5.96</t>
+          <t>6.20</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2.64</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7013,17 +6889,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13.18</t>
+          <t>9.41</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>-1.17</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7039,37 +6915,33 @@
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>43</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>86.21</t>
+          <t>86.36</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>95.4</t>
-        </is>
-      </c>
-      <c r="AH16" t="inlineStr">
-        <is>
-          <t>-0.37</t>
-        </is>
-      </c>
-      <c r="AI16" t="inlineStr">
-        <is>
-          <t>5.15</t>
-        </is>
+          <t>90.86</t>
+        </is>
+      </c>
+      <c r="AH16" t="n">
+        <v>-0.14</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>4.64</v>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>3.66</t>
+          <t>3.89</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
@@ -7078,30 +6950,26 @@
         </is>
       </c>
       <c r="AM16" t="n">
-        <v>203.8</v>
+        <v>204.8</v>
       </c>
       <c r="AN16" t="n">
-        <v>196.6</v>
+        <v>197.13</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>193.37</t>
+          <t>193.75</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>26.64</t>
-        </is>
-      </c>
-      <c r="AQ16" t="inlineStr">
-        <is>
-          <t>5.23</t>
-        </is>
-      </c>
-      <c r="AR16" t="inlineStr">
-        <is>
-          <t>4.13</t>
-        </is>
+          <t>20.18</t>
+        </is>
+      </c>
+      <c r="AQ16" t="n">
+        <v>5.22</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>4.35</v>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
@@ -7110,7 +6978,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-58.78</t>
+          <t>-56.59</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7120,43 +6988,43 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>28225.24042553192</t>
+          <t>28204.36402266289</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>12118.0</t>
+          <t>8529.0</t>
         </is>
       </c>
       <c r="AX16" t="n">
-        <v>19868.4</v>
+        <v>16149.6</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>20209.8</t>
+          <t>18902.6</t>
         </is>
       </c>
       <c r="AZ16" t="n">
-        <v>12862.38</v>
+        <v>12813</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>-341</t>
+          <t>-2752</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>1331.553831026793</t>
+          <t>1057.156661900817</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>351.1662279440243</t>
+          <t>-452.0277682920532</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>12118.0</t>
+          <t>8529.0</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
@@ -7176,7 +7044,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>11.20</t>
+          <t>11.46</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -7226,7 +7094,7 @@
       </c>
       <c r="BR16" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS16" t="inlineStr">
@@ -7236,7 +7104,7 @@
       </c>
       <c r="BT16" t="inlineStr">
         <is>
-          <t>4.73</t>
+          <t>4.79</t>
         </is>
       </c>
       <c r="BU16" t="inlineStr">
@@ -7246,7 +7114,7 @@
       </c>
       <c r="BV16" t="inlineStr">
         <is>
-          <t>12.6</t>
+          <t>12.45</t>
         </is>
       </c>
       <c r="BW16" t="inlineStr">
@@ -7261,12 +7129,12 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>49.79</t>
+          <t>50.05</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>10034</t>
+          <t>9915</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -7291,7 +7159,7 @@
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>217.0</t>
+          <t>215.5</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
@@ -7301,7 +7169,7 @@
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>213.5</t>
+          <t>214.0</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -7323,7 +7191,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>【b】</t>
+          <t>【b1】</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -7333,12 +7201,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>56.0</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7348,7 +7216,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>215.5</t>
+          <t>213.5</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7358,7 +7226,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-2.13</t>
+          <t>-2.4</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -7368,7 +7236,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>-1.69</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7408,7 +7276,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>208.5</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -7428,12 +7296,12 @@
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>6.95</t>
+          <t>5.96</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2.40</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7443,17 +7311,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>17.18</t>
+          <t>13.18</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>-1.17</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7469,69 +7337,61 @@
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>43</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>86.21</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>100.0</t>
-        </is>
-      </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>0.84</t>
-        </is>
-      </c>
-      <c r="AI17" t="inlineStr">
-        <is>
-          <t>5.31</t>
-        </is>
+          <t>95.4</t>
+        </is>
+      </c>
+      <c r="AH17" t="n">
+        <v>-0.37</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>5.15</v>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>3.66</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>213.7</t>
+          <t>214.3</t>
         </is>
       </c>
       <c r="AM17" t="n">
-        <v>202.92</v>
+        <v>203.8</v>
       </c>
       <c r="AN17" t="n">
-        <v>196.07</v>
+        <v>196.6</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>193.0</t>
+          <t>193.37</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>35.12</t>
-        </is>
-      </c>
-      <c r="AQ17" t="inlineStr">
-        <is>
-          <t>5.21</t>
-        </is>
-      </c>
-      <c r="AR17" t="inlineStr">
-        <is>
-          <t>3.85</t>
-        </is>
+          <t>26.64</t>
+        </is>
+      </c>
+      <c r="AQ17" t="n">
+        <v>5.23</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>4.13</v>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
@@ -7540,7 +7400,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-61.52</t>
+          <t>-58.78</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7550,43 +7410,43 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>28225.24042553192</t>
+          <t>28204.36402266289</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>15735.0</t>
+          <t>12118.0</t>
         </is>
       </c>
       <c r="AX17" t="n">
-        <v>21869.2</v>
+        <v>19868.4</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>21736.8</t>
+          <t>20209.8</t>
         </is>
       </c>
       <c r="AZ17" t="n">
-        <v>12717.58</v>
+        <v>12862.38</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>132</t>
+          <t>-341</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>1509.806122496388</t>
+          <t>1331.553831026793</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>1101.508857283279</t>
+          <t>351.1662279440243</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>15735.0</t>
+          <t>12118.0</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
@@ -7606,7 +7466,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>12.24</t>
+          <t>11.20</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -7651,7 +7511,7 @@
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
@@ -7661,12 +7521,12 @@
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
         <is>
-          <t>4.73</t>
+          <t>4.79</t>
         </is>
       </c>
       <c r="BU17" t="inlineStr">
@@ -7676,7 +7536,7 @@
       </c>
       <c r="BV17" t="inlineStr">
         <is>
-          <t>12.6</t>
+          <t>12.45</t>
         </is>
       </c>
       <c r="BW17" t="inlineStr">
@@ -7691,12 +7551,12 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>49.79</t>
+          <t>50.05</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>10034</t>
+          <t>9915</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -7716,22 +7576,22 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>215.0</t>
+          <t>215.5</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>215.5</t>
+          <t>217.0</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
+          <t>212.5</t>
+        </is>
+      </c>
+      <c r="CG17" t="inlineStr">
+        <is>
           <t>213.5</t>
-        </is>
-      </c>
-      <c r="CG17" t="inlineStr">
-        <is>
-          <t>215.5</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7753,7 +7613,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>【b】</t>
+          <t>【b1】</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -7763,12 +7623,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7778,7 +7638,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>214.5</t>
+          <t>215.5</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7788,7 +7648,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-1.66</t>
+          <t>-3.36</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -7798,7 +7658,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7838,7 +7698,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>208.5</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -7858,12 +7718,12 @@
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>6.45</t>
+          <t>6.95</t>
         </is>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3.36</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7873,17 +7733,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>19.06</t>
+          <t>17.18</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7899,7 +7759,7 @@
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>43</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
@@ -7912,56 +7772,48 @@
           <t>100.0</t>
         </is>
       </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>1.18</t>
-        </is>
-      </c>
-      <c r="AI18" t="inlineStr">
-        <is>
-          <t>4.99</t>
-        </is>
+      <c r="AH18" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>5.31</v>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>3.29</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>212.0</t>
+          <t>213.7</t>
         </is>
       </c>
       <c r="AM18" t="n">
-        <v>201.92</v>
+        <v>202.92</v>
       </c>
       <c r="AN18" t="n">
-        <v>195.5</v>
+        <v>196.07</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>192.61</t>
+          <t>193.0</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>39.40</t>
-        </is>
-      </c>
-      <c r="AQ18" t="inlineStr">
-        <is>
-          <t>4.90</t>
-        </is>
-      </c>
-      <c r="AR18" t="inlineStr">
-        <is>
-          <t>3.51</t>
-        </is>
+          <t>35.12</t>
+        </is>
+      </c>
+      <c r="AQ18" t="n">
+        <v>5.21</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>3.85</v>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
@@ -7970,7 +7822,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-64.90</t>
+          <t>-61.52</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7980,43 +7832,43 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>28225.24042553192</t>
+          <t>28204.36402266289</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>17273.0</t>
+          <t>15735.0</t>
         </is>
       </c>
       <c r="AX18" t="n">
-        <v>23978</v>
+        <v>21869.2</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>23524.2</t>
+          <t>21736.8</t>
         </is>
       </c>
       <c r="AZ18" t="n">
-        <v>12876.32</v>
+        <v>12717.58</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>453</t>
+          <t>132</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>1584.041988898771</t>
+          <t>1509.806122496388</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>1746.551582864951</t>
+          <t>1101.508857283279</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>17273.0</t>
+          <t>15735.0</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
@@ -8036,7 +7888,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>11.72</t>
+          <t>12.24</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -8081,22 +7933,22 @@
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
         <is>
-          <t>4.73</t>
+          <t>4.79</t>
         </is>
       </c>
       <c r="BU18" t="inlineStr">
@@ -8106,7 +7958,7 @@
       </c>
       <c r="BV18" t="inlineStr">
         <is>
-          <t>12.6</t>
+          <t>12.45</t>
         </is>
       </c>
       <c r="BW18" t="inlineStr">
@@ -8121,12 +7973,12 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>49.79</t>
+          <t>50.05</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>10034</t>
+          <t>9915</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -8146,7 +7998,7 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>214.5</t>
+          <t>215.0</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
@@ -8156,12 +8008,12 @@
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>213.0</t>
+          <t>213.5</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>214.5</t>
+          <t>215.5</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -8183,7 +8035,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>【b】</t>
+          <t>【b1】</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -8193,42 +8045,42 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
+          <t>0.23</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>214.5</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>-2.88</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>127.0</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>214.0</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>-1.42</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>13.06</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8268,7 +8120,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>208.5</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -8288,12 +8140,12 @@
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>6.20</t>
+          <t>6.45</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2.88</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8303,17 +8155,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>29.88</t>
+          <t>19.06</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8329,7 +8181,7 @@
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>43</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
@@ -8342,56 +8194,48 @@
           <t>100.0</t>
         </is>
       </c>
-      <c r="AH19" t="inlineStr">
-        <is>
-          <t>1.90</t>
-        </is>
-      </c>
-      <c r="AI19" t="inlineStr">
-        <is>
-          <t>4.44</t>
-        </is>
+      <c r="AH19" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>4.99</v>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>3.16</t>
+          <t>3.29</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>210.0</t>
+          <t>212.0</t>
         </is>
       </c>
       <c r="AM19" t="n">
-        <v>201.08</v>
+        <v>201.92</v>
       </c>
       <c r="AN19" t="n">
-        <v>194.92</v>
+        <v>195.5</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>192.22</t>
+          <t>192.61</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>43.25</t>
-        </is>
-      </c>
-      <c r="AQ19" t="inlineStr">
-        <is>
-          <t>4.54</t>
-        </is>
-      </c>
-      <c r="AR19" t="inlineStr">
-        <is>
-          <t>3.17</t>
-        </is>
+          <t>39.40</t>
+        </is>
+      </c>
+      <c r="AQ19" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>3.51</v>
       </c>
       <c r="AS19" t="inlineStr">
         <is>
@@ -8400,7 +8244,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-68.36</t>
+          <t>-64.90</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8410,43 +8254,43 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>28225.24042553192</t>
+          <t>28204.36402266289</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>27093.0</t>
+          <t>17273.0</t>
         </is>
       </c>
       <c r="AX19" t="n">
-        <v>25064</v>
+        <v>23978</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>22168.4</t>
+          <t>23524.2</t>
         </is>
       </c>
       <c r="AZ19" t="n">
-        <v>12662.48</v>
+        <v>12876.32</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>2895</t>
+          <t>453</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>1554.494789995829</t>
+          <t>1584.041988898771</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>2440.878634307883</t>
+          <t>1746.551582864951</t>
         </is>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
-          <t>27093.0</t>
+          <t>17273.0</t>
         </is>
       </c>
       <c r="BE19" t="inlineStr">
@@ -8466,7 +8310,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>11.46</t>
+          <t>11.72</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -8511,7 +8355,7 @@
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
@@ -8521,12 +8365,12 @@
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
         <is>
-          <t>4.73</t>
+          <t>4.79</t>
         </is>
       </c>
       <c r="BU19" t="inlineStr">
@@ -8536,7 +8380,7 @@
       </c>
       <c r="BV19" t="inlineStr">
         <is>
-          <t>12.6</t>
+          <t>12.45</t>
         </is>
       </c>
       <c r="BW19" t="inlineStr">
@@ -8551,12 +8395,12 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>49.79</t>
+          <t>50.05</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>10034</t>
+          <t>9915</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -8576,7 +8420,7 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>215.0</t>
+          <t>214.5</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
@@ -8586,12 +8430,12 @@
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>211.0</t>
+          <t>213.0</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>214.0</t>
+          <t>214.5</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8613,7 +8457,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>【b】</t>
+          <t>【b1】</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -8623,12 +8467,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8648,7 +8492,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>-2.64</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -8658,7 +8502,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>7.97</t>
+          <t>13.06</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8698,7 +8542,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>208.5</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -8723,7 +8567,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2.64</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8733,17 +8577,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>30.12</t>
+          <t>29.88</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8759,7 +8603,7 @@
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>43</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
@@ -8772,56 +8616,48 @@
           <t>100.0</t>
         </is>
       </c>
-      <c r="AH20" t="inlineStr">
-        <is>
-          <t>3.18</t>
-        </is>
-      </c>
-      <c r="AI20" t="inlineStr">
-        <is>
-          <t>3.54</t>
-        </is>
+      <c r="AH20" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>4.44</v>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>3.07</t>
+          <t>3.16</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>207.4</t>
+          <t>210.0</t>
         </is>
       </c>
       <c r="AM20" t="n">
-        <v>200.3</v>
+        <v>201.08</v>
       </c>
       <c r="AN20" t="n">
-        <v>194.34</v>
+        <v>194.92</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>191.84</t>
+          <t>192.22</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>43.78</t>
-        </is>
-      </c>
-      <c r="AQ20" t="inlineStr">
-        <is>
-          <t>4.06</t>
-        </is>
-      </c>
-      <c r="AR20" t="inlineStr">
-        <is>
-          <t>2.83</t>
-        </is>
+          <t>43.25</t>
+        </is>
+      </c>
+      <c r="AQ20" t="n">
+        <v>4.54</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>3.17</v>
       </c>
       <c r="AS20" t="inlineStr">
         <is>
@@ -8830,7 +8666,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-71.78</t>
+          <t>-68.36</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8840,43 +8676,43 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>28225.24042553192</t>
+          <t>28204.36402266289</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>27123.0</t>
+          <t>27093.0</t>
         </is>
       </c>
       <c r="AX20" t="n">
-        <v>21655.6</v>
+        <v>25064</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>20056.7</t>
+          <t>22168.4</t>
         </is>
       </c>
       <c r="AZ20" t="n">
-        <v>12284.3</v>
+        <v>12662.48</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>1598</t>
+          <t>2895</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>1393.334091030001</t>
+          <t>1554.494789995829</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>2293.457328001074</t>
+          <t>2440.878634307883</t>
         </is>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
-          <t>27123.0</t>
+          <t>27093.0</t>
         </is>
       </c>
       <c r="BE20" t="inlineStr">
@@ -8941,12 +8777,12 @@
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
@@ -8956,7 +8792,7 @@
       </c>
       <c r="BT20" t="inlineStr">
         <is>
-          <t>4.73</t>
+          <t>4.79</t>
         </is>
       </c>
       <c r="BU20" t="inlineStr">
@@ -8966,7 +8802,7 @@
       </c>
       <c r="BV20" t="inlineStr">
         <is>
-          <t>12.6</t>
+          <t>12.45</t>
         </is>
       </c>
       <c r="BW20" t="inlineStr">
@@ -8981,12 +8817,12 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>49.79</t>
+          <t>50.05</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>10034</t>
+          <t>9915</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
@@ -9006,17 +8842,17 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
+          <t>215.0</t>
+        </is>
+      </c>
+      <c r="CE20" t="inlineStr">
+        <is>
+          <t>215.5</t>
+        </is>
+      </c>
+      <c r="CF20" t="inlineStr">
+        <is>
           <t>211.0</t>
-        </is>
-      </c>
-      <c r="CE20" t="inlineStr">
-        <is>
-          <t>214.0</t>
-        </is>
-      </c>
-      <c r="CF20" t="inlineStr">
-        <is>
-          <t>210.5</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
@@ -9043,7 +8879,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>【b】</t>
+          <t>【b1】</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -9053,12 +8889,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>105.0</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9068,7 +8904,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>210.5</t>
+          <t>214.0</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9078,7 +8914,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>-2.64</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -9088,7 +8924,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>13.00</t>
+          <t>7.97</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9128,7 +8964,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>208.5</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -9148,12 +8984,12 @@
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>4.47</t>
+          <t>6.20</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2.64</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9163,17 +8999,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>24.71</t>
+          <t>30.12</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9189,7 +9025,7 @@
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>43</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
@@ -9202,56 +9038,48 @@
           <t>100.0</t>
         </is>
       </c>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>2.93</t>
-        </is>
-      </c>
-      <c r="AI21" t="inlineStr">
-        <is>
-          <t>2.52</t>
-        </is>
+      <c r="AH21" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>3.54</v>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>2.93</t>
+          <t>3.07</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>204.5</t>
+          <t>207.4</t>
         </is>
       </c>
       <c r="AM21" t="n">
-        <v>199.48</v>
+        <v>200.3</v>
       </c>
       <c r="AN21" t="n">
-        <v>193.8</v>
+        <v>194.34</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>191.47</t>
+          <t>191.84</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>34.99</t>
-        </is>
-      </c>
-      <c r="AQ21" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
-      </c>
-      <c r="AR21" t="inlineStr">
-        <is>
-          <t>2.52</t>
-        </is>
+          <t>43.78</t>
+        </is>
+      </c>
+      <c r="AQ21" t="n">
+        <v>4.06</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>2.83</v>
       </c>
       <c r="AS21" t="inlineStr">
         <is>
@@ -9260,7 +9088,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-74.87</t>
+          <t>-71.78</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9270,43 +9098,43 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>28225.24042553192</t>
+          <t>28204.36402266289</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>22122.0</t>
+          <t>27123.0</t>
         </is>
       </c>
       <c r="AX21" t="n">
-        <v>20551.2</v>
+        <v>21655.6</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>18187.0</t>
+          <t>20056.7</t>
         </is>
       </c>
       <c r="AZ21" t="n">
-        <v>11819.44</v>
+        <v>12284.3</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>2364</t>
+          <t>1598</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>1229.675320671625</t>
+          <t>1393.334091030001</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>1997.731985848452</t>
+          <t>2293.457328001074</t>
         </is>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
-          <t>22122.0</t>
+          <t>27123.0</t>
         </is>
       </c>
       <c r="BE21" t="inlineStr">
@@ -9326,7 +9154,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>9.64</t>
+          <t>11.46</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
@@ -9371,7 +9199,7 @@
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
@@ -9381,12 +9209,12 @@
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
         <is>
-          <t>4.73</t>
+          <t>4.79</t>
         </is>
       </c>
       <c r="BU21" t="inlineStr">
@@ -9396,7 +9224,7 @@
       </c>
       <c r="BV21" t="inlineStr">
         <is>
-          <t>12.6</t>
+          <t>12.45</t>
         </is>
       </c>
       <c r="BW21" t="inlineStr">
@@ -9411,12 +9239,12 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>49.79</t>
+          <t>50.05</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>10034</t>
+          <t>9915</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
@@ -9436,22 +9264,22 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>208.5</t>
+          <t>211.0</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>211.0</t>
+          <t>214.0</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>208.0</t>
+          <t>210.5</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>210.5</t>
+          <t>214.0</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -9473,7 +9301,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>【b】</t>
+          <t>【b1】</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -9483,12 +9311,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>105.0</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9498,7 +9326,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>207.0</t>
+          <t>210.5</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9508,7 +9336,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>-0.96</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -9518,7 +9346,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>19.04</t>
+          <t>13.00</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9558,7 +9386,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>208.5</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -9578,12 +9406,12 @@
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>2.73</t>
+          <t>4.47</t>
         </is>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9593,17 +9421,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>30.12</t>
+          <t>24.71</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9619,7 +9447,7 @@
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>43</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
@@ -9629,59 +9457,51 @@
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>85.71</t>
-        </is>
-      </c>
-      <c r="AH22" t="inlineStr">
-        <is>
-          <t>1.87</t>
-        </is>
-      </c>
-      <c r="AI22" t="inlineStr">
-        <is>
-          <t>2.15</t>
-        </is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="AH22" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>2.52</v>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>2.89</t>
+          <t>2.93</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>203.2</t>
+          <t>204.5</t>
         </is>
       </c>
       <c r="AM22" t="n">
-        <v>198.92</v>
+        <v>199.48</v>
       </c>
       <c r="AN22" t="n">
-        <v>193.33</v>
+        <v>193.8</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>191.14</t>
+          <t>191.47</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>24.29</t>
-        </is>
-      </c>
-      <c r="AQ22" t="inlineStr">
-        <is>
-          <t>2.85</t>
-        </is>
-      </c>
-      <c r="AR22" t="inlineStr">
-        <is>
-          <t>2.30</t>
-        </is>
+          <t>34.99</t>
+        </is>
+      </c>
+      <c r="AQ22" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>2.52</v>
       </c>
       <c r="AS22" t="inlineStr">
         <is>
@@ -9690,7 +9510,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-77.07</t>
+          <t>-74.87</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9700,43 +9520,43 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>28225.24042553192</t>
+          <t>28204.36402266289</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>26279.0</t>
+          <t>22122.0</t>
         </is>
       </c>
       <c r="AX22" t="n">
-        <v>21604.4</v>
+        <v>20551.2</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>18148.2</t>
+          <t>18187.0</t>
         </is>
       </c>
       <c r="AZ22" t="n">
-        <v>11512</v>
+        <v>11819.44</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>3456</t>
+          <t>2364</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>1090.028654275838</t>
+          <t>1229.675320671625</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>2039.741068992971</t>
+          <t>1997.731985848452</t>
         </is>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
-          <t>26279.0</t>
+          <t>22122.0</t>
         </is>
       </c>
       <c r="BE22" t="inlineStr">
@@ -9756,7 +9576,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>7.81</t>
+          <t>9.64</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
@@ -9811,12 +9631,12 @@
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
         <is>
-          <t>4.73</t>
+          <t>4.79</t>
         </is>
       </c>
       <c r="BU22" t="inlineStr">
@@ -9826,7 +9646,7 @@
       </c>
       <c r="BV22" t="inlineStr">
         <is>
-          <t>12.6</t>
+          <t>12.45</t>
         </is>
       </c>
       <c r="BW22" t="inlineStr">
@@ -9841,12 +9661,12 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>49.79</t>
+          <t>50.05</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>10034</t>
+          <t>9915</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
@@ -9866,22 +9686,22 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>203.5</t>
+          <t>208.5</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
+          <t>211.0</t>
+        </is>
+      </c>
+      <c r="CF22" t="inlineStr">
+        <is>
           <t>208.0</t>
         </is>
       </c>
-      <c r="CF22" t="inlineStr">
-        <is>
-          <t>202.0</t>
-        </is>
-      </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>207.0</t>
+          <t>210.5</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -9903,7 +9723,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>【b】</t>
+          <t>【b1】</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -9913,12 +9733,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>112.0</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9928,7 +9748,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>204.5</t>
+          <t>207.0</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9938,7 +9758,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>3.08</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -9948,7 +9768,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>40.09</t>
+          <t>19.04</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -9988,7 +9808,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>208.5</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -10008,12 +9828,12 @@
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>2.73</t>
         </is>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10023,17 +9843,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>26.35</t>
+          <t>30.12</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10049,7 +9869,7 @@
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>43</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
@@ -10059,59 +9879,51 @@
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>64.29</t>
-        </is>
-      </c>
-      <c r="AH23" t="inlineStr">
-        <is>
-          <t>1.19</t>
-        </is>
-      </c>
-      <c r="AI23" t="inlineStr">
-        <is>
-          <t>1.78</t>
-        </is>
+          <t>85.71</t>
+        </is>
+      </c>
+      <c r="AH23" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>2.15</v>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>2.93</t>
+          <t>2.89</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>202.1</t>
+          <t>203.2</t>
         </is>
       </c>
       <c r="AM23" t="n">
-        <v>198.58</v>
+        <v>198.92</v>
       </c>
       <c r="AN23" t="n">
-        <v>192.93</v>
+        <v>193.33</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>190.87</t>
+          <t>191.14</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>14.78</t>
-        </is>
-      </c>
-      <c r="AQ23" t="inlineStr">
-        <is>
-          <t>2.48</t>
-        </is>
-      </c>
-      <c r="AR23" t="inlineStr">
-        <is>
-          <t>2.16</t>
-        </is>
+          <t>24.29</t>
+        </is>
+      </c>
+      <c r="AQ23" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>2.3</v>
       </c>
       <c r="AS23" t="inlineStr">
         <is>
@@ -10120,7 +9932,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-78.46</t>
+          <t>-77.07</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10130,43 +9942,43 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>28225.24042553192</t>
+          <t>28204.36402266289</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>22703.0</t>
+          <t>26279.0</t>
         </is>
       </c>
       <c r="AX23" t="n">
-        <v>23070.4</v>
+        <v>21604.4</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>16467.7</t>
+          <t>18148.2</t>
         </is>
       </c>
       <c r="AZ23" t="n">
-        <v>11056.48</v>
+        <v>11512</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>6602</t>
+          <t>3456</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>917.3536697818137</t>
+          <t>1090.028654275838</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>1581.513292449679</t>
+          <t>2039.741068992971</t>
         </is>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
-          <t>22703.0</t>
+          <t>26279.0</t>
         </is>
       </c>
       <c r="BE23" t="inlineStr">
@@ -10186,7 +9998,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>6.51</t>
+          <t>7.81</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
@@ -10231,7 +10043,7 @@
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -10241,12 +10053,12 @@
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
         <is>
-          <t>4.73</t>
+          <t>4.79</t>
         </is>
       </c>
       <c r="BU23" t="inlineStr">
@@ -10256,7 +10068,7 @@
       </c>
       <c r="BV23" t="inlineStr">
         <is>
-          <t>12.6</t>
+          <t>12.45</t>
         </is>
       </c>
       <c r="BW23" t="inlineStr">
@@ -10271,12 +10083,12 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>49.79</t>
+          <t>50.05</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>10034</t>
+          <t>9915</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
@@ -10296,22 +10108,22 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
+          <t>203.5</t>
+        </is>
+      </c>
+      <c r="CE23" t="inlineStr">
+        <is>
+          <t>208.0</t>
+        </is>
+      </c>
+      <c r="CF23" t="inlineStr">
+        <is>
           <t>202.0</t>
         </is>
       </c>
-      <c r="CE23" t="inlineStr">
-        <is>
-          <t>205.0</t>
-        </is>
-      </c>
-      <c r="CF23" t="inlineStr">
-        <is>
-          <t>202.0</t>
-        </is>
-      </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>204.5</t>
+          <t>207.0</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">

--- a/Result/checksun_type/HMI.xlsx
+++ b/Result/checksun_type/HMI.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-1.73</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>8.11</t>
+          <t>6.71</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>2.27</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1019,61 +1019,61 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>68.18</t>
+          <t>58.82</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>89.39</t>
+          <t>75.67</t>
         </is>
       </c>
       <c r="AH2" t="n">
-        <v>-0.44</v>
+        <v>-0.39</v>
       </c>
       <c r="AI2" t="n">
-        <v>1.88</v>
+        <v>1.8</v>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-5.99</t>
+          <t>-5.66</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-3.43</t>
+          <t>-3.52</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>20.34</t>
+          <t>20.33</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>19.96</v>
+        <v>19.97</v>
       </c>
       <c r="AN2" t="n">
-        <v>21.24</v>
+        <v>21.17</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>21.99</t>
+          <t>21.94</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>41.38</t>
+          <t>42.62</t>
         </is>
       </c>
       <c r="AQ2" t="n">
-        <v>-0.25</v>
+        <v>-0.22</v>
       </c>
       <c r="AR2" t="n">
-        <v>-0.42</v>
+        <v>-0.38</v>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-106.36</t>
+          <t>-105.75</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1092,43 +1092,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>30081.33144475921</t>
+          <t>30039.46888260255</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>248.0</t>
+          <t>323.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>410.4</v>
+        <v>408.6</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>379.6</t>
+          <t>382.9</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>1080.7</v>
+        <v>1030.88</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>25</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-119.2499695063228</t>
+          <t>-115.6021222454177</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-99.02285334736263</t>
+          <t>-95.5389623104395</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>248.0</t>
+          <t>323.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1193,7 +1193,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1233,7 +1233,7 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>90.14</t>
+          <t>90.48</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1258,17 +1258,17 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>20.2</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>20.4</t>
+          <t>20.25</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>19.8</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1295,7 +1295,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1305,12 +1305,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>-1.73</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>21.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>20.6</t>
+          <t>20.25</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1330,7 +1330,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-1.73</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -1340,7 +1340,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-6.97</t>
+          <t>8.11</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1405,7 +1405,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-5.72</t>
+          <t>-7.32</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1415,17 +1415,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1441,61 +1441,61 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>68.18</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>98.48</t>
+          <t>89.39</t>
         </is>
       </c>
       <c r="AH3" t="n">
-        <v>1.63</v>
+        <v>-0.44</v>
       </c>
       <c r="AI3" t="n">
-        <v>1.39</v>
+        <v>1.88</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-6.16</t>
+          <t>-5.99</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-3.35</t>
+          <t>-3.43</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>20.27</t>
+          <t>20.34</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>19.99</v>
+        <v>19.96</v>
       </c>
       <c r="AN3" t="n">
-        <v>21.3</v>
+ 